--- a/Lebanese_Presidency.xlsx
+++ b/Lebanese_Presidency.xlsx
@@ -413,8 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -450,6 +450,3154 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل الوزيرة الاتحادية للتعاون الاقتصادي والتنمية الألمانية: لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات ونتطلع إلى تعزيز الشراكة الاقتصادية مع ألمانيا</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1608</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل الوزيرة الاتحادية للتعاون الاقتصادي والتنمية الألمانية: لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات ونتطلع إلى تعزيز الشراكة الاقتصادية مع ألمانيا
+رئيس الجمهورية: دعم الجيش والمؤسسات الأمنية اللبنانية
+يشكل استثماراً مباشراً في استقرار لبنان والمنطقة
+------
+الوزيرة رادوفان: حريصون على تعزيز التعاون مع الحكومة اللبنانية وزيارتي تعبيرا
+عن تضامن الحكومة الألمانية ودعمها للبنان في ظل الظروف الصعبة التي يمر بها
+----
+شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتزام بالتفاهمات القائمة، فانه لفت "الى أن الدولة اللبنانية والجيش اللبناني مستعدان لمعالجة أي هواجس أمنية عبر الآليات الرسمية والتنسيق المعتمد، بدلاً من اللجوء إلى العمليات العسكرية".
+ودعا الى تعزيز الدعم الأوروبي للجيش اللبناني، والى أهمية الانتقال تدريجياً من مرحلة المساعدات الطارئة إلى بناء شراكة اقتصادية وتنموية مستدامة.
+موقف الرئيس عون جاء خلال استقباله صباح اليوم في قصر بعبدا، وزيرة التعاون الاقتصادي والتنمية في جمهورية ألمانيا الاتحادية السيدة ريم العبالي رادوفان، على رأس وفد ضمّ السفير الألماني في لبنان توماس تسانايزن وعدداً من المسؤولين الألمان. وجرى خلال الاجتماع عرض للأوضاع في لبنان والمنطقة، وللعلاقات الثنائية وسبل تعزيز التعاون الاقتصادي والتنموي بين البلدين.
+وأكدت الوزيرة الألمانية أن زيارتها إلى لبنان تأتي تعبيراً عن تضامن الحكومة الألمانية ودعمها للبنان في ظل الظروف الصعبة التي يمر بها، مشددة على حرص بلادها على تعزيز التعاون مع الحكومة اللبنانية ومواكبة جهودها الإصلاحية والتنموية. وأشارت إلى أن الحكومة الألمانية تتابع باهتمام التطورات في لبنان، وتلمس تقدماً في مسار الإصلاحات التي يجري تنفيذها، رغم التحديات الاستثنائية، مؤكدة استعداد ألمانيا لمواصلة دعم لبنان ومؤسساته، والعمل على مشاريع تعاون جديدة في عدد من القطاعات.
+من جهته، رحّب الرئيس عون بالوزيرة الألمانية، مثمّناً مواقف ألمانيا الداعمة للبنان، ومؤكداً أهمية الدور الأوروبي في مساندة الجهود الرامية إلى ترسيخ الاستقرار في لبنان والمنطقة.
+وعرض رئيس الجمهورية التطورات الإقليمية وانعكاساتها على الوضع اللبناني، مشيراً إلى أن لبنان يبذل جهوداً متواصلة للحفاظ على استقراره الداخلي وتماسك مؤسساته في ظل التوترات المحيطة به. وشدد على أن لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، انطلاقاً من قناعته بأن الحروب لم تحقق الأهداف المرجوة منها، وأن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها.
+وفي ما يتعلق بالوضع في الجنوب، أكد الرئيس عون ضرورة وقف الاعتداءات الإسرائيلية والالتزام بالتفاهمات القائمة، مشيراً إلى أن استمرار العمليات العسكرية واستهداف المناطق المدنية والبنى التحتية يزيدان من معاناة السكان ويقوّضان الجهود المبذولة لتحقيق الاستقرار. ولفت إلى أن لبنان طرح في الاتصالات والمفاوضات أربعة ملفات أساسية، هي وقف إطلاق النار، والانسحاب الإسرائيلي، وترسيم الحدود، وملف الأسرى، إلا أن التقدم المطلوب لم يتحقق حتى الآن.
+وشدد الرئيس عون على أن استمرار الاعتداءات لا يؤدي إلا إلى تعقيد الوضع وتعزيز منطق المواجهة، في وقت يحتاج فيه سكان الجنوب إلى الأمن والطمأنينة والعودة إلى حياتهم الطبيعية. وأكد أن الدولة اللبنانية والجيش اللبناني مستعدان لمعالجة أي هواجس أمنية عبر الآليات الرسمية والتنسيق المعتمد، بدلاً من اللجوء إلى العمليات العسكرية.
+وفي هذا السياق، دعا الرئيس عون إلى تعزيز الدعم الأوروبي للجيش اللبناني، نظراً إلى المسؤوليات الكبيرة الملقاة على عاتقه، سواء في حفظ الأمن والاستقرار الداخلي، أو مكافحة الإرهاب والاتجار بالمخدرات، وضبط الحدود ومكافحة الهجرة غير النظامية. وأكد أن دعم الجيش والمؤسسات الأمنية اللبنانية يشكل استثماراً مباشراً في استقرار لبنان والمنطقة، وينعكس إيجاباً على أمن أوروبا أيضاً، نظراً إلى الترابط الوثيق بين ضفتي المتوسط.
+وتناول اللقاء كذلك مسار الإصلاحات الاقتصادية والمالية، حيث أشار الرئيس عون إلى استمرار العمل مع صندوق النقد الدولي والمؤسسات المالية الدولية لاستكمال الإصلاحات الضرورية واستعادة الثقة بالاقتصاد اللبناني. وأعربت الوزيرة الألمانية عن تقدير بلادها للخطوات الإصلاحية التي اتخذها لبنان، مؤكدة أهمية مواصلة هذا المسار وتعزيز التعاون مع الوزارات والمؤسسات اللبنانية المعنية.
+كما جرى البحث في تداعيات الأزمات الإقليمية وأعباء النزوح على لبنان ومجتمعاته المضيفة، إضافة إلى حاجات إعادة الإعمار والتعافي. وفي هذا الإطار، أعرب الرئيس عون عن تطلعه إلى مساهمة ألمانيا في الجهود الدولية لدعم إعادة الإعمار، ولا سيما ضمن أي إطار يجري العمل على إعداده بقيادة البنك الدولي وبالتنسيق مع الحكومة اللبنانية.
+وأكد رئيس الجمهورية أهمية الانتقال تدريجياً من مرحلة المساعدات الطارئة إلى بناء شراكة اقتصادية وتنموية مستدامة، داعياً إلى تشجيع القطاع الخاص الألماني على الاستثمار في لبنان والاستفادة من الفرص المتاحة في مختلف القطاعات الإنتاجية والبنى التحتية، بما يساهم في تحفيز النمو وخلق فرص العمل.
+وفي ختام اللقاء، جددت الوزيرة العبالي رادوفان تأكيد التزام ألمانيا الوقوف إلى جانب لبنان، مشددة على أن القرب الجغرافي والروابط الوثيقة بين لبنان وأوروبا يشكلان حافزاً إضافياً لتعميق العلاقات الثنائية وتوسيع مجالات التعاون، بما يخدم مصالح البلدين ويساهم في تحقيق الاستقرار والتنمية.
+تصريح
+وبعد اللقاء، صرحت الوزيرة رادوفان فقالت:
+"جئت الى لبنان لأن بلدكم يقف عند مفترق طرق هام. فبعد أشهر من النزاع في الجنوب، بعد الدمار الكبير والتهجير الداخلي المستمر، بلغ بلدكم أقصى حدود قدرته على التحمل. لقد ألقت الأزمة الاقتصادية والمالية عبئا ثقيلا على الدولة والمجتمع. ويتحدد الآن بالذات الاتجاه الذي سيتطور لبنان فيه. فأنا أتيت إلى هنا لأكون بنفسي صورة واضحة عما يجري على أرض الواقع، عن وضع الناس، عن تبعات المواجهات العسكرية في الجنوب، وأيضا عن الإصلاحات. ولكن أهم شيء أتيت الى هنا لأقول بشكل واضح: ألمانيا تدعم نهج الإصلاحات وبناء مؤسسات دولة فعالة وإرساء شروط حياة أفضل لأهل هذا البلد، لا سيما لأولئك الأكثر تضررا من الأزمة".
+اضافت:"تعمل هذه الحكومة ذات التوجه الإصلاحي برئاسة الرئيس جوزاف عون ورئيس الوزراء نواف سلام لجعل الدولة أكثر فاعلية، للحد من الفساد وتعزيز وجود الدولة المركزية في كافة أنحاء البلاد. الحوكمة الرشيدة، الشفافية، وقدر أكبر أيضا من المحاسبة، الرعاية الأساسية الموثوقة وأيضا سياسة اجتماعية أكثر عدالة، جميعها تعتبر مداميك لبداية جديدة. وألمانيا تعول في تعاونها التنموي على هذا النهج، وحكومتنا، وأيضا دعمنا يركزان على ثلاثة محاور سأتطرق إليها الآن.
+أولا: تعزيز مؤسسات الدولة وتطبيق الإصلاحات. إن الدولة الفعالة هي شرط محوري وجوهري من أجل أن تصل الخدمات العامة لجميع الأشخاص بشكل متساو. نحن ندعم مشاريع من أجل تعزيز الإدارة لمكافحة الفساد، وأيضا لتحسين الشفافية والمحاسبة والإصلاحات في القطاعات الأساسية وأهمها قطاع المياه والتعليم والأمان الاجتماعي.
+ثانيا: النمو الاقتصادي وإتاحة الفرص لجميع أطياف المجتمع. في هذا البلد الذي يزخر بهذا القدر من المواهب وروح ريادة الأعمال، يحتاج الشباب والعائلات إلى شيء محوري، ألا وهو آفاق للمستقبل. نحن ندعم تحسين التعليم المهني وتطوير القطاع الخاص لنخلق فرص عمل جيدة وعادلة لجميع اللبنانيات واللبنانيين وأيضا للفئات الأخرى التي تعيش في بلادكم.
+ثالثا: نحن ندعم الناس للتغلب على تبعات النزاعات الإقليمية والأزمات المستمرة لا سيما في الجنوب. ألمانيا تدعم إعادة بناء وتعزيز البنى التحتية في البلديات وأيضا لتأمين الخدمات الأساسية ومنها المياه واستعادة سبل الحياة. كل ذلك بالتنسيق مع الحكومة اللبنانية وبالتعاون مع المنظمات الدولية ومع شركائنا المحليين. وأهم شيء أن دعمنا يهدف إلى تعزيز فعالية الدولة لأن على الأشخاص أن يشعروا بان الدولة موجودة هنا لهم. السلام المستدام في لبنان يشترط أن يكون هناك استقرار وأيضا ان يتم احترام السيادة وسلامة الأراضي وأن تقدم الدولة الأمان والخدمات الأساسية للناس. الأشخاص في لبنان وكذلك في الدول المجاورة يحتاجون إلى الأمان، الى الأمل، والثقة في المستقبل. الأزمات ليست أحداث من الطبيعة ويمكن التغلب عليها من خلال القرارات السياسية الشجاعة. طبعا أيضا أن يكون لبنان مستقر وأن تكون فيه إصلاحات. هذا مهم جدا له وأيضا للمنطقة وكذلك لأوروبا. ولذلك زيارتي هي إشارة من أجل تضامن ألمانيا مع لبنان وأيضا مع أهله.
+حوار
+سئلت: قمت بمحادثات مع رئيس الجمهورية وهو رئيس يتطلع وأيضا يطبق نهجا للإصلاحات. فما كان انطباعك؟ وهل هناك تقدم في هذا الصدد؟
+اجابت: لقد كانت محادثاتي مع الرئيس عون جيدة جدا وبناءة. ورغم الصعوبات التي تواجهها الحكومة اللبنانية والشعب اللبناني، نحن نرى تقدما في الإصلاحات التي تبذلها الحكومة. ونحن سوف ندعم هذا النهج الآن وفي المستقبل. طبعا، هذا ليس سهلا في ظل الأوضاع الصعبة التي تمر بها المنطقة، ولكننا سوف نتابع التعاون التنموي من أجل دعم الحكومة. ودعوني هنا أنوه بمثل مهم جدا. فلقد كان عدد المهاجرين داخليا يبلغ أكثر من مليون شخص. والآن قد تم خفضه إلى 200 ألف شخص. فهذا بالفعل تقدم مهم جدا ونحن نريد متابعة هذا الدعم على هذا النحو.
+سئلت: ما هو الدور الذي تريد المانيا ان تتولاه في المنطقة وما هي التوقعات في هذا الصدد من قبل الرئيس اللبناني؟
+اجابت: ان التوقعات بالنسبة للطرف الألماني والاوروبي ان نكون شريكا ذي موثوقية لا سيما في ما يتعلق بالتغلب على الازمات والتعافي الاقتصادي وبالتحسن على المستوى الاجتماعي. ولذلك، نحن نطالب دوما بعدم نسيان الوضع هنا في لبنان. ونحث على دعمه وسنقوم بذلك الان وفي المستقبل.
+سئلت: هل ألمانيا على استعداد لتشكيل قوة أوروبية بديلة عن "اليونيفيل"؟ وأيضا هل من جهد ألماني لدعم موقف لبنان لانتشار الجيش ووقف الحرب؟
+اجابت: شاركت ألمانيا في قوات "اليونيفيل" على مدى أعوام طويلة. وفي ما يتعلق بمستقبل هذه القوات، طبعا هناك جهات أخرى مختصة تماما ومسؤولة عن هذا الموضوع، لاسيما مجلس الأمن التابع للأمم المتحدة. ونحن نراقب الوضع عن كثب. وطبعا لا يجب أن يكون هناك فراغ في هذا الشأن. ولكن في المجتمع الدولي نريد أن ندعم الجيش اللبناني لأنه بالفعل ركن أساسي لاستقرار البلد وسنقوم بذلك الان وفي المستقبل.
+سئلت: هل لدى ألمانيا نية بالضغط على إسرائيل لوقف الاعتداءات جنوب لبنان؟
+اجابت: في الأشهر الماضية طبعا كان هذا موضوعا هاما بالنسبة للحكومة الاتحادية الألمانية. المواجهات العسكرية بين حزب الله وإسرائيل. ونحن أيضا نخاطب الحكومة الإسرائيلية حول هذا الموضوع بشكل مباشر، لاسيما بعد الاعتداءات على بيروت. كان هذا الأمر بالنسبة لنا أمرا واضحا. وسوف نتابع هذا النهج ونتابع مخاطبة إسرائيل حول هذا الموضوع.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:01:49.311933+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>الرئيس عون مستقبلاً هيئة إدارة مؤسسة مطار بيروت بحضور الوزير رسامني: مطار رفيق الحريري الدولي ليس مجرد مرفق للنقل الجوي بل هو بوابة لبنان الى العالم وتقع على عاتقكم مسؤولية تطوير أدائه وتحسين الخدمات فيه وضمان اعلى معايير السلامة</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1607</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>الرئيس عون مستقبلاً هيئة إدارة مؤسسة مطار بيروت بحضور الوزير رسامني: مطار رفيق الحريري الدولي ليس مجرد مرفق للنقل الجوي بل هو بوابة لبنان الى العالم وتقع على عاتقكم مسؤولية تطوير أدائه وتحسين الخدمات فيه وضمان اعلى معايير السلامة
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة ديزي حنا. واطلع الرئيس من الوفد على الخطوط العريضة للخطة التي تعتزم الهيئة وضعها لتطوير مطار رفيق الحريري الدولي والإجراءات الواجب اتخاذها في هذا الصدد.
+وتمنى الرئيس عون لرئيس الهيئة واعضائها التوفيق في المهام الموكولة اليهم، مؤكدا دعمه للخطوات الآيلة الى تطوير مطار رفيق الحريري الدولي، ومواكبة التقدم الحاصل في المطارات الدولية المتطورة من مختلف النواحي.
+وقال الرئيس عون ان مطار رفيق الحريري الدولي ليس مجرد مرفق للنقل الجوي، بل هو بوابة لبنان الى العالم، وواجهته امام الوافدين اليه، ومنه تنطلق صورة الدولة اللبنانية. لذلك تقع على عاتقكم مسؤولية تطوير أدائه وتحسين الخدمات فيه، وضمان اعلى معايير السلامة بما يعكس صورة لبنان الذي نريد استعادته دولة حديثة ومنظمة وقادرة على مواكبة التطور.
+ودعا الرئيس عون أعضاء المؤسسة الى العمل بروح الفريق الواحد بعيدا عن المصالح الشخصية والحسابات الضيقة، لأن المطلوب إدارة قائمة على الكفاءة والشفافية والمحاسبة، تحافظ على المال العام، وتضع المصلحة الوطنية فوق كل اعتبار، وتعمل على تعزيز الثقة بمؤسسات الدولة من خلال النتائج الملوسة لا الوعود.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:01:51.540807+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>نشاط الرئيس العماد جوزاف عون في 28-10-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1606</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>نشاط الرئيس العماد جوزاف عون في 28-10-2026
+الرئيس عون استقبل خمسة نواب فرنسيين من مجموعة دراسات مسيحيي الشرق:
+لبنان رسالة للحرية والتعددية في المنطقة والعالم
+ولا يمكن أن يحيا من دون جناحيه المسيحي والمسلم
+رئيس الجمهورية: لا خطر على الوجود المسيحي في لبنان
+وما حصل في عدد من الدول المجاورة لا يمكن أن يتكرر فيه
+الرئيس عون: حماية العيش المشترك في لبنان ليست مسؤولية لبنانية فحسب بل تتصل
+بمستقبل المنطقة لأن نجاح تجربة الشراكة الإسلامية-المسيحية يعزز فرص الأعتدال
+الوفد الفرنسي اكد دعم شعب بلاده للبنان وشعبه المميز
+بدوره وثقافته وحضوره داخل لبنان ودول العالم
+الرئيس عون عرض مع وزير العدل الواقع القضائي وعمل المحاكم
+رئيس الجمهورية مستقبلاً مجلس رجال الاعمال اللبناني-القبرصي:
+لا مكان لليأس واللبناني بما يملك من طاقات قادر على النهوض ببلده من جديد
+الرئيس عون: لا اقتصاد من دون استقرار ولا يمكن حل مشاكل لبنان
+الا عبر اعتماد لغة التروّي والحوار بعيداً عن التصادم
+الرئيس عون تسلم من وفد من الجامعة الانطونية دعوة لحضور افتتاحية تساعية الميلاد
+واطلع من رئيس مجلس إدارة "بيبسي كولا" على التحضيرات للاحتفال
+بمرور خمسة وسبعين عاماً على تأسيس الشركة
+أبلغ رئيس الجمهورية العماد جوزاف عون خمسة نواب فرنسيين من مجموعة دراسات مسيحيي الشرق خلال استقبالهم قبل ظهر اليوم في قصر بعبدا في حضور السفير الفرنسي في لبنان باتريك دوريل، أن لبنان رسالة للحرية والتعددية في المنطقة والعالم، ولا يمكن أن يحيا من دون جناحيه المسيحي والمسلم. فإذا فقد الجناح المسيحي، فإن التطرف هو البديل، وسيمتد الى اوروبا وإذا فقد الجناح المسلم لأي سبب، فإن الاعتدال سيفقد. والمسيحيون في لبنان حريصون على المحافظة على التعايش المسيحي-الإسلامي، وهم من خلال ممارساتهم يؤكدون على أهمية الدور الذي يلعبونه في دول الشرق والغرب.
+وقال الرئيس عون للوفد النيابي الفرنسي أن لا خطر على الوجود المسيحي في لبنان وما حصل في عدد من الدول المجاورة لا يمكن أن يتكرر في لبنان. فالمسيحيون يشكلون مع إخوتهم المسلمين حالة نموذجية فريدة لأن التعايش الإسلامي - المسيحي في لبنان ليس مجرد صيغة سياسية فرضتها الظروف، بل هو خيار وطني وحضاري وتجربة إنسانية أثبتت أن التنوع يمكن أن يكون مصدر قوة، وأن الاختلاف لا يتناقض مع الوحدة بل يغنيها ويعززها، إضافة إلى أن هذا التعايش هو الشراكة الكاملة في بناء الدولة وصون مؤسساتها وتقرير مستقبل الوطن. واعتبر رئيس الجمهورية أن قوة لبنان الحقيقية تكمن في قدرته على حماية هذا النموذج وتطويره وترسيخ الثقة بين أبنائه بعيداً عن منطق الغلبة والإقصاء، وما يضمن احترام خصوصية كل مكوّن في إطار دولة واحدة عادلة وقوية.
+وفيما اعتبر الرئيس عون أن الوحدة بين المسيحيين والمسلمين شرط أساسي لحماية لبنان واستقراره، وصمام أمان في مواجهة الفتنة ومحاولات زرع الانقسام بين أبنائه، شدد على أن التجارب التي مر بها لبنان والمنطقة أثبتت أن الانقسامات الداخلية لا تنتج إلا الضعف، وأن استغلال الدين والمذهب لتحقيق أهداف سياسية أو لتبرير العنف لا يهدد جماعة بعينها بل يهدد المجتمعات بأكملها. وأكد رئيس الجمهورية أن حماية العيش المشترك في لبنان ليست مسؤولية لبنانية فحسب، بل هي مسؤولية تتصل بمستقبل المنطقة لأن نجاح تجربة الشراكة الإسلامية-المسيحية يعزز فرص الأعتدال ويقدم دليلا عمليا على إمكان بناء مجتمعات تحترم التعددية وتحمي كرامة الإنسان وحقوقه.
+وعرض الرئيس عون، ردا على أسئلة أعضاء الوفد، لتجذر العلاقات اللبنانية -الفرنسية، شاكرا الرئيس الفرنسي إيمانويل ماكرون على الدعم المستمر للبنان في مختلف المجالات، وإصراره على الوقوف إلى جانبه في الظروف الصعبة التي مر بها ولا يزال. وشرح رئيس الجمهورية الأوضاع في الجنوب في ظل استمرار اعتداءات إسرائيل التي لا تزال تقصف وتدمر وتجرف القرى والبلدات الجنوبية التي تحتلها، خلافا لمندرجات اتفاق الإطار الذي تم التوصل إليه بين لبنان وإسرائيل برعاية أميركية، معربا عن أمله في أن تتمكن الولايات المتحدة الأميركية والمجتمع الدولي من الضغط على إسرائيل لوقف اعتداءاتها والانسحاب من الجنوب وينتشر الجيش اللبناني حتى الحدود وإعادة الأسرى وبدء إعادة الإعمار وعودة الجنوبيين إلى أرضهم.
+وأكد الرئيس عون حرص لبنان على بقاء قوات "اليونيفيل" في الجنوب أو إحلال قوات أوروبية مكانها، تكون نواة لقوات من دول صديقة ترغب في مساعدة لبنان والمساهمة في تحقيق الأمن والاستقرار في الجنوب، مكررا التأكيد بأن لا حلول آمنة ومستدامة من خلال الحرب، بل من خلال التفاوض الدبلوماسي لأن الحروب لا يمكن أن تحقق أي نتيجة عملية، بل هي تدمر وتشرد وتوقع قتلى وجرحى ولا تنهي الصراعات. وحده التفاوض الدبلوماسي يمكن أن يحقق الأمان للدول والشعوب.
+وأكد الرئيس عون للوفد النيابي الفرنسي أن الدولة ساهرة على سلامة أبناء القرى الجنوبية الحدودية الصامدين في منازلهم وممتلكاتهم وتعمل مع المنظمات الإنسانية و"اليونيفيل" والجيش اللبناني على تأمين كل مقومات الصمود الصحية والتربوية والغذائية لهم إلى حين زوال الاحتلال الإسرائيلي.
+وأوضح ردا على سؤال، أن لبنان يعمل من أجل تحقيق استراتيجية للشراكة مع الاتحاد الأوروبي كما سبق للرئيس عون أن دعا لقيام سوق عربية مشتركة انطلاقا من القناعة أن في الاتحاد قوة.
+وكان أعضاء الوفد عرضوا للرئيس عون أهداف زيارتهم إلى لبنان للاطلاع على الأوضاع فيه عن كثب، واعداد تقرير مفصل ضمن مجموعة العمل النيابية لمسيحيي الشرق في مجلس النواب الفرنسي، مشيرين إلى أنهم زاروا منطقة مرجعيون والقرى المجاورة والتقوا مجموعة من أبنائها وطلابها واطلعوا على أوضاعهم وحاجاتهم، مؤكدين دعم الشعب الفرنسي للبنان وشعبه المميز بدوره وثقافته وحضوره داخل لبنان ودول العالم.
+وضم الوفد النواب: رئيسة مجموعة دراسات مسيحيي الشرق السيدة CENDRINE FOUCHER-CHAZE، والسيدات والسادة: ELIZABETH DE MAISTRE، ERIC LIEGEON DOMINIQUE POTIER، ERIC MARTINEAU، و AMELIA LAKRAFI.
+وزير العدل
+وعرض الرئيس عون مع وزير العدل المحامي عادل نصار الواقع القضائي في البلاد وعمل المؤسسات القضائية والمحاكم.
+مجلس رجال الاعمال اللبناني-القبرصي
+على صعيد آخر، استقبل الرئيس عون رئيس مجلس رجال الاعمال اللبناني- القبرصي السيد دافيد عيسى على رأس وفد بحضور رئيس الهيئات الاقتصادية الوزير السابق محمد شقير. في مستهل اللقاء، القى السيد عيسى كلمة قال فيها:
+"يشرفني، كما يشرّف أعضاء مجلس الأعمال اللبناني- القبرصي، أن نلتقي فخامتكم اليوم، بحضور رئيس الهيئات الاقتصادية، معالي الأستاذ محمد شقير، حاملين إليكم رسالة عنوانها الإيمان الراسخ بلبنان، والتمسك بدوره ومكانته، والاستعداد الكامل للمساهمة في فتح آفاق جديدة أمام اقتصاده، ودعم مسيرة النهوض والتعافي، وتعزيز علاقاته وشراكاته مع محيطه العربي وامتداده الأوروبي.
+نحن ندرك تمامًا حجم التحديات الاستثنائية التي رافقت بداية عهدكم، وندرك كذلك أنكم تسلمتم مسؤولية قيادة هذا الوطن في واحدة من أكثر المراحل دقة وحساسية وتعقيدًا في تاريخه الحديث، في ظرف لم يكن عاديًا بأي مقياس، وكأنكم حملتم بين أيديكم كرة نار، وسط أزمات متراكمة واستحقاقات وطنية متشابكة.
+لقد بدأ عهدكم في ظل حرب ألقت بثقلها على البلاد، واقتصاد أنهكته سنوات الأزمات، وشعب لبناني أثقلته الهواجس على أمنه وحاضره ومستقبله، فيما كانت مؤسسات الدولة تواجه تحديات جسيمة على المستويات السياسية والأمنية والاقتصادية والاجتماعية.
+وفي خضم هذا الواقع شديد التعقيد، لم تكن مسؤولية القيادة مجرّد إدارة مرحلة صعبة، بل كانت مواجهة إرث ثقيل ومحاولة استعادة زمام الدولة في وقت كانت فيه البلاد بأمسّ الحاجة إلى الاستقرار والثقة والأمل.
+ونحن نرى، فخامة الرئيس، الجهود التي تبذلونها في الداخل والخارج، وندرك حجم الاتصالات والتحركات التي تقومون بها من أجل حماية لبنان، ووقف الحرب، وتجنيب وطننا المزيد من الخسائر والمعاناة. ونرى جولاتكم واتصالاتكم مع الدول الشقيقة والصديقة، وسعيكم إلى حشد الدعم للبنان، وإلى فتح الأبواب أمام كل مبادرة يمكن أن تساهم في وقف الحرب وتثبيت الاستقرار.
+ومن هنا، نقول لكم اليوم بكل صراحة ووضوح: نحن إلى جانبكم، ونقدّر عاليًا الجهود التي تبذلونها، كما نقدّر حجم المسؤولية الوطنية الكبيرة التي تحمّلتم أعباءها في هذا الظرف الدقيق والاستثنائي. ونتمنى لكم كل القوة والثبات والتوفيق في تحمّل هذه المسؤولية، والمضي بلبنان نحو مرحلة جديدة يسودها الأمن والاستقرار، وتستعيد فيها الدولة عافيتها ومكانتها، ويستعيد اللبنانيون ثقتهم بمستقبل وطنهم."
+أضاف:"نحن نؤمن بأن الاستقرار ليس مجرد مطلب سياسي وأمني، بل هو المدخل الحقيقي إلى النهوض الاقتصادي، وإلى الاستثمار، وخلق فرص العمل، وإعادة الشباب اللبناني إلى دائرة الأمل، بدل أن تصبح الهجرة خياره الوحيد. ومن هذا الإيمان بلبنان، ومن رغبتنا في أن نكون جزءًا من مسيرة نهوضه، نزور فخامتكم اليوم، بعد انتخاب الهيئة الجديدة لمجلس الأعمال اللبناني -القبرصي، التي لي شرف رئاستها، حاملين معنا إرادةً حقيقية للعمل، وليس مجرد الرغبة في الحديث عن الفرص."
+وإذ رأى ان قبرص تستطيع ان تكون بوابة أوروبية الى العالم العربي كما يستطيع لبنان ان يكون بوابة للعالم العربي الى أوروبا، متطلعا الى الانتقال بالعلاقة اللبنانية القبرصية من اطارها التقليدي الى شراكة اقتصادية واستثمارية استراتيجية، فانه تحدث عن عدد من المجالات الواعدة منها:
+أولا: تفعيل الاستثمارات المتبادلة وتسهيل حركة المستثمرين ورؤوس الاموال والخبرات بين البلدين.
+ثانيا: تعزيز التعاون في قطاع الطاقة.
+ثالثا: تطوير النقل البحري والخدمات اللوجستية والسياحة.
+رابعًا: تشجيع التعاون في التكنولوجيا والاقتصاد الرقمي والشركات الناشئة، وفتح المجال أمام الشباب اللبناني والقبرصي لبناء مشاريع مشتركة تتطلع إلى المستقبل.
+خامسًا: إنشاء منصة دائمة للتواصل بين القطاعين الخاصين في البلدين، لا تكتفي بتبادل الأفكار، بل تعمل على تحويل الأفكار إلى مشاريع، والفرص إلى استثمارات، والعلاقات التاريخية إلى نتائج اقتصادية ملموسة".
+وختم: "نضع أنفسنا وإمكانات مجلس الأعمال اللبناني -القبرصي في تصرف فخامتكم، لأننا نؤمن بأن النهوض الاقتصادي ليس مشروعاً منفصلاً عن النهوض الوطني، بل هو أحد أعمدته الأساسية. ونريد في مجلس الاعمال اللبناني -القبرصي ان نكون جزءا فاعلا من هذا المسار وان نضع خبراتنا وعلاقاتنا وامكاناتنا في خدمة هذا الهدف. ونجدد لفخامتكم شكرنا على هذا الاستقبال الكريم، ونعرب عن ثقتنا بأن المرحلة المقبلة، بقيادتكم، قادرة على أن تعيد إلى لبنان استقراره، وتطلق اقتصاده، وتستعيد له دوره ومكانته.
+ونتمنى أن يحمل عهدكم للبنانيين الأمن والسلام والاستقرار، وأن يستعيد لبنان عافيته وسيادته ودوره، وأن يبقى وطناً قادراً على حماية أبنائه، واحتضان طاقاته، وصناعة مستقبله. "
+الرئيس عون
+ورد الرئيس عون مرحّبًا بالوفد، مشدداً على دور رجال الأعمال اللبنانيين في دعم الاقتصاد وتشجيع الاستثمار وتطوير مختلف القطاعات والمساعدة على فتح أسواق جديدة وتعزيز التعاون مع الدول ومنها قبرص. وأكد رئيس الجمهورية ان مجلس رجال الاعمال اللبناني -القبرصي يساهم في تعزيز العلاقات اللبنانية-القبرصية ويوسع افق التعاون بين البلدين، إلا أنه اعتبر ان الاستقرار الامني هو الشرط الأساسي لإنماء لبنان وتعزيز ثقة المستثمرين ورجال الاعمال فيه. وقال :"إن اللبناني مبدع وكفوء، وهو بما يملك من طاقات، قادر على النهوض ببلده من جديد في حال استقرت الاوضاع وساد الامن"، مشيراً الى أن" الاقتصاد اللبناني حقق في العام 2025 نمواً بارزاً كما سجلت وزارة المال فائضاً وزادت موجودات البنك المركزي، ولكن للاسف كان للحرب اثر سلبي على مختلف الصعد، إلا انه لا مكان لليأس ولذلك اتخذنا قرار التفاوض لإنقاذ لبنان ونقله من حالة الحرب الى حالة السلم. فاللبنانيون، بمختلف اطيافهم، تعبوا من الحروب التي لا تجلب الا المزيد من الدماء والدمار والفقر. وانا افكر بمصلحة لبنان وبمصلحة جميع اللبنانيين واشدد على انه لا يمكن حل مشاكل لبنان الا عبر اعتماد لغة التروّي والحوار بعيداً عن التصادم وذلك للمحافظة على كيانه وبنيته وتعدديته التي يتميز بها."
+وتطرق الرئيس عون الى الازمات الاقتصادية العالمية والحروب الاقليمية والنزاعات بين الدول لا سيما ما يحصل عند مضيقي هرمز وباب المندب وتأثيرها على الاقتصاد اللبناني، ولفت الى "أن لبنان يعتمد بدرجة كبيرة على الاستيراد ما ادى الى ارتفاع أسعار الطاقة والمواد الأولية وكلفة النقل وبالتالي أسعار السلع على المواطنين وكلفة الإنتاج. ومن هنا تبرز أهمية تطوير العلاقات الاقتصادية بن لبنان وقبرص وتعزيز دور المجلس اللبناني القبرصي بهدف تشجيع الاستثمارات خصوصاً أن هناك جالية لبنانية كبيرة في قبرص ولها ثقلها وتأثيرها في المجتمع والاقتصاد القبرصيين، كما ان قبرص عبّرت عن استعدادها لمساعدة لبنان لا سيما في مجال قطاع الطاقة."
+رئيس مجلس إدارة "بيبسي كولا"
+وفي قصر بعبدا، رئيس مجلس الإدارة للشركة العصرية اللبنانية للتجارة المساهمة معبئة "بيبسي كولا" في لبنان السيد وليد عساف الذي اطلع رئيس الجمهورية على التحضيرات الجارية للاحتفال بمرور خمسة وسبعين عاماً على تأسيس الشركة والذي سيشارك فيه، الرئيس العالمي لشركة "بيبسي كولا" السيد EUGENE WILLEMSEN خلال زيارته لبنان في شهر كانون الأول المقبل.
+وفد من الجامعة الانطونية
+الى ذلك، استقبل الرئيس عون، وفد من الجامعة الانطونية ضم رئيسها الاب ميشال السغبيني وامينها العام الاب جان العلم والقيّم الاب جو بوجوده ، نقلوا إليه دعوة لحضور افتتاحية تساعية الميلاد المجيد التي تقام في ١٥ كانون الاول ويترأس الصلاة البطريرك الماروني مار بشارة بطرس الراعي.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:01:53.769769+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من وفد من الجامعة الانطونية دعوة لحضور افتتاحية تساعية الميلاد واطلع من رئيس مجلس إدارة "بيبسي كولا" على التحضيرات للاحتفال بمرور خمسة وسبعين عاماً على تأسيس الشركة</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1605</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من وفد من الجامعة الانطونية دعوة لحضور افتتاحية تساعية الميلاد واطلع من رئيس مجلس إدارة "بيبسي كولا" على التحضيرات للاحتفال بمرور خمسة وسبعين عاماً على تأسيس الشركة
+استقبل الرئيس عون، وفد من الجامعة الانطونية ضم رئيسها الاب ميشال السغبيني وامينها العام الاب جان العلم والقيّم الاب جو بوجوده ، نقلوا إليه دعوة لحضور افتتاحية تساعية الميلاد المجيد التي تقام في ١٥ كانون الاول ويترأس الصلاة البطريرك الماروني مار بشارة بطرس الراعي.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:01:55.987126+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل رئيس مجلس إدارة "بيبسي كولا"</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1604</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل رئيس مجلس إدارة "بيبسي كولا"
+استقبل الرئيس عون رئيس مجلس الإدارة للشركة العصرية اللبنانية للتجارة المساهمة معبئة "بيبسي كولا" في لبنان السيد وليد عساف الذي اطلعه على التحضيرات الجارية للاحتفال بمرور خمسة وسبعين عاماً على تأسيس الشركة والذي سيشارك فيه، الرئيس العالمي لشركة "بيبسي كولا" السيد EUGENE WILLEMSEN خلال زيارته لبنان في شهر كانون الأول المقبل.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:01:58.187549+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية مستقبلاً مجلس رجال الاعمال اللبناني-القبرصي: لا مكان لليأس واللبناني بما يملك من طاقات قادر على النهوض ببلده من جديد</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1603</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية مستقبلاً مجلس رجال الاعمال اللبناني-القبرصي: لا مكان لليأس واللبناني بما يملك من طاقات قادر على النهوض ببلده من جديد
+الرئيس عون: لا اقتصاد من دون استقرار ولا يمكن حل مشاكل لبنان
+الا عبر اعتماد لغة التروّي والحوار بعيداً عن التصادم
+استقبل الرئيس عون رئيس مجلس رجال الاعمال اللبناني- القبرصي السيد دافيد عيسى على رأس وفد بحضور رئيس الهيئات الاقتصادية الوزير السابق محمد شقير. في مستهل اللقاء، القى السيد عيسى كلمة قال فيها:
+"يشرفني، كما يشرّف أعضاء مجلس الأعمال اللبناني- القبرصي، أن نلتقي فخامتكم اليوم، بحضور رئيس الهيئات الاقتصادية، معالي الأستاذ محمد شقير، حاملين إليكم رسالة عنوانها الإيمان الراسخ بلبنان، والتمسك بدوره ومكانته، والاستعداد الكامل للمساهمة في فتح آفاق جديدة أمام اقتصاده، ودعم مسيرة النهوض والتعافي، وتعزيز علاقاته وشراكاته مع محيطه العربي وامتداده الأوروبي.
+نحن ندرك تمامًا حجم التحديات الاستثنائية التي رافقت بداية عهدكم، وندرك كذلك أنكم تسلمتم مسؤولية قيادة هذا الوطن في واحدة من أكثر المراحل دقة وحساسية وتعقيدًا في تاريخه الحديث، في ظرف لم يكن عاديًا بأي مقياس، وكأنكم حملتم بين أيديكم كرة نار، وسط أزمات متراكمة واستحقاقات وطنية متشابكة.
+لقد بدأ عهدكم في ظل حرب ألقت بثقلها على البلاد، واقتصاد أنهكته سنوات الأزمات، وشعب لبناني أثقلته الهواجس على أمنه وحاضره ومستقبله، فيما كانت مؤسسات الدولة تواجه تحديات جسيمة على المستويات السياسية والأمنية والاقتصادية والاجتماعية.
+وفي خضم هذا الواقع شديد التعقيد، لم تكن مسؤولية القيادة مجرّد إدارة مرحلة صعبة، بل كانت مواجهة إرث ثقيل ومحاولة استعادة زمام الدولة في وقت كانت فيه البلاد بأمسّ الحاجة إلى الاستقرار والثقة والأمل.
+ونحن نرى، فخامة الرئيس، الجهود التي تبذلونها في الداخل والخارج، وندرك حجم الاتصالات والتحركات التي تقومون بها من أجل حماية لبنان، ووقف الحرب، وتجنيب وطننا المزيد من الخسائر والمعاناة. ونرى جولاتكم واتصالاتكم مع الدول الشقيقة والصديقة، وسعيكم إلى حشد الدعم للبنان، وإلى فتح الأبواب أمام كل مبادرة يمكن أن تساهم في وقف الحرب وتثبيت الاستقرار.
+ومن هنا، نقول لكم اليوم بكل صراحة ووضوح: نحن إلى جانبكم، ونقدّر عاليًا الجهود التي تبذلونها، كما نقدّر حجم المسؤولية الوطنية الكبيرة التي تحمّلتم أعباءها في هذا الظرف الدقيق والاستثنائي. ونتمنى لكم كل القوة والثبات والتوفيق في تحمّل هذه المسؤولية، والمضي بلبنان نحو مرحلة جديدة يسودها الأمن والاستقرار، وتستعيد فيها الدولة عافيتها ومكانتها، ويستعيد اللبنانيون ثقتهم بمستقبل وطنهم."
+أضاف:"نحن نؤمن بأن الاستقرار ليس مجرد مطلب سياسي وأمني، بل هو المدخل الحقيقي إلى النهوض الاقتصادي، وإلى الاستثمار، وخلق فرص العمل، وإعادة الشباب اللبناني إلى دائرة الأمل، بدل أن تصبح الهجرة خياره الوحيد. ومن هذا الإيمان بلبنان، ومن رغبتنا في أن نكون جزءًا من مسيرة نهوضه، نزور فخامتكم اليوم، بعد انتخاب الهيئة الجديدة لمجلس الأعمال اللبناني -القبرصي، التي لي شرف رئاستها، حاملين معنا إرادةً حقيقية للعمل، وليس مجرد الرغبة في الحديث عن الفرص."
+وإذ رأى ان قبرص تستطيع ان تكون بوابة أوروبية الى العالم العربي كما يستطيع لبنان ان يكون بوابة للعالم العربي الى أوروبا، متطلعا الى الانتقال بالعلاقة اللبنانية القبرصية من اطارها التقليدي الى شراكة اقتصادية واستثمارية استراتيجية، فانه تحدث عن عدد من المجالات الواعدة منها:
+أولا: تفعيل الاستثمارات المتبادلة وتسهيل حركة المستثمرين ورؤوس الاموال والخبرات بين البلدين.
+ثانيا: تعزيز التعاون في قطاع الطاقة.
+ثالثا: تطوير النقل البحري والخدمات اللوجستية والسياحة.
+رابعًا: تشجيع التعاون في التكنولوجيا والاقتصاد الرقمي والشركات الناشئة، وفتح المجال أمام الشباب اللبناني والقبرصي لبناء مشاريع مشتركة تتطلع إلى المستقبل.
+خامسًا: إنشاء منصة دائمة للتواصل بين القطاعين الخاصين في البلدين، لا تكتفي بتبادل الأفكار، بل تعمل على تحويل الأفكار إلى مشاريع، والفرص إلى استثمارات، والعلاقات التاريخية إلى نتائج اقتصادية ملموسة".
+وختم: "نضع أنفسنا وإمكانات مجلس الأعمال اللبناني -القبرصي في تصرف فخامتكم، لأننا نؤمن بأن النهوض الاقتصادي ليس مشروعاً منفصلاً عن النهوض الوطني، بل هو أحد أعمدته الأساسية. ونريد في مجلس الاعمال اللبناني -القبرصي ان نكون جزءا فاعلا من هذا المسار وان نضع خبراتنا وعلاقاتنا وامكاناتنا في خدمة هذا الهدف. ونجدد لفخامتكم شكرنا على هذا الاستقبال الكريم، ونعرب عن ثقتنا بأن المرحلة المقبلة، بقيادتكم، قادرة على أن تعيد إلى لبنان استقراره، وتطلق اقتصاده، وتستعيد له دوره ومكانته.
+ونتمنى أن يحمل عهدكم للبنانيين الأمن والسلام والاستقرار، وأن يستعيد لبنان عافيته وسيادته ودوره، وأن يبقى وطناً قادراً على حماية أبنائه، واحتضان طاقاته، وصناعة مستقبله. "
+الرئيس عون
+ورد الرئيس عون مرحّبًا بالوفد، مشدداً على دور رجال الأعمال اللبنانيين في دعم الاقتصاد وتشجيع الاستثمار وتطوير مختلف القطاعات والمساعدة على فتح أسواق جديدة وتعزيز التعاون مع الدول ومنها قبرص. وأكد رئيس الجمهورية ان مجلس رجال الاعمال اللبناني -القبرصي يساهم في تعزيز العلاقات اللبنانية-القبرصية ويوسع افق التعاون بين البلدين، إلا أنه اعتبر ان الاستقرار الامني هو الشرط الأساسي لإنماء لبنان وتعزيز ثقة المستثمرين ورجال الاعمال فيه. وقال :"إن اللبناني مبدع وكفوء، وهو بما يملك من طاقات، قادر على النهوض ببلده من جديد في حال استقرت الاوضاع وساد الامن"، مشيراً الى أن" الاقتصاد اللبناني حقق في العام 2025 نمواً بارزاً كما سجلت وزارة المال فائضاً وزادت موجودات البنك المركزي، ولكن للاسف كان للحرب اثر سلبي على مختلف الصعد، إلا انه لا مكان لليأس ولذلك اتخذنا قرار التفاوض لإنقاذ لبنان ونقله من حالة الحرب الى حالة السلم. فاللبنانيون، بمختلف اطيافهم، تعبوا من الحروب التي لا تجلب الا المزيد من الدماء والدمار والفقر. وانا افكر بمصلحة لبنان وبمصلحة جميع اللبنانيين واشدد على انه لا يمكن حل مشاكل لبنان الا عبر اعتماد لغة التروّي والحوار بعيداً عن التصادم وذلك للمحافظة على كيانه وبنيته وتعدديته التي يتميز بها."
+وتطرق الرئيس عون الى الازمات الاقتصادية العالمية والحروب الاقليمية والنزاعات بين الدول لا سيما ما يحصل عند مضيقي هرمز وباب المندب وتأثيرها على الاقتصاد اللبناني، ولفت الى "أن لبنان يعتمد بدرجة كبيرة على الاستيراد ما ادى الى ارتفاع أسعار الطاقة والمواد الأولية وكلفة النقل وبالتالي أسعار السلع على المواطنين وكلفة الإنتاج. ومن هنا تبرز أهمية تطوير العلاقات الاقتصادية بن لبنان وقبرص وتعزيز دور المجلس اللبناني القبرصي بهدف تشجيع الاستثمارات خصوصاً أن هناك جالية لبنانية كبيرة في قبرص ولها ثقلها وتأثيرها في المجتمع والاقتصاد القبرصيين، كما ان قبرص عبّرت عن استعدادها لمساعدة لبنان لا سيما في مجال قطاع الطاقة."</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:00.399745+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>الرئيس عون عرض مع وزير العدل الواقع القضائي وعمل المحاكم</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1602</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:02.726523+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل خمسة نواب فرنسيين من مجموعة دراسات مسيحيي الشرق: لبنان رسالة للحرية والتعددية في المنطقة والعالم ولا يمكن أن يحيا من دون جناحيه المسيحي والمسلم</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1601</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل خمسة نواب فرنسيين من مجموعة دراسات مسيحيي الشرق: لبنان رسالة للحرية والتعددية في المنطقة والعالم ولا يمكن أن يحيا من دون جناحيه المسيحي والمسلم
+رئيس الجمهورية: لا خطر على الوجود المسيحي في لبنان
+وما حصل في عدد من الدول المجاورة لا يمكن أن يتكرر فيه
+الرئيس عون: حماية العيش المشترك في لبنان ليست مسؤولية لبنانية فحسب بل تتصل
+بمستقبل المنطقة لأن نجاح تجربة الشراكة الإسلامية-المسيحية يعزز فرص الاعتدال
+الوفد الفرنسي اكد دعم شعب بلاده للبنان وشعبه المميز
+بدوره وثقافته وحضوره داخل لبنان ودول العالم
+أبلغ رئيس الجمهورية العماد جوزاف عون خمسة نواب فرنسيين من مجموعة دراسات مسيحيي الشرق خلال استقبالهم قبل ظهر اليوم في قصر بعبدا في حضور السفير الفرنسي في لبنان باتريك دوريل، أن لبنان رسالة للحرية والتعددية في المنطقة والعالم، ولا يمكن أن يحيا من دون جناحيه المسيحي والمسلم. فإذا فقد الجناح المسيحي، فإن التطرف هو البديل، وسيمتد الى اوروبا وإذا فقد الجناح المسلم لأي سبب، فإن الاعتدال سيفقد. والمسيحيون في لبنان حريصون على المحافظة على التعايش المسيحي-الإسلامي، وهم من خلال ممارساتهم يؤكدون على أهمية الدور الذي يلعبونه في دول الشرق والغرب.
+وقال الرئيس عون للوفد النيابي الفرنسي أن لا خطر على الوجود المسيحي في لبنان وما حصل في عدد من الدول المجاورة لا يمكن أن يتكرر في لبنان. فالمسيحيون يشكلون مع إخوتهم المسلمين حالة نموذجية فريدة لأن التعايش الإسلامي - المسيحي في لبنان ليس مجرد صيغة سياسية فرضتها الظروف، بل هو خيار وطني وحضاري وتجربة إنسانية أثبتت أن التنوع يمكن أن يكون مصدر قوة، وأن الاختلاف لا يتناقض مع الوحدة بل يغنيها ويعززها، إضافة إلى أن هذا التعايش هو الشراكة الكاملة في بناء الدولة وصون مؤسساتها وتقرير مستقبل الوطن. واعتبر رئيس الجمهورية أن قوة لبنان الحقيقية تكمن في قدرته على حماية هذا النموذج وتطويره وترسيخ الثقة بين أبنائه بعيداً عن منطق الغلبة والإقصاء، وما يضمن احترام خصوصية كل مكوّن في إطار دولة واحدة عادلة وقوية.
+وفيما اعتبر الرئيس عون أن الوحدة بين المسيحيين والمسلمين شرط أساسي لحماية لبنان واستقراره، وصمام أمان في مواجهة الفتنة ومحاولات زرع الانقسام بين أبنائه، شدد على أن التجارب التي مر بها لبنان والمنطقة أثبتت أن الانقسامات الداخلية لا تنتج إلا الضعف، وأن استغلال الدين والمذهب لتحقيق أهداف سياسية أو لتبرير العنف لا يهدد جماعة بعينها بل يهدد المجتمعات بأكملها. وأكد رئيس الجمهورية أن حماية العيش المشترك في لبنان ليست مسؤولية لبنانية فحسب، بل هي مسؤولية تتصل بمستقبل المنطقة لأن نجاح تجربة الشراكة الإسلامية-المسيحية يعزز فرص الاعتدال ويقدم دليلا عمليا على إمكان بناء مجتمعات تحترم التعددية وتحمي كرامة الإنسان وحقوقه.
+وعرض الرئيس عون، ردا على أسئلة أعضاء الوفد، لتجذر العلاقات اللبنانية -الفرنسية، شاكرا الرئيس الفرنسي إيمانويل ماكرون على الدعم المستمر للبنان في مختلف المجالات، وإصراره على الوقوف إلى جانبه في الظروف الصعبة التي مر بها ولا يزال. وشرح رئيس الجمهورية الأوضاع في الجنوب في ظل استمرار اعتداءات إسرائيل التي لا تزال تقصف وتدمر وتجرف القرى والبلدات الجنوبية التي تحتلها، خلافا لمندرجات اتفاق الإطار الذي تم التوصل إليه بين لبنان وإسرائيل برعاية أميركية، معربا عن أمله في أن تتمكن الولايات المتحدة الأميركية والمجتمع الدولي من الضغط على إسرائيل لوقف اعتداءاتها والانسحاب من الجنوب وينتشر الجيش اللبناني حتى الحدود وإعادة الأسرى وبدء إعادة الإعمار وعودة الجنوبيين إلى أرضهم.
+وأكد الرئيس عون حرص لبنان على بقاء قوات "اليونيفيل" في الجنوب أو إحلال قوات أوروبية مكانها، تكون نواة لقوات من دول صديقة ترغب في مساعدة لبنان والمساهمة في تحقيق الأمن والاستقرار في الجنوب، مكررا التأكيد بأن لا حلول آمنة ومستدامة من خلال الحرب، بل من خلال التفاوض الدبلوماسي لأن الحروب لا يمكن أن تحقق أي نتيجة عملية، بل هي تدمر وتشرد وتوقع قتلى وجرحى ولا تنهي الصراعات. وحده التفاوض الدبلوماسي يمكن أن يحقق الأمان للدول والشعوب.
+وأكد الرئيس عون للوفد النيابي الفرنسي أن الدولة ساهرة على سلامة أبناء القرى الجنوبية الحدودية الصامدين في منازلهم وممتلكاتهم وتعمل مع المنظمات الإنسانية و"اليونيفيل" والجيش اللبناني على تأمين كل مقومات الصمود الصحية والتربوية والغذائية لهم إلى حين زوال الاحتلال الإسرائيلي.
+وأوضح ردا على سؤال، أن لبنان يعمل من أجل تحقيق استراتيجية للشراكة مع الاتحاد الأوروبي كما سبق للرئيس عون أن دعا لقيام سوق عربية مشتركة انطلاقا من القناعة أن في الاتحاد قوة.
+وكان أعضاء الوفد عرضوا للرئيس عون أهداف زيارتهم إلى لبنان للاطلاع على الأوضاع فيه عن كثب، واعداد تقرير مفصل ضمن مجموعة العمل النيابية لمسيحيي الشرق في مجلس النواب الفرنسي، مشيرين إلى أنهم زاروا منطقة مرجعيون والقرى المجاورة والتقوا مجموعة من أبنائها وطلابها واطلعوا على أوضاعهم وحاجاتهم، مؤكدين دعم الشعب الفرنسي للبنان وشعبه المميز بدوره وثقافته وحضوره داخل لبنان ودول العالم.
+وضم الوفد النواب: رئيسة مجموعة دراسات مسيحيي الشرق السيدة CENDRINE FOUCHER-CHAZE، والسيدات والسادة: ELIZABETH DE MAISTRE، ERIC LIEGEON DOMINIQUE POTIER، ERIC MARTINEAU، و AMELIA LAKRAFI.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:04.808776+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من السفير البابوي رسالة شكر من الحبر الأعظم على تمنيات رئيس الجمهورية له بالشفاء بعد العملية الجراحية</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1600</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من السفير البابوي رسالة شكر من الحبر الأعظم على تمنيات رئيس الجمهورية له بالشفاء بعد العملية الجراحية
+استقبل رئيس الجمهورية العماد جوزاف عون بعد ظهر اليوم في قصر بعبدا، السفير البابوي في لبنان المونسنيور باولو بورجيا الذي نقل اليه رسالة من قداسة البابا لاون الرابع عشر، شكره فيها على الرسالة التي كان وجهها اليه بعد الجراحة الناجحة التي أجريت له، والتي تمنى فيها لقداسته، باسمه الشخصي وباسم الشعب اللبناني، الصحة والعافية.
+وعبّر الاب الاقدس في رسالته، عن شكره للرئيس عون على لفتته الكريمة وعلى المشاعر التي تضمنتها. وقال: "امنحكم من صميم القلب بركتي الرسولية التي اسديها ايضاً الى عائلتكم والى الشعب اللبناني"</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:07.075911+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>لقاءات نيابية وبيئية واقتصادية في قصر بعبدا</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1599</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>لقاءات نيابية وبيئية واقتصادية في قصر بعبدا
+رئيس الجمهورية عرض مع النائب عطية الاوضاع العامة وشؤون منطقة الشمال
+الرئيس عون تابع مع رئيس مجلس إدارة الهيئة الوطنية لإدارة النفايات الصلبة
+التقدّم المحرز في معالجة ملف النفايات والمسائل التي لا تزال عالقة في هذا المجال
+رئيس الجمهورية لوفد نقابة مستوردي ومصدري الخضار والفاكهة:
+الزراعة ركيزة اساسية للاقتصاد اللبناني ونحرص على متابعة مطالب النقابة
+ومعالجة التحديات التي تواجه القطاع
+شهد قصر بعبدا قبل ظهر اليوم لقاءات نيابية واقتصادية وبيئية عرض خلالها رئيس الجمهورية العماد جوزاف عون مع زواره الاوضاع العامة وآخر المستجدات والشؤون الانمائية.
+وفي هذا الاطار استقبل الرئيس عون النائب سجيع عطية الذي تابع مع الرئيس عون المستجدات الداخلية والاقليمية اضافة الى الاوضاع في منطقة الشمال لا سيما لجهة المشاريع الانمائية فيها. وقال بعد اللقاء: "كان لقاءا ايجابيا ومتنوعا حيث بحثنا عناوين كبيرة على مستوى الوطن. والرئيس عون ما زال مصممًا على التأكيد على الوحدة الوطنية والمحافظة على السلم الأهلي، وعلى حياد لبنان وبقائه بعيدًا عن كل النزاعات وكل المحاور، وما زال عازمًا على تحقيق السيادة والاصلاح السياسي والمالي."
+اضاف:"تحدثنا بشكل أساسي عن أموال المودعين. وإن شاء الله، سيبذل الرئيس عون جهداً قويا في الضغط لحل هذا الموضوع مع الحكومة طبعا. كما ناقشنا مواضيع إنمائية، وخاصةً في منطقة الشمال وضرورة الاسراع في انهاء موضوع مطار الرئيس رينيه معوض في القليعات والصيد البحري كما موضوع الجامعة اللبنانية و قد اخبرنا بأنه سيتم بدء العمل به فورًا .ونتمنى تشريف الرئيس عون الى المنطقة وتدشين هذه المشاريع. هذا هو العهد وهذا هو النفس الوطني الذي يعتمده الرئيس عون خلال ممارسته لمسؤولياته، وهو من مؤسسة عسكرية كبيرة. وفي عكار، الجيش دائمًا هو في صلب هذه المؤسسة الوطنية . لذلك بحثنا اليوم وبشكل دقيق جدًا في المواضيع الوطنية، والاقتصادية وضرورة وضع موازنة مع بداية السنة الجديدة تمنع الحرمان وتحقق الانماء المتوازن."
+رئيس مجلس ادارة الهيئة الوطنية لادارة النفايات
+واستقبل رئيس الجمهورية رئيس مجلس إدارة الهيئة الوطنية لإدارة النفايات الصلبة مروان رزق الله، واطّلع منه على مستجدات قطاع النفايات في لبنان والتحديات التي تواجهه.
+وقدّم رزق الله عرضاً شاملاً حول الوضع الراهن، والتقدّم المحرز في معالجة ملف النفايات، والمسائل التي لا تزال عالقة.
+كما تناول اللقاء الخطط والحلول المطروحة على المديين القصير والطويل، والتحديات التي تعترض تنفيذها، وسبل تذليل العقبات بالتنسيق مع الجهات المعنية.
+ويأتي اللقاء في إطار حرص رئيس الجمهورية على متابعة هذا الملف الحيوي والإحاطة بمختلف جوانبه قبيل مناقشته في مجلس الوزراء، بما يساهم في الدفع نحو حلول عملية ومستدامة لإدارة النفايات الصلبة في لبنان.
+نقابة مستوردي ومصدري الخضار
+وتابع رئيس الجمهورية شؤون نقابة مستوردي ومصدري الخضار والفاكهة في لبنان مع وفد من النقابة تحدث باسمهم في مستهل اللقاء رئيس النقابة نعيم صالح فقال :"تتقدم نقابة مستوردي ومصدري الخضار والفاكهة في لبنان من فخامتكم بجزيل الشكر، وتعرب عن بالغ ارتياحها وترحيبها بالخطوة الإيجابية المتمثلة في اعادة فتح أسواق المملكة العربية السعودية أمام الصادرات اللبنانية، لما لهذه الخطوة من أهمية كبيرة في دعم القطاع الزراعي اللبناني، وتعزيز فرص المزارعين والمصدرين، واستعادة حركة التبادل التجاري بين البلدين الشقيقين.
+كما نتوجه إلى فخامتكم بخالص الشكر والتقدير على تفضلكم باستقبالنا لما يمثله هذا اللقاء من فرصة لعرض هواجس القطاع ومطالبه، ووضع القضايا التي تهم العاملين فيه أمام فخامتكم، انطلاقا من حرصنا على تعزيز التواصل والتعاون مع رئاسة الجمهورية لما فيه مصلحة القطاع الزراعي والاقتصاد الوطني.
+وفي هذا الإطار، نود أن نلفت عناية فخامتكم إلى الملف العالق منذ فترة طويلة مع المؤسسة العامة لتشجيع الاستثمارات في لبنان (إيدال)، والذي سبق للنقابة أن عرضت تفاصيله ومطالبها بشأنه في كتاب وجهته إلى معالي وزير المالية. ونظرًا إلى طول أمد هذا الملف وما يترتب عليه من انعكاسات على النقابة والعاملين في القطاع، نلتمس من فخامتكم التكرم بالاطلاع عليه والتدخل لدى الجهات المعنية، بما يساعد على متابعة الموضوع بجدية، وتسريع معالجته، والوصول إلى حل منصف يضع حدًا لهذا التأخير ويعيد مؤسسة (إيدال) لدعم قطاع الزراعة مجددا.شاكرين لفخامتكم حسن اهتمامكم وتعاونكم، ومتمنين للبنان دوام الاستقرار والازدهار، ولعلاقات لبنان مع الدول الشقيقة مزيدًا من التعاون والتقدم وتفضلوا، فخامة الرئيس، بقبول فائق الاحترام والتقدير."
+امين سر النقابة
+ثم تحدث امين سر النقابة ابراهيم الترشيشي الذي عدد ايضاً لمطالب النقابة لا سيما لجهة معالجة القانون الخاص المتعلق بتسجيل سيارات وشاحنات النقل الخاصة بالخضار والفاكهة والعمل على وضع تسهيلات للشحن والانتقال خصوصا عبر دول الخليج، لافتاً أيضا الى ضرورة اعادة تفعيل عمل مؤسسة "ايدال" في هذه المرحلة ما من شأنه تعزيز حضور المنتجات الزراعية اللبنانية في الاسواق الخارجية.
+الرئيس عون
+وردّ الرئيس عون مرحّبا بالوفد، معتبرا ان القطاع الزراعي في لبنان يشكل ركيزة أساسية للاقتصاد اللبناني ومصدر رزق لآلاف العائلات في مختلف المناطق، ومشدداً على انه من واجب الدولة الوقوف الى جانب المزارعين ومستوردي ومصدري الخضار والفاكهة ودعمهم، نظراً لأهمية ذلك في تعزيز الأمن الغذائي وتوفير فرص العمل وسد حاجات السوق اللبناني.
+وأثنى رئيس الجمهورية على عمل النقابة وثقة افرادها بلبنان وتمسكهم بأرضهم داعياً الى مواصلة تحسين جودة الإنتاج والمثابرة لتحقيق مطالبهم التي تساعد على تعزيز ثقة الأسواق الخارجية به وتسهيل تصديره لا سيما الى دول الخليج ما يعيد الزراعة اللبنانية إلى المكانة التي تستحقّها.
+وأكد رئيس الجمهورية في ختام اللقاء حرصه على متابعة مطالب النقابة مع الجهات المعنية ومعالجة التحديات التي تواجه القطاع.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:09.301313+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون وفد من نقابة مستوردي ومصدري الخضار</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1598</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون وفد من نقابة مستوردي ومصدري الخضار
+تابع رئيس الجمهورية شؤون نقابة مستوردي ومصدري الخضار والفاكهة في لبنان مع وفد من النقابة تحدث باسمهم في مستهل اللقاء رئيس النقابة نعيم صالح فقال :"تتقدم نقابة مستوردي ومصدري الخضار والفاكهة في لبنان من فخامتكم بجزيل الشكر، وتعرب عن بالغ ارتياحها وترحيبها بالخطوة الإيجابية المتمثلة في اعادة فتح أسواق المملكة العربية السعودية أمام الصادرات اللبنانية، لما لهذه الخطوة من أهمية كبيرة في دعم القطاع الزراعي اللبناني، وتعزيز فرص المزارعين والمصدرين، واستعادة حركة التبادل التجاري بين البلدين الشقيقين.
+كما نتوجه إلى فخامتكم بخالص الشكر والتقدير على تفضلكم باستقبالنا لما يمثله هذا اللقاء من فرصة لعرض هواجس القطاع ومطالبه، ووضع القضايا التي تهم العاملين فيه أمام فخامتكم، انطلاقا من حرصنا على تعزيز التواصل والتعاون مع رئاسة الجمهورية لما فيه مصلحة القطاع الزراعي والاقتصاد الوطني.
+وفي هذا الإطار، نود أن نلفت عناية فخامتكم إلى الملف العالق منذ فترة طويلة مع المؤسسة العامة لتشجيع الاستثمارات في لبنان (إيدال)، والذي سبق للنقابة أن عرضت تفاصيله ومطالبها بشأنه في كتاب وجهته إلى معالي وزير المالية. ونظرًا إلى طول أمد هذا الملف وما يترتب عليه من انعكاسات على النقابة والعاملين في القطاع، نلتمس من فخامتكم التكرم بالاطلاع عليه والتدخل لدى الجهات المعنية، بما يساعد على متابعة الموضوع بجدية، وتسريع معالجته، والوصول إلى حل منصف يضع حدًا لهذا التأخير ويعيد مؤسسة (إيدال) لدعم قطاع الزراعة مجددا.شاكرين لفخامتكم حسن اهتمامكم وتعاونكم، ومتمنين للبنان دوام الاستقرار والازدهار، ولعلاقات لبنان مع الدول الشقيقة مزيدًا من التعاون والتقدم وتفضلوا، فخامة الرئيس، بقبول فائق الاحترام والتقدير."
+امين سر النقابة
+ثم تحدث امين سر النقابة ابراهيم الترشيشي الذي عدد ايضاً لمطالب النقابة لا سيما لجهة معالجة القانون الخاص المتعلق بتسجيل سيارات وشاحنات النقل الخاصة بالخضار والفاكهة والعمل على وضع تسهيلات للشحن والانتقال خصوصا عبر دول الخليج، لافتاً أيضا الى ضرورة اعادة تفعيل عمل مؤسسة "ايدال" في هذه المرحلة ما من شأنه تعزيز حضور المنتجات الزراعية اللبنانية في الاسواق الخارجية.
+الرئيس عون
+وردّ الرئيس عون مرحّبا بالوفد، معتبرا ان القطاع الزراعي في لبنان يشكل ركيزة أساسية للاقتصاد اللبناني ومصدر رزق لآلاف العائلات في مختلف المناطق، ومشدداً على انه من واجب الدولة الوقوف الى جانب المزارعين ومستوردي ومصدري الخضار والفاكهة ودعمهم، نظراً لأهمية ذلك في تعزيز الأمن الغذائي وتوفير فرص العمل وسد حاجات السوق اللبناني.
+وأثنى رئيس الجمهورية على عمل النقابة وثقة افرادها بلبنان وتمسكهم بأرضهم داعياً الى مواصلة تحسين جودة الإنتاج والمثابرة لتحقيق مطالبهم التي تساعد على تعزيز ثقة الأسواق الخارجية به وتسهيل تصديره لا سيما الى دول الخليج ما يعيد الزراعة اللبنانية إلى المكانة التي تستحقّها.
+وأكد رئيس الجمهورية في ختام اللقاء حرصه على متابعة مطالب النقابة مع الجهات المعنية ومعالجة التحديات التي تواجه القطاع.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:11.530186+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون رئيس مجلس ادارة الهيئة الوطنية لادارة النفايات الصلبة مروان رزق الله</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1597</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون رئيس مجلس ادارة الهيئة الوطنية لادارة النفايات الصلبة مروان رزق الله
+استقبل رئيس الجمهورية رئيس مجلس إدارة الهيئة الوطنية لإدارة النفايات الصلبة مروان رزق الله، واطّلع منه على مستجدات قطاع النفايات في لبنان والتحديات التي تواجهه.
+وقدّم رزق الله عرضاً شاملاً حول الوضع الراهن، والتقدّم المحرز في معالجة ملف النفايات، والمسائل التي لا تزال عالقة.
+كما تناول اللقاء الخطط والحلول المطروحة على المديين القصير والطويل، والتحديات التي تعترض تنفيذها، وسبل تذليل العقبات بالتنسيق مع الجهات المعنية.
+ويأتي اللقاء في إطار حرص رئيس الجمهورية على متابعة هذا الملف الحيوي والإحاطة بمختلف جوانبه قبيل مناقشته في مجلس الوزراء، بما يساهم في الدفع نحو حلول عملية ومستدامة لإدارة النفايات الصلبة في لبنان.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:13.724770+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون النائب سجيع عطية وعرض معو الاوضاع العامة وشؤون منطقة الشمال</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1596</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون النائب سجيع عطية وعرض معو الاوضاع العامة وشؤون منطقة الشمال
+استقبل الرئيس عون النائب سجيع عطية الذي تابع مع الرئيس عون المستجدات الداخلية والاقليمية اضافة الى الاوضاع في منطقة الشمال لا سيما لجهة المشاريع الانمائية فيها. وقال بعد اللقاء: "كان لقاءا ايجابيا ومتنوعا حيث بحثنا عناوين كبيرة على مستوى الوطن. والرئيس عون ما زال مصممًا على التأكيد على الوحدة الوطنية والمحافظة على السلم الأهلي، وعلى حياد لبنان وبقائه بعيدًا عن كل النزاعات وكل المحاور، وما زال عازمًا على تحقيق السيادة والاصلاح السياسي والمالي."
+اضاف:"تحدثنا بشكل أساسي عن أموال المودعين. وإن شاء الله، سيبذل الرئيس عون جهداً قويا في الضغط لحل هذا الموضوع مع الحكومة طبعا. كما ناقشنا مواضيع إنمائية، وخاصةً في منطقة الشمال وضرورة الاسراع في انهاء موضوع مطار الرئيس رينيه معوض في القليعات والصيد البحري كما موضوع الجامعة اللبنانية و قد اخبرنا بأنه سيتم بدء العمل به فورًا .ونتمنى تشريف الرئيس عون الى المنطقة وتدشين هذه المشاريع. هذا هو العهد وهذا هو النفس الوطني الذي يعتمده الرئيس عون خلال ممارسته لمسؤولياته، وهو من مؤسسة عسكرية كبيرة. وفي عكار، الجيش دائمًا هو في صلب هذه المؤسسة الوطنية . لذلك بحثنا اليوم وبشكل دقيق جدًا في المواضيع الوطنية، والاقتصادية وضرورة وضع موازنة مع بداية السنة الجديدة تمنع الحرمان وتحقق الانماء المتوازن."</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:15.808486+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية مستقبلاً وزيرة الخارجية والدفاع الايرلندية: لبنان يرغب في ان تستكمل قوات "اليونيفيل" مهمتها العملانية في الجنوب ويرحّب بأي قوة أوروبية بديلة بالتعاون مع الامم المتحدة في حال تعذر التمديد</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1595</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية مستقبلاً وزيرة الخارجية والدفاع الايرلندية: لبنان يرغب في ان تستكمل قوات "اليونيفيل" مهمتها العملانية في الجنوب ويرحّب بأي قوة أوروبية بديلة بالتعاون مع الامم المتحدة في حال تعذر التمديد
+الرئيس عون: الدعم اللوجستي والتقني الذي يمكن ان تقدمه القوة البديلة لـ"اليونيفيل"
+سيكون له اثرا إيجابيا في تسهيل مهمة الجيش اللبناني وحياة المجتمع الجنوبي
+رئيس الجمهورية: الاتصالات مستمرة مع واشنطن من اجل
+وضع حد للاعتداءات الاسرائيلية
+الرئيس عون : إسرائيل وعبر اعتداءاتها تضع العراقيل امام تطبيق اتفاق الاطار
+ما يحول دون تمكين الجيش اللبناني من بسط سيادة الدولة حتى الحدود واعادة الاستقرار
+الرئيس عون: لبنان يتطلع الى دعم الدول الصديقة ومنها ايرلندا
+للضغط على إسرائيل لوقف اعتداءاتها والانسحاب من الجنوب وإعادة الاسرى
+وتمكين الدولة من إعادة اعمار القرى المهدمة وإعادة اهاليها اليها
+الوزيرة الايرلندية: دعم ايرلندا للبنان سوف يتواصل رغم الظروف الصعبة التي تمر بها المنطقة
+ابلغ رئيس الجمهورية العماد جوزاف عون وزيرة الخارجية والدفاع في ايرلندا السيدة Helen McEntee ان لبنان يرغب في ان تستكمل القوات الدولية العاملة في الجنوب(اليونيفيل) مهمتها العملانية خلال السنة المقبلة المحددة لانسحابها بموجب قرار مجلس الامن نظرا لأهمية وجودها في الجنوب لمراقبة ما يجري من جهة، ولمساعدة الجيش اللبناني حين ينتشر حتى الحدود الجنوبية الدولية بعد انسحاب إسرائيل، فضلا عن أهمية المهام الإنسانية والاجتماعية والصحية التي تقوم بها قوات "اليونيفيل" لمساعدة أبناء القرى الجنوبية الذين يرحبون بوجود حفظة السلام على ارضهم.
+ولفت الرئيس عون الوزيرة الأيرلندية الى انه في حال عدم التجاوب مع المطلب اللبناني في التمديد لمهام "اليونيفيل" فإن لبنان يرحب بمشاركة أي قوة أوروبية وفق صيغة يتم الاتفاق حولها مع الاتحاد الأوروبي او مع الدول المعنية بالتعاون مع الأمم المتحدة، لان حصول أي فراغ في الجنوب نتيجة مغادرة "اليونيفيل" يخشى ان تكون له انعكاسات سلبية على الاستقرار في المنطقة، معتبرا ان الدعم اللوجستي والتقني الذي يمكن ان تقدمه القوة البديلة لــ "اليونيفيل" سيكون له اثرا إيجابيا في تسهيل مهمة الجيش اللبناني وحياة المجتمع الجنوبي.
+وأشار الرئيس عون الى ان إسرائيل لم تلتزم بالاتفاق الذي تم التوصل اليه في المفاوضات في واشنطن وهي تواصل اعتداءاتها على القرى والبلدات الجنوبية قصفا وتدميرا وجرفا للمنازل، لافتا الى ان الاتصالات التي اجراها لبنان مع الولايات المتحدة الأميركية بصفتها راعية الاتفاق من اجل وضع حد لهذه الاعتداءات، لا تزال من دون نتيجة، لا بل ان إسرائيل تضع العراقيل امام تطبيق الاتفاق ما يزيد الأمور تعقيدا ويحول دون تمكين الجيش اللبناني من بسط سيادة الدولة حتى الحدود الدولية ومنع المظاهر المسلحة وإعادة الاستقرار.
+وأشار الرئيس عون الى ان لبنان يتطلع الى دعم الدول الصديقة ومنها ايرلندا، للضغط على إسرائيل لوقف اعتداءاتها والانسحاب من الجنوب وإعادة الاسرى اللبنانيين وتمكين الدولة من إعادة اعمار القرى والبلدات المهدمة وإعادة اهاليها اليها.
+وفي الشأن الداخلي اكد رئيس الجمهورية للوزيرة الايرلندية ان الحكومة ماضية في الإصلاحات الاقتصادية والمالية بالتعاون مع مجلس النواب على رغم الظروف الصعبة التي مرت بها البلاد، مرحّبا بأي دعم تقدمه ايرلندا للبنان في المجالات الإنسانية والاجتماعية والعسكرية والتربوية، شاكرا لأيرلندا مساهمتها في القوات الدولية العاملة في الجنوب منذ العام 1978 ومحييا ذكرى العسكريين الايرلنديين الذين استشهدوا على ارض الجنوب.
+وكانت الوزيرة Helen McEntee قد أعربت عن سرورها لزيارة لبنان والاطلاع على الأوضاع فيه وتفقد القوى الايرلندية العاملة في الجنوب، مؤكدة على استمرار ايرلندا في المشاركة في عمليات حفظ السلام في الجنوب ودعم الجيش اللبناني والمجتمع المدني اللبناني إضافة الى التعاون مع الإدارات والمؤسسات العامة لتقديم المساعدات التي يحتاجها لبنان، لافتة الى ان هذا الدعم سوف يتواصل رغم الظروف الصعبة التي تمر بها المنطقة.
+وضم الوفد المرافق للوزيرة الايرلندية: سفير ايرلندا في لبنان AIDAN O’HARA، مدير عام وزارة الدفاع الايرلندية JACQUELINE McCRUM، رئيس الأركان العامة للجيش الايرلندي MAJ.GRN.ROSSA MULCAHY، مساعد مدير عام وزارة الدفاع BERNIE MAGUIRE، مدير الشؤون السياسية في وزارة الخارجية GERARD KEOWN، مستشار خاص لوزير الدفاع EVAN HENRY، القنصل الفخري العام لايرلندا في لبنان GEORGES SIAM.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:18.109549+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>الرئيس عون إستقبل السيدة ميسم سكاف وعرض معها حاجات منطقة البقاع الغربي وراشيا</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1594</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>الرئيس عون إستقبل السيدة ميسم سكاف وعرض معها حاجات منطقة البقاع الغربي وراشيا
+إستقبل رئيس الجمهورية العماد جوزاف عون، بعد ظهر اليوم في قصر بعبدا، السيدة ميسم سكاف، أرملة النائب الراحل الدكتور غسان سكاف، وشقيقها السيد وليد يونس.
+وتم خلال اللقاء، عرض الأوضاع العامة في البلاد عموما وفي منطقة البقاع الغربي وراشيا خصوصاً، وحاجات المواطنين لا سيما مع إقتراب بدء فصل الشتاء.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:20.121889+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من وفد المركز التربوي للبحوث والانماء المنهاج الوطني للتعليم العام ما قبل الجامعي: معركتنا لبناء الدولة تبدأ ايضاً من المدرسة والتوعية التربوية</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1593</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من وفد المركز التربوي للبحوث والانماء المنهاج الوطني للتعليم العام ما قبل الجامعي: معركتنا لبناء الدولة تبدأ ايضاً من المدرسة والتوعية التربوية
+رئيس الجمهورية: التربية الوطنية ليست مجرد تعليم عن الوطن
+بل التربية على العيش معاً واحترام الدولة وتحمّل المسؤولية وصون الوحدة الوطنية
+الرئيس عون لوفد نواب واتحاد بلديات كسروان –الفتوح:
+البلديات شريكة الدولة في الانماء لا بديلة عنها
+النائب شمعون: نريد ان ندعم فخامة الرئيس في المهام التي يقوم بها مع رئيس الحكومة
+وهناك فرصة ذهبية اليوم قد لا تتكرر علينا الاستفادة منها
+رئيس الجمهورية عرض الاوضاع العامة في البلاد وتطورات المنطقة
+مع النائب افرام والوزير السابق فرعون
+شدد رئيس الجمهورية العماد جوزاف عون على ان "معركتنا من أجل بناء الدولة لا تقتصر على الإصلاحات السياسية والإدارية والاقتصادية، بل تبدأ أيضاً من المدرسة ومن نوعية التربية التي نقدّمها لأبنائنا."
+واكد أن التربية الوطنية ليست مجرد تعليم عن الوطن، بل هي" تربية على العيش معاً، واحترام الدولة، وتحمل المسؤولية، وصون الوحدة الوطنية، ولا سيما في مرحلة يحتاج فيها لبنان إلى تعزيز مناعته الداخلية وتحصين أجياله الشابة من الانقسامات".
+موقف الرئيس عون جاء امام وفد المركز التربوي للبحوث والانماء برئاسة رئيسته الدكتورة هيام اسحق، وضم رؤساء الوحدات في المركز، وممثلين عن المؤسسات التربوية المشاركة في وضع المنهاج العام للتعليم ما قبل الجامعي.
+في بداية اللقاء، القت السيدة اسحق الكلمة التالية:
+"يشرفني، باسم المركز التربوي للبحوث والإنماء، وباسم وفد الخبراء والاختصاصيين المرافق، أن أتوجّه إلى فخامتكم بخالص الاحترام، وأن أعبّر عن اعتزازنا بهذا اللقاء الذي يشكّل محطة وطنية مهمة في مسيرة تطوير التربية والتعليم في لبنان.
+فخامة الرئيس، إنّ التربية ليست مجرّد قطاع من قطاعات الدولة، بل هي أساس بناء الإنسان، ورافعة التنمية، وركيزة أساسية في بناء دولة قوية بمؤسساتها، متماسكة بمجتمعها، وقادرة على حماية مستقبل أبنائها. فمن خلال التربية تتشكّل شخصية المواطن، وتتعمّق قيم الانتماء والمسؤولية، ويتعزّز احترام التنوع ضمن الوحدة، وتتأسّس القدرة على الحوار والتفكير والعمل المشترك. وانطلاقاً من هذه المسؤولية الوطنية، عمل المركز التربوي للبحوث والإنماء، بالتعاون مع وزارة التربية والتعليم العالي، وبمشاركة واسعة من الخبراء والاختصاصيين والتربويين، على إعداد المنهاج الوطني للتعليم العام ما قبل الجامعي، في مسار إصلاحي يواكب التحوّلات المعرفية والتكنولوجية والاجتماعية، ويستجيب لحاجات المتعلّمين ومتطلبات الحياة والاقتصاد وسوق العمل، مع الحفاظ على الثوابت الوطنية والقيم الإنسانية التي يقوم عليها التعليم في لبنان."
+اضافت:"يكتسب هذا الإنجاز أهمية خاصة لأنّه يأتي بعد نحو ثلاثين عامًا على إقرار المنهاج السابق عام 1997، وفي مرحلة باتت فيها الحاجة ملحّة إلى تعليم لا يقتصر على نقل المعرفة، بل يمكّن المتعلّم من توظيفها، وينمّي لديه التفكير النقدي والإبداع، ومهارات التواصل والتعاون، والقدرة على ممارسة المواطنة المسؤولة ومواكبة التحوّلات المتسارعة في العالم. وقد تُوّج هذا المسار الوطني بصدور المرسوم رقم 3445 تاريخ 15 تموز 2026، المتعلّق بالمنهاج الوطني للتعليم العام ما قبل الجامعي، بعد إقراره في مجلس الوزراء واستكمال الإجراءات الدستورية اللازمة لإصداره. ويشكّل هذا المرسوم محطة مفصلية في مسيرة التربية اللبنانية، وينقل العمل من إقرار الرؤية الوطنية إلى مسؤولية مواصلة تطوير المنظومة التربوية وتحقيق أهداف المنهاج.
+فخامة الرئيس، في لقائنا السابق مع فخامتكم، في 19 شباط 2025، تشرفنا بتقديم الإطار الوطني اللبناني لمنهاج التعليم العام ما قبل الجامعي، ووضعنا أمامكم أمانة استكمال هذا المشروع الوطني، مؤكدين التزامنا مواصلة العمل على تطوير المناهج التربوية بما يواكب تطلعات لبنان وحاجات أبنائه. وقد عبّرتم يومها عن أهمية العلم والتربية بوصفهما ثروة لبنان الحقيقية، وعن استعدادكم لبحث الأفكار والمقترحات التي تسهم في تطوير التعليم وتعزيز الإصلاح التربوي. وها نحن اليوم نعود إلى فخامتكم، وفاءً لما التزمنا به، لنضع بين أيديكم المنهاج الوطني للتعليم العام ما قبل الجامعي، ثمرة مسار علمي وتربوي شارك فيه أكثر من ستمئة خبير واختصاصي في مختلف مراحل إعداد المنهاج وتطويره. ونرى في هذه المحطة تجسيدًا لاستمرارية العمل المؤسسي، وانتقالًا من وضع الإطار الوطني إلى بلورة المنهاج في صورته التفصيلية، بما يعكس رؤية تربوية متجددة تضع المتعلّم في صلب العملية التعليمية، وتعزّز المعارف والكفايات والقيم اللازمة لبناء المواطن المسؤول."
+وتابعت:"إنّ تسليم هذه النسخة ليس نهاية المسار، بل محطة أساسية فيه، ومسؤولية تقتضي مواصلة العمل والتعاون بين المؤسسات المعنية والخبراء والأسرة التربوية، حتى تتحوّل أهداف المنهاج ورؤيته إلى واقع تعليمي يواكب التطور، ويرتقي بجودة التعليم، ويعزّز الإنصاف في فرص التعلّم لجميع أبناء لبنان. وإنّ وجود هذا الوفد من الخبراء والاختصاصيين اليوم أمام فخامتكم يعبّر عن قيمة الشراكة الوطنية التي قام عليها هذا العمل، وعن قدرة لبنان، رغم التحديات التي يواجهها، على جمع طاقاته العلمية والتربوية حول مشروع مشترك، تكون فيه مصلحة الأجيال المقبلة فوق المصالح الفردية والاعتبارات الضيّقة.
+وأودّ، فخامة الرئيس، أن أعبّر عن اعتزازي بالمسؤولية التي أُنيطت بي بقرار من مجلس الوزراء، وعن إدراكي لما تحمله من أمانة وطنية في هذه المرحلة المفصلية. وإنني أؤكد التزامي مواصلة العمل، من خلال المركز التربوي للبحوث والإنماء، على تطوير المناهج والبحث التربوي، ومواكبة الإصلاح وتقويم نتائجه، بالتعاون مع وزارة التربية والتعليم العالي وسائر المؤسسات المعنية، بما يضمن خدمة التعليم العام والمصلحة الوطنية.
+فخامة الرئيس، إنّ أهمية المنهاج الجديد لا تكمن في تحديث المواد الدراسية فحسب، بل في الرؤية التي يحملها لمستقبل الإنسان اللبناني والمجتمع الذي نطمح إلى بنائه. فمن أهم أهدافه إعداد جيل يعتزّ بهويته الوطنية، ويحترم تنوّع مجتمعه، ويؤمن بالمواطنة والمساواة في الحقوق والواجبات، ويقدّر الحوار والاختلاف، ويرفض أن تتحوّل الاختلافات إلى انقسامات وحواجز تفصل بين أبناء الوطن الواحد".
+وقالت: "نطمح إلى مدرسة تجمع أبناء لبنان على المعرفة والقيم الإنسانية المشتركة، وتتيح لهم فهم تاريخهم ومجتمعهم، وتنمية قدرتهم على التفكير النقدي والتحاور باحترام والعمل معًا، بعيدًا عن التعصّب والانغلاق والانقسام. فالتربية، وإن لم تكن قادرة وحدها على معالجة جميع التحديات التي تواجه المجتمع، تظلّ ركيزة أساسية في بناء الوعي، وتعزيز الثقة المتبادلة، وترسيخ ثقافة العيش المشترك، وإعداد مواطنين فاعلين يشاركون في بناء دولة القانون والمؤسسات. ومن هنا، فإنّ الاستثمار في المنهاج الجديد هو استثمار في الإنسان اللبناني، وفي قدرة الأجيال المقبلة على تحويل التنوع إلى مصدر غنى، والاختلاف إلى فرصة للحوار، والمعرفة إلى أداة للتقدّم، والمواطنة إلى ممارسة يومية ومسؤولية مشتركة.
+فخامة الرئيس، نتطلّع إلى أن يشكّل هذا المنهاج خطوة تأسيسية في مسار تربوي وطني مستدام، تتضافر فيه جهود المؤسسات الرسمية والتربوية والخبراء والمجتمع، لترجمة رؤيته وأهدافه إلى تعليم ذي جودة، يضمن الإنصاف في فرص التعلّم، ويتيح لكل متعلّم تنمية قدراته وإمكاناته في المدارس الرسمية والخاصة على امتداد لبنان. وفي الختام، أتوجّه إلى فخامتكم بخالص الشكر والتقدير على استقبالنا وإتاحة الفرصة لعرض هذا الإنجاز الوطني، مؤكدين أهمية إبقاء التربية في صلب الاهتمام الوطني، لما لها من دور أساسي في بناء الإنسان، وصون وحدة المجتمع، وتعزيز قدرة لبنان على النهوض. وإنّ المنهاج الذي نضعه اليوم بين أيديكم ليس مجرّد وثيقة تربوية، بل رؤية لمستقبل المتعلّم اللبناني، وأمل بمدرسة أكثر قدرة على بناء الإنسان، وخطوة نحو وطن يتّسع لجميع أبنائه، وتجمعهم المواطنة والعلم والمسؤولية المشتركة".
+وختمت:"بالتربية نبني الإنسان، وبالعلم ننهض بالوطن، وبالشراكة الوطنية نصنع مستقبل لبنان."
+الرئيس عون
+ورحب الرئيس عون بالوفد، محيياً اعضاءه على الجهود التي يقومون بها بالنسبة الى تطوير المناهج وتفعيلها، وقال: نريد جيلاً يؤمن بلبنان، ويتمسّك بوحدته، ويحترم دستوره وقوانينه، ويؤمن بأن المواطنة مسؤولية قبل أن تكون حقاً، وأن الاختلاف لا يلغي الشراكة الوطنية. إن المركز التربوي للبحوث والإنماء مدعوّ إلى مواكبة هذه المرحلة من خلال مناهج تعزّز الانتماء الوطني، وتحصّن الأجيال في مواجهة الانقسامات، وتربّي على الحوار والاعتدال واحترام الآخر. فلبنان الذي نطمح إلى بنائه يحتاج إلى مواطنين يعرفون حقوقهم وواجباتهم، ويثقون بدولتهم، ويؤمنون بأن مستقبلهم لا يُصان إلا بوحدتهم وتمسّكهم بوطنهم".
+واضاف: "الرسالة الأساسية التي يجب أن تكون محور عمل المركز هي أن التربية الوطنية ليست مجرد تعليم عن الوطن، بل هي تربية على العيش معاً، واحترام الدولة، وتحمل المسؤولية، وصون الوحدة الوطنية، ولا سيما في مرحلة يحتاج فيها لبنان إلى تعزيز مناعته الداخلية وتحصين أجياله الشابة من الانقسامات".
+وشدد رئيس الجمهورية على انه لا ينبغي ان يكون التعليم للمنحى السلبي كالتعصب الطائفي والمذهبي وغيرها، "لان هذا الامر من شأنه تسميم افكار الجيل الناشىء الذي نعتمد عليه ليقود لبنان في المستقبل، بل يجب الاهتمام به وتلقينه المبادىء والقيم الانسانية السامية والنبيلة"
+وتابع الرئيس عون: على المناهج الجديدة ان تركّز على مصلحة الجيل الجديد الذي يجب ان ينمو على اسس وطنية، وان يعي ان لا فرق بين اللبنانيين، ولو ان حق الاختلاف مقدس، فالشراكة يجب ان تكون راسخة، كما الهوية والعلم والانتماء الواحد للوطن.
+وفي نهاية اللقاء، قدمت الدكتورة اسحق الى الرئيس عون النسخة الاولى من منهاج التعليم العام ما قبل الجامعي الصادر بموجب المرسوم رقم 3445 تاريخ 15 تموز 2026.
+وفد نواب واتحاد بلديات كسروان-الفتوح
+واستقبل الرئيس عون وفد نواب واتحاد بلديات كسروان- الفتوح الذي ضم النواب السادة: سليم الصايغ، نعمة افرام، فريد الخازن، شوقي دكاش، ورئيس الاتحاد ايلي بعينو، ونائبه بيار دكاش. وجرى عرض لاوضاع المنطقة وحاجاتها، والحلول المقترحة لبعض الملفات التي يمكن اللجوء اليها لتسهيل امور الكسروانيين.
+وخلال الاجتماع، تحدث النواب ورئيس الاتحاد عن حاجات القضاء، مركّزين على ايمانهم بأن اللامركزية ليست انتقاصاً من سلطة الدولة، ولا خروجاً عن مسؤولياتها، بل هي تعزيز لحضورها وتفعيل لمؤسساتها وتوزيع متوازن للمسؤوليات، بما يجعل القرار اقرب الى المواطن، والخدمة العامة اكثر فعالية واستجابة لحاجاته. واشار الوفد الى ان القانون الرقم 38 الصادر بتاريخ 5 كانون الثاني 2026، والمعدّل للمادة 28 من قانون الادارة المتكاملة للنفايات الصلبة رقم 80، ليصبح اطاراً جديداً لمسؤولية الادارة المحلية في جمع النفايات ونقلها واستيفاء الرسوم المتوجبة، مع ابقاء مسؤولية المعالجة على عاتق الدولة.
+واعتبر اعضاء الوفد ان هذا القانون خطوة مهمة في الاتجاه الصحيح، وتكمن قيمته الفعلية في استكماله بالقرارات والاجراءات التنفيذية والمالية التي تتيح تطبيقه على ارض الواقع. ولفتوا الى ان كسروان-الفتوح لا تأتي اليوم لعرض مشكلة فحسب، بل لتقديم استعداد واضح للمشاركة في الحل. وان كشروان، رؤساء بلديات ونوابًا وفعاليات سياسية واقتصادية واجتماعية، تلتقي على رؤية واحدة تقوم على تعزيز اللامركزية الإدارية، ولا سيما في إدارة ملف النفايات، انطلاقًا من الإيمان بقدرة السلطات المحلية على تحمل مسؤولياتها متى توافرت لها الإمكانات والأطر القانونية اللازمة. وفي غوسطا مركز لمعالجة النفايات، حائز التراخيص اللازمة، ولا سيما البيئية منها، وهو في مرحلة استكمال التجهيزات والمعدات الضرورية لوضعه في الخدمة.
+ورفع الوفد مطالب محددة، رأى في تحقيقها مدخلاً أساسيًا لمعالجة هذا الملف:
+اولاً: إستكمال الإجراءات الإدارية والمالية اللازمة لتفعيل دور الهيئة المعنية بإدارة النفايات، بما ينعكس ايجاباً على تشغيل مراكز المعالجة، وفي مقدمها مركز غوسطا.
+ثانياً: تأمين المعدات والتجهيزات اللازمة لوضع هذا المركز في الخدمة، وفق المعايير البيئية والصحية المعتمدة.
+ثالثاً: تحويل المستحقات المالية العائدة للبلديات، بما يمكنها من القيام بواجباتها واستثمار مواردها في خدمة المواطنين.
+رابعاً: العمل على إقرار قانون يعفي البلديات من الديون المتراكمة عليها تجاه الحكومة المركزية في ملف النفايات، والمترتبة على حساباتها لدى الصندوق البلدي المستقل.
+خامساً: توسيع أوتوستراد نهر الكلب - طبرجا - مدخل كسروان، توسيع طريق زوق مصبح –جعيتا- فاريا، إستكمال الطريق الداخلي الذي يربط كسروان بالفتوح.
+وختم الوفد بالتأكيد على أن كسروان - الفتوح مستعدة لتحمل مسؤولياتها كاملة، وأن طموحها ليس أن تحل البلديات مكان الدولة، بل أن تعمل معها وتحت سقف مؤسساتها، من أجل إدارة أكثر كفاءة، وإنماء أكثر توازناً، وخدمة أفضل للمواطن. فالدولة القوية ليست تلك التي تحتكر كل المسؤوليات، بل تلك التي تعرف كيف توزعها، وتضمن حسن ممارستها".
+الرئيس عون
+ورد الرئيس عون مرحباً بأعضاء الوفد، وحياهم على المسار الذي يتبعونه لتعزيز دور البلديات واقتراح الحلول الكفيلة بتسهيل شؤون سكان المناطق التي تتبع لاتحاد بلديات كسروان- الفتوح، داعياً البلديات في كل لبنان الى القيام بالمثل، لان التعاون بينها وبين الدولة من شأنه ان يعزز التكامل المطلوب، وينعكس ايجاباً على المواطنين ويسهّل امورهم.
+وشدد الرئيس عون على ان ملف معالجة النفايات يحظى باهتمام كبير من قبل الدولة، مبدياً دعمه للحل المقترح من قبل الوفد لجهة تولي مهمة معالجة نفايات المنطقة من خلال معامل فيها، مطابقة للشروط والمواصفات البيئية المطلوبة. وقال ان قيام البلديات بدورها كاملاً لا يتنافى مع حضور الدولة، فالبلديات شريكة الدولة في الإنماء، لا بديلة عنها.
+تصريح رئيس اتحاد بلديات كسروان-الفتوح
+وبعد اللقاء، تحدث السيد بعينو فقال:
+"تشرفنا اليوم بلقاء فخامة الرئيس للبحث في موضوع معالجة النفايات في كسروان – الفتوح بحضور نواب المنطقة. الهدف من اللقاء كان اعتماد اللامركزية الادارية في ادارة ملف نفايات المنطقة، في ظل وجود الحل من خلال المعمل في غوسطا، وهذا الطلب يحظى باجماع بلديات المنطقة.
+كما تم الحديث عن توسيع اوتوستراد نهر الكلب- نهر ابراهيم، وتوسيع طريق زوق مصبح حتى فاريا. وطلبنا دعم فخامة الرئيس للوقوف الى جانبنا في هذه المواضيع الحياتية- الاقتصادية- الانمائية للمنطقة، بهدف تسهيل الامور، واتحاد بلديات كسروان-الفتوح يقوم بعمله ويقدم الحلول العملية، خصوصاً لجهة النفايات التي يمكن معالجتها في المعمل المقام في غوسطا بدل نقلها الى مطمر الجديدة.
+سئل: ماذا كان موقف الرئيس عون من هذه الطروحات؟
+احاب: كان الموقف ممتازاً، واكد دعمه لكل ما يساعد في تحقيق هذه المواضيع.
+النائب نعمة افرام
+نيابياً أيضا، استقبل الرئيس عون رئيس حركة "مشروع وطن الانسان" النائب نعمة افرام واجرى معه جولة افق تناولت الأوضاع الراهنة محلياً وإقليمياً في ضوء التطورات الراهنة. وتطرق البحث أيضاً الى ملف الكهرباء والعوائق التي تحول دون إيجاد حلول فاعلة له.
+وأشار النائب افرام الى انه أشاد بحكمة الرئيس عون في قيادة سفينة البلاد في هذه المرحلة الدقيقة من تاريخ لبنان، والمواقف التي يتخذها في حفظ السيادة وبسط سلطة الدولة على الأراضي اللبنانية كافة.
+النائب شمعون
+واستقبل الرئيس عون النائب كميل شمعون على رأس وفد من حزب "الوطنيين الاحرار" شكره على تمثيله في قداس وجناز الأربعين لراحة نفس النائب السابق الراحل دوري كميل شمعون في انطلياس.
+وبعد اللقاء، صرح النائب شمعون فقال:
+"رغبنا اليوم بالقيام بزيارة لرئيس الجمهورية كوفد من حزب "الوطنيين الاحرار" ومن عائلة شمعون، لشكره أولا على مشاركته في كل الواجبات منذ وفاة الوالد دوري شمعون وتمثيله من خلال النائب إبراهيم كنعان بالأمس في قداس انطلياس. كذلك، اردنا التحدث في عدد من المواضيع التي شدد الرئيس عون عليها، وهي أولا: الوحدة الوطنية التي يحتاجها لبنان في ظل الأزمة التي يعيشها، والمحاور التي تتحكم بسياساتنا وهي غير منتجة. فليس هناك سوى التضامن الذي يمكنه ان ينقذ البلد ويلغي التجاذبات والتشنج الحاصل بين أعضاء الاسرة اللبنانية الواحدة، بداية، بالطبع، بالعائلة والأحزاب المسيحية، لانه اذا ما اتفقوا مع بعضهم البعض أعتقد ان لبنان بكامله يصل الى اتفاق. ونريد ان ندعم جميعا فخامة الرئيس في المهام التي يقوم بها الى جانب رئيس الحكومة، لان هناك فرصة ذهبية اليوم قد لا تتكرر، وعلينا الاستفادة منها لنشهد دعما دوليا وعربيا واوروبيا واميركيا، ولهذا السبب يجب الا تضيع هذه الفرصة".
+وختم:" يجب ان يعود لبنان لينهض من جديد ويستعيد الشعب اللبناني قراره بكل ما للكلمة من معنى".
+سئل: كان هدف الرئيس شمعون وآل شمعون في المحطات المفصلية في لبنان على مدى خمسين عاما، توحيد الناس ان كان على المستوى المسيحي او على المستوى الوطني، الا ترى ان الوضع الذي نعيشه يلزمه هذا النمط من السياسة؟
+أجاب: هذا هو المطلوب، الا ان مشكلة وجود السلاح غير الشرعي تعرقل هذا الامر وتؤدي الى نوع من التشنج بين الطوائف اللبنانية بما لا يفيد اللبنانيين باي طريقة من الطرق. لا بل على العكس، لا يجب ان نخاف من بعضنا البعض. نخاف من بعضنا البعض عندما يفاوضنا احدهم وهو يشهر سلاحاً في وجهنا، من المؤكد انه لا يمكننا ان تتفاوض مع هذا الشخص. ولكن عندما نبدأ بالتفاوض من الند للند وننظر الى مصلحة الطوائف في البلد، ومصلحة كل طائفة على حدة، ففي النتيجة يمكن ان يكون التنوع الذي نتميز به سببا للانقسام، او اذا ما استغل في الشكل المناسب يمكن ان يشكل سببا للغنى في البلد في ظل تعدد الثقافات الموجودة. والأهم هو المحافظة على وطنيتنا وان ننظر الى لبنان على انه الهدف الأعلى لتأتي بعد ذلك الأحزاب والطوائف. لكن الأهم اننا جميعا لبنانيون وعلينا التفكير بمستقبل البلد ومستقبل أولادنا، وان ننظر الى الهجرة التي نشهدها اليوم على انها غير مسبوقة. كما علينا ان نخلق مناخا للادمغة، والشباب الذين تعلموا ليعودوا الى لبنان ليبنوا بلدا كما نحلم.
+سئل: الى أي مدى انتم قلقون من التطورات المتسارعة، وهل تعتبرون ان لبنان امام مرحلة جديدة من التصعيد؟
+أجاب: بالطبع هناك نوايا تصعيدية في المنطقة، ونعلم ان هناك حربا قائمة. وفي النتيجة لن يريحنا الا قيام سلام شامل، لاني اعتقد اننا كلبنانيين عانينا منذ العام 1975 وحتى اليوم من حروب متتالية كانت بمعظمها حروب الاخرين على ارضنا، والمحاور التي هي غير لبنانية بل مستوردة. لذلك نقول آن الأوان لنعي الأمور ونفكر جديا بالسلام، وبالحياد قبله. فلبنان اذا عاد بلدا حياديا كما كان في السابق همزة وصل بين الشرق والغرب، اعتقد انه يتعافى بسرعة كبيرة.
+سئل: هل نقل اليكم رئيس الجمهورية معطيات تطمئن الى إمكانية عدم جر لبنان الى حرب إقليمية اذا ما وقعت؟
+أجاب: الرئيس عون متفائل ويدرك جيدا الى اين يمكن ان نصل في المفاوضات. وفي النهاية هو رجل وطني يفكر بمصلحة البلد. والحرب التي وقعت بين لبنان وإسرائيل لم تقررها الدولة، ولم يكن القرار لبنانيا بل من خارجه. ولهذا السبب نتحمل هذه المتاعب وبالأخص الطائفة الشيعية الكريمة التي عانت اكثر من هذا الامر، وفي النتيجة اعتقد ان الحلول قريبة وسنبقى متفائلين.
+الوزير السابق ميشال فرعون
+الى ذلك، استقبل الرئيس عون الوزير والنائب السابق ميشال فرعون الذي اطلعه على نتائج المداولات التي يجريها مع مجموعة من المفكرين والمثقفين والسياسيين حول موضوع الحياد، لاسيما بعد انجاز الكتاب الثاني المتضمن حصيلة هذه المداولات استعداداً لإصداره. ووضع الوزير السابق فرعون رئيس الجمهورية في حصيلة اللقاءات التي عقدها مع فعاليات سياسية وروحية واجتماعية لبلورة فكرة الحياد، لافتاً الى ان هذه الاتصالات تمحورت حول ثلاثة مسارات متكاملة هي:
+"أولاً: المسار الذي يقوده رئيس الجمهورية ورئيس الحكومة والحكومة في الجنوب لجهة حصر السلاح بيد الدولة. وهذا مسار يجب ان نقف جميعاً الى جانبه، وان نطلب الدعم الداخلي والخارجي للجيش والمؤسسات الأمنية، لتمكينها من تطبيقه.
+ثانياً: المسار المستدام الذي يمر عبر تطبيق الميثاق والدستور واعتماد اللامركزية الإدارية الموسعة التي تمنح المناطق صلاحيات حقيقية في إدارة شؤونها المحلية والخدمية ضمن وحدة الدولة، والحياد الإيجابي ضمن جامعة الدول العربية، انطلاقاً من الأسس التي قام عليها لبنان. وهذا ما يتيح لنا الخروج من "جحيم لبنان الساحة" الى ما يمكن ان نسميه "فردوس لبنان الرسالة". وحين نقول الحياد ضمن جامعة الدول العربية، فهذا يعني انه في حال تعرض أي بلد عربي لاعتداء على استقلاله وسيادته، نبقى ملتزمين بالتنديد بهذا الاعتداء، ورفضه وحشد الموقف العربي في مواجهته.
+ثالثاً: مسار الإصلاح الذي يتطلب شجاعة اكبر وعملاً اكثر جدية في الاصلاح والمساءلة والمحاسبة. وهذا المسار لا يقل أهمية عن المسارين الاخرين، لأننا من دونه لا نستطيع إعادة الثقة بالدولة وبالبلد".</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:24.625372+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية العماد جوزاف عون استقبل الوزير السابق ميشال فرعون و عرض معه الاوضاع العامة في البلاد وتطورات المنطقة</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1592</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية العماد جوزاف عون استقبل الوزير السابق ميشال فرعون و عرض معه الاوضاع العامة في البلاد وتطورات المنطقة
+استقبل الرئيس عون الوزير والنائب السابق ميشال فرعون الذي اطلعه على نتائج المداولات التي يجريها مع مجموعة من المفكرين والمثقفين والسياسيين حول موضوع الحياد، لاسيما بعد انجاز الكتاب الثاني المتضمن حصيلة هذه المداولات استعداداً لإصداره. ووضع الوزير السابق فرعون رئيس الجمهورية في حصيلة اللقاءات التي عقدها مع فعاليات سياسية وروحية واجتماعية لبلورة فكرة الحياد، لافتاً الى ان هذه الاتصالات تمحورت حول ثلاثة مسارات متكاملة هي:
+"أولاً: المسار الذي يقوده رئيس الجمهورية ورئيس الحكومة والحكومة في الجنوب لجهة حصر السلاح بيد الدولة. وهذا مسار يجب ان نقف جميعاً الى جانبه، وان نطلب الدعم الداخلي والخارجي للجيش والمؤسسات الأمنية، لتمكينها من تطبيقه.
+ثانياً: المسار المستدام الذي يمر عبر تطبيق الميثاق والدستور واعتماد اللامركزية الإدارية الموسعة التي تمنح المناطق صلاحيات حقيقية في إدارة شؤونها المحلية والخدمية ضمن وحدة الدولة، والحياد الإيجابي ضمن جامعة الدول العربية، انطلاقاً من الأسس التي قام عليها لبنان. وهذا ما يتيح لنا الخروج من "جحيم لبنان الساحة" الى ما يمكن ان نسميه "فردوس لبنان الرسالة". وحين نقول الحياد ضمن جامعة الدول العربية، فهذا يعني انه في حال تعرض أي بلد عربي لاعتداء على استقلاله وسيادته، نبقى ملتزمين بالتنديد بهذا الاعتداء، ورفضه وحشد الموقف العربي في مواجهته.
+ثالثاً: مسار الإصلاح الذي يتطلب شجاعة اكبر وعملاً اكثر جدية في الاصلاح والمساءلة والمحاسبة. وهذا المسار لا يقل أهمية عن المسارين الاخرين، لأننا من دونه لا نستطيع إعادة الثقة بالدولة وبالبلد".</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:26.680714+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون النائب كميل شمعون .</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1591</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون النائب كميل شمعون .
+استقبل الرئيس عون النائب كميل شمعون على رأس وفد من حزب "الوطنيين الاحرار" شكره على تمثيله في قداس وجناز الأربعين لراحة نفس النائب السابق الراحل دوري كميل شمعون في انطلياس.
+وبعد اللقاء، صرح النائب شمعون فقال:
+"رغبنا اليوم بالقيام بزيارة لرئيس الجمهورية كوفد من حزب "الوطنيين الاحرار" ومن عائلة شمعون، لشكره أولا على مشاركته في كل الواجبات منذ وفاة الوالد دوري شمعون وتمثيله من خلال النائب إبراهيم كنعان بالأمس في قداس انطلياس. كذلك، اردنا التحدث في عدد من المواضيع التي شدد الرئيس عون عليها، وهي أولا: الوحدة الوطنية التي يحتاجها لبنان في ظل الأزمة التي يعيشها، والمحاور التي تتحكم بسياساتنا وهي غير منتجة. فليس هناك سوى التضامن الذي يمكنه ان ينقذ البلد ويلغي التجاذبات والتشنج الحاصل بين أعضاء الاسرة اللبنانية الواحدة، بداية، بالطبع، بالعائلة والأحزاب المسيحية، لانه اذا ما اتفقوا مع بعضهم البعض أعتقد ان لبنان بكامله يصل الى اتفاق. ونريد ان ندعم جميعا فخامة الرئيس في المهام التي يقوم بها الى جانب رئيس الحكومة، لان هناك فرصة ذهبية اليوم قد لا تتكرر، وعلينا الاستفادة منها لنشهد دعما دوليا وعربيا واوروبيا واميركيا، ولهذا السبب يجب الا تضيع هذه الفرصة".
+وختم:" يجب ان يعود لبنان لينهض من جديد ويستعيد الشعب اللبناني قراره بكل ما للكلمة من معنى".
+سئل: كان هدف الرئيس شمعون وآل شمعون في المحطات المفصلية في لبنان على مدى خمسين عاما، توحيد الناس ان كان على المستوى المسيحي او على المستوى الوطني، الا ترى ان الوضع الذي نعيشه يلزمه هذا النمط من السياسة؟
+أجاب: هذا هو المطلوب، الا ان مشكلة وجود السلاح غير الشرعي تعرقل هذا الامر وتؤدي الى نوع من التشنج بين الطوائف اللبنانية بما لا يفيد اللبنانيين باي طريقة من الطرق. لا بل على العكس، لا يجب ان نخاف من بعضنا البعض. نخاف من بعضنا البعض عندما يفاوضنا احدهم وهو يشهر سلاحاً في وجهنا، من المؤكد انه لا يمكننا ان تتفاوض مع هذا الشخص. ولكن عندما نبدأ بالتفاوض من الند للند وننظر الى مصلحة الطوائف في البلد، ومصلحة كل طائفة على حدة، ففي النتيجة يمكن ان يكون التنوع الذي نتميز به سببا للانقسام، او اذا ما استغل في الشكل المناسب يمكن ان يشكل سببا للغنى في البلد في ظل تعدد الثقافات الموجودة. والأهم هو المحافظة على وطنيتنا وان ننظر الى لبنان على انه الهدف الأعلى لتأتي بعد ذلك الأحزاب والطوائف. لكن الأهم اننا جميعا لبنانيون وعلينا التفكير بمستقبل البلد ومستقبل أولادنا، وان ننظر الى الهجرة التي نشهدها اليوم على انها غير مسبوقة. كما علينا ان نخلق مناخا للادمغة، والشباب الذين تعلموا ليعودوا الى لبنان ليبنوا بلدا كما نحلم.
+سئل: الى أي مدى انتم قلقون من التطورات المتسارعة، وهل تعتبرون ان لبنان امام مرحلة جديدة من التصعيد؟
+أجاب: بالطبع هناك نوايا تصعيدية في المنطقة، ونعلم ان هناك حربا قائمة. وفي النتيجة لن يريحنا الا قيام سلام شامل، لاني اعتقد اننا كلبنانيين عانينا منذ العام 1975 وحتى اليوم من حروب متتالية كانت بمعظمها حروب الاخرين على ارضنا، والمحاور التي هي غير لبنانية بل مستوردة. لذلك نقول آن الأوان لنعي الأمور ونفكر جديا بالسلام، وبالحياد قبله. فلبنان اذا عاد بلدا حياديا كما كان في السابق همزة وصل بين الشرق والغرب، اعتقد انه يتعافى بسرعة كبيرة.
+سئل: هل نقل اليكم رئيس الجمهورية معطيات تطمئن الى إمكانية عدم جر لبنان الى حرب إقليمية اذا ما وقعت؟
+أجاب: الرئيس عون متفائل ويدرك جيدا الى اين يمكن ان نصل في المفاوضات. وفي النهاية هو رجل وطني يفكر بمصلحة البلد. والحرب التي وقعت بين لبنان وإسرائيل لم تقررها الدولة، ولم يكن القرار لبنانيا بل من خارجه. ولهذا السبب نتحمل هذه المتاعب وبالأخص الطائفة الشيعية الكريمة التي عانت اكثر من هذا الامر، وفي النتيجة اعتقد ان الحلول قريبة وسنبقى متفائلين.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:29.229978+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون النائب نعمة افرام .</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1590</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون النائب نعمة افرام .
+استقبل الرئيس عون رئيس حركة "مشروع وطن الانسان" النائب نعمة افرام واجرى معه جولة افق تناولت الأوضاع الراهنة محلياً وإقليمياً في ضوء التطورات الراهنة. وتطرق البحث أيضاً الى ملف الكهرباء والعوائق التي تحول دون إيجاد حلول فاعلة له.
+وأشار النائب افرام الى انه أشاد بحكمة الرئيس عون في قيادة سفينة البلاد في هذه المرحلة الدقيقة من تاريخ لبنان، والمواقف التي يتخذها في حفظ السيادة وبسط سلطة الدولة على الأراضي اللبنانية كافة.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:31.479433+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون وفد نواب واتحاد بلديات كسروان- الفتوح .</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1589</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون وفد نواب واتحاد بلديات كسروان- الفتوح .
+استقبل الرئيس عون وفد نواب واتحاد بلديات كسروان- الفتوح الذي ضم النواب السادة: سليم الصايغ، نعمة افرام، فريد الخازن، شوقي دكاش، ورئيس الاتحاد ايلي بعينو، ونائبه بيار دكاش. وجرى عرض لاوضاع المنطقة وحاجاتها، والحلول المقترحة لبعض الملفات التي يمكن اللجوء اليها لتسهيل امور الكسروانيين.
+وخلال الاجتماع، تحدث النواب ورئيس الاتحاد عن حاجات القضاء، مركّزين على ايمانهم بأن اللامركزية ليست انتقاصاً من سلطة الدولة، ولا خروجاً عن مسؤولياتها، بل هي تعزيز لحضورها وتفعيل لمؤسساتها وتوزيع متوازن للمسؤوليات، بما يجعل القرار اقرب الى المواطن، والخدمة العامة اكثر فعالية واستجابة لحاجاته. واشار الوفد الى ان القانون الرقم 38 الصادر بتاريخ 5 كانون الثاني 2026، والمعدّل للمادة 28 من قانون الادارة المتكاملة للنفايات الصلبة رقم 80، ليصبح اطاراً جديداً لمسؤولية الادارة المحلية في جمع النفايات ونقلها واستيفاء الرسوم المتوجبة، مع ابقاء مسؤولية المعالجة على عاتق الدولة.
+واعتبر اعضاء الوفد ان هذا القانون خطوة مهمة في الاتجاه الصحيح، وتكمن قيمته الفعلية في استكماله بالقرارات والاجراءات التنفيذية والمالية التي تتيح تطبيقه على ارض الواقع. ولفتوا الى ان كسروان-الفتوح لا تأتي اليوم لعرض مشكلة فحسب، بل لتقديم استعداد واضح للمشاركة في الحل. وان كشروان، رؤساء بلديات ونوابًا وفعاليات سياسية واقتصادية واجتماعية، تلتقي على رؤية واحدة تقوم على تعزيز اللامركزية الإدارية، ولا سيما في إدارة ملف النفايات، انطلاقًا من الإيمان بقدرة السلطات المحلية على تحمل مسؤولياتها متى توافرت لها الإمكانات والأطر القانونية اللازمة. وفي غوسطا مركز لمعالجة النفايات، حائز التراخيص اللازمة، ولا سيما البيئية منها، وهو في مرحلة استكمال التجهيزات والمعدات الضرورية لوضعه في الخدمة.
+ورفع الوفد مطالب محددة، رأى في تحقيقها مدخلاً أساسيًا لمعالجة هذا الملف:
+اولاً: إستكمال الإجراءات الإدارية والمالية اللازمة لتفعيل دور الهيئة المعنية بإدارة النفايات، بما ينعكس ايجاباً على تشغيل مراكز المعالجة، وفي مقدمها مركز غوسطا.
+ثانياً: تأمين المعدات والتجهيزات اللازمة لوضع هذا المركز في الخدمة، وفق المعايير البيئية والصحية المعتمدة.
+ثالثاً: تحويل المستحقات المالية العائدة للبلديات، بما يمكنها من القيام بواجباتها واستثمار مواردها في خدمة المواطنين.
+رابعاً: العمل على إقرار قانون يعفي البلديات من الديون المتراكمة عليها تجاه الحكومة المركزية في ملف النفايات، والمترتبة على حساباتها لدى الصندوق البلدي المستقل.
+خامساً: توسيع أوتوستراد نهر الكلب - طبرجا - مدخل كسروان، توسيع طريق زوق مصبح –جعيتا- فاريا، إستكمال الطريق الداخلي الذي يربط كسروان بالفتوح.
+وختم الوفد بالتأكيد على أن كسروان - الفتوح مستعدة لتحمل مسؤولياتها كاملة، وأن طموحها ليس أن تحل البلديات مكان الدولة، بل أن تعمل معها وتحت سقف مؤسساتها، من أجل إدارة أكثر كفاءة، وإنماء أكثر توازناً، وخدمة أفضل للمواطن. فالدولة القوية ليست تلك التي تحتكر كل المسؤوليات، بل تلك التي تعرف كيف توزعها، وتضمن حسن ممارستها".
+الرئيس عون
+ورد الرئيس عون مرحباً بأعضاء الوفد، وحياهم على المسار الذي يتبعونه لتعزيز دور البلديات واقتراح الحلول الكفيلة بتسهيل شؤون سكان المناطق التي تتبع لاتحاد بلديات كسروان- الفتوح، داعياً البلديات في كل لبنان الى القيام بالمثل، لان التعاون بينها وبين الدولة من شأنه ان يعزز التكامل المطلوب، وينعكس ايجاباً على المواطنين ويسهّل امورهم.
+وشدد الرئيس عون على ان ملف معالجة النفايات يحظى باهتمام كبير من قبل الدولة، مبدياً دعمه للحل المقترح من قبل الوفد لجهة تولي مهمة معالجة نفايات المنطقة من خلال معامل فيها، مطابقة للشروط والمواصفات البيئية المطلوبة. وقال ان قيام البلديات بدورها كاملاً لا يتنافى مع حضور الدولة، فالبلديات شريكة الدولة في الإنماء، لا بديلة عنها.
+تصريح رئيس اتحاد بلديات كسروان-الفتوح
+وبعد اللقاء، تحدث السيد بعينو فقال:
+"تشرفنا اليوم بلقاء فخامة الرئيس للبحث في موضوع معالجة النفايات في كسروان – الفتوح بحضور نواب المنطقة. الهدف من اللقاء كان اعتماد اللامركزية الادارية في ادارة ملف نفايات المنطقة، في ظل وجود الحل من خلال المعمل في غوسطا، وهذا الطلب يحظى باجماع بلديات المنطقة.
+كما تم الحديث عن توسيع اوتوستراد نهر الكلب- نهر ابراهيم، وتوسيع طريق زوق مصبح حتى فاريا. وطلبنا دعم فخامة الرئيس للوقوف الى جانبنا في هذه المواضيع الحياتية- الاقتصادية- الانمائية للمنطقة، بهدف تسهيل الامور، واتحاد بلديات كسروان-الفتوح يقوم بعمله ويقدم الحلول العملية، خصوصاً لجهة النفايات التي يمكن معالجتها في المعمل المقام في غوسطا بدل نقلها الى مطمر الجديدة.
+سئل: ماذا كان موقف الرئيس عون من هذه الطروحات؟
+احاب: كان الموقف ممتازاً، واكد دعمه لكل ما يساعد في تحقيق هذه المواضيع.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:33.673204+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من وفد المركز التربوي للبحوث والانماء المنهاج الوطني للتعليم العام ما قبل الجامعي: معركتنا لبناء الدولة تبدأ ايضاً من المدرسة والتوعية التربوية</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1588</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من وفد المركز التربوي للبحوث والانماء المنهاج الوطني للتعليم العام ما قبل الجامعي: معركتنا لبناء الدولة تبدأ ايضاً من المدرسة والتوعية التربوية
+شدد رئيس الجمهورية العماد جوزاف عون على ان "معركتنا من أجل بناء الدولة لا تقتصر على الإصلاحات السياسية والإدارية والاقتصادية، بل تبدأ أيضاً من المدرسة ومن نوعية التربية التي نقدّمها لأبنائنا."
+واكد أن التربية الوطنية ليست مجرد تعليم عن الوطن، بل هي" تربية على العيش معاً، واحترام الدولة، وتحمل المسؤولية، وصون الوحدة الوطنية، ولا سيما في مرحلة يحتاج فيها لبنان إلى تعزيز مناعته الداخلية وتحصين أجياله الشابة من الانقسامات".
+موقف الرئيس عون جاء امام وفد المركز التربوي للبحوث والانماء برئاسة رئيسته الدكتورة هيام اسحق، وضم رؤساء الوحدات في المركز، وممثلين عن المؤسسات التربوية المشاركة في وضع المنهاج العام للتعليم ما قبل الجامعي.
+في بداية اللقاء، القت السيدة اسحق الكلمة التالية:
+"يشرفني، باسم المركز التربوي للبحوث والإنماء، وباسم وفد الخبراء والاختصاصيين المرافق، أن أتوجّه إلى فخامتكم بخالص الاحترام، وأن أعبّر عن اعتزازنا بهذا اللقاء الذي يشكّل محطة وطنية مهمة في مسيرة تطوير التربية والتعليم في لبنان.
+فخامة الرئيس، إنّ التربية ليست مجرّد قطاع من قطاعات الدولة، بل هي أساس بناء الإنسان، ورافعة التنمية، وركيزة أساسية في بناء دولة قوية بمؤسساتها، متماسكة بمجتمعها، وقادرة على حماية مستقبل أبنائها. فمن خلال التربية تتشكّل شخصية المواطن، وتتعمّق قيم الانتماء والمسؤولية، ويتعزّز احترام التنوع ضمن الوحدة، وتتأسّس القدرة على الحوار والتفكير والعمل المشترك. وانطلاقاً من هذه المسؤولية الوطنية، عمل المركز التربوي للبحوث والإنماء، بالتعاون مع وزارة التربية والتعليم العالي، وبمشاركة واسعة من الخبراء والاختصاصيين والتربويين، على إعداد المنهاج الوطني للتعليم العام ما قبل الجامعي، في مسار إصلاحي يواكب التحوّلات المعرفية والتكنولوجية والاجتماعية، ويستجيب لحاجات المتعلّمين ومتطلبات الحياة والاقتصاد وسوق العمل، مع الحفاظ على الثوابت الوطنية والقيم الإنسانية التي يقوم عليها التعليم في لبنان."
+اضافت:"يكتسب هذا الإنجاز أهمية خاصة لأنّه يأتي بعد نحو ثلاثين عامًا على إقرار المنهاج السابق عام 1997، وفي مرحلة باتت فيها الحاجة ملحّة إلى تعليم لا يقتصر على نقل المعرفة، بل يمكّن المتعلّم من توظيفها، وينمّي لديه التفكير النقدي والإبداع، ومهارات التواصل والتعاون، والقدرة على ممارسة المواطنة المسؤولة ومواكبة التحوّلات المتسارعة في العالم. وقد تُوّج هذا المسار الوطني بصدور المرسوم رقم 3445 تاريخ 15 تموز 2026، المتعلّق بالمنهاج الوطني للتعليم العام ما قبل الجامعي، بعد إقراره في مجلس الوزراء واستكمال الإجراءات الدستورية اللازمة لإصداره. ويشكّل هذا المرسوم محطة مفصلية في مسيرة التربية اللبنانية، وينقل العمل من إقرار الرؤية الوطنية إلى مسؤولية مواصلة تطوير المنظومة التربوية وتحقيق أهداف المنهاج.
+فخامة الرئيس، في لقائنا السابق مع فخامتكم، في 19 شباط 2025، تشرفنا بتقديم الإطار الوطني اللبناني لمنهاج التعليم العام ما قبل الجامعي، ووضعنا أمامكم أمانة استكمال هذا المشروع الوطني، مؤكدين التزامنا مواصلة العمل على تطوير المناهج التربوية بما يواكب تطلعات لبنان وحاجات أبنائه. وقد عبّرتم يومها عن أهمية العلم والتربية بوصفهما ثروة لبنان الحقيقية، وعن استعدادكم لبحث الأفكار والمقترحات التي تسهم في تطوير التعليم وتعزيز الإصلاح التربوي. وها نحن اليوم نعود إلى فخامتكم، وفاءً لما التزمنا به، لنضع بين أيديكم المنهاج الوطني للتعليم العام ما قبل الجامعي، ثمرة مسار علمي وتربوي شارك فيه أكثر من ستمئة خبير واختصاصي في مختلف مراحل إعداد المنهاج وتطويره. ونرى في هذه المحطة تجسيدًا لاستمرارية العمل المؤسسي، وانتقالًا من وضع الإطار الوطني إلى بلورة المنهاج في صورته التفصيلية، بما يعكس رؤية تربوية متجددة تضع المتعلّم في صلب العملية التعليمية، وتعزّز المعارف والكفايات والقيم اللازمة لبناء المواطن المسؤول."
+وتابعت:"إنّ تسليم هذه النسخة ليس نهاية المسار، بل محطة أساسية فيه، ومسؤولية تقتضي مواصلة العمل والتعاون بين المؤسسات المعنية والخبراء والأسرة التربوية، حتى تتحوّل أهداف المنهاج ورؤيته إلى واقع تعليمي يواكب التطور، ويرتقي بجودة التعليم، ويعزّز الإنصاف في فرص التعلّم لجميع أبناء لبنان. وإنّ وجود هذا الوفد من الخبراء والاختصاصيين اليوم أمام فخامتكم يعبّر عن قيمة الشراكة الوطنية التي قام عليها هذا العمل، وعن قدرة لبنان، رغم التحديات التي يواجهها، على جمع طاقاته العلمية والتربوية حول مشروع مشترك، تكون فيه مصلحة الأجيال المقبلة فوق المصالح الفردية والاعتبارات الضيّقة.
+وأودّ، فخامة الرئيس، أن أعبّر عن اعتزازي بالمسؤولية التي أُنيطت بي بقرار من مجلس الوزراء، وعن إدراكي لما تحمله من أمانة وطنية في هذه المرحلة المفصلية. وإنني أؤكد التزامي مواصلة العمل، من خلال المركز التربوي للبحوث والإنماء، على تطوير المناهج والبحث التربوي، ومواكبة الإصلاح وتقويم نتائجه، بالتعاون مع وزارة التربية والتعليم العالي وسائر المؤسسات المعنية، بما يضمن خدمة التعليم العام والمصلحة الوطنية.
+فخامة الرئيس، إنّ أهمية المنهاج الجديد لا تكمن في تحديث المواد الدراسية فحسب، بل في الرؤية التي يحملها لمستقبل الإنسان اللبناني والمجتمع الذي نطمح إلى بنائه. فمن أهم أهدافه إعداد جيل يعتزّ بهويته الوطنية، ويحترم تنوّع مجتمعه، ويؤمن بالمواطنة والمساواة في الحقوق والواجبات، ويقدّر الحوار والاختلاف، ويرفض أن تتحوّل الاختلافات إلى انقسامات وحواجز تفصل بين أبناء الوطن الواحد".
+وقالت: "نطمح إلى مدرسة تجمع أبناء لبنان على المعرفة والقيم الإنسانية المشتركة، وتتيح لهم فهم تاريخهم ومجتمعهم، وتنمية قدرتهم على التفكير النقدي والتحاور باحترام والعمل معًا، بعيدًا عن التعصّب والانغلاق والانقسام. فالتربية، وإن لم تكن قادرة وحدها على معالجة جميع التحديات التي تواجه المجتمع، تظلّ ركيزة أساسية في بناء الوعي، وتعزيز الثقة المتبادلة، وترسيخ ثقافة العيش المشترك، وإعداد مواطنين فاعلين يشاركون في بناء دولة القانون والمؤسسات. ومن هنا، فإنّ الاستثمار في المنهاج الجديد هو استثمار في الإنسان اللبناني، وفي قدرة الأجيال المقبلة على تحويل التنوع إلى مصدر غنى، والاختلاف إلى فرصة للحوار، والمعرفة إلى أداة للتقدّم، والمواطنة إلى ممارسة يومية ومسؤولية مشتركة.
+فخامة الرئيس، نتطلّع إلى أن يشكّل هذا المنهاج خطوة تأسيسية في مسار تربوي وطني مستدام، تتضافر فيه جهود المؤسسات الرسمية والتربوية والخبراء والمجتمع، لترجمة رؤيته وأهدافه إلى تعليم ذي جودة، يضمن الإنصاف في فرص التعلّم، ويتيح لكل متعلّم تنمية قدراته وإمكاناته في المدارس الرسمية والخاصة على امتداد لبنان. وفي الختام، أتوجّه إلى فخامتكم بخالص الشكر والتقدير على استقبالنا وإتاحة الفرصة لعرض هذا الإنجاز الوطني، مؤكدين أهمية إبقاء التربية في صلب الاهتمام الوطني، لما لها من دور أساسي في بناء الإنسان، وصون وحدة المجتمع، وتعزيز قدرة لبنان على النهوض. وإنّ المنهاج الذي نضعه اليوم بين أيديكم ليس مجرّد وثيقة تربوية، بل رؤية لمستقبل المتعلّم اللبناني، وأمل بمدرسة أكثر قدرة على بناء الإنسان، وخطوة نحو وطن يتّسع لجميع أبنائه، وتجمعهم المواطنة والعلم والمسؤولية المشتركة".
+وختمت:"بالتربية نبني الإنسان، وبالعلم ننهض بالوطن، وبالشراكة الوطنية نصنع مستقبل لبنان."
+الرئيس عون
+ورحب الرئيس عون بالوفد، محيياً اعضاءه على الجهود التي يقومون بها بالنسبة الى تطوير المناهج وتفعيلها، وقال: نريد جيلاً يؤمن بلبنان، ويتمسّك بوحدته، ويحترم دستوره وقوانينه، ويؤمن بأن المواطنة مسؤولية قبل أن تكون حقاً، وأن الاختلاف لا يلغي الشراكة الوطنية. إن المركز التربوي للبحوث والإنماء مدعوّ إلى مواكبة هذه المرحلة من خلال مناهج تعزّز الانتماء الوطني، وتحصّن الأجيال في مواجهة الانقسامات، وتربّي على الحوار والاعتدال واحترام الآخر. فلبنان الذي نطمح إلى بنائه يحتاج إلى مواطنين يعرفون حقوقهم وواجباتهم، ويثقون بدولتهم، ويؤمنون بأن مستقبلهم لا يُصان إلا بوحدتهم وتمسّكهم بوطنهم".
+واضاف: "الرسالة الأساسية التي يجب أن تكون محور عمل المركز هي أن التربية الوطنية ليست مجرد تعليم عن الوطن، بل هي تربية على العيش معاً، واحترام الدولة، وتحمل المسؤولية، وصون الوحدة الوطنية، ولا سيما في مرحلة يحتاج فيها لبنان إلى تعزيز مناعته الداخلية وتحصين أجياله الشابة من الانقسامات".
+وشدد رئيس الجمهورية على انه لا ينبغي ان يكون التعليم للمنحى السلبي كالتعصب الطائفي والمذهبي وغيرها، "لان هذا الامر من شأنه تسميم افكار الجيل الناشىء الذي نعتمد عليه ليقود لبنان في المستقبل، بل يجب الاهتمام به وتلقينه المبادىء والقيم الانسانية السامية والنبيلة"
+وتابع الرئيس عون: على المناهج الجديدة ان تركّز على مصلحة الجيل الجديد الذي يجب ان ينمو على اسس وطنية، وان يعي ان لا فرق بين اللبنانيين، ولو ان حق الاختلاف مقدس، فالشراكة يجب ان تكون راسخة، كما الهوية والعلم والانتماء الواحد للوطن.
+وفي نهاية اللقاء، قدمت الدكتورة اسحق الى الرئيس عون النسخة الاولى من منهاج التعليم العام ما قبل الجامعي الصادر بموجب المرسوم رقم 3445 تاريخ 15 تموز 2026.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:35.867904+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>زيارة للرئيس عون الى طرابلس هي الأولى لرئيس جمهورية منذ اكثر من 15 عاما شملت السرايا والدوائر الأمنية وقصر العدل والمرفأ والمنطقة الاقتصادية والمعرض</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1587</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>زيارة للرئيس عون الى طرابلس هي الأولى لرئيس جمهورية منذ اكثر من 15 عاما شملت السرايا والدوائر الأمنية وقصر العدل والمرفأ والمنطقة الاقتصادية والمعرض
+زيارتي تأكيد على ان الدولة موجودة الى جانب طرابلس وأهلها
+وكل الالتزام بالعمل من اجل مستقبل افضل لها ولكل لبنان
+----
+الانماء ليس منة بل حق للمواطنين والدولة التي نريدها
+هي التي تصل الى جميع أبنائها وتضمن لهم حقوقهم وتشكل ضمانتهم
+---
+لبنان لا ينهض بفريق او منطقة او طائفة وحدها
+بل عندما يلتقي أبناؤه على مشروع الدولة ويتقدم الانتماء الوطني على كل انتماء آخر
+---
+لنعمل معا من اجل دولة قوية وعادلة واقتصاد منتج
+ومجتمع متضامن ووطن يطمئن أبناؤه الى مستقبلهم فيه
+---
+الرئيس عون من مديرية امن الدولة: لا تتهاونوا ولا تخضعوا للضغوط
+وادوا واجبكم بضمير وكونوا على قدر المسؤولية
+---
+رئيس الجمهورية من مركز الامن العام: نفتخر بالتطور الذي تحققونه
+وخدمة المواطن مقدسة
+---
+الرئيس عون لقوى الامن الداخلي: نعتز بكم
+واللبنانيون امانة في اعناقنا
+---
+رئيس الجمهورية من قصر العدل: الامن والقضاء متلازمان
+ولقضاء مستقل ومحاربة الفساد أولوية
+----
+الرئيس عون اطلع على عمل مرفأ طرابلس ومحطة الحاويات والمنطقة الاقتصادية: انضمام لبنان الى IMEC بمرفأين يتطلب خطوات متتابعة لترجمته على ارض الواقع
+----
+رئيس الجمهورية لاعضاء مجلس إدارة معرض رشيد كرامي الدولي:
+الأهم تأمين فرص عمل لابناء المنطقة
+----
+اكد رئيس الجمهورية العماد جوزاف عون على ان زيارته الى طرابلس اليوم هي للتأكيد على وجود الدولة الى جانبها والى جانب أهلها، معربا عن التزامه العمل من اجل مستقبل افضل لها ولكل لبنان.
+وشدد على ان الانماء ليس منة من الدولة بل حق للمواطنين، وعلى ان الدولة "التي نريدها هي التي تصل الى جميع أبنائها وتضمن لهم حقوقهم وتشكل لهم ضمانتهم". وقال "لا انماء من دون امن الذي هو حاجة الجميع"، وهنا دور الأجهزة الأمنية والجيش، مشددا على "ان زمن التهميش والاقصاء ولى".
+وإذ اكد شرط تلازم الامن والقضاء لقيام الدولة القوية، فانه شدد على أهمية استقلالية القضاء، داعيا الى ابقائه فوق التجاذبات فلا يدين القاضي بريئا او يبرىء مجرما.
+وأعاد التأكيد على ان لبنان لا ينهض بفريق او منطقة او طائفة وحدها بل عندما يلتقي أبناؤه على مشروع الدولة "لان لا بديل عنها" وعندما يتقدم الانتماء الوطني على كل انتماء آخر، معتبرا "ان إضعاف الدولة لا يمنح القوة لأي مكوّن من مكوناتها".
+مواقف الرئيس عون جاءت في خلال زيارته الى طرابلس حيث اطلع على عمل عدد من اداراتها ومرافقها العامة، في زيارته الى كل من السرايا وقصر العدل ومرفأ طرابلس حيث جال على محطة الحاويات والمنطقة الاقتصادية، بالإضافة الى معرض رشيد كرامي الدولي حيث التقى نواب المدينة وفاعلياتها والرؤساء الروحيين فيها. وقد ازدانت شوارع المدينة بلافتات وشعارات مرحبة برئيس الجمهورية ومؤيدة مواقفه الوطنية.
+الوصول
+وكان الرئيس عون وصل الى سرايا طرابلس عند الثامنة والربع صباحا، حيث كان في استقباله وزيرا الداخلية والبلديات احمد الحجار والعدل عادل نصار، ومدير عام الامن العام اللواء حسن شقير، ومدير عام قوى الامن الداخلي اللواء رائد عبد الله، ومدير عام امن الدولة اللواء ادغار لاوندوس ومحافظ الشمال بالوكالة ايمان الرافعي، ورؤساء بلديات طرابلس، المينا، البداوي، القلمون وقائمقامون وقائد الدرك العميد جان عواد ورؤساء الدوائر.
+ومن باحة السرايا، توجه الرئيس عون والحضور الى مكتب المحافظ حيث عقد اجتماعا موسعا حضره وزيرا العدل والداخلية، المدراء العامون لأجهزة الامن العام، وقوى الامن الداخلي، وامن الدولة، محافظ الشمال بالوكالة، رئيس اتحاد الفيحاء السيد وائل زمرلي، رئيس بلدية طرابلس وعدد من رؤساء البلديات، والنائب العام الاستئنافي في الشمال القاضي هاني الحجار، وقائد منطقة الشمال العسكرية العميد الركن باسم الاحمدية، ورئيس فرع مخابرات الشمال العميد الركن هارون سيور، وقائد درك منطقة الشمال الإقليمية العميد مصطفى بدران، والمدير الإقليمي لامن الدولة في الشمال العقيد بسام الحكم وعدد من كبار الضباط والموظفين.
+في مستهل اللقاء، القت السيدة الرافعي الكلمة الاتية:
+"فخامة الرئيس
+أهلا بكم في طرابلس الفيحاء
+ان ترحيب طرابلس بالزيارة الميمونة لها دلالات خاصة إذ تبعث رسالة أمل وثقة بالدولة ومؤسساتها وتعزز التطلع إلى إدارة عامة فاعلة قائمة على خدمة المواطن وترسيخ سيادة القانون وتحقيق الإنماء المتوازن والعدالة الاجتماعية.
+هي ليست الزيارة الأولى إذ كانت طرابلس والجوار، خزان الجيش اللبناني، في صلب اهتماماتكم دائما ملمين بوضعها أثناء ولايتكم كقائد للجيش اللبناني وحين توليكم سدة الرئاسة استبشر المواطنون خيرا بالقامة الكبيرة القادرة على تخطي الصعاب وحماية البلد من أزمات كبيرة وعاصفة".
+اضافت:"ان مدينة طرابلس تواجه جملة من التحديات المتداخلة الاجتماعية والاقتصادية والأمنية والبيئية التي تتطلب معالجة متكاملة قوامها خطة إنقاذ وتنمية شاملة تجمع بين الأمن والاستقرار وتحسين الخدمات وإطلاق الاستثمارات وفرص العمل.
+ونثمن الجهود المبذولة في العهد الواعد برئاسة فخامتكم والحكومة العتيدة والوزراء المختصين على متابعتهم الحثيثة لشؤون مدينة طرابلس والجوار وخاصة من الناحية الأمنية التي يتابعها معالي وزير الداخلية والبلديات بشكل شبه يومي وكذلك تذليل العقبات التي تعترض البلديات في اداء مهامها واهتمام الوزراء المعنيين في تفعيل المرافق الاقتصادية في المدينة وتوظيف الإمكانات لتحويل الفرص الاقتصادية إلى مشاريع منتجة والاستثمارات إلى فرص عمل والتنمية إلى واقع ملموس يشعر به المواطن.
+والتكامل الحقيقي بين المرافق الاقتصادية والمؤسسات الاستثمارية والقطاع العام هو الركيزة الأساسية لتنمية اقتصادية محلية ووطنية تعزز الاستقرار الاجتماعي والأمني وترسخ الثقة بالدولة ومؤسساتها."
+الرئيس عون
+ورد الرئيس عون بالقول:" على الدولة ان تقف الى جانبكم طوال الوقت، وليس فقط في اوقات محددة، وعندها تتم استعادة الثقة بها، وعليكم تسهيل امور المواطنين وخدمتهم بأفضل طريقة ممكنة، والحفاظ على كرامتهم وحصولهم على حقوقهم، بغض النظر عن موقعهم الاجتماعي، فالجميع سواسية امام الحقوق والواجبات".
+واضاف: "لا انماء من دون امن الذي يكفل جذب الاستقرار الذي يؤمّن بدوره النمو الاقتصادي، وهنا يبرز دور الجيش والاجهزة الامنية التي تقوم بواجباتها ونحن نتابع عملها والاجراءات التي تتخذها في هذه المنطقة، ومع وزارة العدل ايضاً. فهذه المنطقة العزيزة على قلبنا عانت كثيراً من الاهمال، وآن الاوان لوقفه، وقد ولّى زمن التهميش والاقصاء. هناك مشاريع كثيرة يمكن ان يستفيد منها ابناء المنطقة، علينا تنميتها وتطويرها وهي تتكامل مع بعضها (المرفأ، المنطقة الاقتصادية، معرض رشيد كرامي الدولي، مطار القليعات، السكة الحديدية...)".
+وتابع:"ان الظروف الصعبة التي تعاني منها المنطقة تشمل كل البلد، ولكن هذا لا يلغي مسؤولية الدولة تجاه الشعب، فالصعوبات تزول امام الارادة الصلبة، ووضع مصلحة الوطن والمواطن فوق كل اعتبار وفوق المصالح الطائفية والفئوية المذهبية والسياسية، فلتبق السياسة للمسؤولين السياسيين، وعليكم القيام بواجبكم تجاه المواطن وتأمين الحد الادنى له للعيش بكرامة وامان، فلا عذر لاحد في التقصير او التخلّف عن عمله وتقديم الخدمات بشفافية ومسؤولية."
+رئيس البلدية
+من جهته، رحب رئيس بلدية طرابلس بالرئيس عون، واكد ان المدينة سعيدة لاستقباله، وان مطلبها الاساسي هو توفير الامن. وقال انه لاول مرة تشعر طرابلس بوجود اهتمام مباشر بها من خلال مواقف الرئيس عون ومتابعته وحرصه على مصلحة المدنية.
+وبعد انتهاء اللقاء، قدم الدكتور كريمة لوحتين الى الرئيس عون: الاولى عبارة عن مخطوطة لكلماته من خطاب القسم، والثانية لوحة تمثل مدينة طرابلس وساعتها الشهيرة.
+امن الدولة
+ثم توجه رئيس الجمهورية والوزراء والحضور الى المديرية العامة لامن الدولة حيث كان في استقباله العقيد الحكم وكبار الضباط. واستمع رئيس الجمهورية خلال الزيارة الى شرح عن واقع مكافحة الفساد والمهمات التي يقوم بها الفرع والمشاكل والصعوبات التي تعترضه، فاكد على اهمية الامن "الذي لا يميّز بين غني وفقير او طائفة او مذهب، فهو حاجة للجميع، ومن واجبنا تجاه المواطنين تأمينه للجميع". واشاد بالمهام التي تقوم بها المديرية العامة لامن الدولة تحت اشراف اللواء لاوندوس، على الرغم من تواضع الامكانات، "وهذا دليل على ان الارادة تتغلب على العوائق، والتكامل مع القضاء اساسي، خصوصاً في ظل وجود اشخاص بكفاءة عالية في هذا المجال".
+وتابع: ان الآفة الاهم هي المخدرات التي تفتك بالمجتمعات والعائلات، ومن يروّج لها يرتكب جريمة كبيرة بحق الشباب، ويجب بالتالي عدم التهاون معه او الخضوع للضغوطات، بل الالتزام بالقسم وتطبيق القوانين.
+كما نوّه بالعمل الذي يقوم به "امن الدولة" لجهة مكافحة الفساد، والتقدم الذي حصل في هذا المجال، "وثقة الناس بكم هي اقوى سلاح في وجه الانتقادات والتهجم، إن في وسائل الاعلام او وسائل التواصل الاجتماعي او حتى من قبل السياسيين، وهذا يعني انكم تسيرون على الطريق الصحيح وهذا ما يزيد من افتخار الناس ولبنان بأكمله، بكم".
+وقدّم العقيد الحكم، شرحاً لرئيس الجمهورية حول المهام التي يقوم بها عناصر امن الدولة، وتم عرض فيلم وثائقي لما تحقق.
+ثم جال الرئيس عون في ارجاء المقر.
+مقر قوى الامن الداخلي
+بعد ذلك، انتقل الرئيس عون الى مقر قوى الامن الداخلي في السرايا مطلعا على الوضع فيه، وزار غرفة العمليات حيث شرح العميد بدران عمل المديرية العامة في طرابلس، وتوالى على الكلام ايضاً الوزير الحجار واللواء رائد عبد الله وقائد الدرك وكبار الضباط، فعددوا الانجازات التي حصلت حتى اليوم ومنها على سبيل المثال، تراجع مخالفات البناء بنسبة 90%، بعد رفع الغطاء السياسي عنها، كما تراجعت نسبة الجريمة، وتم تكثيف الدوريات.
+ثم عرض الرائد طوني الخواجا لابرز الاجراءات التي تتخذها قوى الامن في الشمال، وتلك التي تحفظ الامن بالتنسيق مع مختلف الاجهزة الامنية.
+وبعدها، انتقل الجميع الى مكتب العميد بدران، حيث تحدث الرئيس فقال: "اعتز بزيّ قوى الامن الداخلي، ولا انسى فضلها عليّ لان والدي كان من عدادها، وبالاعتماد على ارادتكم للقيام بواجبكم على الرغم من الظروف القاسية ومن اجل مصلحة الناس الذين تعبوا من الاحزاب والكلام الطائفي والاستغلال. الدولة هي مطلب اللبنانيين، وهذا ما يجب توفيره لهم، فلا بديل عنها وقد شاهد الجميع ما حصل في غيابها في السبعينات، وها هي اليوم تعود للعب دورها بكل اجهزتها لخدمة المواطنين واعادة ثقتهم بها، وبالتالي، مواجهة الصعوبات وتذليلها".
+وتابع الرئيس عون: الظروف الصعبة هي التي تصقل الكفاءة والقدرة، وانتم تتمتعون بها، ونحن الى جانبكم وندعمكم للقيام بواجبكم وفق ما يمليه عليكم ضميركم، بعدالة ومساواة وشفافية في التعاطي مع الناس، ونثق بكم ونرغب في ان تنجحوا في المهام الموكلة اليكم، والاستمرار في السير الى الامام، والشعب اللبناني امانة في اعناقنا.
+مركز الامن العام
+ثم انتقل رئيس الجمهورية والحضور الى مركز الامن العام في الشمال حيث استمع من رئيسه العقيد عازار الشامي الى الجهود التي يقوم بها المركز في سبيل تسهيل امور المواطنين اداريا، ومواكبتهم على الصعيد الأمني. ولفت الى اصدار المكتب حوالى 30 الف جواز سفر سنوياً، كما انه لم تسجل اية حالة فرار من الامن العام، وانه اضيفت الى المهام التقليدية، مهمة جديدة وهي ملاحقة التهرب الضريبي الذي كان يحصل في مرفأ طرابلس.
+واثنى الرئيس عون على الجهود التي يبذلها الامن العام واللواء شقير لتسهيل امور المواطنين، ودعاه الى الاستمرار على هذا المنحى لما فيه مصلحة اللبنانيين، ومواصلة مسار التطور في الخدمات المقدمة الى المواطنين وهي "مقدسة"، وتساهم في توفير الوقت ومحاربة الفساد وتعزيز الشفافية.
+ثم شرح اللواء شقير الخطوط العريضة التي يعمل في ظلها "الامن العام" في كل المناطق اللبنانية وبالاخص في الشمال وطرابلس، والمهام المنوطة به امنياً وادارياً، وكل ذلك بالتنسيق مع الجيش وباقي الاجهزة الامنية، ما ادى الى تحسين الاداء وتعزيز الامن في هذه المنطقة.
+قصر العدل
+وعند التاسعة والنصف، وصل رئيس الجمهورية الى قصر العدل حيث كان في استقباله وزير العدل، والرئيسة الاولى القاضية نضال شمس الدين، والنائب العام القاضي هاني حلمي الحجار، وقاضي التحقيق الأول ناجي الدحداح ونقيب المحامين في طرابلس والشمال الأستاذ مروان ضاهر.
+بداية، كان اللقاء في مكتب القاضي الحجار الذي اشاد بالحرص الذي يوليه الرئيس عون لاستقلالية القضاء وتحصينه، لافتاً الى ان زيارته اتت بعد يوم على توقيعه مرسوم التشكيلات القضائية الثاني في عهده، وهو امر مهم، وبعد ثلاثة ايام على الاشكال الذي شهدته قاعة المحكمة في قصر العدل والذي تم احتواؤه بفضل التدخل السريع للاجهزة الامنية وتفادي كارثة حقيقية، مشدداً على اهمية توفير الامن في قصور العدل.
+واشار الى ان النيابة العامة في طرابلس استلمت من 1/10/2025 وحتى 1/10/2026، 25 الف ملف تحقيق اولي من الاجهزة الامنية، و9 آلاف شكوى تم تقديمها امام النيابة العامة تم تحويل 2330 ملف منها الى قاضي التحقيق.
+وحضر اللقاء المحامون العامون وقضاة التحقيق في الشمال.
+الرئيس عون
+ورد الرئيس عون بالتأكيد على تلازم الامن والقضاء للوصول الى النتائج المطلوبة، مشدداً على اهمية استقلالية المسؤولين في الجسم القضائي، لان القوانين لا تضمن استقلالية المحامين والقضاة وحدها، بل ما يضمنها قناعتهم الشخصية بحيث انه على القاضي الا يدين بريئا والا يبرىء مجرما. وشدد على ان محاربة الفساد تقوم على امرين اساسيين: الحكومة الرقمية والقضاء، وقيام مؤسسات الدولة منوط بمحاربة الفساد وعدالة القضاء.
+واثنى على الجهود التي يقوم بها وزير العدل لتحسين وضع القضاء في لبنان، والانجازات التي حققها الجسم القضائي خصوصا خلال العام الحالي، واكد على وجوب الاعتماد على صلابة القضاة والاحكام العادلة التي يصدرونها، مشيراً الى ان هناك توجها لاقامة قصر عدل في عكار الا ان الامكانات حالياً لا تسمح بذلك.
+وشدد على اهمية الاسراع في البت بالملفات قدر الامكان، وعلى ان الثقة بالقضاء كبيرة، داعيا الى ان يبقى القضاء فوق التجاذبات، مؤكدا ان طرابلس بما تمثله من ثقل وطني واجتماعي واقتصادي تحتاج الى قضاء فاعل يسهم في حماية الحقوق وصون الاستقرار وتشجيع الاستثمار.
+وزار الرئيس عون قلم النيابة العامة واطلع على الملفات الموجودة فيه، واستمع من المسؤولين الى حجم العمل المنجز، والصعوبات التي تواجه البت بالملفات. ومن هناك، انتقل الى مكتب القاضية شمس الدين التي القت كلمة قالت فيها:
+"شرف كبير لنا حضوركم إلى لبنان الشمالي، هذا الحضور يؤكد ما ورد في خطاب القسم لناحية رعاية الرئاسة لكل المناطق اللبنانية، كما أن حضوركم الى قصر العدل في طرابلس يجسّد حرصكم وحرص معالي وزير العدل على تعزيز القضاء والحفاظ على استقلاليته. وهذا ما شجعنا ويشجعنا في الحاضر والمستقبل، على أداء مهامنا بعزم واستقلالية وتحدي الصعاب اللوجستية والأمنية التي تعترض عمل القضاء في هذه المنطقة.
+ولن أطيل الكلام عليكم لضيق الوقت، وإنما نعاهد جميعاً فخامتكم بالعمل الدؤوب والمستمر على تأمين العدالة والاستقرار لأبناء هذا الوطن الحبيب".
+وقدمت القاضية شمس الدين للرئيس عون درعا تذكاريا.
+نقابة المحامين
+ثم انتقل الرئيس عون الى مقر نقابة المحامين في طرابلس والشمال حيث التقى النقيب ضاهر وعددا من أعضائها والنقباء السابقين في الشمال. وفي كلمة للنقيب ضاهر رحب فيها بالرئيس عون الذي يجمع "قيادة تدرك ان قوة الرئاسة في قدرتها على توحيد الارادة الوطنية، وان هيبة الدولة من هيبة قانونها، وان حماية الوطن تبدأ من وحدة ابنائه ورسوخ مؤسساته". وشدد على ان نقابة المحامين في طرابلس ستبقى سنداً لمواقف رئيس الجمهورية الوطنية وخياراته الدبلوماسية، "ايماناً منها بأنها السبيل الاجدى لاخراج لبنان من اتون حرب زجّ فيها".
+وقال" السلام الذي يحفظ حقوق الشعب وكرامته وسيادة الوطن، ليس تنازلاً، بل هو انتصار لمنطق الدولة، وللبنان".
+الرئيس عون
+ورد الرئيس عون شاكراً للنقابة حفاوة الاستقبال، واستشهد بقول مأثور للشهيد كمال جنبلاط: "خوفي ان نصبح في شريعة الغاب، ولكن خوفي الاكبر ان نصبح في الغاب بلا شريعة". وقال ان صلابة الدولة وقوتها غير محصورة فقط بمؤسساتها الادارية، بل ايضاً بمؤسساتها القانونية والدستورية، وعلى القانون ان يطبّق على الجميع.
+أضاف:"ان القضاء هو ركيزة اساسية، وهناك من يسيء اليه من داخل الجسم القضائي، لذلك يجب ان يتولى تطهير نفسه ليحافظ على نفسه وعلى حقوق الناس، والمحامون اساسيون في هذا المجال وفي هذه المعادلة. فهم، كما القضاة، يتولون مسؤولية مهمة تتعلق بحرية الانسان، لذلك على الشفافية ان تكون مصانة، وعليكم مسؤولية كبيرة، والجميع يعتمد عليكم للقيام بمهامكم وواجباتكم كما يمليه عليه ضميركم".
+وبعد اخذ الصورة التذكارية، قدم النقيب ضاهر الى الرئيس عون ميدالية النقابة .
+تجمع شعبي
+وخلال انتقال رئيس الجمهورية من قصر العدل الى مرفأ طرابلس، توقف امام تجمع شعبي كبير هتف بحياته، فيما كانت الموسيقى والاغاني الوطنية تصدح ممزوجة بهتافات المواطنين الذين انتشروا في الشوارع المزينة بالاعلام اللبناينة وصور رئيس الجمهورية ولافتات الترحيب.
+وترجل الرئيس عون من السيارة والتقى الحشد الذي تجمع لتحيته وهتف" الله معك فخامة الرئيس"، وتبادل اطراف الحديث مع بعضهم قبل اكمال طريقه الى المرفأ.
+مرفأ طرابلس
+وحوالي العاشرة والدقيقة الخامسة والأربعين، وصل رئيس الجمهورية والوفد الوزاري والأمني المرافق الى مرفأ طرابلس. وكان في استقباله وزيرا الاقتصاد والتجارة عامر البساط والاشغال العامة والنقل فايز رسامني، ورئيس هيئة إدارة المرفأ المهندس إسكندر بندلي، وأعضاء مجلس إدارة الهيئة ومدير مصلحة استثمار المرفأ الدكتور احمد تامر، ورئيس مجلس إدارة المنطقة الاقتصادية الخاصة في طرابلس الدكتور حسان ضناوي.
+وعقد رئيس الجمهورية لقاء حضره الوزراء رسامني والبساط ونصار والحجار وقادة الأجهزة الامنية ورئيس هيئة إدارة المرفأ، ونائبة رئيس مجلس الإدارة السيدة سارة شريف وأعضاء المجلس ورئيسة إقليم الجمارك السيدة باسكال إيليا ورئيس دائرة الجمارك السيد وسام الرواس. كما حضر اللقاء رئيس اتحاد غرف التجارة والصناعة والزراعة الوزير السابق محمد شقير ورئيس المجلس الاقتصادي والاجتماعي والبيئي شارل عربيد ورئيس غرفة التجارة في الشمال توفيق دبوسي.
+في مستهل اللقاء، رحب المهندس بندلي بالرئيس عون وشرح الخطوات التي تم انجازها لتحسين تقديمات وقدرات المرفأ، وتوقف عند التوقيع على انضمام المرفأ مع مرفأ بيروت الى "نادي موانئ الممر الاقتصادي (IMEC) والمسؤولية الكبيرة التي يتطلبها لتحسين البنى التحتية وتطبيق الحوكمة والتحول الرقمي، وغيرها من المسائل التي تسهل عمل المواطنين وتحسن وضع المرفأ. وتحدث ايضا عن المشاريع المستقبلية التي تنتظر المرفأ واهمية ما يقوم به لما فيه مصلحة الناس وتسهيل تقديماته.
+الرئيس عون
+وهنّأ الرئيس عون القيّمين على مرفأ طرابلس لانضمامه الى نادي موانىء الممر الاقتصادي ( IMEC) وعلى التعيينات التي اقرت، داعياً اياهم الى الالتزام بمسؤولياتهم. ولفت الى ان تخصيص لبنان بمرفأين للانضمام الى هذا النادي هو امر لافت بحد ذاته ويستحق التهنئة لوزير الاشغال وكل من ساهم في تحقيق هذا الإنجاز الذي يجب الحفاظ عليه، وهناك فرصة كبيرة لابراز حضور مرفأي طرابلس وبيروت في ظل الاوضاع التي تشهدها المنطقة، واثبات احقيتهما في تأمين الخدمات اللازمة للبنان ودول المنطقة ايضاً.
+واشاد بالانجازات الكبيرة التي شهدها المرفأ اخيراً، بعد 23 سنة على انشائه، آملاً ان تتواصل الانجازات والجهود للتقدم الى الامام والتميّز بين سائر المرافىء في المنطقة واستغلال كل الفرص السانحة حالياً لتعزيز العمل في المرفأ وتطوره، لان من لا يواكب التطور سيتخطاه التاريخ.
+مدير المصلحة
+ثم تحدث السيد تامر، فشدد على اهمية اعادة القدرة التنافسية الى مرفأي طرابلس وبيروت من خلال اعادة العمل بسكك الحديد الذي لا توجد مشكلة امامه الا التمويل لان الممرات اساسية، وايضاً سياسة الحكومة اللبنانية ووجوب ان تتكامل مع المرافىء السورية وعدم التنافس في ما بينها.
+السجل الذهبي
+ودوّن الرئيس عون في السجل الذهبي للمرفأ الكلمة التالية:
+"إن زيارتنا اليوم لمرفأ طرابلس، نافذة لبنان الاقتصادية على المتوسط وحاضنة تاريخه العريق، تأكيدٌ راسخٌ على إيماننا المطلق بدور العاصمة الثانية وشمالنا الحبيب في مسيرة النهوض الوطني والتعافي الشامل. لقد أثبت أبناء طرابلس والعاملون في هذا المرفق الحيوي صموداً وعزماً كبيرين، وجعلوا منه صلة وصل فاعلة بين لبنان ومحيطه والعالم. وإننا نعوّل اليوم، أكثر من أي وقت مضى، على طاقات هذا المرفق وبناه التحتية ليكون رافداً أساسياً للاقتصاد الوطني، ورمزاً للعمل المنتج والشفاف.
+كل التقدير للجهود التي بذلها القيمون على ادارة مرفأ طرابلس ، والعهد بأن تبقى الدولة إلى جانب كل مؤسسة وطنية تُعلي شأن العمل والإنتاج. وعهدنا للوطن ولطرابلس أن نمضي معاً نحو مستقبل يليق بتاريخنا وتطلعات أبنائنا. وفقكم الله، وسدد ، على طريق الخير ، خطاكم".
+ثم جال الرئيس عون في ارجاء المرفأ وزار مركز السكانر وعاين طريقة المراقبة، كما اطلع ايضاً على محطات المستوعبات التي يستقبلها المرفأ.
+وبعد انتهاء الزيارة وقبيل مغادرته مقر مرفأ طرابلس، اكد الرئيس عون رداً على سؤال صحافي، ان الهدف من زيارته الى طرابلس هو للتأكيد على وقوفه الى جانب هذه المدينة والطرابلسيين وان زمن الاقصاء والتهميش قد ولّى، وان الشمال وطرابلس هما في قلب اللبنانيين جميعاً.
+وطمأن، رداً على سؤال آخر، الى ان لا خوف على السلم الاهلي، وانه لا يجب حصول تدخل سياسي في القضاء الذي عليه القيام بواجبه.
+ثم انتقل الرئيس عون والوفد الوزاري والأمني المرافق يرافقهم رئيس مجلس إدارة المرفأ ورئيسة إقليم الجمارك السيدة باسكال إيليا وممثلو الجمارك وكبار الموظفين من مبنى الإدارة الى غرفة التحكم والمراقبة، حيث استمع الى شرح موجز من العميد السيور عن منظومة المراقبة المجهزة بكاميرات تعمل بتقنيات الذكاء الاصطناعي وتغطي مدينة طرابلس باشراف مديرية المخابرات في الجيش.
+وقد اطلقت السفن الراسية في المرفأ، بالتزامن مع تنقل رئيس الجمهورية في ارصفة المرفأ، ابواقها تحية لرئيس الجمهورية.
+بعدها، انتقل الى موقع جهاز السكانر حيث كان في استقباله المدير الاقليمي لشركة CMA CGM السيد جوزاف دقاق وكبار الموظفين فيها. وقدم السيد دقاق شرحا لكيفية شراء الشركة جهاز السكانر وتشغيله وتولي صيانته فيما تتولى مديرية الجمارك الكشف على الحاويات، والمشاريع التي تقوم بها الشركة في المرفأ لتطويره وتحسين التقديمات فيه.
+المنطقة الاقتصادية
+ثم انتقل الرئيس عون الى المنطقة الاقتصادية الخاصة حيث كان في استقباله على سطح شركة CMA CGM الدكتور ضناوي وأعضاء مجلس الادارة والوزير السابق شقير. واطلع الدكتور ضناوي على مستجدات تطوير مشروع المركز اللوجستي الصناعي التابع للمنطقة الاقتصادية حيث شرح تفاصيل المخطط التوجيهي للمنطقة، الصناعات المتوقع اطلاقها، أهمية تكامل المنطقة مع المرفأ وسكك الحديد والمطار والمعرض. وشدد على ضرورة إغلاق جميع المكبات والمطامر المحيطة بالمنطقة لما لها من اثر سلبي على استقطاب المستثمرين، كما اطلع الرئيس عون على قرب إطلاق جولة تأهيل الشركات العالمية ضمن آلية إطلاق المزايدة العالمية لتطوير وإدارة المركز اللوجستي الصناعي قريبا حيث تبدي العديد من الشركات العالمية اهتمامها بالمشاركة في هذه المزايدة العالمية.
+معرض رشيد كرامي الدولي
+وعلى الأثر، توجه رئيس الجمهورية والوفد المرافق الى معرض رشيد كرامي الدولي حيث استقبله رئيسه السيد هاني الشعراني. ثم اجتمع الرئيس عون مع هيئة إدارة المعرض حيث كانت كلمة للسيد الشعراني، شدد فيها على اهمية الزيارة وقدم عرضاً شاملاً للمراحل التي قطعها المعرض، والتطور الذي مر به على مرّ السنوات، واهميته بالنسبة الى طرابلس ولبنان بشكل عام، مركّزاً على اعتماده بشكل تام على الطاقة الشمسية، وعلى ان التجهيزات التي يستفيد منها المعرض لا تكلف الدولة اموالاً. وقال ان المعرض شهد 186 نشاطا خلال 14 شهرا، منها نشاطات ثقافية ورياضية ومعارض، لافتا الى ان إيرادات المعرض بلغت خلال هذه الفترة ما يقارب 500 الف دولار.
+واشاد الوزير البساط من جهته، بالعمل الذي يقوم به مجلس ادارة المعرض على المستويات الثقافية والسياحية والاقتصادية، معتبراً انه عمل جبار.
+الرئيس عون
+واعرب الرئيس عون عن التقدير للعمل الذي يتم انجازه في معرض رشيد كرامي الدولي، على الرغم من كل الصعوبات، وهو "يعبّر عن الرؤية الواحدة التي نريدها لطرابلس والشمال والتي تقوم على استثمار الامكانات المتوافرة، وتفعيل المرافق الحيوية، وتحويلها الى محركات للنمو وفرص العمل".
+ولفت الى ان الانجازات التي تحققت تعبّر عن ارادة اللبنانيين وصلابتهم وتخطي الظروف الصعبة، مؤكداً استعداد الدولة للقيام بكل ما يلزم، وفق الامكانات المتوافرة، للاستمرار بالعمل في هذا المعرض، لتتحول الانجازات التي تحققت الى مسار دائم.
+كلمة في السجل
+ودون الرئيس عون في السجل الذهبي للمعرض الكلمة التالية:
+" يشكّل معرض رشيد كرامي الدولي في طرابلس صرحاً وطنياً يجسّد طموح لبنان إلى التقدّم والانفتاح، ويختزن إرثاً معمارياً وثقافياً واقتصادياً يعكس مكانة طرابلس ودورها في نهضة لبنان.
+وإننا، إذ نزور هذا المعلم الوطني، نؤكد حرصنا على صونه وتفعيله، ليعود مساحةً واعدة للاستثمار والإنتاج والتلاقي، ورافعةً لإنماء طرابلس والشمال، بما يعزّز دورهما في بناء لبنان الذي نطمح إليه، وطناً موحّداً، مزدهراً، وعادلاً في التنمية بين جميع مناطقه".
+لقاء موسع
+وبعد جولات في ارجاء المعرض في "غولف كار"عقد لقاء موسع حضره الى الوزراء رسامني والحجار ونصار، النواب فيصل كرامي، واشرف ريفي، وكريم كبارة، وايلي خوري، وحيدر ناصر، وطه ناجي، وعدد من الوزراء السابقين من أبناء المدينة، ومحافظ الشمال بالوكالة، ورئيس اتحاد الفيحاء، وعدد من رؤساء البلدية، ورؤساء الأجهزة الأمنية المرافقون وقيادات عسكرية وامنية.
+كما حضر مفتي الشمال الشيخ محمد امام، ومطران الموارنة في طرابلس يوسف سويف، ومتروبوليت الروم الأرثوذكس افرام كرياكوس، ومطران الروم الكاثوليك أدوار ضاهر، ورئيس المجلس الإسلامي العلوي الشيخ علي قدور وفاعليات طرابلس ونقباء مهن حرة، وممثلون عن المؤسسات الاقتصادية والمصرفية.
+واستهل اللقاء السيد الشعراني بكلمة شدد فيها على ان طرابلس تتطلع اليوم، كما كانت دائماً، الى شراكة فاعلة مع الدولة، ترسّخ الانماء المتوازن، وتعيد الى مؤسساتها الحيوية، والى اقتصادها، الحركة وتفتح امام شبابها ابواب العمل والابداع. وقال: كلنا امل في ان تكون زيارتكم الكريمة فاتحة لآفاق جديدة، تنتقل فيها التطلعات من حيّز الامل الى ميدان العمل، وتتحول الفرص الواعدة الى مشاريع ملموسة.
+واكد انه "حين تنهض طرابلس، ينهض معها لبنان، وحين نفتح امام شبابها ابواب الفرص، نفتح امام الوطن نوافذ الامل والازدهار".
+الرئيس عون
+ثم عرض فيلم صغير حول المعرض قبل ان يلقي الرئيس عون الكلمة التالية:
+" بداية، ارغب في تحية القيمين على المعرض الذين حرصوا على وضع النشيد الوطني بشكل كامل، وادعو كل المؤسسات والشركات الى القيام بالمثل.
+أيها الحضور الكريم، لقد مّر لبنان بسنوات صعبة دفع خلالها اللبنانيون أثماناً باهظة من أمنهم واستقرارهم واقتصادهم وثقتهم بمستقبلهم. وأثبتت التجارب ان الانقسام لا يحمي أحداً، وأن إضعاف الدولة لا يمنح القوة لأي مكوّن، وأن الوطن لا يستطيع النهوض إلا بأبنائه مجتمعين تحت سقف واحد هو الدستور والقانون والمؤسسات. من هنا أقول إن مسؤوليتنا اليوم هي أن نتعلم من تجارب الماضي، وأن نضع مصلحة لبنان فوق الحسابات الضيقة، وأن نعمل على تحصين وحدتنا الوطنية لا بالشعارات وحدها، بل بالممارسة وبالعدالة وبالمساواة في الحقوق والواجبات.
+إن قوة لبنان في تنوّعه، لكن هذا التنوع لا يكتسب معناه الحقيقي إلا عندما يكون مصدر غنى وتكامل، لا سبباً للخلاف والانقسام. والعيش المشترك ليس مجرد تعايش بين جماعات مختلفة، بل هو إيمان راسخ بأننا شركاء في وطن واحد، وأن مستقبلنا واحد، وأن حقوق أي لبناني لا يمكن أن تكون على حساب حقوق لبناني آخر.
+إن الدولة الحديثة القوية، الموحدة والمزدهرة تقوم على مركزية السلاح بيد جيشها الواحد، ولا مركزية الإنماء، أي الإنماء على مساحة كل الوطن ولكل مواطن، الركيزتين اللتين تتحققان الانتماء والولاء للوطن. إن مسؤوليتنا الوطنية تقتضي أن نعيد الاعتبار إلى العمل والإنتاج، وأن نفتح أمام شبابنا آفاق المستقبل في وطنهم، بدلاً من أن يضطروا إلى البحث عن فرصهم خارجه. وطرابلس بما تملكه من طاقات وكفاءات ومرافق اقتصادية، قادرة على أن تكون شريكاً أساسياً في نهضة لبنان، إذا توافرت لها الرؤية والإدارة والاستثمارات اللازمة. أؤكد أن لا إنماء من دون دولة، ولا دولة من دون مؤسسات فاعلة، ولا مؤسسات من دون احترام القانون والمساءلة والمحاسبة. إن الدولة ليست في مواجهة أبنائها، بل هي ضمانتهم، وليست ملكاً لفئة أو طائفة أو فريق، بل هي ملك اللبنانيين جميعاً ومرجعيتهم المشتركة. من هذا المنطلق، فإن بناء الدولة وتعزيز سلطتها على كامل الأراضي اللبنانية وصون سيادة الوطن واستقلال قراره، مسؤولية وطنية جامعة لا تستقيم بالتجزئة أو الانتقائية، بل بالتزام الجميع بالدستور والقوانين وباحتكام الجميع إلى المؤسسات الشرعية.
+وجودي اليوم في طرابلس، هذه المدينة العريقة التي تختزن تاريخاً من الوطنية والكرامة والتنوع، يحمل رسالة تتجاوز حدود الزيارة والمناسبة. طرابلس ليست مدينة على هامش الوطن، ولا يجوز أن تكون كذلك، إنها مدينة أساسية في تاريخ لبنان وحاضره ومستقبله،. وأبناؤها شركاء كاملون في بناء الدولة وصناعة القرار الوطني وتحديد الخيارات التي ترسم مستقبل البلاد. أتوجه هنا إلى طرابلس وأهلها، وإلى كل الشمال، لأؤكد ان الإنماء ليس منّة من الدولة، بل حق للمواطنين، وواجب على المؤسسات. لا يجوز لأي لبناني أن يشعر بأنه متروك أو أن منطقته خارج حسابات الدولة. فالدولة التي نريدها هي التي تصل إلى جميع أبنائها، وتوفّر لهم فرص العمل والتعليم والاستشفاء والحماية الاجتماعية، وتضمن لهم الأمن والعدالة والكرامة.
+إن طرابلس التي أنجبت رجالاً وطنيين كباراً واحتضنت ثقافة والعلم والانفتاح، قادرة على أن تكون نموذجاً في التلاقي والتعاون والتطلع إلى المستقبل. وما أتمناه، هو أن نجعل من هذه الزيارة محطة لتعزيز الثقة بين الدولة وأهل المدينة، وأن نترجم الأقوال إلى خطوات عملية والوعود إلى مشاريع والآمال إلى نتائج يشعر بها المواطن في حياته اليومية. إن التنمية ليست وعوداً فقط، بل هي استثمارات فعلية ومؤسسات أكثر كفاءة وفرص عمل للشباب. فطرابلس ليست مجموعة مشاريع منفصلة، هي مدينة تملك مقومات اقتصادية وبشرية وثقافية حقيقية تستحق أن تكون في صلب التنمية الوطنية. المرفأ، المنطقة الاقتصادية، المعرض، المطار لاحقاً، يجب أن تعمل ضمن رؤية واحدة وليست كمشاريع منفصلة. طرابلس المدينة العريقة التي ظلمها على مدى عقود، إهمال الدولة للأسف، وعبث العصابات المقنعة بالسياسة، حتى استبيحت وصارت صندوق بريد أسود لتبادل الرسائل المسمومة، رسائل كانت تتساقط قنابل ورصاصاً على الشوارع والأحياء والناس الطيّبين والطلاب الساعين للعمل. وللأسف، فإنني عشت شخصياً المرحلة السوداء بتاريخ طرابلس.
+أنا اليوم هنا فيها لأضع في صندوق بريدها رسالة أخرى عنوانها: طرابلس درّة لبنان، صاحبة الحق المستلب والحق المكتسب. طرابلس اليوم تنفض عنها غبار السنوات التي طالت وتقف لتقول بملء الثقة إنها مدينة الفيحاء الغنية بمرافقها وتراثها وجامعاتها ومعاهدها والغنية بأهلها. طرابلس التاريخ، طرابلس القلعة، طرابلس مدينة العلم والعلماء وقلب الشمال، كل الشمال. طرابلس شارع الكنائس ومساجد إيمان السكينة. طرابلس الشيخ محمد الجسر والرئيس الشهيد رشيد كرامي والرئيس الراحل عمر كرامي وعشرات رجالات لبنان. طرابلس المدينة التي قدمت شهداء بمعركة الاستقلال عام 1943، وما بخلت يوماً على لبنان. أنا رئيس للجمهورية اللبنانية، ومسؤوليتي أن أكون على مسافة واحدة من جميع اللبنانيين، وأن أعمل من أجل لبنان الذي يتسع للجميع، ويحمي الجميع، ويمنح الجميع الفرصة نفسها في المواطنة والكرامة والمستقبل. لبنان لا ينهض بفريق وحده، ولا بمنطقة وحدها، ولا بطائفة وحدها، بل عندما يلتقي أبناؤه على مشروع الدولة، وعندما يتقدم الانتماء الوطني على كل انتماء آخر في إدارة شؤون الوطن ومصالحه. فلنعمل معاً من أجل دولة قوية وعادلة واقتصاد منتج ومجتمع متضامن، ووطن يطمئن أبناؤه إلى مستقبلهم فيه. مني لطرابلس وأهلها كل المحبة والتقدير، وكل الالتزام بالعمل من أجل مستقبل أفضل لها وللشمال وكل لبنان. احييكم وأؤكد لكم ان جيشكم والأجهزة الأمنية هم أبناؤكم الذين يضحون من أجلكم في أصعب الظروف. .
+أنا اليوم جئت لأقول لكم: انتهى زمن الحرمان، وزمن الإقصاء والتهميش. طرابلس "أنتو القلب، وأنتو بالقلب". كل الشكر لكم، وكل الحب لطرابلس وللشمال ولكل لبنان. عشتم، عاشت طرابلس، وعاش الشمال، وعاش لبنان".
+كلمات
+ثم كانت كلمات للنواب: كرامي وريفي وناجي وخوري وناصر، والمفتي امام والمطران سويف والشيخ قدور الذين رحبوا بالرئيس عون في طرابلس واثنوا على مواقفه وخياراته الوطنية وعرضوا للمشاكل التي تعاني منها المدينة على الصعد كافة: امنياً وادارياً وانمائياً، والحرمان التي عانت منه طوال سنوات، وشددوا على ان الامل هذه المرة اكبر بكثير بفعل الاهتمام الذي يبديه الرئيس عون بالمدينة واهلها، واهمية تنفيذ الوعود والافكار التي من شأنها الارتقاء بالمدينة الى حيث يجب ان تكون.
+وشدد رجال الدين على ان السمعة السائدة عن طرابلس لا تعكس واقعها الحقيقي ولا تاريخها الغني بالتعايش بين كل الطوائف، وانهم يعملون على اعادة الصورة الحقيقية، واكدوا انهم عائلة واحدة لا تتجزأ.
+كما شددت الشخصيات الطرابلسية الفاعلة، على اهمية رسالة الامل والوطنية والمؤسسات التي حملها الرئيس عون معه، وعلى اهمية تحقيق الانماء المتوازن، والتأكيد على رفع الغبن والحرمان عن هذه المدينة.
+الرئيس عون
+ورد الرئيس عون بالقول ان صورة طرابلس قبل الحرب لا تزال محفورة في ذاكرته ، وقد عاد اليها عام 2013 وتفاجأ بالصورة التي رآها لجهة الاقتتال بين اهلها، فيما اللافت كان ان ابن طرابلس كان في الجبل وابن الجبل كان في طرابلس، وهذا الامر كان غريباً بالفعل في ظل المواجهات التي كانت دائرة. وقال:"هنا تظهر طيبة اهل طرابلس واهل الجبل الذين تم استغلالهم، عبر الرسائل المسمومة التي كانت من خلال الرصاص والقنابل، وقد دفع ثمنها ابناء المدينة".
+وختم الرئيس عون:"عدت كقائد للجيش وزرت رجال الدين فيها وقلت ان طرابلس ليست بلد الارهاب، وهذه الزيارة لي كرئيس للجمهورية هي للتشديد على ان زمن التهميش والرسائل السياسية المسمومة قد ولّى، والمسؤولية مشتركة بين الدولة وبينكم، ونحن واياكم سنعمل لمصلحة ابناء طرابلس والشمال".
+وغادر الرئيس عون بعد ذلك طرابلس عائدا الى القصر الجمهوري في بعبدا بمثل ما استقبل به من حفاوة وتكريم.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:38.475296+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>الرئيس عون دان جريمة الكرك في الأردن: عمل اجرامي يؤكد ان الإرهاب هدفه ضرب العيش المشترك وبث الفتنة بين المجتمعات المتآخية</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1586</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>الرئيس عون دان جريمة الكرك في الأردن: عمل اجرامي يؤكد ان الإرهاب هدفه ضرب العيش المشترك وبث الفتنة بين المجتمعات المتآخية
+الرئيس عون دان جريمة الكرك في الأردن:
+عمل اجرامي يؤكد ان الإرهاب هدفه ضرب العيش المشترك وبث الفتنة بين المجتمعات المتآخية
+----
+تلقّى رئيس الجمهورية العماد جوزاف عون ببالغ الأسى والاستنكار نبأ الهجوم الإرهابي الآثم الذي استهدف اليوم المصلّين في كنيسة الكرك في المملكة الأردنية الهاشمية، وأسفر عن سقوط شهداء وجرحى أبرياء . وفيما دان الرئيس عون الجريمة، اعتبر انّ هذا العمل الإجرامي، الذي طال دور العبادة وحرمة الموت والمشيّعين، يتنافى مع كل القيم الدينية والإنسانية، ويؤكد مجدداً أن الإرهاب لا دين له ولا وطن، وأن هدفه ضرب العيش المشترك وبثّ الفتنة بين أبناء المجتمعات المتآخية.
+وقال الرئيس عون: إذ أعبّر عن إدانة لبنان الشديدة لهذا الاعتداء، أتقدم من جلالة الملك عبدالله الثاني ابن الحسين، ومن الحكومة والشعب الأردني الشقيق، ومن عائلات الضحايا، بأحرّ التعازي وصادق المواساة، سائلاً المولى أن يتغمّد الراحلين بواسع رحمته، وأن يمنّ على الجرحى بالشفاء العاجل .
+إنّ لبنان يقف إلى جانب الأردن في مواجهة الإرهاب، ويثق بقدرة الأجهزة الأردنية على كشف الجناة واحقاق العدالة .</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:40.810316+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية أصدر مرسوم التشكيلات والمناقلات القضائية الجزئية</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1585</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2017-06-01</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية أصدر مرسوم التشكيلات والمناقلات القضائية الجزئية
+المرسوم حمل تواقيع رئيس مجلس الوزراء والوزراء المعنيّين
+---
+أصدر رئيس الجمهورية العماد جوزاف عون المرسوم الرقم ٤١٥٠ تاريخ ٢٣ تشرين الاول ٢٠٢٦ المتضمن التشكيلات والمناقلات القضائية الجزئية.
+وحمل المرسوم تواقيع كلّ من: رئيس مجلس الوزراء الدكتور نواف سلام، ووزراء المالية ياسين جابر، والدفاع الوطني اللواء ميشال منسى، والعدل عادل نصار.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:43.134142+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية في رسالة الى غوتيريش بمناسبة يوم الامم المتحدة: لبنان يثمّن الدور الذي تضطلع به المنظمة الدولية في دعم الاستقرار والسلام ويتمسّك بالشرعية الدولية وبمبادئ الميثاق -------- الرئيس عون اطلع من الامين العام لمؤتمر لاهاي للقانون الدولي على</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1584</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية في رسالة الى غوتيريش بمناسبة يوم الامم المتحدة: لبنان يثمّن الدور الذي تضطلع به المنظمة الدولية في دعم الاستقرار والسلام ويتمسّك بالشرعية الدولية وبمبادئ الميثاق -------- الرئيس عون اطلع من الامين العام لمؤتمر لاهاي للقانون الدولي على
+رئيس الجمهورية في رسالة الى غوتيريش بمناسبة يوم الامم المتحدة:
+لبنان يثمّن الدور الذي تضطلع به المنظمة الدولية في دعم الاستقرار والسلام
+ويتمسّك بالشرعية الدولية وبمبادئ الميثاق
+--------
+الرئيس عون اطلع من الامين العام لمؤتمر لاهاي للقانون الدولي على نطاق عمل المؤتمر واهمية انضمام لبنان اليه
+-------
+رئيس الجمهورية عرض العلاقات اللبنانية-الكويتية والأوضاع في لبنان والمنطقة مع سفير الكويت
+----------
+رئيس الجمهورية اطلع من حاكم مصرف لبنان على نتائج لقاءاته في بانكوك على هامش الاجتماعات السنوية لصندوق النقد الدولي والمشاورات التي سيجريها مع كبار المسؤولين في السلطات المالية الفرنسية
+---------
+الرئيس عون اكد على أهمية صون الاستقرار النقدي والمضي قدماً في إصلاح القطاع المصرفي وحماية حقوق المودعين
+-----------
+أكد رئيس الجمهورية العماد جوزاف عون في رسالة تهنئة وجهها الى الامين العام للامم المتحدة انطونيو غوتيريش بمناسبة يوم الامم المتحدة الذي يصادف غداً، أن لبنان يثمّن الدور الذي تضطلع به الأمم المتحدة في دعم الاستقرار والسلام ويتمسّك بالشرعية الدولية وبمبادئ الميثاق، ويحرص على مواصلة التعاون مع المنظمة الدولية في مواجهة التحديات المشتركة. وجاء في الرسالة:
+" معالي السيد أنطونيو غوتيريش المحترم
+الأمين العام للأمم المتحدة
+بمناسبة يوم الأمم المتحدة، يسرني أن أتوجه إليكم، ومن خلالكم إلى أسرة الأمم المتحدة كافة، بأصدق التهاني وأطيب التمنيات.
+إن هذه المناسبة تشكل محطة سنوية لتجديد الالتزام بالمبادئ والقيم التي قام عليها ميثاق الأمم المتحدة، وفي مقدمها صون السلم والأمن الدوليين، واحترام سيادة الدول، وتعزيز التعاون بين الشعوب والدول، والعمل من أجل عالم أكثر عدلاً واستقراراً.
+وإذ يثمّن لبنان الدور الذي تضطلع به الأمم المتحدة في دعم الاستقرار والسلام، أؤكد تمسّك لبنان بالشرعية الدولية وبمبادئ الميثاق، وحرصه على مواصلة التعاون مع المنظمة الدولية في مواجهة التحديات المشتركة.
+أغتنم هذه المناسبة لأعرب لكم عن تقديري للجهود التي تبذلونها في سبيل تعزيز السلام والتعاون الدولي، متمنياً لكم دوام النجاح، وللأمم المتحدة وأسرة العمل الدولي مزيداً من القدرة على تحقيق أهدافها السامية.
+وتفضلوا، معالي الأمين العام، بقبول فائق الاحترام والتقدير."
+الامين العام لمؤتمر لاهاي
+الى ذلك، استقبل الرئيس عون قبل ظهر اليوم في قصر بعبدا في حضور وزير العدل عادل نصار، والسفير الهولندي في لبنان Frank Mollen، الامين العام لمؤتمر لاهاي للقانون الدولي الخاص السيد Christophe Bernasconi الذي عرض نطاق عمل المؤتمر وعضوية العديد من الدول العربية والمتوسطية فيه، داعياً لبنان إلى الانضمام اليه نظراً لاهمية التعاون في نطاق تطبيق قواعد القانون الدولي الخاص وتسهيل المعاملات والإجراءات. وقد أبدى رئيس الجمهورية استعداد لبنان للتعاون في هذا المجال وتشجيعه المضي في هذا السياق. وحضر اللقاء رئيس مؤسسة IHOPE الدكتور احمد الايوبي.
+السفير الكويتي
+ديبلوماسياً، عرض رئيس الجمهورية مع سفير الكويت في لبنان محمد سلطان الشرجي العلاقات اللبنانية -الكويتية وسبل تطويرها في المجالات كافة ، كما تناول البحث الأوضاع في لبنان والمنطقة في ضوء التطورات الأخيرة . وشكر الرئيس عون الكويت اميراً وحكومة وشعباً على الدعم الذي قدمته ولا تزال للبنان متمنيا لها وللشعب الكويتي الشقيق الخير والتقدم والاستقرار.
+حاكم مصرف لبنان
+واطلع الرئيس عون من حاكم مصرف لبنان كريم سعيد على نتائج لقاءاته الأخيرة التي عقدها في بانكوك على هامش الاجتماعات السنوية لصندوق النقد الدولي.
+وشملت هذه اللقاءات مسؤولين رفيعي المستوى في كلّ من صندوق النقد الدولي، وصندوق النقد العربي، والاحتياطي الفيدرالي الأميركي، بالإضافة إلى عدد من حكّام المصارف المركزية في الدول العربية.
+كما عرض الحاكم سعيد لرئيس الجمهورية آخر التطورات النقدية والمالية في لبنان، والإجراءات التي يتخذها مصرف لبنان للحفاظ على الاستقرار النقدي . كذلك أطلع الحاكم رئيس الجمهورية على زيارته المرتقبة إلى فرنسا، حيث سيجري مشاورات مع كبار المسؤولين في السلطات المالية الفرنسية، ويشارك في مباحثات رفيعة المستوى مرتبطة بمجموعة الدول السبع G7 تتناول مكافحة تبييض الأموال وتمويل الإرهاب. وجدّد رئيس الجمهورية، خلال اللقاء، تأكيد أهمية صون الاستقرار النقدي والمضي قدماً في إصلاح القطاع المصرفي، وحماية حقوق المودعين .</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:45.386835+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية اطلع من حاكم مصرف لبنان على نتائج لقاءاته في بانكوك على هامش الاجتماعات السنوية لصندوق النقد الدولي والمشاورات التي سيجريها مع كبار المسؤولين في السلطات المالية الفرنسية</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1583</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية اطلع من حاكم مصرف لبنان على نتائج لقاءاته في بانكوك على هامش الاجتماعات السنوية لصندوق النقد الدولي والمشاورات التي سيجريها مع كبار المسؤولين في السلطات المالية الفرنسية
+الرئيس عون اكد على أهمية صون الاستقرار النقدي والمضي قدماً في إصلاح القطاع المصرفي وحماية حقوق المودعين
+-----------
+اطلع الرئيس عون من حاكم مصرف لبنان كريم سعيد على نتائج لقاءاته الأخيرة التي عقدها في بانكوك على هامش الاجتماعات السنوية لصندوق النقد الدولي.
+وشملت هذه اللقاءات مسؤولين رفيعي المستوى في كلّ من صندوق النقد الدولي، وصندوق النقد العربي، والاحتياطي الفيدرالي الأميركي، بالإضافة إلى عدد من حكّام المصارف المركزية في الدول العربية.
+كما عرض الحاكم سعيد لرئيس الجمهورية آخر التطورات النقدية والمالية في لبنان، والإجراءات التي يتخذها مصرف لبنان للحفاظ على الاستقرار النقدي . كذلك أطلع الحاكم رئيس الجمهورية على زيارته المرتقبة إلى فرنسا، حيث سيجري مشاورات مع كبار المسؤولين في السلطات المالية الفرنسية، ويشارك في مباحثات رفيعة المستوى مرتبطة بمجموعة الدول السبع G7 تتناول مكافحة تبييض الأموال وتمويل الإرهاب. وجدّد رئيس الجمهورية، خلال اللقاء، تأكيد أهمية صون الاستقرار النقدي والمضي قدماً في إصلاح القطاع المصرفي، وحماية حقوق المودعين</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:47.655702+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض العلاقات اللبنانية-الكويتية والأوضاع في لبنان والمنطقة مع سفير الكويت</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1582</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض العلاقات اللبنانية-الكويتية والأوضاع في لبنان والمنطقة مع سفير الكويت
+عرض رئيس الجمهورية مع سفير الكويت في لبنان محمد سلطان الشرجي العلاقات اللبنانية -الكويتية وسبل تطويرها في المجالات كافة ، كما تناول البحث الأوضاع في لبنان والمنطقة في ضوء التطورات الأخيرة . وشكر الرئيس عون الكويت اميراً وحكومة وشعباً على الدعم الذي قدمته ولا تزال للبنان متمنيا لها وللشعب الكويتي الشقيق الخير والتقدم والاستقرار.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:49.838619+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من الامين العام لمؤتمر لاهاي للقانون الدولي على نطاق عمل المؤتمر واهمية انضمام لبنان اليه</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1581</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من الامين العام لمؤتمر لاهاي للقانون الدولي على نطاق عمل المؤتمر واهمية انضمام لبنان اليه
+استقبل الرئيس عون قبل ظهر اليوم في قصر بعبدا في حضور وزير العدل عادل نصار، والسفير الهولندي في لبنان Frank Mollen، الامين العام لمؤتمر لاهاي للقانون الدولي الخاص السيد Christophe Bernasconi الذي عرض نطاق عمل المؤتمر وعضوية العديد من الدول العربية والمتوسطية فيه، داعياً لبنان إلى الانضمام اليه نظراً لاهمية التعاون في نطاق تطبيق قواعد القانون الدولي الخاص وتسهيل المعاملات والإجراءات. وقد أبدى رئيس الجمهورية استعداد لبنان للتعاون في هذا المجال وتشجيعه المضي في هذا السياق. وحضر اللقاء رئيس مؤسسة IHOPE الدكتور احمد الايوبي.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:52.107661+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية في رسالة الى غوتيريش بمناسبة يوم الامم المتحدة:</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1580</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية في رسالة الى غوتيريش بمناسبة يوم الامم المتحدة:
+لبنان يثمّن الدور الذي تضطلع به المنظمة الدولية في دعم الاستقرار والسلام
+ويتمسّك بالشرعية الدولية وبمبادئ الميثاق
+أكد رئيس الجمهورية العماد جوزاف عون في رسالة تهنئة وجهها الى الامين العام للامم المتحدة انطونيو غوتيريش بمناسبة يوم الامم المتحدة الذي يصادف غداً، أن لبنان يثمّن الدور الذي تضطلع به الأمم المتحدة في دعم الاستقرار والسلام ويتمسّك بالشرعية الدولية وبمبادئ الميثاق، ويحرص على مواصلة التعاون مع المنظمة الدولية في مواجهة التحديات المشتركة. وجاء في الرسالة:
+" معالي السيد أنطونيو غوتيريش المحترم
+الأمين العام للأمم المتحدة
+بمناسبة يوم الأمم المتحدة، يسرني أن أتوجه إليكم، ومن خلالكم إلى أسرة الأمم المتحدة كافة، بأصدق التهاني وأطيب التمنيات.
+إن هذه المناسبة تشكل محطة سنوية لتجديد الالتزام بالمبادئ والقيم التي قام عليها ميثاق الأمم المتحدة، وفي مقدمها صون السلم والأمن الدوليين، واحترام سيادة الدول، وتعزيز التعاون بين الشعوب والدول، والعمل من أجل عالم أكثر عدلاً واستقراراً.
+وإذ يثمّن لبنان الدور الذي تضطلع به الأمم المتحدة في دعم الاستقرار والسلام، أؤكد تمسّك لبنان بالشرعية الدولية وبمبادئ الميثاق، وحرصه على مواصلة التعاون مع المنظمة الدولية في مواجهة التحديات المشتركة.
+أغتنم هذه المناسبة لأعرب لكم عن تقديري للجهود التي تبذلونها في سبيل تعزيز السلام والتعاون الدولي، متمنياً لكم دوام النجاح، وللأمم المتحدة وأسرة العمل الدولي مزيداً من القدرة على تحقيق أهدافها السامية.
+وتفضلوا، معالي الأمين العام، بقبول فائق الاحترام والتقدير."</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:54.328223+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>مجلس الوزراء شدد على ضرورة السير بالتحقيق في موضوع المتفجرات تحت سقف القانون وقرر متابعة البحث في طلب وزارة العدل إحالة القضية الى المجلس العدلي</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1579</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>مجلس الوزراء شدد على ضرورة السير بالتحقيق في موضوع المتفجرات تحت سقف القانون وقرر متابعة البحث في طلب وزارة العدل إحالة القضية الى المجلس العدلي
+المجلس وافق على التعاقد مع أساتذة في الجامعة اللنبانية على اربع دفعات
+وتمديد العقد مع شركة "لافاجيت" لكنس وتنظيف الطرقات
+مجلس الوزراء عيّن أعضاء مجلس إدارة مصلحة سكك الحديد والنقل المشترك
+الرئيس عون اثنى على كلام الرئيس بري حول اعتبار الجيش "خط احمر"
+والحفاظ على السلم الأهلي والانفتاح على الحوار كأفضل وسيلة لحماية لبنان وانقاذه
+رئيس الجمهورية دعا اللبنانيين التعامل بحكمة ووعي وروية مع التطورات التي تشهدها المنطقة
+لابعاد لبنان عن أي تداعيات سلبية قد تحصل جراء هذه التطورات والتحديات
+الرئيس سلام: حصرية السلاح بيد الدولة هي في أساس قيامها ودستورها وقوانينها
+والجهات المجاز لها حمل السلاح مذكورة في إعلان وقف العمليات العدائية
+رئيس الحكومة: سأدعو إلى جلسة لمجلس الوزراء خلال الأسبوعين المقبلين
+تخصَّص حصراً لموضوع الكهرباء وجلسة ثانية لحل أزمة النفايات
+قرر مجلس الوزراء في جلسته التي عقدها بعد ظهر اليوم في قصر بعبدا، برئاسة رئيس الجمهورية العماد جوزاف عون وحضور رئيس مجلس الوزراء الدكتور نواف سلام والوزراء، السير بالتحقيق في ملف المتفجرات دون أي قيد او سقف الا سقف القانون، ومتابعة البحث في طلب وزارة العدل إحالة القضية الى المجلس العدلي، في ضوء تقدم مراحل التحقيق.
+وقرر المجلس أيضا تمديد العقد مع شركة "لافاجيت" لكنس وتنظيف الطرقات، وجمع النفايات وترحيلها من مدن اتحاد بلديات الفيحاء، لحين الانتهاء من عملية اجراء المناقصة، وتسلم الملتزم الاعمال، وذلك ضمن مهلة زمنية لا تتعدى نهاية العام الجاري.
+وتمت ايضاً الموافقة على التعاقد مع أساتذة في الجامعة اللبنانية يتم اختيارهم من بين الأسماء المرفوعة سابقاً والذين تتوفر فيهم المعايير التي اقرّها مجلس الوزراء ، وموزعين على ثلاث دفعات متتالية تضم (٤٥٢) اسماً في الدفعة الاولى و (٤٥٢) اسماً في الدفعة الثانية (٤٥٣) اسماً في الدفعة الثالثة، والموافقة على اللائحة المرفوعة من الجامعة اللبنانية الدفعة الرابعة على أن تكون هذه الموافقة مشروطة باستكمال العدد المطلوب، بما لا يتجاوز (٥۳۷) اسماً.
+وعيّن المجلس أعضاء مجلس إدارة مصلحة سكك الحديد والنقل المشترك.
+وكان الرئيس عون قد جدد خلال الجلسة، التهنئة للأجهزة الأمنية على جهودها لضبط الامن في مختلف المناطق وعلى كل الأصعدة، مؤكداً الوقوف الى جانبها، واصفاً إياها بالعمود الفقري للدولة.
+واثنى رئيس الجمهورية على كلام رئيس مجلس النواب الأستاذ نبيه بري لجهة اعتبار الجيش اللنباني "خط احمر" ودعوته الى الحفاظ على السلم الأهلي والانفتاح على الحوار، معتبراً انها الوسيلة الأفضل لجماية لبنان وانقاذه. كما دعا اللبنانيين الى التحلي بالحكمة والوعي والروية في التعامل مع التحديات التي تواجهها المنطقة والتي تهدد بمسار تصعيدي، وذلك لتجنيب لبنان أي تداعيات سلبية.
+من جهته، أعاد الرئيس سلام التأكيد على ثوابت الدولة في حصرية السلاح وقرار الحرب والسلم، مشدداً على ضرورة ملاحقة المخالفين للقوانين، وذلك في أعقاب قضية شاحنة ضهر البيدر وضبط المتفجرات.
+وأعلن من جهة أخرى عن إحراز تقدّم في المباحثات مع دولة قطر لمعالجة أزمة الكهرباء، من دون أعباء استثمارية مسبقة على الخزينة، وكشف عن عقد جلستين لمجلس الوزراء خلال الأسبوعين المقبلين، تُخصَّص الأولى لملف الكهرباء والثانية لمعالجة أزمة النفايات، مع إعطاء الأولوية للمعالجة العاجلة للوضع في طرابلس.
+وسبق الجلسة لقاء بين الرئيسين عون وسلام، عرضا خلاله المواضيع المدرجة على جدول الاعمال.
+الرئيس عون
+في بداية الجلسة، تحدث الرئيس عون فأشاد بالخطوات التي يتخذها وزير الصحة في ما يتعلق بمسألة مكافحة الادوية الفاسدة والمهرّبة، كما هنأه على انتخابه رئيساً للدورة الثالثة والسبعين لمنظمة الصحة العالمية لشرق المتوسط (EMRO)، واعتبر ان التهنئة تتخطى الوزير لتصل الى لبنان ككل. كما أشاد بالاجهزة الأمنية وما تقوم به من جهود لضبط الامن في مختلف المناطق وعلى كل الأصعدة (مكافحة الإرهاب والمخدرات، تهريب الأسلحة، مكافحة الجرائم...)، وذلك على الرغم من الدور الاقتصادي الضاغط الذي تمرّ به، وقال: لا يسعنا الا ان نقف الى جانبها، فهي العمود الفقري للدولة، وركيزتها الأساسية.
+وثمّن فخامة الرئيس موقف دولة رئيس مجلس النواب نبيه بري، خصوصاً لجهة اعتبار الجيش اللبناني بمثابة خط احمر، والحفاظ على السلم الأهلي، والانفتاح على الحوار والتفاهم، كونها الوسيلة الأفضل لحماية لبنان وانقاذه.
+وأوضح فخامة الرئيس ان التحديات التي تواجه المنطقة كبيرة جداً، وأمل الا يكون مسارها نحو التصعيد او الانفجار، داعياً الى ان يتحلى الافرقاء اللبنانيون بالحكمة والوعي والروية، لابعاد تأثير هذه التحديات على لبنان الذي يعاني اصلاً من تداعيات اقتصادية صعبة، وهذا يتطلب من الجميع- وزراء ومسؤولين سياسيين- التعامل بحكمة لتجنيب لبنان أي تداعيات سلبية قد تشهدها المنطقة. وجدد فخامة الرئيس تضامن لبنان مع المملكة العربية السعودية في وجه الاعتداءات التي تتعرض لها وكل ما يهدد سيادتها وامنها وامن مواطنيها، وأوضح ان هناك اتصالات معها لعودة الخطوط الجوية والاشقاء السعوديين الى لبنان. كما توجّه بالشكر الى دولة قطر على مساعيها لمساعدة لبنان في موضوع الطاقة، وتمنى ان يُدعى مجلس الوزراء لدراسة ملف الطاقة وملف البيئة على امل ان يتم حلهما في ولاية المجلس الحالي.
+ودعا وزير الاتصالات الى السير بقانون "ليبان تيليكوم" لتحرير قطاع الاتصالات وجعله اكثر فاعلية.
+ثم انتقل فخامة الرئيس الى الحديث عن الانتخابات الفرعية (المقعد الأرثوذكسي في البقاع الغربي)، معتبراً انه استحقاق دستوري يجب ان يتم، ولا يجب ان يبقى المقعد شاغراً بعد وفاة النائب غسان سكاف وتأجيل الانتخابات النيابية."
+الرئيس سلام
+ثم تحدث دولة الرئيس سلام، وقال:
+"ثلاثة أمور أود أن أتكلم فيها:
+1- مسألة شاحنة ضهر البيدر وما تبعها وسبقها من عمليات نقل وضبط للسلاح.
+2- زيارة رئيس وزراء قطر والمباحثات بشأن معالجة أزمة الكهرباء.
+3- قضية معالجة النفايات.
+في الموضوع الأول:
+باستقلال عن البند المطروح على جدول الأعمال بشأن مشروع إحالة مسألة شاحنة ضهر البيدر على المجلس العدلي، أرى أنه لا بد من التأكيد على الثوابت التالية التي لم تعد تقبل النقاش:
+أولا : إن حصرية السلاح بيد الدولة هي أصلاً في أساس قيام الدولة ودستورها وقوانينها، وبالذات قانون العقوبات وقانون الدفاع الوطني، فضلاً عن اتفاق الطائف والقرار 1701 وإعلان وقف العمليات العدائية في شهر تشرين الثاني 2024.
+ثانياً: إن الجهات المجاز لها حمل السلاح في لبنان هي حصراً الجيش اللبناني، قوى الأمن الداخلي، المديرية العامة للأمن العام، المديرية العامة لأمن الدولة، الجمارك اللبنانية، والشرطة البلدية. وهذا ما ورد في مقدمة إعلان وقف العمليات العدائية الذي ذكرته، والذي وافقت عليه الحكومة السابقة، وأعادت التأكيد عليه حكومتنا في بيانها الوزاري الذي نالت عليه ثقة مجلس النواب وقراراتها اللاحقة. وعبارة "حصراً" واردة في أصل النص وليست إضافة لاحقة من أي جهة.
+ثالثاً : لا شريك للدولة في قرار الحرب والسلم، وهذا في أساس دستور البلاد، وقد عدنا وأكدنا عليه في بياننا الوزاري وفي عدد من قرارات الحكومة، ولا ضرر من إعادة التأكيد عليه بعد كل ما تكبّده الشعب اللبناني من كلف نتيجة التفرّد في زجّ البلاد في حروب من خارج المؤسسات الدستورية.
+رابعاً : تنفيذاً لهذه المبادئ، ولا سيما حصرية السلاح بيد الدولة كنا قد طلبنا من الجيش إعداد خطة لوضعها موضع التنفيذ، وقد رحبنا بها في مجلس الوزراء في أيلول الماضي، وعدنا وأكدنا على ضرورة استكمال تطبيقها في كل المناطق اللبنانية في آذار من العام الحالي، ولا أحد، أياً كان له صفة أو صلاحية لإعادة النظر في ذلك غير مجلس الوزراء.
+خامساً : إن تخزين السلاح أو نقله من خارج الجهات التي لها حصراً شرعية القيام بذلك، تحت أي ذريعة كانت، لا يشكّل فقط خروجاً على هذه الثوابت والقوانين النافذة وقرارات مجلس الوزراء، بل يشكّل خطراً على السلامة العامة، ويهدّد أمن المواطنين، ويقتضي المتابعة الأمنية والملاحقة القضائية لإنزال اشد العقاب الذي تفرضه القوانين بحق المرتكبين. ولا أحد يمكن أن يفرض علينا سقفاً لذلك غير السقف الذي يحدّده القانون ولا شيء عندنا يمكن أن يعلو على سلامة البلاد وأمن المواطنين.
+سادسا : يقتضي التوضيح، قبل البتّ في البند الذي أُدرج على جدول الأعمال بناءً على طلب وزير العدل والمتعلق بإحالة قضية المتفجرات المضبوطة في منطقتَي ضهر البيدر والقصر إلى المجلس العدلي، أنني لم أرفق بجدول الاعمال نصّ مشروع المرسوم الذي وضعه بهذا الخصوص، كي لا يبدأ النقاش فيه خارج مجلس الوزراء وقبل انعقاده. لذلك، سأطلب من الأمين العام، عند طرح هذا البند أن يتلو المشروع عليكم."
+وأضاف دولة الرئيس: "في الموضوع الثاني: أفيدكم بأنني ومعالي وزير الطاقة قد أحرزنا تقدماً كبيراً في مباحثاتنا مع الجانب القطري بشأن العرض الإطاري المقدم إلينا لمعالجة وضع الكهرباء، وهو عرض متكامل لإعادة تأهيل البنية التحتية لإنتاج الكهرباء وتطويرها وتحديثها ، ويشمل مختلف مصادر إنتاج الكهرباء، ويقوم على نموذج التصميم والبناء والتشغيل ونقل الملكية، المعروف اختصاراً بـ ( BOT) والذي تتولى بموجبه الجهات القطرية التمويل والتنفيذ والتشغيل، من دون أن تتحمل الخزينة اللبنانية أي كلفة استثمارية مسبقة، مما سيوفر الكهرباء بشروط أكثر استقراراً وبكلفة أقل للمواطنين.
+ويقوم معالي الوزير وفريق وزارته الفني بمتابعة جميع الجوانب التقنية. وعندما تكتمل جميع عناصر هذا المشروع، سنقوم بعرضه على مجلس الوزراء لمناقشته واتخاذ القرار المناسب بشأنه.
+ولكن، لما كانت معالجة أزمة الكهرباء لا تتعلق بالإنتاج وحده، بل تقتضي التصدّي أيضاً لمسألتي التوزيع والجباية، فإنني سأدعو، بالاتفاق مع الوزير صدي، إلى عقد جلسة لمجلس الوزراء تُخصَّص حصراً لموضوع الكهرباء خلال الأسبوعين المقبلين."
+ثم قال دولة الرئيس: "في الموضوع الثالث: في ما يتعلّق بمسألة معالجة النفايات، وإن كان علينا التصدّي اليوم للمسائل العاجلة، وفي مقدّمها الوضع في طرابلس، الذي تابعته خلال الأسابيع الماضية مع الوزيرة الزين والوزير الحجار ومجلس الإنماء والإعمار والهيئة الوطنية لإدارة النفايات الصلبة والجهات المعنية في الشمال، فإن ذلك لا يعفينا من ضرورة البحث في مسألة معالجة النفايات بصورة شاملة، ومن مختلف جوانبها.
+ولذلك، فإنني سأدعو إلى عقد جلسة ثانية لمجلس الوزراء خلال أسبوعين المقبلين، تُخصص حصراً لهذا الموضوع، كما سبق ان اتفقنا."
+الوزير مرقص
+وبعد انتهاء الجلسة، تلا الوزير مرقص المقررات، وقال:
+"عقد مجلس الوزراء جلسته الاسبوعية في قصر بعبدا في برئاسة فخامة رئيس الجمهورية العماد جوزاف عون وحضور دولة رئيس مجلس الوزراء والسيدات والسادة الوزراء، بغياب وزراء: الثقافة، الدفاع، السياحة، الطاقة، والشؤون الاجتماعية.
+وكان هناك كلمة لفخامة الرئيس في مستهل الجلسة ثم كلمة لدولة الرئيس جرى توزيعها عليكم، وأيضا مداخلة لوزير المال شرح فيها الاجتماعات الدورية التي تجرى مع صندوق النقد الدولي، بالتعاون مع مصرف لبنان، وأيضا المشاورات الجارية مع البنك الدولي، حول موضوع عقد مؤتمر او ملتقى للتكامل الاقتصادي الإقليمي في أواخر هذا العام، او بداية السنة الجديدة.
+وقبل الدخول في جدول الاعمال، قرر مجلس الوزراء، بناء لطلب وزير الصحة، تجميد التداول بالادوية الشبيهة بالدواء الأصلي، من دول غير مرجعية، وشراء ادوية بديلة من دول مرجعية، او ادوية ال BRANDS.
+قرر مجلس الوزراء أيضا تمديد العقد مع شركة لافاجيت لكنس وتنظيف الطرقات، وجمع النفايات وترحيلها من مدن اتحاد بلديات الفيحاء، لحين الانتهاء من عملية اجراء المناقصة، وتسلم الملتزم الاعمال، وذلك ضمن مهلة زمنية لا تتعدى نهاية العام الجاري.
+في موضوع التعيينات، عيّن مجلس الوزراء أعضاء مجلس إدارة مصلحة سكك الحديد والنقل المشترك، وهم أعضاء غير متفرغين، السادة: جوزف عقيقي، وليد سعد، فادي مخلوطة، وموسى عواضة.
+اذكر ان هذا المجلس مهمته أساسية، في سبيل استكمال إزالة التعديات على سكك الحديد، وغداً من السراي، هناك اعلان لخطة تطوير النقل المشترك لتشمل مختلف الأراضي اللبنانية.
+وفي موضوع النفايات قرر مجلس الوزراء ما يلي:
+1. الموافقة على موضوع استقبال النفايات وطمرها في المطر الحالي، بصورة موقتة الى حين جهوزية خلية طمر جديدة. ونتكلم هنا عن العقار المحدد في المرسوم رقم 12623/1969، ثم نقل الكميات المطمورة موقتا اليها.
+2. الطلب من مجلس الانماء والاعمارالمباشرة بتدعيم المطمر الحالي واجراء التحسينات الهندسية اللازمة بما يسمح باستيعاب الكميات الإضافية، شرط التأكد من سلامة المنشآت والاستقرار فيها، وقدرتها الاستيعابية وفق الأصول الفنية المعتمدة.
+3. الطلب من الهيئة الوطنية لادارة النفايات الصلبة بالتعاون مع مجلس الانماء والاعمار، تطوير وصيانة معمل معالجة النفايات الصلبة التابع للاتحاد عبر الهبة المخصصة من الصندوق الكويتي للتنمية الاقتصادية عبر مجلس الانماء والاعمار، على ان يتم التشغيل وفق الأنظمة المرعية الاجراء.
+4. الموافقة على وضع العقارات المحددة بالمرسوم رقم 12623 المشار اليه، وارض المكب الأول بتصرف الهيئة الوطنية لادارة النفايات الصلبة بالتعاون مع مجلس الانماء والاعمار، وذلك للمياشرة بتنفيذ حل مستدام لمعالجة النفايات الصلبة مع التشديد على ضرورة التكثيف من الفرز وإعادة التدوير بهدف الوصول الى طمر العوادم فقط بعد المباشرة بتجديد معمل المعالجة.
+5. تشكيل لجنة متابعة لملف النفايات برئاسة دولة الرئيس وعضوية كل من وزير الداخلية والبلديات، وزير المال، وزيرة البيئة، وزير الطاقة والمياه، وزير الصناعة، وزير الزراعة، رئيس مجلس الانماء والاعمار، ورئيس الهيئة الوطنية لادارة النفايات الصلبة. وتم الموافقة على عقد جلسة لمجلس الوزراء الخميس المقبل بتاريخ 29 الحالي، تخصص لقطاع النفايات بحضور رئيس مجلس الانماء والاعمار، ورئيس الهيئة الوطنية لادارة النفايات الصلبة.
+بالعودة الى جدول الاعمال، تم إقرار معظم البنود ومنها:
+- طلب وزارة المال الموافقة على قطع حساب الموازنة العامة لعام 2022
+- عرض وزارة الطاقة والمياه بموضوع التوقيف الجنائي في بوارج انتاج الطاقة الكهربائية لكهرباء لبنان، وصفقات الفيول المرتبطة بها. وهنا تم التأكيد على استكمال إجراءات فض العروض، وعلى التدقيق الجنائي.
+- أيضا بناء على طلب وزارة الطاقة والمياه، تمت الموافقة على تحميل الخزينة العامة جميع المبالغ التي صدر بشأنها قوانين، وصدر قانون آخر باعفاءات من مستحقات لصالح مؤسسة كهرباء لبنان، ومؤسسات المياه، لكن التفاصيل ستكون في مشروع قانون يصاغ في ما بين وزارة المال ووزارة الطاقة والمياه تأكيدا وتفصيلا لما سبق.
+- في موضوع المتفجرات المضبوطة، وبعدما اطلع المجلس على تفاصيل القضية من معالي وزير العدل، وبعدما اعتبر ان هذه القضية من الخطورة بمكان لأنها تهدد امن البلاد وسلامة المواطنين، شدد على ضرورة السير بالتحقيق دون أي قيد او سقف الا سقف القانون. كما قرر متابعة البحث في طلب وزارة العدل إحالة القضية الى المجلس العدلي، كل ذلك في ضوء تقدم مراحل التحقيق.
+- في موضوع تفرغ أساتذة الجامعة اللبنانية، ساعطي المجال لمعالي وزيرة التربية ان تجيب على الأسئلة المختصة بهذا الموضوع، لكن سأتلو عليكم قرار مجلس الوزراء تسهيلا لفهم ما هو هذا القرار اولاً:
+"قرر المجلس الموافقة على ما يأتي:
+اولاً: التأكيد على اعتماد المعايير الأكاديمية والموضوعية القائمة على توافر عقود تعاقد قانونية، والتثبت من حاجات الكليات والتحقق من نصاب ساعات عقود التعليم في السنتين الأخيرتين، والقواعد المجتمعة التي أقرها مجلس الوزراء في قراريه رقم ۱۱ تاريخ 6/2/2026 و ۱۷ تاريخ 16/2/2026، والمتمثلة بالأقدمية وحاجات الكليات والاختصاص والكفاءة ومتطلبات الإنصاف، على أن تستوفي كلّ دفعة بذاتها هذه القواعد مجتمعةً.
+ثانياً: ونظراً للحاجة الملحة لتغطية النقص الناتج عن الإحالة على التقاعد ، الموافقة على التعاقد مع أساتذة يتم اختيارهم من بين الأسماء المرفوعة سابقاً والذين تتوفر فيهم المعايير التي اقرّها مجلس الوزراء ، وموزعين على ثلاث دفعات متتالية تضم (٤٥٢) اسماً في الدفعة الاولى و (٤٥٢) اسماً في الدفعة الثانية (٤٥٣) اسماً في الدفعة الثالثة.
+ثالثاً : الموافقة على اللائحة المرفوعة من الجامعة اللبنانية الدفعة الرابعة على أن تكون هذه الموافقة مشروطة باستكمال العدد المطلوب، بما لا يتجاوز (٥۳۷) اسماً، وبما يُحقق مبدأ الإنصاف وحاجات الكليات والاختصاصات، وإعادة عرض اللائحة على مجلس الوزراء لإتخاذ القرار النهائي بشأنها كاملةً ودفعةً واحدة، وذلك بمهلة أقصاها 1/4/2027. وفي هذا الخصوص، وفي سبيل استكمال لائحة الدفعة الرابعة، يُعطى رئيس الجامعة صلاحية اختيار الأسماء من بين الأساتذة المتعاقدين مع الجامعة أو من أساتذة جُدُد من ذوي الكفاءة يجري التعاقد معهم وفقاً للأصول في وفقاً للأصول في الاختصاصات التي تحتاجها الجامعة، ويُكلف رئيس الجامعة، بالتشاور مع مجلس الجامعة، بتحديد شروط أهليتهم للتفرغ.
+رابعا: يعدل تنفيذا لمضمون ما ورد أعلاه، العدد الإجمالي المقرر في القرار رقم 11 تاريخ 6/2/2026، ليصبح حدا اقصى 1894 اسماً، ضمن الاعتمادات التي ترصد لهذه الغاية في موازنات الأعوام 2027 و 2028 و 2029 و 2030.
+خامسا: التأكيد على وجوب تصفية حقوق جميع الموظفين في القطاع العام المشمولين بالتفرغ، وذلك قبل إقرار تفرغهم في الجامعة.
+حوار
+ثم دار بين الوزير مرقص والصحافيين الحوار التالي:
+سئل: هل سيتم إعادة البحث باحالة قضية المتفجرات، ام سيتم طي الملف؟
+أجاب: لم يتم طي هذا الملف مطلقاً. القرار واضح لجهة تأكيد خطورة هذا الامر ومتابعة مجلس الوزراء له والعودة الى المجلس.
+سئل: ماذا عن المفاوضات الأمنية والعسكرية التي حصلت امس بين لبنان وإسرائيل؟
+أجاب: لم يتم التطرق اليوم الى هذا الموضوع.
+سئل: الى ماذا استند مجلس الوزراء في قراره تأجيل البت بإحالة ملف المتفجرات الى المجلس العدلي؟
+احاب: ليس هناك من تأجيل. قرأت القرار كما صدر وسينشر بصيغته الرسمية بعد ان يطبع، ونحن تحدثنا عن فحواه. وهذا القرار هو نتيجة نقاش عارم بين الوزراء حول الجدوى والبحث في الايحابيات والسلبيات، وهناك حديث عن ان المجلس العدلي ليس بالضرورة اسرع من المحاكم العادية، وهناك امثلة عن قضايا بقيت لسنوات في المجلس العدلي، وهذا ليس استبعاداً لاحالة الملف اليه، بل مجرد امثلة وجو المناقشات التي سادت في المجلس. والاهم ان التحقيق لا يزال مستمراً للوصول الى نتيجة، وهناك توقيفات ومتابعة لعمل النيابة العامة التي تقوم بدورها مع مفوض الحكومة والأجهزة الأمنية.
+تم أيضا طرح الإشكاليات القانونية، بأبعادها المختلفة، حول ما اذا كان من الصحيح قانوناً اكتمال الإجراءات ورفع دعوى كما ينص عليه نص المادة 355 وما يليها من أصول المحاكمات الجزائية، خصوصاً وانه ليس هناك من ملف مكتمل، وفق المحادثات التي دارت في الجلسة، بل تم درس عنصر الملاءمة ولم يتم استبعاد الإحالة الى المجلس العدلي، بل متابعة فحوى القرار الذي قرأت ابرز ما تضمنه.
+سئل: الى اين ستصل التحقيقات في الملف اذا اعلن فريق ان المتفجرات تابعة له وان وجهة استعمالها هي لمحاربة إسرائيل. وكيف للدولة التي لا تستطيع ان تحارب إسرائيل منع من يحاول محاربتها؟
+أجاب: لا ارغب في تكرار القرار بموضونه الواضح والنقاش الذي دار، ولكن القضية ستبقى موضع متابعة من مجلس الوزراء نظراً الى خطورتها.
+سئل: منذ حوالى أسبوعين، حصلت عملية اختطاف في المنصورية، واصابع الاتهام اتجهت للمخابرات السورية والتركية. هل تطرقتم في الجلسة الى هذا الموضوع، وهل هناك من إجراءات في هذا الخصوص؟
+أجاب: تحدثنا في السياق الأمني العام، ولكننا لم نتحدث في تفاصيل القضايا، وكلنا ثقة بالاجهزة القضائية والأمنية.
+الوزيرة كرامي
+ثم اجابت الوزيرة كرامي على أسئلة الصحافيين:
+سئلت: في ما خص الأسماء، تم حجز الاعداد، فمتى تصدر الاسماء، وماذا عن التوازن الطائفي الذي لم يكن مؤمّناً في الجلسات السابقة؟
+اجابت: احدى الحوافز كما ذكر معالي الوزير، هي التزامنا بثلاثة معايير، واحداها هو معيار الانصاف او كما تسمونها "توازن". اليوم تطرقنا الى هذا الموضوع لتحسين النسب التي نرغب في الوصول اليها وان ترضي الجميع.
+الهدف الأساسي هو الاقتراب قدر المستطاع من النسب الحالية، أي عدم اعتماد طريقة لتغيير النسب الموجودة ضمن الجامعة اللبنانية حالياً، وهذا الطرح يحقق هذا الامر. اريد ان أؤكد للجميع، ان مجلس الجامعة أي الوزارة والجامعة اللبنانية، حددنا الأسماء في الأصل ضمن المعايير، وهي عملية طويلة تابعتموها، ولم تتم ازالة أي من الأسماء الموجودة سابقاً او تغييرها، بل تمكنا من الحصول على موافقة من وزارة المالية لزيادة العدد، أي انه كان من المقرر في السنوات الثلاث الأولى تقديم 400 في كل سنة، اليوم رفعنا العدد الى 450 ليصبح 1350 بدلاً من 1200، يلبي التوازن والمعايير الثلاثة. والدفعة الرابعة من الأسماء الموجودة اصلاً، سيضاف عددها للوصول الى التوازن، مع امكان فتح المجال للجامعة لاقتراح أسماء تستوفي بقية المعايير وهذا ما استغرق وقتاً. وكأننا جزأنا هذه العملية الى مرحلتين.
+سئلت: هل تغيّر التاريخ المحدد؟
+اجابت: لم يتغيّر، اول دفعة ستكون في 1/1/2027، وتمت الموافقة عليها ورصد الاعتمادات اللازمة لها. اما الدفعات الثلاث المتبقية سيتم وضع الأسماء في الجلسة المقبلة ويعلن عنها، وتبقى الدفعة الرابعة التي سيعلن عن اسمائها كاملة في شهر آذار.
+سئلت: هل حصلت ضغوط سياسية لاضافة او استبعاد أسماء؟
+اجابت: اعتدنا على ان يكون المعيار الأساسي في ملف التفرغ هو التوازن، وهو كان سبب عرقلة هذا الملف في السابق، كما ان الطريقة التي تمت فيها محاولات احقاق هذا التوازن في السابق كانت عشوائية. اما خلال هذه الفترة، فالتزمنا بالمعايير التي وضعها مجلس الوزراء، وهي تراعي حاجات كل كلية، وحقوق الأساتذة وفق اقدمية العقود، بحيث ان الدفعة الأولى تشمل الأكثر حاجة والاقدم في التعاقد، وذلك لانصاف الأساتذة وتقدير خدماتهم للجامعة. وهذا العمل تم بدقة كبيرة، وسأتحفظ عن استخدام كلمة ضغوط، لانه كان هناك تمنّ من مكونات المجتمع اللبناني لعدم كسر التوازن الذي كان سائداً في المرة الأخيرة التي حصل فيها التفرغ، وهذا ما دفعنا الى محاولة أخيرة انتهينا منها، وتم طرحها في مجلس الوزراء بروح الاجماع والجهوزية من قبل الجميع ان الملف وصل الى خواتيمه ولم يتبق سوى رفع الأسماء من مجلس الجامعة ضمن المعايير.
+سئلت: هل صحيح انه تم تعديل الأسماء من دون الرجوع الى مجلس الجامعة؟
+اجابت: كلا. آلية الأسماء بدأت بإعلان من الجامعة لجميع الأساتذة الذين يلبون المعايير ويملكون رغبة في التفرغ، وهذا ما حصل منذ اكثر من عام، وتم تقديم الطلبات في الجامعة ورفعها الى مجلس الجامعة أي وزيرة التربية ورئيس الجامعة، وتم درسها منذ فترة طويلة لان بعضها لا يستوفي الشروط، وتم درس الاختصاص والتطابق، وقررنا قبل العدوان، انه من الناحية المالية، لا يمكن رفع الملف بأكمله، فتم رفعه تدريجياً وفق الحاجات الملحة للجامعة والاقدمية، وأؤكد ان كل الأسماء الموجودة على القوائم قبل 2 آذار لا تزال موجودة، ولكن الدفعة الرابعة هي التي ستشهد اضافات.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:02:56.648030+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>لقاءات نيابية ودبلوماسية في قصر بعبدا</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1578</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>لقاءات نيابية ودبلوماسية في قصر بعبدا
+الرئيس عون اطلع من وزير الاقتصاد على مسار قانون حماية المستهلك وزيارة بانكوك
+الوزير البساط: حملة المولدات مستمرة وقانون حماية المستهلك سيعطينا بعد اقراره أدوات قوية للامساك بالاقتصاد والتخفيف من الجشع ومن اقتصاد الحرب
+الرئيس عون عرض مع النائب سامي الجميل للأوضاع العامة في البلاد
+ومع النائب اديب عبد المسيح لحاجات منطقة الكورة خصوصا والشمال عموما
+في قصر بعبدا الوزير السابق ايلي سالم وسفير لبنان في الصين
+شهد قصر بعبدا قبل ظهر اليوم لقاءات وزارية ونيابية ودبلوماسية.
+وزاريا، اطلع رئيس الجمهورية العماد جوزاف عون من وزير الاقتصاد الدكتور عامر البساط على مسار قانون حماية المستهلك بعدما اعاده الرئيس عون الى المجلس النيابي لاعادة النظر به، واطلع منه على نتائج زيارة بانكوك.
+تصريح الوزير البساط
+وبعد اللقاء، صرح الوزير البساط الى الصحافيين فقال: "تشرفت بالاجتماع برئيس الجمهورية، وسبب زيارتي اليوم هو قانون حماية المستهلك الذي اقر في البرلمان ونقوم بمراجعته، وقد اكد الرئيس عون على أهميته. ففي النهاية، هناك مشكلة واضحة ونعلمها جميعا، وهي مشكلة كبيرة في لبنان تتمثل في الغلاء والاحتكار والجشع واقتصاد الحرب أيضا. ان الادوات القانونية الموجودة بين ايدينا يجب تقويتها. وهذا القانون، ان شاء الله يمر في غضون أسابيع، ونحن نعمل في البرلمان لنتمكن من تمريره في هذه الفترة، سيعطينا أدوات قوية جدا من خلال رفع الغرامة وتسريع الأمور كما تسريع الاجراءات القضائية، كي نتمكن من الامساك بالاقتصاد والتخفيف من الجشع ومن اقتصاد الحرب".
+أضاف:" هناك أناس كثيرون اضيموا في البلد. لكن هناك لسوء الحظ مشاكل موجودة نراها في الموتورات والسوبرماركت والامن الغذائي. وهذا القانون مهم جدا، ويهمنا ان يمر في اسرع وقت كي نتمكن ومراقبونا الذين يقومون بعمل جبار من القيام بعملنا. فمنذ بداية العام حتى الان جرى 19400 كشف ميداني على الأرض من قبل مراقبي حمياة المستهلك الذين ردوا على 1200 شكوى تصلنا تقريبا يوميا. ونحن لدينا التزام بان كل مواطن مراقب فننزل على الأرض. لقد سطرنا اكثر من الف محضر قضائي، ونلجأ الى القضاء والمدعي العام التمييزي والمدعي العام المالي. ان هذا القانون، اعود وأكرر، ان شاء الله يقر بسرعة، سيعطينا أدوات مهمة جدا كي نتمكن من تقوية الحملات المطلوبة ".
+وتابع:"هناك موضوع آخر كان لي شرف التطرق اليه مع فخامة الرئيس بعد عودتي من بانكوك ووزير المالية وحاكم مصرف لبنان حيث تكلمنا مع البنك الدولي وصندوق النقد الدولي. وقد وضعت الرئيس عون في ملخص ما حدث. ان الصدى إيجابي، ومن دون شك، ان شركاءنا الدوليين مهتمون ويشهدون للتطورات والإصلاحات التي نقوم بها، ومن الواضح انهم يريدون العمل معا كي نتمكن من الوصول الى بر الأمان من خلال اتفاقية مع صندوق النقد التي لا زلنا ملتزمين بها".
+وقال: "كما تعرفون ستأتي بعثة في 12 و13 تشرين الثاني المقبل كي تتحدث بالمواضيع ذات الصلة بما فيها قانون الفجوة المالية. وهناك اتفاق داخلي صار واضحا على الاطار العام لهذا القانون. والسؤال اليوم يتعلق بالتفاصيل التقنية. وان شاء الله، وبعد إقرار الموازنة التي سيدرسها البرلمان حتى شهر نوفمبر، يقوم بالعمل بكل جدية على موضوع الفجوة المالية فنتمكن من الوصول الى النهاية مع بداية العام المقبل اذا ما سارت الأمور بشكل جيد."
+سئل: ما هي تطورات موضوع المولدات؟
+أجاب: هذا يشكل جزءا مهما جدا مما نقوم به يوميا. ان المبادرة مستمرة وساتكلم عنها بالتفصيل الأسبوع المقبل. بدأت في بيروت، من ثم جبل لبنان وبعد ذلك في الضاحية الجنوبية، والان في عاليه وبشامون وطرابلس حيث كان هناك عمل كبير جدا وفي البقاع والجنوب. انجزنا حوالي 800 كشف، وقمنا ب64 مصادرة وهذا شيء مهم جدا. والاطار الذي عملنا عليه هو الاتي: توثق وزارة الاقتصاد المخالفة، وهناك مخالفات كثيرة، ثم تذهب بمؤازرة القوى الأمنية خاصة امن الدولة الذي يؤازرنا ويعمل معنا بشكل جدي، وعندما تكون المخالفة موثقة نرسلها الى المدعي العام التمييزي الذي يعطي إشارة بالمصادرة. وكي لا تتم مصادرة المولد وتتوقف تغذية الناس بالكهرباء، نسلمها الى البلدية . تمت 64 مصادرة في المناطق التي تحدثنا عنها وقامت البلديات بما عليها. وحتى الان لم تتوقف التغذية بالكهرباء ولم يشعر المواطنون بالفرق. اننا نأخذ تعهدا من صاحب المولد وهناك مراقبة دائمة عليه، والحملة مستمرة ولم نوقفها ابدا. وهناك معطيات لدينا بتحسن الالتزام. ان المشكلة كبيرة جدا وجميعنا يعلم ان وجع الناس في كلفة الكهرباء كبير جدا. قسم منها مستورد فلسوء الحظ تضاعف سعر المازوت، وارتفعت الكلفة، الا ان ذلك لا يفسر ابدا الجشع الحاصل وهنا تكمن أهمية المراقبة والحملة القائمة.
+النائب سامي الجميل
+نيابيا، عرض الرئيس عون مع رئيس حزب "الكتائب اللبنانية" النائب سامي الجميل الأوضاع العامة في لبنان والمنطقة والمواقف من التطورات السياسية الأخيرة.
+النائب اديب عبد المسيح
+كما عرض رئيس الجمهورية مع النائب اديب عبد المسيح مواضيع سياسية وانمائية وحاجات منطقة الكورة خصوصا والشمال عموما.
+الوزير السابق ايلي سالم
+كما اجرى الرئيس عون مع الوزير السابق ايلي سالم جولة افق تناولت الأوضاع المحلية والاقليمية في ضوء التطورات الراهنة.
+سفير لبنان في الصين
+دبلوماسيا، عرض رئيس الجمهورية مع سفير لبنان في الصين ميلاد رعد العلاقات اللبنانية - الصينية وسبل تطويرها في مختلف المجالات.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:01.233088+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل سفير لبنان في الصين</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1577</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:03.434160+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل الوزير السابق ايلي سالم</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1576</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:05.647689+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>الرئيس عون عرض مع النائب اديب عبد المسيح لحاجات منطقة الكورة خصوصا والشمال عموما</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1575</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:07.919074+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>الرئيس عون عرض مع النائب سامي الجميل للأوضاع العامة في البلاد</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1574</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:10.122071+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من وزير الاقتصاد على مسار قانون حماية المستهلك وزيارة بانكوك</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1573</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من وزير الاقتصاد على مسار قانون حماية المستهلك وزيارة بانكوك
+الوزير البساط: حملة المولدات مستمرة وقانون حماية المستهلك سيعطينا بعد اقراره
+أدوات قوية للامساك بالاقتصاد والتخفيف من الجشع ومن اقتصاد الحرب
+اطلع رئيس الجمهورية العماد جوزاف عون من وزير الاقتصاد الدكتور عامر البساط على مسار قانون حماية المستهلك بعدما اعاده الرئيس عون الى المجلس النيابي لاعادة النظر به، واطلع منه على نتائج زيارة بانكوك.
+تصريح الوزير البساط
+وبعد اللقاء، صرح الوزير البساط الى الصحافيين فقال: "تشرفت بالاجتماع برئيس الجمهورية، وسبب زيارتي اليوم هو قانون حماية المستهلك الذي اقر في البرلمان ونقوم بمراجعته، وقد اكد الرئيس عون على أهميته. ففي النهاية، هناك مشكلة واضحة ونعلمها جميعا، وهي مشكلة كبيرة في لبنان تتمثل في الغلاء والاحتكار والجشع واقتصاد الحرب أيضا. ان الادوات القانونية الموجودة بين ايدينا يجب تقويتها. وهذا القانون، ان شاء الله يمر في غضون أسابيع، ونحن نعمل في البرلمان لنتمكن من تمريره في هذه الفترة، سيعطينا أدوات قوية جدا من خلال رفع الغرامة وتسريع الأمور كما تسريع الاجراءات القضائية، كي نتمكن من الامساك بالاقتصاد والتخفيف من الجشع ومن اقتصاد الحرب".
+أضاف:" هناك أناس كثيرون اضيموا في البلد. لكن هناك لسوء الحظ مشاكل موجودة نراها في الموتورات والسوبرماركت والامن الغذائي. وهذا القانون مهم جدا، ويهمنا ان يمر في اسرع وقت كي نتمكن ومراقبونا الذين يقومون بعمل جبار من القيام بعملنا. فمنذ بداية العام حتى الان جرى 19400 كشف ميداني على الأرض من قبل مراقبي حماية المستهلك الذين ردوا على 1200 شكوى تصلنا تقريبا يوميا. ونحن لدينا التزام بان كل مواطن مراقب فننزل على الأرض. لقد سطرنا اكثر من الف محضر قضائي، ونلجأ الى القضاء والمدعي العام التمييزي والمدعي العام المالي. ان هذا القانون، اعود وأكرر، ان شاء الله يقر بسرعة، سيعطينا أدوات مهمة جدا كي نتمكن من تقوية الحملات المطلوبة ".
+وتابع:"هناك موضوع آخر كان لي شرف التطرق اليه مع فخامة الرئيس بعد عودتي من بانكوك ووزير المالية وحاكم مصرف لبنان حيث تكلمنا مع البنك الدولي وصندوق النقد الدولي. وقد وضعت الرئيس عون في ملخص ما حدث. ان الصدى إيجابي، ومن دون شك، ان شركاءنا الدوليين مهتمون ويشهدون للتطورات والإصلاحات التي نقوم بها، ومن الواضح انهم يريدون العمل معا كي نتمكن من الوصول الى بر الأمان من خلال اتفاقية مع صندوق النقد التي لا زلنا ملتزمين بها".
+وقال: "كما تعرفون ستأتي بعثة في 12 و13 تشرين الثاني المقبل كي تتحدث بالمواضيع ذات الصلة بما فيها قانون الفجوة المالية. وهناك اتفاق داخلي صار واضحا على الاطار العام لهذا القانون. والسؤال اليوم يتعلق بالتفاصيل التقنية. وان شاء الله، وبعد إقرار الموازنة التي سيدرسها البرلمان حتى شهر نوفمبر، يقوم بالعمل بكل جدية على موضوع الفجوة المالية فنتمكن من الوصول الى النهاية مع بداية العام المقبل اذا ما سارت الأمور بشكل جيد."
+سئل: ما هي تطورات موضوع المولدات؟
+أجاب: هذا يشكل جزءا مهما جدا مما نقوم به يوميا. ان المبادرة مستمرة وساتكلم عنها بالتفصيل الأسبوع المقبل. بدأت في بيروت، من ثم جبل لبنان وبعد ذلك في الضاحية الجنوبية، والان في عاليه وبشامون وطرابلس حيث كان هناك عمل كبير جدا وفي البقاع والجنوب. انجزنا حوالي 800 كشف، وقمنا ب64 مصادرة وهذا شيء مهم جدا. والاطار الذي عملنا عليه هو الاتي: توثق وزارة الاقتصاد المخالفة، وهناك مخالفات كثيرة، ثم تذهب بمؤازرة القوى الأمنية خاصة امن الدولة الذي يؤازرنا ويعمل معنا بشكل جدي، وعندما تكون المخالفة موثقة نرسلها الى المدعي العام التمييزي الذي يعطي إشارة بالمصادرة. وكي لا تتم مصادرة المولد وتتوقف تغذية الناس بالكهرباء، نسلمها الى البلدية . تمت 64 مصادرة في المناطق التي تحدثنا عنها وقامت البلديات بما عليها. وحتى الان لم تتوقف التغذية بالكهرباء ولم يشعر المواطنون بالفرق. اننا نأخذ تعهدا من صاحب المولد وهناك مراقبة دائمة عليه، والحملة مستمرة ولم نوقفها ابدا. وهناك معطيات لدينا بتحسن الالتزام. ان المشكلة كبيرة جدا وجميعنا يعلم ان وجع الناس في كلفة الكهرباء كبير جدا. قسم منها مستورد فلسوء الحظ تضاعف سعر المازوت، وارتفعت الكلفة، الا ان ذلك لا يفسر ابدا الجشع الحاصل وهنا تكمن أهمية المراقبة والحملة القائمة.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:12.314983+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>الرئيس عون في الذكرى 36 لاغتيال داني شمعون: علّمتنا سنوات الحرب أن لبنان لا يمكن أن يكون ساحة لحروب الآخرين أو صندوق بريد لصراعاتهم</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1572</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>الرئيس عون في الذكرى 36 لاغتيال داني شمعون: علّمتنا سنوات الحرب أن لبنان لا يمكن أن يكون ساحة لحروب الآخرين أو صندوق بريد لصراعاتهم
+عِبَر التجارب المريرة تفرض علينا التمسّك بوحدتنا
+وصون سيادة وطننا وحصر قرار الحرب والسلم في يد الدولة
+في الذكرى السادسة والثلاثين لاغتيال المهندس داني شمعون، قال رئيس الجمهورية العماد جوزاف عون:
+"في ذكرى اغتيال داني شمعون، نستحضر محطة أليمة من تاريخ لبنان، ونحيّي ذكرى رجل من رجالاته الذين تركوا بصمتهم في الحياة الوطنية. لقد علّمتنا سنوات الحرب أن لبنان لا يمكن أن يكون ساحة لحروب الآخرين أو صندوق بريد لصراعاتهم، وأن اللبنانيين هم الذين يدفعون الثمن من أرواحهم وأمنهم واستقرار وطنهم، فيما لا تحصد البلاد سوى الانقسام والدمار.
+إن العِبر التي استخلصناها من تلك التجارب المريرة تفرض علينا التمسّك بوحدتنا الوطنية، وصون سيادة لبنان واستقلال قراره، وحصر قرار الحرب والسلم في يد الدولة ومؤسساتها الشرعية، بما يحمي اللبنانيين جميعاً ويصون مستقبل الأجيال المقبلة.
+وفي هذه الذكرى، يبقى واجبنا أن نحوّل آلام الماضي إلى إرادة مشتركة لبناء دولة قوية وعادلة، تحتضن جميع أبنائها، وتحمي أرضها وشعبها، وتمنع تكرار المآسي التي دفع اللبنانيون أثمانها غالياً".</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:14.542519+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>لقاءات نيابية وانمائية تناولت ملفي الاتصالات والكهرباء في قصر بعبدا والرئيس عون استقبل البطريرك يازجي على رأس وفد من المطارنة</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1571</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>لقاءات نيابية وانمائية تناولت ملفي الاتصالات والكهرباء في قصر بعبدا والرئيس عون استقبل البطريرك يازجي على رأس وفد من المطارنة
+رئيس الجمهورية: انا رئيس جمهورية لبنان ولست رئيسا لاي مذهب او طائفة
+وواجباتي تحقيق مصلحة جميع الاطياف اللبنانية من دون استثناء
+الرئيس عون: القوة والشجاعة والحكمة لا تكمن في القدرة على شن الحروب فحسب
+بل في انهائها عبر اختيار الدبلوماسية
+البطريرك يازجي: نحن في زمن غير تقليدي احتاج منكم وبحكمة ودراية التصدر لقرارات غير تقليدية لتعبروا بلبنان وسط الغام السياسة الدولية التي انفجرت وتنفجر صراع محاور
+رئيس الجمهورية: للمضي قدما في استكمال انشاء شركة " ليبان تيليكوم" وانتقال موظفي "اوجيرو" اليها مع جميع الضمانات اللازمة بما يحفظ حقوق الموظفين ومستقبلهم
+الرئيس عون رأس اجتماعا لمجلس إدارة كهرباء لبنان
+مؤكدا دعمه لكل جهد إصلاحي جدي يساهم في إعادة النهوض بالمؤسسة
+الرئيس عون عرض الأوضاع العامة مع النائبين أبو فاعور وطرابلسي
+واطلع من مدير عام وزارة الصحة على شؤون الوزارة
+اكد رئيس الجمهورية العماد جوزاف عون انه رئيس جمهورية لبنان وليس رئيس جمهورية للموارنة او للمسلمين او لأي مذهب او طائفة، وان من واجباته تحقيق مصلحة جميع الاطياف اللبنانية من دون استثناء، مشددا على أهمية الوحدة الوطنية وعلى "ان الهدف الأساسي هو إعادة الثقة بين الشعب والدولة وبين لبنان المقيم والمغترب" والمضي قدما بالإصلاحات.
+واعتبر انه عندما يكون الجنوب جريحا فان الجرح يطال كل لبنان، مشددا على ان القوة والشجاعة والحكمة لا تكمن في القدرة على شن الحروب فحسب بل في انهائها عبر اختيار الدبلوماسية.
+مواقف الرئيس عون جاءت خلال استقباله قبل ظهر اليوم في قصر بعبدا، بطريرك أنطاكية وسائر المشرق للروم الأرثوذكس يوحنا العاشر يازجي على رأس وفد من آباء سينودوس كنيسة الروم الأرثوذكس.
+كلمة البطريرك يازجي
+في مستهل اللقاء، القى البطريرك يازجي كلمة قال فيها:
+" فخامة الرئيس.
+يطيب لي باسمي وباسم آباء المجمع الأنطاكي المقدس أن أحييكم وأحيي عبركم بلدنا لبنان الذي نحب ونعشق. إذا أردنا أن نترجم كلمة "سينودوس" إلى العربية، فهي تعني حرفيا الجماعة التي تسير معا في درب واحدة، وهذه حالنا اليوم في كنيستنا الأنطاكية. صوت واحد في معيّة واحدة وخطى واحدة بهدي نور المسيح لما فيه خير الإنسان ومجد الله.
+نتوجه إليكم فخامة الرئيس ونعول على حكمتكم في لم شمل اللبنانيين إلى معية واحدة أيضاً، وهي لبنان ولبنان أولاً وآخراً حتى آخر شبر من أراضيه وبكامل كرامته الوطنية التي تستمد قوتها من قوة إيمان شعبه بمؤسساته وعلى رأسها المؤسسة العسكرية التي كنتم على رأسها. نعول على حكمتكم في هذه الظروف الصعبة التي يتناطح فيها صوت العقل والتعقل الذي يرتجي حقن الدماء وإحلال العدل والحق مع صوت العنف والتدمير والاحتلال. ونثق بحكمتكم التي راهن ويراهن عليها جميع اللبنانيين في جمع كلمتهم والعبور بهم إلى وحدة صف واحد وسط ألغام هذا الشرق والعالم وما أكثرها!!"
+اضاف:" فخامة الرئيس، نحن في زمن غير تقليدي احتاج منكم وبحكمة ودراية التصدر لقرارات غير تقليدية لتعبروا بلبنان وسط الغام السياسة الدولية التي انفجرت وتنفجر صراع محاور.
+أنتم تعشقون كما نعشق لبنان البلد الرسالة والذي تعملون لتجنبوه أن يكون صندوق بريد لرسائل من هنا وهناك.على مر تاريخ هذا البلد، كانت الكنيسة الأنطاكية الأرثوذكسية جسر تواصل ولقيًا بين سائر المكونات يوم علت لغة المتاريس. ونحن ههنا لنكون معكم فخامة الرئيس في دوركم الذي وضعكم أمام مسؤوليتكم التاريخية جسر تواصل ولقيا بين سائر مكونات هذا الوطن لتقولوا وتفصلوا كلمة حق أمام الله والتاريخ.
+نقول هذا وتمتثل أمامنا ملفات ثقيلة منها وقف آلة الحرب التي تستهدف لبنان كله إذ تستهدف جنوبه أو أي جزء منه. ومنها أيضاً عودة المهجرين وتحقيق الانسحاب الاسرائيلي الكامل وإعادة البناء وتعزيز قوة الجيش ليكون ضامناً لسلطة الدولة، ناهيك عن الوضع الاقتصادي المترنح تحت أزمة المودعين في المصارف وتحت رحمة الصراعات الدولية، كما وملف العدالة المنتظرة لانفجار مرفأ بيروت وغيرها الكثير."
+وختم:"كمسيحيين مشرقيين، نرى في لبنان القائم على المناصفة رمزاً لحضورنا المسيحي في هذا الشرق. نحن باقون فيه بقاء الأرز في لبنان الذي ينمو صديق الله كأرزه مؤكدين على ضرورة مدّ اليد في لقيا مع إخوتنا المسلمين للنهوض بهذا البلد.
+كان الله بعونكم فخامة الرئيس، نحن هنا لنقول إن كنيسة أنطاكية في الوطن والانتشار تصلي من أجلكم ومن أجل كل شعب لبنان. عشتم وعاش لبنان".
+متروبوليت بيروت
+ثم تحدث متروبوليت بيروت وتوابعها المطران الياس عودة الذي قال: "نشكر ربنا على وجود فخامة الرئيس عون في سدة الرئاسة الذي يحاول ان يعطي صورة مختلفة عن لبنان، وعلى كل ذي ضمير حر ان يفرح بهذه الهدية" .
+اضاف:" نحن ابناء قرى، وعملنا في الحقول وزراعة العنب والزيتون ونعلم انه اذا لم نهتم بالنباتات بشكل جيد لن نحصل على انتاج جيد. ورجاؤنا اليوم معونة الرب ليساعد فخامة الرئيس على تحقيق اهدافه بكل محبة التي جوهرها وسندها الصبر والايمان، فنطلب منه ان لا يترك رئيسنا ليبقى لديه الرجاء للاستمرار في مهمته وتحقيق اهدافه".
+متروبوليت نيويورك واميركا الشمالية
+ثم اشار متروبوليت نيويورك وسائر اميركا الشمالية المطران سابا اسبر الى ان" كل فرد من هذه الكنيسة يحمل اوجاعنا وآلامنا وهو سفير حقيقي للبنان في البلد الموجود فيه" وقال:"نطلب من الرب العافية والقوة لتستمروا بهذا الطريق القويم الذي تسيرون به وتبذلون جهدا من اجل رفعة لبنان وتخليصه من كل الاعباء والارث الثقيل الذي تحملونه جراء الاوضاع الصعبة والحرب وتراكم سنوات من الفساد ".
+متروبوليت ساو باولو- البرازيل
+وتحدث متروبوليت ساو باولو المطران دامسكينوس منصور الذي اشار الى ان عدد اللبنانيين في البرازيل اكبر من عدد اللبنانيين الموجودين في لبنان ولهم الحق بأن يزورهم رئيس الجمهورية .وقال:"كل صلواتنا تبدأ وبشكل دائم بالدعاء لجميع حكام هذا البلد ومؤازرتهم في كل عمل صالح، ونحن نصلي ليمنحكم الرب القوة لتتابعوا المسيرة تجاه شعبكم. "
+متروبوليت صور وصيدا
+ثم القى متروبوليت صور وصيدا وتوابعهما المطران الياس كفوري كلمة فقال:" باسم ابنائكم في الجنوب اشكركم على الجهود التي تبذلونها من اجل مساعدتهم وهذا ليس غريبا عليكم، فأنتم ابن الجنوب ونصفكم من الشمال، وتخدمون جميع اللبنانيين ولكم بصمات في الجنوب والشعب يراها ويعرفها ونأمل أن يتحقق ما تعملون من اجله وهو وقف اطلاق النار ومساعدة العائلات التي تشردت بسبب الحرب."
+الرئيس عون
+وردّ الرئيس عون مرحبا بالوفد ومشددا على ان القوة والشجاعة والحكمة لا تكمن في القدرة على شن الحروب فحسب، بل في انهائها عبر اختيار الدبلوماسية، مشيراً الى ان مسار الحروب دائماً يختلف عما يتوقعه طرفاها وهي لا يمكن ان تنتهي إلا عبر التفاوض والحوار، في حين ان استمرارها يؤدي الى مزيد من الدمار والضحايا والدم.
+وتطرق الرئيس عون الى الاوضاع العامة في لبنان وخصوصا في الجنوب، لافتا الى ان "الهدف الاساسي من التفاوض هو تحقيق الانسحاب الاسرائيلي من الاراضي المحتلة وعودة النازحين وإعادة الاعمار وانتشار الجيش على كامل الأراضي اللبنانية، مشيراً الى أنه لا يوجد اختلاف في لبنان حول هذه الاهداف إنما الاختلاف يتمثل في اسلوب وطريقة تحقيقها. فهناك فئة متمسكة بالحرب وقد رأينا الى ما اوصلتنا اليه وما حققته هذه الحرب للبنان، وهناك فئة اخرى، اختارت التفاوض والحوار للوصول الى هذه الاهداف المنشودة."
+وجدد رئيس الجمهورية التأكيد على"ان ابن الجنوب ومنذ عام 1969 يدفع ثمن حروب الآخرين على ارضه، وقد يأس وتعب، ويحق له ان يعيش بأمان وكرامة بعيدا عن الحروب والدمار". وقال:"عندما يكون الجنوب مجروحا، فان الجرح يطال كل لبنان، والدولة هي المسؤولة عن مواطنيها، إلا أن الحروب التي فرضت علينا انعكست سلباً على مسار عودة مؤسساتها الى الجنوب، وعلى تحقيق العديد من الانجازات، علماً أنه تم تسجيل نقلة نوعية في الكثير من المجالات لا سيما في ما خص الاصلاحات الاقتصادية والمالية والادارية كما القضائية".
+وإذ اوضح "صعوبة تحقيق اصلاحات كبيرة وجبارة خلال فترة قصيرة"، فانه شدد على وجود ارادة وتصميم لذلك، "والهدف الاساسي هو اعادة بناء الثقة بين الشعب والدولة وبين لبنان المقيم والمغترب"، مؤكدا على "ان وحدتنا هي الاساس، فلدينا وطن واحد وعلم واحد وهوية واحدة، ولبنان كما قال البابا يوحنا بولس الثاني رسالة، وهو غني بتنوعه وتعدديته وعلينا الاستفادة من هذه الميزة."
+وأسف الرئيس عون لفقدان البعض في لبنان حسهم الوطني، ولتغذيتهم النعرات الطائفية والمذهبية لمصالح شخصية على حساب مصلحة وطنهم، مشيرا الى "ان هناك من يتعاون مع الخارج ضد اخيه اللبناني في الداخل، وهذه هي مشكلتنا في لبنان في حين ان علينا الاستقواء ببعضنا البعض في الداخل ضد الآخر في الخارج."
+وختم الرئيس عون بالتأكيد على انه من واجباته كرئيس للجمهورية تحقيق مصلحة جميع الاطياف اللبنانية من دون استثناء، وقال:" أنا رئيس جمهورية لبنان ولست رئيس جمهورية للموارنة او للمسلمين او لأي مذهب اوطائفة، فالمسيح قال "اتيت لكي أخدم، وليس لكي أُخدم"، وجميعنا هنا لخدمة شعبنا ورعايانا ودوركم كمطارنة مهم جداً في تنمية الروح الوطنية في لبنان والخارج وعلى كافة الاصعدة".
+وضم الوفد إضافة الى المطارنة عودة واسبر ومنصور وكفوري، مطارنة كل من: سانتياغو وتشيلي، حمص وتوابعها، جبيل والبترون وتوابعهما، عكار وتوابعها، طرابلس والكورة وتوابعهما، فرنسا وأوروبا، ألمانيا وأوروبا الوسطى، حوران وجبل العرب، الجزر البريطانية وإيرلندا، زحلة وبعلبك وتوابعهما، أستراليا ونيوزيلندا والفلبين، المكسيك وفنزويلا والكاريبي، حماة وتوابعها، اللاذقية وتوابعها، حلب واسكندرون وتوابعهما، وبوينس ايريس وسائر الارجنتين، والمعتمد البطريركي في موسكو.
+ملف "اوجيرو" و "ليبان تيليكوم"
+الى ذلك، كانت للرئيس عون اجتماعات إنمائية عرضت ملفي الاتصالات والكهرباء.
+على صعيد الاتصالات، رأس رئيس الجمهورية اجتماعا تناول ملف انتقال موظفي هيئة " اوجيرو" الى شركة " ليبان تيليكوم"، حضره وزير الاتصالات شارل الحاج، ورئيس مجلس إدارة "اوجيرو" المدير العام احمد عويدات، ورئيس الاتحاد العمالي العام بشارة الأسمر، ورئيسة نقابة موظفي "اوجيرو" السيدة اميلي نصار وأعضاء مجلس إدارة النقابة. وخلال الاجتماع شدد الرئيس عون على المضي قدما في استكمال انشاء شركة " ليبان تيليكوم" وانتقال موظفي "اوجيرو" اليها، مع جميع الضمانات اللازمة واكثر، بما يحفظ حقوق الموظفين ومستقبلهم.
+واكد الوزير الحاج التزام الحكومة بانتقال جميع العاملين في "اوجيرو" الى "ليبان تيليكوم" مع حفظ اقدمياتهم وجميع حقوقهم والتقديمات الاجتماعية المعطاة لهم. وقال:"لن يترك احد خلفنا. سنعتمد عقد عمل جماعيا، ونوحد الرواتب لإزالة الفارق بين المياومين والموظفين في الملاك، وسنستثمر في الشبكة. "ليبان تيليكوم" ستكون من أكبر الشركات في لبنان، وموظفو "اوجيرو" هم عمادها".
+وأشار الى ان الشركة ستؤسس فور تعيين مجلس الوزراء مجلس ادارتها وإصدار ترخيصها.
+مجلس إدارة كهرباء لبنان
+الى ذلك، رأس الرئيس عون اجتماعا حضره رئيس مجلس الإدارة لمؤسسة كهرباء لبنان المهندس نسيب نصر، وأعضاء المجلس السادة: المهندس سامر الحسنية، المهندس مازن شبارو، المحامي علي برو، والمحامية السيدة جويل الشكر. وجرى خلال اللقاء عرض واقع المؤسسة والتحديات التي تواجهها، والخطوات الإصلاحية والإدارية التي يعمل مجلس الإدارة على تنفيذها.
+وأوضح المهندس نصر أن الزيارة تهدف إلى الاستماع إلى توجيهات رئيس الجمهورية في إطار مسار الإصلاح، مؤكداً حرص مجلس الإدارة على العمل بحيادية تامة، بعيداً عن التجاذبات السياسية، وبالتعاون مع مختلف الجهات المعنية، من وزارات ولجان نيابية وهيئات رقابية، إضافة إلى إدارة المؤسسة وموظفيها والنقابة والمورّدين، بما يضمن تكامل الجهود للنهوض بقطاع الكهرباء.
+وأشار إلى أن مجلس الإدارة يعمل على بناء فريق عمل متكامل، وعلى معالجة التعقيدات الإدارية والتحديات المتراكمة، بما يتطلب اتخاذ قرارات جريئة وحازمة، مع الالتزام بالقوانين والأنظمة المرعية الإجراء.
+كما أطلع الوفد رئيس الجمهورية على خطة الحوكمة التي أعدّها مجلس الإدارة وأقرّها، بالتعاون مع البنك الدولي، والخطوات الجارية لاستكمال تنفيذها، إضافة إلى عدد من الملفات المرتقب عرضها على مجلس الوزراء.
+من جهته، أكد الرئيس عون أن إصلاح قطاع الكهرباء يشكّل أولوية وطنية استراتيجية، تتجاوز جميع الانتماءات السياسية والطائفية، وهو من أبرز الملفات التي يوليها المستثمرون اهتماماً عند النظر في فرص الاستثمار في لبنان.
+وشدّد على أهمية أن يعمل مجلس الإدارة باستقلالية وشفافية، وألّا يتأثر بالانتقادات ما دام ملتزماً بالقانون والمصلحة العامة، قائلاً: "دعوا إنجازاتكم تتحدث عنكم، ولا تترددوا في اتخاذ القرارات الصحيحة، مهما كانت صعبة".
+ولفت إلى أن مسؤولية الدولة والحكومة تقضي بتسهيل عمل المؤسسة وتذليل العقبات الإدارية التي تعترضها، من دون المساس بالقوانين والضوابط المعتمدة.
+وفي ختام اللقاء، تمنى الرئيس عون التوفيق لرئيس وأعضاء مجلس الإدارة في مهامهم، مؤكداً دعمه لكل جهد إصلاحي جدي يساهم في إعادة النهوض بمؤسسة كهرباء لبنان وتحسين أدائها، بما يخدم جميع اللبنانيين.
+النائب ابو فاعور
+على صعيد آخر، كانت للرئيس عون لقاءات نيابية حيث اجرى مع عضو "اللقاء الديموقراطي" النائب وائل أبو فاعور جولة افق تناولت الأوضاع الراهنة محليا وإقليميا في ضوء التطورات الأخيرة.
+النائب طرابلسي
+كما عرض رئيس الجمهورية مع عضو "تكتل لبنان القوي" النائب ادغار طرابلسي الملف التربوي من جوانبه كافة.
+مدير عام وزارة الصحة
+وفي قصر بعبدا، مدير عام وزارة الصحة وئام أبو حمدان الذي عرض مع الرئيس عون عددا من القضايا التي تتعلق بالوزارة، واثنى رئيس الجمهورية على الاجراءات التي اتخذتها الوزارة في مكافحة الادوية الفاسدة والمهربة والتي لا تنطبق عليها المواصفات الصحية.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:16.800128+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل مدير عام وزارة الصحة</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1570</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>عرض رئيس الجمهورية العماد جوزاف عون مع مدير عام وزارة الصحة وئام أبو حمدان عددا من القضايا التي تتعلق بالوزارة، واثنى رئيس الجمهورية على الاجراءات التي اتخذتها الوزارة في مكافحة الادوية الفاسدة والمهربة والتي لا تنطبق عليها المواصفات الصحية.
+شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:19.047168+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل النائب الطرابلسي</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1569</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:21.170409+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل النائب بو فاعور</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1568</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون عضو "اللقاء الديموقراطي" النائب وائل أبو فاعور واجرى معه جولة افق تناولت الأوضاع الراهنة محليا وإقليميا في ضوء التطورات الأخيرة.
+شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:23.420341+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>الرئيس عون رأس اجتماعا لمجلس إدارة كهرباء لبنان مؤكدا دعمه لكل جهد إصلاحي جدي يساهم في إعادة النهوض بالمؤسسة</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1567</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>الرئيس عون رأس اجتماعا لمجلس إدارة كهرباء لبنان مؤكدا دعمه لكل جهد إصلاحي جدي يساهم في إعادة النهوض بالمؤسسة
+رأس الرئيس عون اجتماعا حضره رئيس مجلس الإدارة لمؤسسة كهرباء لبنان المهندس نسيب نصر، وأعضاء المجلس السادة: المهندس سامر الحسنية، المهندس مازن شبارو، المحامي علي برو، والمحامية السيدة جويل الشكر. وجرى خلال اللقاء عرض واقع المؤسسة والتحديات التي تواجهها، والخطوات الإصلاحية والإدارية التي يعمل مجلس الإدارة على تنفيذها.
+وأوضح المهندس نصر أن الزيارة تهدف إلى الاستماع إلى توجيهات رئيس الجمهورية في إطار مسار الإصلاح، مؤكداً حرص مجلس الإدارة على العمل بحيادية تامة، بعيداً عن التجاذبات السياسية، وبالتعاون مع مختلف الجهات المعنية، من وزارات ولجان نيابية وهيئات رقابية، إضافة إلى إدارة المؤسسة وموظفيها والنقابة والمورّدين، بما يضمن تكامل الجهود للنهوض بقطاع الكهرباء.
+وأشار إلى أن مجلس الإدارة يعمل على بناء فريق عمل متكامل، وعلى معالجة التعقيدات الإدارية والتحديات المتراكمة، بما يتطلب اتخاذ قرارات جريئة وحازمة، مع الالتزام بالقوانين والأنظمة المرعية الإجراء.
+كما أطلع الوفد رئيس الجمهورية على خطة الحوكمة التي أعدّها مجلس الإدارة وأقرّها، بالتعاون مع البنك الدولي، والخطوات الجارية لاستكمال تنفيذها، إضافة إلى عدد من الملفات المرتقب عرضها على مجلس الوزراء.
+من جهته، أكد الرئيس عون أن إصلاح قطاع الكهرباء يشكّل أولوية وطنية استراتيجية، تتجاوز جميع الانتماءات السياسية والطائفية، وهو من أبرز الملفات التي يوليها المستثمرون اهتماماً عند النظر في فرص الاستثمار في لبنان.
+وشدّد على أهمية أن يعمل مجلس الإدارة باستقلالية وشفافية، وألّا يتأثر بالانتقادات ما دام ملتزماً بالقانون والمصلحة العامة، قائلاً: "دعوا إنجازاتكم تتحدث عنكم، ولا تترددوا في اتخاذ القرارات الصحيحة، مهما كانت صعبة".
+ولفت إلى أن مسؤولية الدولة والحكومة تقضي بتسهيل عمل المؤسسة وتذليل العقبات الإدارية التي تعترضها، من دون المساس بالقوانين والضوابط المعتمدة.
+وفي ختام اللقاء، تمنى الرئيس عون التوفيق لرئيس وأعضاء مجلس الإدارة في مهامهم، مؤكداً دعمه لكل جهد إصلاحي جدي يساهم في إعادة النهوض بمؤسسة كهرباء لبنان وتحسين أدائها، بما يخدم جميع اللبنانيين.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:25.639600+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية: للمضي قدما في استكمال انشاء شركة "ليبان تيليكوم" وانتقال موظفي "اوجيرو" اليها مع جميع الضمانات اللازمة بما يحفظ حقوق الموظفين ومستقبلهم</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1566</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية: للمضي قدما في استكمال انشاء شركة "ليبان تيليكوم" وانتقال موظفي "اوجيرو" اليها مع جميع الضمانات اللازمة بما يحفظ حقوق الموظفين ومستقبلهم
+رأس رئيس الجمهورية اجتماعا تناول ملف انتقال موظفي هيئة " اوجيرو" الى شركة " ليبان تيليكوم"، حضره وزير الاتصالات شارل الحاج، ورئيس مجلس إدارة "اوجيرو" المدير العام احمد عويدات، ورئيس الاتحاد العمالي العام بشارة الأسمر، ورئيسة نقابة موظفي "اوجيرو" السيدة اميلي نصار وأعضاء مجلس إدارة النقابة. وخلال الاجتماع شدد الرئيس عون على المضي قدما في استكمال انشاء شركة " ليبان تيليكوم" وانتقال موظفي "اوجيرو" اليها، مع جميع الضمانات اللازمة واكثر، بما يحفظ حقوق الموظفين ومستقبلهم.
+واكد الوزير الحاج التزام الحكومة بانتقال جميع العاملين في "اوجيرو" الى "ليبان تيليكوم" مع حفظ اقدمياتهم وجميع حقوقهم والتقديمات الاجتماعية المعطاة لهم. وقال:"لن يترك احد خلفنا. سنعتمد عقد عمل جماعيا، ونوحد الرواتب لإزالة الفارق بين المياومين والموظفين في الملاك، وسنستثمر في الشبكة. "ليبان تيليكوم" ستكون من أكبر الشركات في لبنان، وموظفو "اوجيرو" هم عمادها".
+وأشار الى ان الشركة ستؤسس فور تعيين مجلس الوزراء مجلس ادارتها وإصدار ترخيصها.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:27.827288+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل البطريرك يازجي على رأس وفد من المطارنة</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1565</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل البطريرك يازجي على رأس وفد من المطارنة
+رئيس الجمهورية: انا رئيس جمهورية لبنان ولست رئيسا لاي مذهب او طائفة
+وواجباتي تحقيق مصلحة جميع الاطياف اللبنانية من دون استثناء
+الرئيس عون: القوة والشجاعة والحكمة لا تكمن في القدرة على شن الحروب فحسب
+بل في انهائها عبر اختيار الدبلوماسية
+البطريرك يازجي: نحن في زمن غير تقليدي احتاج منكم وبحكمة ودراية التصدر لقرارات غير
+تقليدية لتعبروا بلبنان وسط الغام السياسة الدولية التي انفجرت وتنفجر صراع محاور
+اكد رئيس الجمهورية العماد جوزاف عون انه رئيس جمهورية لبنان وليس رئيس جمهورية للموارنة او للمسلمين او لأي مذهب او طائفة، وان من واجباته تحقيق مصلحة جميع الاطياف اللبنانية من دون استثناء، مشددا على أهمية الوحدة الوطنية وعلى "ان الهدف الأساسي هو إعادة الثقة بين الشعب والدولة وبين لبنان المقيم والمغترب" والمضي قدما بالإصلاحات.
+واعتبر انه عندما يكون الجنوب جريحا فان الجرح يطال كل لبنان، مشددا على ان القوة والشجاعة والحكمة لا تكمن في القدرة على شن الحروب فحسب بل في انهائها عبر اختيار الدبلوماسية.
+مواقف الرئيس عون جاءت خلال استقباله قبل ظهر اليوم في قصر بعبدا، بطريرك أنطاكية وسائر المشرق للروم الأرثوذكس يوحنا العاشر يازجي على رأس وفد من آباء سينودوس كنيسة الروم الأرثوذكس.
+كلمة البطريرك يازجي
+في مستهل اللقاء، القى البطريرك يازجي كلمة قال فيها:
+" فخامة الرئيس.
+يطيب لي باسمي وباسم آباء المجمع الأنطاكي المقدس أن أحييكم وأحيي عبركم بلدنا لبنان الذي نحب ونعشق. إذا أردنا أن نترجم كلمة "سينودوس" إلى العربية، فهي تعني حرفيا الجماعة التي تسير معا في درب واحدة، وهذه حالنا اليوم في كنيستنا الأنطاكية. صوت واحد في معيّة واحدة وخطى واحدة بهدي نور المسيح لما فيه خير الإنسان ومجد الله.
+نتوجه إليكم فخامة الرئيس ونعول على حكمتكم في لم شمل اللبنانيين إلى معية واحدة أيضاً، وهي لبنان ولبنان أولاً وآخراً حتى آخر شبر من أراضيه وبكامل كرامته الوطنية التي تستمد قوتها من قوة إيمان شعبه بمؤسساته وعلى رأسها المؤسسة العسكرية التي كنتم على رأسها. نعول على حكمتكم في هذه الظروف الصعبة التي يتناطح فيها صوت العقل والتعقل الذي يرتجي حقن الدماء وإحلال العدل والحق مع صوت العنف والتدمير والاحتلال. ونثق بحكمتكم التي راهن ويراهن عليها جميع اللبنانيين في جمع كلمتهم والعبور بهم إلى وحدة صف واحد وسط ألغام هذا الشرق والعالم وما أكثرها!!"
+اضاف:" فخامة الرئيس، نحن في زمن غير تقليدي احتاج منكم وبحكمة ودراية التصدر لقرارات غير تقليدية لتعبروا بلبنان وسط الغام السياسة الدولية التي انفجرت وتنفجر صراع محاور.
+أنتم تعشقون كما نعشق لبنان البلد الرسالة والذي تعملون لتجنبوه أن يكون صندوق بريد لرسائل من هنا وهناك على مر تاريخ هذا البلد، كانت الكنيسة الأنطاكية الأرثوذكسية جسر تواصل ولقيًا بين سائر المكونات يوم علت لغة المتاريس. ونحن ههنا لنكون معكم فخامة الرئيس في دوركم الذي وضعكم أمام مسؤوليتكم التاريخية جسر تواصل ولقيا بين سائر مكونات هذا الوطن لتقولوا وتفصلوا كلمة حق أمام الله والتاريخ.
+نقول هذا وتمتثل أمامنا ملفات ثقيلة منها وقف آلة الحرب التي تستهدف لبنان كله إذ تستهدف جنوبه أو أي جزء منه. ومنها أيضاً عودة المهجرين وتحقيق الانسحاب الاسرائيلي الكامل وإعادة البناء وتعزيز قوة الجيش ليكون ضامناً لسلطة الدولة، ناهيك عن الوضع الاقتصادي المترنح تحت أزمة المودعين في المصارف وتحت رحمة الصراعات الدولية، كما وملف العدالة المنتظرة لانفجار مرفأ بيروت وغيرها الكثير."
+وختم:"كمسيحيين مشرقيين، نرى في لبنان القائم على المناصفة رمزاً لحضورنا المسيحي في هذا الشرق. نحن باقون فيه بقاء الأرز في لبنان الذي ينمو صديق الله كأرزه مؤكدين على ضرورة مدّ اليد في لقيا مع إخوتنا المسلمين للنهوض بهذا البلد.
+كان الله بعونكم فخامة الرئيس، نحن هنا لنقول إن كنيسة أنطاكية في الوطن والانتشار تصلي من أجلكم ومن أجل كل شعب لبنان. عشتم وعاش لبنان".
+متروبوليت بيروت
+ثم تحدث متروبوليت بيروت وتوابعها المطران الياس عودة الذي قال: "نشكر ربنا على وجود فخامة الرئيس عون في سدة الرئاسة الذي يحاول ان يعطي صورة مختلفة عن لبنان، وعلى كل ذي ضمير حر ان يفرح بهذه الهدية" .
+اضاف:" نحن ابناء قرى، وعملنا في الحقول وزراعة العنب والزيتون ونعلم انه اذا لم نهتم بالنباتات بشكل جيد لن نحصل على انتاج جيد. ورجاؤنا اليوم معونة الرب ليساعد فخامة الرئيس على تحقيق اهدافه بكل محبة التي جوهرها وسندها الصبر والايمان، فنطلب منه ان لا يترك رئيسنا ليبقى لديه الرجاء للاستمرار في مهمته وتحقيق اهدافه".
+متروبوليت نيويورك واميركا الشمالية
+ثم اشار متروبوليت نيويورك وسائر اميركا الشمالية المطران سابا اسبر الى ان" كل فرد من هذه الكنيسة يحمل اوجاعنا وآلامنا وهو سفير حقيقي للبنان في البلد الموجود فيه" وقال:"نطلب من الرب العافية والقوة لتستمروا بهذا الطريق القويم الذي تسيرون به وتبذلون جهدا من اجل رفعة لبنان وتخليصه من كل الاعباء والارث الثقيل الذي تحملونه جراء الاوضاع الصعبة والحرب وتراكم سنوات من الفساد ".
+متروبوليت ساو باولو- البرازيل
+وتحدث متروبوليت ساو باولو المطران دامسكينوس منصور الذي اشار الى ان عدد اللبنانيين في البرازيل اكبر من عدد اللبنانيين الموجودين في لبنان ولهم الحق بأن يزورهم رئيس الجمهورية .وقال:"كل صلواتنا تبدأ وبشكل دائم بالدعاء لجميع حكام هذا البلد ومؤازرتهم في كل عمل صالح، ونحن نصلي ليمنحكم الرب القوة لتتابعوا المسيرة تجاه شعبكم. "
+متروبوليت صور وصيدا
+ثم القى متروبوليت صور وصيدا وتوابعهما المطران الياس كفوري كلمة فقال:" باسم ابنائكم في الجنوب اشكركم على الجهود التي تبذلونها من اجل مساعدتهم وهذا ليس غريبا عليكم، فأنتم ابن الجنوب ونصفكم من الشمال، وتخدمون جميع اللبنانيين ولكم بصمات في الجنوب والشعب يراها ويعرفها ونأمل أن يتحقق ما تعملون من اجله وهو وقف اطلاق النار ومساعدة العائلات التي تشردت بسبب الحرب."
+الرئيس عون
+وردّ الرئيس عون مرحبا بالوفد ومشددا على ان القوة والشجاعة والحكمة لا تكمن في القدرة على شن الحروب فحسب، بل في انهائها عبر اختيار الدبلوماسية، مشيراً الى ان مسار الحروب دائماً يختلف عما يتوقعه طرفاها وهي لا يمكن ان تنتهي إلا عبر التفاوض والحوار، في حين ان استمرارها يؤدي الى مزيد من الدمار والضحايا والدم.
+وتطرق الرئيس عون الى الاوضاع العامة في لبنان وخصوصا في الجنوب، لافتا الى ان "الهدف الاساسي من التفاوض هو تحقيق الانسحاب الاسرائيلي من الاراضي المحتلة وعودة النازحين وإعادة الاعمار وانتشار الجيش على كامل الأراضي اللبنانية، مشيراً الى أنه لا يوجد اختلاف في لبنان حول هذه الاهداف إنما الاختلاف يتمثل في اسلوب وطريقة تحقيقها. فهناك فئة متمسكة بالحرب وقد رأينا الى ما اوصلتنا اليه وما حققته هذه الحرب للبنان، وهناك فئة اخرى، اختارت التفاوض والحوار للوصول الى هذه الاهداف المنشودة."
+وجدد رئيس الجمهورية التأكيد على"ان ابن الجنوب ومنذ عام 1969 يدفع ثمن حروب الآخرين على ارضه، وقد يأس وتعب، ويحق له ان يعيش بأمان وكرامة بعيدا عن الحروب والدمار". وقال:"عندما يكون الجنوب مجروحا، فان الجرح يطال كل لبنان، والدولة هي المسؤولة عن مواطنيها، إلا أن الحروب التي فرضت علينا انعكست سلباً على مسار عودة مؤسساتها الى الجنوب، وعلى تحقيق العديد من الانجازات، علماً أنه تم تسجيل نقلة نوعية في الكثير من المجالات لا سيما في ما خص الاصلاحات الاقتصادية والمالية والادارية كما القضائية".
+وإذ اوضح "صعوبة تحقيق اصلاحات كبيرة وجبارة خلال فترة قصيرة"، فانه شدد على وجود ارادة وتصميم لذلك، "والهدف الاساسي هو اعادة بناء الثقة بين الشعب والدولة وبين لبنان المقيم والمغترب"، مؤكدا على "ان وحدتنا هي الاساس، فلدينا وطن واحد وعلم واحد وهوية واحدة، ولبنان كما قال البابا يوحنا بولس الثاني رسالة، وهو غني بتنوعه وتعدديته وعلينا الاستفادة من هذه الميزة."
+وأسف الرئيس عون لفقدان البعض في لبنان حسهم الوطني، ولتغذيتهم النعرات الطائفية والمذهبية لمصالح شخصية على حساب مصلحة وطنهم، مشيرا الى "ان هناك من يتعاون مع الخارج ضد اخيه اللبناني في الداخل، وهذه هي مشكلتنا في لبنان في حين ان علينا الاستقواء ببعضنا البعض في الداخل ضد الآخر في الخارج."
+وختم الرئيس عون بالتأكيد على انه من واجباته كرئيس للجمهورية تحقيق مصلحة جميع الاطياف اللبنانية من دون استثناء، وقال:" أنا رئيس جمهورية لبنان ولست رئيس جمهورية للموارنة او للمسلمين او لأي مذهب او طائفة، فالمسيح قال "اتيت لكي أخدم، وليس لكي أُخدم"، وجميعنا هنا لخدمة شعبنا ورعايانا ودوركم كمطارنة مهم جداً في تنمية الروح الوطنية في لبنان والخارج وعلى كافة الاصعدة".
+وضم الوفد إضافة الى المطارنة عودة واسبر ومنصور وكفوري، مطارنة كل من: سانتياغو وتشيلي، حمص وتوابعها، جبيل والبترون وتوابعهما، عكار وتوابعها، طرابلس والكورة وتوابعهما، فرنسا وأوروبا، ألمانيا وأوروبا الوسطى، حوران وجبل العرب، الجزر البريطانية وإيرلندا، زحلة وبعلبك وتوابعهما، أستراليا ونيوزيلندا والفلبين، المكسيك وفنزويلا والكاريبي، حماة وتوابعها، اللاذقية وتوابعها، حلب واسكندرون وتوابعهما، وبوينس ايريس وسائر الارجنتين، والمعتمد البطريركي في موسكو.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:30.060648+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>الرئيس عون هنأ نادي الحكمة على فوزه ببطولة الأندية العربية لكرة السلة: فوزكم مصدر فخر للبنان ورسالة أمل تؤكد أن الرياضة تبقى مساحة للتلاقي والمنافسة الشريفة وجسراً لتعزيز حضور لبنان العربي والدولي</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1564</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>الرئيس عون هنأ نادي الحكمة على فوزه ببطولة الأندية العربية لكرة السلة: فوزكم مصدر فخر للبنان ورسالة أمل تؤكد أن الرياضة تبقى مساحة للتلاقي والمنافسة الشريفة وجسراً لتعزيز حضور لبنان العربي والدولي
+الرئيس عون هنأ نادي الحكمة على فوزه ببطولة الأندية العربية لكرة السلة:
+فوزكم مصدر فخر للبنان ورسالة أمل تؤكد أن الرياضة
+تبقى مساحة للتلاقي والمنافسة الشريفة وجسراً لتعزيز حضور لبنان العربي والدولي
+هنأ رئيس الجمهورية العماد جوزاف عون نادي الحكمة، إدارةً ولاعبين وجهازاً فنياً وجمهوراً، بفوزه ببطولة الأندية العربية لكرة السلة بعد ٢٧ عاماً ، معتبرا أن هذا الفوز يشكل إنجازاً رياضياً مشرّفاً يضاف إلى سجلّ النادي العريق، ويؤكد مكانة لبنان الرياضية وقدرة شبابه على تحقيق الانتصارات ورفع اسم وطنهم عالياً.
+وقال الرئيس عون : " إن هذا الفوز هو ثمرة الإرادة والتصميم والعمل الجماعي، ويشكّل مصدر فخر للبنان، ورسالة أمل تؤكد أن الرياضة تبقى مساحة للتلاقي والمنافسة الشريفة، وجسراً لتعزيز حضور لبنان العربي والدولي.
+وختم : "مبروك لنادي الحكمة هذا الإنجاز المستحق، مع التمنيات بمزيد من النجاحات والبطولات".</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:32.292681+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون رجل الأعمال اللبناني المهندس رضا جفال</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1563</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون رجل الأعمال اللبناني المهندس رضا جفال
+رئيس الجمهورية العماد جوزاف عون استقبل رجل الأعمال اللبناني المهندس رضا جفال، يرافقه المحامي كريم قبيسي. واطلع رئيس الجمهورية خلال اللقاء على المشاريع الاستثمارية التي تنفذها مجموعة شركات المهندس جفال في لبنان وحول العالم، واكد على ان لبنان يبقى، رغم كل الظروف، قبلة أنظار المستثمرين، وهذا ما تدأب الدولة على تشجيعه عبر تأمينها عوامل الاستقرار كافة لهم ولكل مستثمر في لبنان.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:36.869078+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض مع رئيس الحكومة الاوضاع في الجنوب واجراءات الدولة التي تتخذها ضمن خطة التعافي وتعزيز حضورها في القرى غير المحتلة</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1562</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض مع رئيس الحكومة الاوضاع في الجنوب واجراءات الدولة التي تتخذها ضمن خطة التعافي وتعزيز حضورها في القرى غير المحتلة
+الرئيس عون بحث مع الرئيس سلام للإجراءات التي ينفذها الجيش والقوى الامنية
+لحفظ الاستقرار في البلاد والتنسيق القائم مع القضاء لملاحقة المخليّن بالامن
+استقبل رئيس الجمهورية العماد جوزاف عون بعد ظهر اليوم في قصر بعبدا، رئيس مجلس الوزراء الدكتور نواف سلام وعرض معه الأوضاع العامة في البلاد عموما وفي الجنوب خصوصا في اطار مواكبة الاجراءات التي تتخذها الدولة ضمن خطة التعافي وتعزيز حضور المؤسسات الامنية والمدنية في القرى والبلدات غير الخاضعة للاحتلال.
+وتم خلال اللقاء تقييم نتائج الزيارة التي قام بها إلى بيروت رئيس مجلس الوزراء وزير الخارجية القطري الشيخ محمد بن عبد الرحمن بن جاسم آل ثاني والمشاريع الانمائية التي تم الاتفاق على اطلاقها لا سيما في مجالي الطاقة والكهرباء، وكذلك زيارة وزير الخارجية الفرنسية جان نويل بارو والوزيرة المنتدبة لدى وزيرة القوات المسلحة وقدامى المحاربين السيدةً أليس روفو والمواضيع التي طرحت لا سيما مرحلة ما بعد انتهاء المهمة العملانية لقوة "اليونيفيل " والدور الأوروبي الداعم للبنان في الفترة المقبلة. كما تم تقييم زيارة الامين العام لجامعة الدول العربية نبيل فهمي والتضامن الذي أبداه مع لبنان في هذه المرحلة. وعرض الرئيس عون مع الرئيس سلام للإجراءات التي ينفذها الجيش والقوى الامنية لحفظ الاستقرار في البلاد والتنسيق القائم مع القضاء لملاحقة المخليّن بالامن .
+واطلع الرئيس سلام رئيس الجمهورية على جدول اعمال جلسة مجلس الوزراء التي ستعقد الخميس في قصر بعبدا .</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:39.072993+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>لقاءات وزارية ودبلوماسية وتربوية وثقافية في قصر بعبدا</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1561</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>لقاءات وزارية ودبلوماسية وتربوية وثقافية في قصر بعبدا
+الرئيس عون شكر السفير السعودي على دعم القيادة السعودية للشعب اللبناني لاسيما
+في مجال تسهيل انسياب الصادرات اللبنانية وجدد ادانته للاعتداءات التي تعرضت لها المملكة
+وزير الإعلام: الرهان كبير على دور وسائل الإعلام ويقظتها في سبيل الحفاظ على المكتسبات الاجتماعية
+ومحاذرة الأخبار المضلِّلة التي من شأنها زعزعة الأمان الاجتماعي
+رئيس الجمهورية عرض مع وفد من لجنة مهرجانات بعلبك الدولية
+التحضيرات الجارية لتنظيم المهرجانات في الصيف المقبل
+شهد قصر بعبدا قبل ظهر اليوم، لقاءات وزارية ودبلوماسية وتربوية وثقافية.
+الوزير مرقص
+وفي هذا الاطار، استقبل رئيس الجمهورية العماد جوزاف عون وزير الاعلام بول مرقص، وعرض معه شؤون وزارته، وعددا من الملفات الإعلامية.
+وبعد اللقاء، أدلى الوزير مرقص بالتصريح التالي الى الصحافيين:
+"تشرفت اليوم بلقاء فخامة رئيس الجمهورية. وكالعادة تطرقنا الى المواضيع العامة لا سيما الإعلامية منها تحديدا، والإستراتيجية الجديدة التي ستطلق لتلفزيون لبنان، والتي تضم سلسلة برامج وتحديثات على المضمون والشكل. وتطرقنا أيضا الى وسائل الإعلام العام وورشة التحديث القائمة فيها، إضافة الى التشريعات الإعلامية وضرورة تطبيقها على نحو سليم ولا سيما قانون الإعلام الجديد. واغتنم المناسبة للتأكيد على أهمية دور جميع وسائل الإعلام في هذا الظرف الدقيق لحماية المجتمع، لكي تبقى لنا الحرية لنمارسها."
+أضاف: "إن قانون الإعلام الجديد اتى لحماية وتكريس الحريات الإعلامية. ولكن في الوقت عينه هناك رهان كبير على دور وسائل الإعلام ويقظتها في سبيل الحفاظ على المكتسبات الاجتماعية ومحاذرة الأخبار المضلِّلة او تبني أي اخبار زائفة من شأنها زعزعة الأمان الاجتماعي، حيث ان الحرية مسؤولية تراعي دقة المرحلة. وكلنا ثقة بدور الإعلام اللبناني في هذا المجال."
+وردا على سؤال حول التعديلات على قانون الإعلام التي كان وعد بإنجازها، أجاب: "لقد حصل تواصل مع الجهات المعنية بهذه التعديلات، سواء النقابية منها او الإعلامية او التشريعية، وأصبحت الأمور في المسار التشريعي. وهذا مسار ملك مجلس النواب سواء النواب بصورة منفردة، او عبر اللجان النيابية المختصة، وصولا الى الهيئة العامة. ونحن سنبقى مواكبين لهذه التعديلات وندفع بها قدما."
+السفير السعودي
+الرئيس عون عرض مع السفير السعودي في لبنان فهد بن عبد الرحمن الدوسري، العلاقات الثنائية بين البلدين وسبل تطويرها في المجالات كافة، وحمّله شكر لبنان للدعم الذي تقدمه القيادة السعودية للشعب اللبناني لاسيما في مجال تسهيل انسياب الصادرات اللبنانية ، مؤكدا ان اللبنانيين ينتظرون عودة أبناء المملكة الى زيارة الربوع اللبنانية وعودة الطيران السعودي إلى لبنان. وجدد الرئيس عون ادانته للاعتداءات التي تعرضت لها المملكة، لاسيما المنشآت الحيوية والمرافق الجوية، مؤكدا تضامن اللبنانيين مع الشعب السعودي الشقيق.
+سفير لبنان في سوريا
+ثم استقبل الرئيس عون سفير لبنان في سوريا هنري قسطون، وعرض معه العلاقات اللبنانية-السورية والتنسيق بين الوزارلات المختصة في البلدين، لا سيما في المجالات الصناعية والإقتصادية، والأمنية والسياحية، في ضوء الرغبة المتبادلة في تعزيز هذه العلاقات وتطويرها في المجالات كافة.
+رئيس الجامعة الأميركية
+وفي قصر بعبدا، رئيس الجامعة الاميركية البروفسور فضلو خوري اطلع رئيس الجمهورية على نتائج جولاته على عدد من الدول لمتابعة اوضاع الطلاب، كما بحث معه شؤوناً أكاديمية تتعلق بالسنة الجامعية.
+لجنة مهرجانات بعلبك الدولية
+كما عرض الرئيس عون مع وفد من لجنة مهرجانات بعلبك الدولية، ضم السيدة جومانة دبانة والسيدة لميا مبيض البساط والسيد نبيل نجار، التحضيرات الجارية لتنظيم المهرجانات في الصيف المقبل، وحاجات اللجنة المالية واللوجستية.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:41.275663+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>عرض رئيس الجمهورية العماد جوزاف عون مع وفد من لجنة مهرجانات بعلبك الدولية التحضيرات الجارية لتنظيم المهرجانات في الصيف المقبل</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1560</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>عرض رئيس الجمهورية العماد جوزاف عون مع وفد من لجنة مهرجانات بعلبك الدولية التحضيرات الجارية لتنظيم المهرجانات في الصيف المقبل
+عرض رئيس الجمهورية العماد جوزاف عون مع وفد من لجنة مهرجانات بعلبك الدولية، ضم السيدة جومانة دبانة والسيدة لميا مبيض البساط والسيد نبيل نجار، التحضيرات الجارية لتنظيم المهرجانات في الصيف المقبل، وحاجات اللجنة المالية واللوجستية.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:43.467140+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون رئيس الجامعة الاميركية البروفسور فضلو خوري</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1559</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون رئيس الجامعة الاميركية البروفسور فضلو خوري
+استقبل رئيس الجمهورية العماد جوزاف عون رئيس الجامعة الاميركية البروفسور فضلو خوري الذي اطلعه على نتائج جولاته على عدد من الدول لمتابعة اوضاع الطلاب، كما بحث معه شؤوناً أكاديمية تتعلق بالسنة الجامعية.
+شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:45.698268+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون سفير لبنان في سوريا هنري قسطون</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1558</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون سفير لبنان في سوريا هنري قسطون
+استقبل رئيس الجمهورية العماد جوزاف عون سفير لبنان في سوريا هنري قسطون، وعرض معه العلاقات اللبنانية-السورية والتنسيق بين الوزارلات المختصة في البلدين، لا سيما في المجالات الصناعية والإقتصادية، والأمنية والسياحية، في ضوء الرغبة المتبادلة في تعزيز هذه العلاقات وتطويرها في المجالات كافة.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:47.884444+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>الرئيس عون شكر السفير السعودي على دعم القيادة السعودية للشعب اللبناني لاسيما في مجال تسهيل انسياب الصادرات اللبنانية وجدد ادانته للاعتداءات التي تعرضت لها المملكة</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1557</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>الرئيس عون شكر السفير السعودي على دعم القيادة السعودية للشعب اللبناني لاسيما في مجال تسهيل انسياب الصادرات اللبنانية وجدد ادانته للاعتداءات التي تعرضت لها المملكة
+الرئيس عون عرض مع السفير السعودي في لبنان فهد بن عبد الرحمن الدوسري، العلاقات الثنائية بين البلدين وسبل تطويرها في المجالات كافة، وحمّله شكر لبنان للدعم الذي تقدمه القيادة السعودية للشعب اللبناني لاسيما في مجال تسهيل انسياب الصادرات اللبنانية ، مؤكدا ان اللبنانيين ينتظرون عودة أبناء المملكة الى زيارة الربوع اللبنانية وعودة الطيران السعودي إلى لبنان. وجدد الرئيس عون ادانته للاعتداءات التي تعرضت لها المملكة، لاسيما المنشآت الحيوية والمرافق الجوية، مؤكدا تضامن اللبنانيين مع الشعب السعودي الشقيق.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:50.111946+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون وزير الاعلام بول مرقص</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1556</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون وزير الاعلام بول مرقص
+استقبل رئيس الجمهورية العماد جوزاف عون وزير الاعلام بول مرقص، وعرض معه شؤون وزارته، وعددا من الملفات الإعلامية.
+وبعد اللقاء، أدلى الوزير مرقص بالتصريح التالي الى الصحافيين:
+"تشرفت اليوم بلقاء فخامة رئيس الجمهورية. وكالعادة تطرقنا الى المواضيع العامة لا سيما الإعلامية منها تحديدا، والإستراتيجية الجديدة التي ستطلق لتلفزيون لبنان، والتي تضم سلسلة برامج وتحديثات على المضمون والشكل. وتطرقنا أيضا الى وسائل الإعلام العام وورشة التحديث القائمة فيها، إضافة الى التشريعات الإعلامية وضرورة تطبيقها على نحو سليم ولا سيما قانون الإعلام الجديد. واغتنم المناسبة للتأكيد على أهمية دور جميع وسائل الإعلام في هذا الظرف الدقيق لحماية المجتمع، لكي تبقى لنا الحرية لنمارسها."
+أضاف: "إن قانون الإعلام الجديد اتى لحماية وتكريس الحريات الإعلامية. ولكن في الوقت عينه هناك رهان كبير على دور وسائل الإعلام ويقظتها في سبيل الحفاظ على المكتسبات الاجتماعية ومحاذرة الأخبار المضلِّلة او تبني أي اخبار زائفة من شأنها زعزعة الأمان الاجتماعي، حيث ان الحرية مسؤولية تراعي دقة المرحلة. وكلنا ثقة بدور الإعلام اللبناني في هذا المجال."
+وردا على سؤال حول التعديلات على قانون الإعلام التي كان وعد بإنجازها، أجاب: "لقد حصل تواصل مع الجهات المعنية بهذه التعديلات، سواء النقابية منها او الإعلامية او التشريعية، وأصبحت الأمور في المسار التشريعي. وهذا مسار ملك مجلس النواب سواء النواب بصورة منفردة، او عبر اللجان النيابية المختصة، وصولا الى الهيئة العامة. ونحن سنبقى مواكبين لهذه التعديلات وندفع بها قدما."</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:52.382423+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية ترأس اجتماعاً امنياً حضره قادة الأجهزة الأمنية: لضرورة التشدد في تطبيق القوانين ومنع المظاهر المسلحة ومصادرة الأسلحة والذخائر والإسراع في التحقيقات وإحالة المخالفين على القضاء المختص لاجراء اللازم</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1555</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية ترأس اجتماعاً امنياً حضره قادة الأجهزة الأمنية: لضرورة التشدد في تطبيق القوانين ومنع المظاهر المسلحة ومصادرة الأسلحة والذخائر والإسراع في التحقيقات وإحالة المخالفين على القضاء المختص لاجراء اللازم
+الرئيس عون: المرحلة الراهنة تتطلب متابعة دقيقة للأوضاع واعتماد الاجراءات الاستباقية
+وقطع الطريق على اي استغلال للشأن الاقتصادي لتحويله إلى إخلال بالامن
+رئيس الجمهورية: لا يمكن تحقيق الأمن والاستقرار إلا بفرض سلطة القانون
+وتعزيز حضور المؤسسات الأمنية والعسكرية والتنسيق الكامل في ما بينها
+الرئيس عون: المرحلة الراهنة تتطلّب أعلى درجات الجهوزية والتنسيق بين الأجهزة
+وتبادلاً مستمراً للمعلومات وتقييماً دقيقاً للتطورات بعيداً عن أي ازدواجية في الأدوار
+رئيس الجمهورية: لتعزيز وجود قوى الامن الداخلي والامن العام وأمن الدولة
+في القرى والبلدات الجنوبية غير الخاضعة للاحتلال الإسرائيلي لتسهيل الخدمات للأهالي
+ترأس رئيس الجمهورية العماد جوزاف عون، بعد ظهر اليوم في قصر بعبدا، اجتماعاً امنياً حضره كل من: قائد الجيش العماد رودولف هيكل، والمدير العام لقوى الامن الداخلي اللواء رائد عبدالله، والمدير العام للامن العام اللواء حسن شقير، والمدير العام لامن الدولة اللواء ادغار لاوندس ونائبه العميد مرشد الحاج سليمان، ومدير المخابرات العميد طوني قهوجي، ورئيس فرع المعلومات العميد محمود قبرصلي، ورئيس مكتب المعلومات في الامن العام العميد جوني الصيصا.
+وتم خلال الاجتماع عرض الأوضاع الامنية في البلاد والاجراءات التي يتخذها الجيش والأجهزة الامنية للمحافظة على الامن والاستقرار، وتنفيذ قرارات السلطة السياسية في مختلف المجالات.
+وفي هذا السياق، اكد الرئيس عون على ضرورة التشدد في تطبيق القوانين ومنع المظاهر المسلحة ومصادرة الأسلحة والذخائر والإسراع في التحقيقات، وإحالة المخالفين على القضاء المختص لاجراء اللازم.
+كما شدد رئيس الجمهورية على ان المرحلة الراهنة تتطلب متابعة دقيقة للأوضاع واعتماد الاجراءات الاستباقية الضرورية ، إضافة إلى قطع الطريق على اي استغلال للشأن الاقتصادي لتحويله إلى إخلال بالامن.
+وقال الرئيس عون : "إنّ الأمن والاستقرار يشكّلان الأساس الذي تقوم عليه الدولة، ولا يمكن تحقيقهما إلا من خلال فرض سلطة القانون، وتعزيز حضور المؤسسات الأمنية والعسكرية، والتنسيق الكامل في ما بينها، بما يضمن حماية المواطنين وصون سلامتهم وطمأنينتهم. ولا يجوز التهاون مع أيّ محاولة للإخلال بالأمن أو المساس باستقرار البلاد."
+ولفت رئيس الجمهورية الى "أن المرحلة الراهنة تتطلّب أعلى درجات الجهوزية والتنسيق بين الأجهزة الأمنية والعسكرية، وتبادلاً مستمراً للمعلومات وتقييماً دقيقاً للتطورات، بعيداً عن أي ازدواجية في الأدوار أو تضارب في الصلاحيات. المطلوب أن يكون كل جهاز على مستوى المسؤولية الملقاة على عاتقه، وأن تتكامل الجهود في خدمة هدف واحد هو حماية لبنان واللبنانيين، وترسيخ الثقة بالدولة ومؤسساتها."
+وطلب الرئيس عون تعزيز وجود قوى الامن الداخلي والامن العام وأمن الدولة في القرى والبلدات الجنوبية غير الخاضعة للاحتلال الإسرائيلي، لتوفير الطمأنينة للأهالي وتسهيل الخدمات الإدارية لهم.
+ونوه الرئيس عون بعمل الجيش والقوى الأمنية، وبجهوزيتها وسرعة تحركها وفعاليتها في كشف الجرائم ومرتكبيها وملاحقتهم وتوقيفهم.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:54.654280+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون رئيس الاتحاد العربي لكرة السلة اللواء اسماعيل القرقاوي</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1554</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون رئيس الاتحاد العربي لكرة السلة اللواء اسماعيل القرقاوي
+استقبل الرئيس عون رئيس الاتحاد العربي لكرة السلة اللواء اسماعيل القرقاوي، يرافقه نائبا الرئيس السيدان عبد الرحمن المسعد ونديم حكيم، والامين العام للاتحاد العميد عبدالله شلبي والاعلامي ابراهيم وهبه. وشكر رئيس الاتحاد الرئيس عون على رعايته بطولة الاندية العربية للرجال في كرة السلة في دورتها الـ 38 التي يستضيفها لبنان والتي حققت نجاحاً مهماً وتختتم غداً على ملعب غزير، ووجه له دعوة لحضور المباراة النهائية.
+وقال اللواء القرقاوي "ان الاتحاد يكنّ كل التقدير والاحترام لمواقف الرئيس عون المشجعة للرياضة، وللاهتمام الذي يبديه بالنشاطات الرياضية"، مطلعا رئيس الجمهورية على ابرز ما يقوم به الاتحاد لا سيما لناحية مواكبة الفئات العمرية.
+الرئيس عون
+ورحب الرئيس عون بالوفد، واكد ان الرياضة هي اساس في حياة الشباب، وان استضافة لبنان لبطولة الاندية العربية للرجال، تشكل تأكيداً على مكانته الرياضية، وعلى قدرته على احتضان الاشقاء العرب في اجواء من الاخوّة والتنافس الرياضي الشريف. وقال: "نأمل ان تسهم هذه البطولة في تعزيز حضور كرة السلة العربية وتطويرها، وان تكون مناسبة لترسيخ العلاقات بين الاندية والاتحادات العربية، وان تلعب دوراً في جمع العرب وتعزيز التواصل في ما بينهم. فلبنان الذي لطالما شكّل مساحة لقاء بين الاشقاء، يرحّب بكل حدث رياضي يعزز الروابط بين العرب ويكرّس صورة الرياضة كرسالة وحدة وتعاون وسلام".
+وشدد الرئيس عون على ان الرياضة ليست مجرد منافسة لتحقيق الفوز، بل هي رسالة انسانية واخلاقية تعزز روح الانضباط والتعاون والمثابرة، وتكرّس قيم الاحترام والروح الرياضية، وتشكّل جسر عبور للتواصل بين الشعوب، وتتيح للشباب العربي فرصة اللقاء والتفاعل وتعزيز روابط الاخوّة.
+واشاد رئيس الجمهورية بالجهود التي يقوم بها الاتحاد اللبناني لكرة السلة لتطوير هذه الرياضة وتعزيز الروابط مع الدول العربية، عبر المشاركة الدائمة في بطولات ومنافسات ان من خلال استضافتها او عبر حضوره فيها.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:56.888692+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون نائب رئيس مجلس النواب السابق ايلي الفرزلي</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1553</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>شدد رئيس الجمهورية العماد جوزاف عون على ان لبنان يتمسك بالحلول الدبلوماسية والتفاوضية لمعالجة النزاعات، معتبرا أن الاستقرار الدائم لا يمكن أن يتحقق بالقوة العسكرية وحدها. واذ اكد ضرورة وقف الاعتداءات الإسرائيلية والالتز...
+استقبل رئيس الجمهورية العماد جوزاف عون في حضور وزير الاشغال العامة والنقل فايز رسامني، وفد هيئة إدارة مؤسسة مطار بيروت برئاسة المهندس محمد شاتيلا وعضوية السادة: وليد شقير، سليمان جابر، جلال حيدر، عادل حسن الدين، والسيدة...</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:03:59.146338+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون وزير الداخلية والبلديات احمد الحجار</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1552</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>استقبل رئيس الجمهورية العماد جوزاف عون وزير الداخلية والبلديات احمد الحجار
+عرض رئيس الجمهورية العماد جوزاف عون مع وزير الداخلية والبلديات احمد الحجار الوضع الأمني في البلاد واطلع منه على الإجراءات التي تتخذها الوزارة لتعزيز الامن والاستقرار باعتبار أن أمن المواطنين وسلامتهم أولوية لا تهاون فيها. وفي هذا السياق، تم استعراض التدابير التي تتخذها المديرية العامة لقوى الأمن الداخلي بالتنسيق مع الجيش اللبناني لتعزيز الانتشار الأمني والدوريات في مختلف المناطق، لا سيما في العاصمة بيروت. كما تم التشديد على اتخاذ التدابير الاستباقية اللازمة من قبل الأجهزة الامنية المعنية لمنع حصول اية تهديدات للأمن الداخلي وفقاً لما تقرر في مجلس الامن الداخلي المركزي في جلسته الأخيرة الأسبوع الفائت. كما تم التأكيد على أهمية تعزيز حضور الدولة ومؤسساتها الأمنية والإدارية في الجنوب، ودعم البلديات وتمكينها من القيام بدورها في تحسين الخدمات العامة، بما يسهم في تلبية احتياجات المواطنين وتعزيز صمودهم وتمسّكهم بأرضهم.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:01.334184+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل الامين العام للجامعة العربية وشدد على تمسك لبنان بالحل الدبلوماسي</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1551</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل الامين العام للجامعة العربية وشدد على تمسك لبنان بالحل الدبلوماسي
+رئيس الجمهورية: اسرائيل لم تلتزم بصيغة الاطار
+ولبنان يرحب بأي جهد ومسعى للجامعة لمساعدته على تخطي هذه المرحلة
+السيد فهمي وضع امكانات الجامعة في تصرف لبنان وقضاياه المحقة
+وشدد على ان الامن والسلم في الجنوب اساسيان
+امين عام الجامعة العربية: الموقف العربي موحد تجاه لبنان
+وما نحاول القيام به هو تشجيع هذا الموقف بخطوات عملية وبدعم عملي ومالي
+اكد رئيس الجمهورية العماد جوزاف عون تمسك لبنان بالحل الدبلوماسي "على الرغم من صعوبته، لانه اقل كلفة بكثير من الحرب المدمّرة التي يدفع اللبنانيون، وبالاخص ابناء الجنوب، ثمناً لها، وانه آن الاوان كي يرتاح لبنان."
+ورحّب بأي جهد ومسعى للجامعة العربية لمساعدة لبنان على تخطي هذه المرحلة الصعبة التي يمرّ بها.
+في المقابل، اكد الامين العام لجامعة الدول العربية السيد نبيل فهمي، على تأييده والتزامه، والجامعة العربية، بشكل تام، بالدولة والمؤسسات اللبنانية، وعدم المساس بسيادة هذا البلد، كاشفاً انه سيزور الجنوب غداً وانه على استعداد لاجراء كل الاتصالات اللازمة، من موقعه كأمين عام للجامعة، مع الدول العربية والغربية لدعم لبنان واللبنانيين.
+وكان الرئيس عون استقبل السيد فهمي في قصر بعبدا قبل ظهر اليوم، على رأس وفد ضم مديرة ادارة المشرق الوزيرة المفوضة لمى قاسم، ونائب رئيس البعثة في بيروت المستشار يوسف السبعاوي، ومدير مكتب الامين العام المستشار احمد شديد، والمستشار اسلام العمري.
+وخلال اللقاء، اعرب السيد فهمي عن اهتمامه بلبنان وتطورات الاوضاع فيه، وجدد تأييده والتزامه، والجامعة العربية، بشكل تام، بالدولة والمؤسسات اللبنانية، وعدم المساس بسيادة هذا البلد، واضعاً امكانات الجامعة في تصرف لبنان وقضاياه المحقة والعادلة. واشار الى ان الامن والسلم في الجنوب اساسيان بالنسبة الى الجامعة، وانه سيزور المناطق الجنوبية غداً للاطلاع عن كثب على الاوضاع هناك، واستعداده لاجراء كل الاتصالات اللازمة، من موقعه كأمين عام للجامعة، مع الدول العربية والغربية لدعم لبنان واللبنانيين.
+واعرب عن تأييده للحوار وفق اسس وشروط واضحة، وانه يعمل من اجل تعزيز موقف الدول العربية حول قضايا المنطقة والعالم.
+ورحب الرئيس عون بالامين العام والوفد المرافق، وجدد التهنئة للسيد فهمي على انتخابه اميناً عاماً للجامعة، خصوصاً في هذا الظرف الدقيق، مشيداً بمواقفه ودعوته الى الحوار والتفاوض، وهي افضل الحلول بدلاً من الحروب.
+وشرح الرئيس عون الوضع اللبناني الحالي، والمساعي التي تبذلها الدولة لاعادة النهوض بلبنان، وعودة السلم والاستقرار التام الى ربوعه، في ظل استمرار الاعتداءات الاسرائيلية وقرب انتهاء وجود "اليونيفيل" في الجنوب. ولفت الى ان الاسرائيليين لم يلتزموا بصيغة الاطار، وما زال الجنوب عرضة للانتهاكات اليومية، علماً ان هذا الامر لن يؤدي الى نتيجة، بل سيزيد تعلّق اللبنانيين بأرضهم وبحقوقهم، لكنه في المقابل لا يساعد الدولة اللبنانية على تنفيذ الاهداف التي وضعتها.
+وشدد رئيس الجمهورية على تمسك لبنان بالحل الدبلوماسي، على الرغم من صعوبته، لانه اقل كلفة بكثير من الحرب المدمّرة التي يدفع اللبنانيون، وبالاخص ابناء الجنوب، ثمناً لها، وانه آن الاوان كي يرتاح لبنان.
+ورحّب بأي جهد ومسعى للجامعة العربية لمساعدة لبنان على تخطي هذه المرحلة الصعبة التي يمرّ بها، خصوصاً وانه لطالما وقفت الجامعة الى جانب لبنان في مختلف المراحل، مثنياً على جهود السيد فهمي، ومتمنياً له التوفيق في مهمته الجديدة.
+تصريح السيد فهمي
+وبعد اللقاء، صرح السيد فهمي للصحافيين فقال:
+"تشرفت اليوم بلقاء رئيس الجمهورية، وهذا تكريم وشرف كبير لي كأمين عام لجامعة الدول العربية، وذلك في اول زيارة لي للبنان بعدما توليت هذا المنصب، بعد زيارات لي حينما كنت في مناصب سابقة في العمل الدبلوماسي. وحضوري اليوم هو من منطلق الأمانة التي حملتها من قبل الرؤساء العرب بالاجماع، والمسؤولية تجاه كافة الساحات العربية عامة التي تتعرض لظروف خاصة بشكل خاص. ولذلك، فإن لبنان هو من اوائل الدول التي زرتها".
+أضاف:"لقد استمعت اليوم لتقييم ثري من فخامة الرئيس سأستفيد منه في اتصالاتي القادمة، وأكدت له أيضاً ان لبنان هو من أولويات الجامعة، ومن اولوياتي كأمين عام لها، الدولة اللبنانية الوطنية السيادية بكافة مؤسساتها، وباعتزازنا الكامل باللبنانيين، وستعمل الجامعة، احتراما وحفاظا على الدولة اللبنانية ومواطنيها، على تأكيد الدعم الإقليمي العربي سياسيا واقتصاديا واجتماعياً. وعقب هذا اللقاء الكبير لي اليوم، سألتقي مع ومسؤولين لبنانيين، ثم سأقوم بزيارة للجنوب تقديراً واحتراماً للوضع هناك في ظل الهجوم الوحشي والمتكرر من قبل إسرائيل تجاه مواطنين أبرياء ومصالح لبنانية".
+وختم: "انا هنا اتحمّل امانة لصالح لبنان، وفي المرحلة القادمة سأوجه جهود الجامعة العربية بما يخدم القضية اللبنانية والدولة اللبنانية".
+سئل: ما الرسالة التي تحملونها للبنان في هذه الزيارة وما الذي يمكن ان يخرج به لبنان عمليا من لقاءاتكم، وهل ستترجم نتائج هذه اللقاءات في بيروت الى اجتماع عربي على مستوى وزراء الخارجية؟
+أجاب: كما ذكرت، بدأت منذ مدة قصيرة زياراتي الى الدول العربية، ولبنان من أوائل هذه الدول. هذه الرسالة سياسية وتعكس اهتمام الجامعة العربية بالوضع اللبناني. لقاءاتي مع المسؤولين تعكس احترامنا الكامل لمؤسسات الدولة اللبنانية التي تقرر هي مصيرها والاحتياجات اللازمة لمواطنيها. وانا احمل ايضاً رسالة في اعقاب اجتماع المجلس الوزاري على المستوى العربي منذ اقل من شهر، وقد شمل لبنان قرار خاص تحدث عن التزامنا وتأييدنا ودعمنا للحقوق اللبنانية بمختلف جوانبها، وأيضاً السعي لتأمين استقراره وحمايته من المخاطر الخارجية، فضلا عن دعمه وسلطاته لتمكينه من توفير الخدمات لمواطنيه.
+ان حضوري هو رسالة إيجابية تجاه لبنان، كما اترك لبنان بعد انتهاء الزيارة غدا حاملا مسؤوليات إضافية في ضوء ما استمعت اليه من رئيس الجمهورية وما سأستمع اليه من مسؤولين اخرين ومن لقاءاتي مع عدد من السياسيين اللبنانيين.
+اما عن مسألة المؤتمر، فإن الازمات العربية كثيرة جدا واهتمامنا يتجاوز عقد مؤتمر. حتما قد يكون مؤتمر ضمن آليات تشجيع الدعم والاتصالات السياسية، انما أولى الخطوات تجاه أي تجمع تكمن في أوسع اتصالات دبلوماسية مكثفة بين الأمانة العامة والاستفادة من ممثلي الدول في القاهرة او من تواجدنا نحن في الدول المختلفة. وهذا يعني ان الاتصال الدبلوماسي والسياسي سيتم تكثيفه تمهيداً لاي محافل أخرى.
+سئل: هل سنكون امام تحرك عربي موحد في ظل الأوضاع التي يعيشها لبنان وفي ظل الجهود التي تقوم بها الحكومة لاستعادة استقرار البلاد ولمواجهة اعتداءات إسرائيل واستمرارها في خرق السيادة اللبنانية؟
+أجاب: اعتقد ان قرار المجلس الوزاري للجامعة كان بتوافق الآراء بالاجماع، تأكيدا على السيادة اللبنانية والحق اللبناني وسيطرة لبنان على كل محافل الحياة في الساحة اللبنانية ورفضا كاملا وباتا للاعتداءات الإسرائيلية على الحقوق اللبنانية. اذا الموقف العربي موحد. وما نحاول القيام به راهناً هو تشجيع هذا الموقف بخطوات عملية وبدعم عملي ومالي يساعد المؤسسات اللبنانية وينعكس في الساحة اللبنانية على المواطن اللبناني.
+سئل: هل نقلتم تحذيرات الى الرئيس عون من حرب إقليمية محتملة وتداعياتها على لبنان؟
+أجاب: لم انقل تحذيرات بهذا المعنى، وفي النهاية يعلم فخامة الرئيس الوضع السياسي والإقليمي كما اعلمه واكثر. انما تحدثت شخصيا عن خطورة الوضع الإقليمي وتعدد النزاعات واحتمال الانفجار، فهذا حديث تم بوضوح بيني وفخامة الرئيس.
+سئل: كيف تنظر جامعة الدول العربية الى المفاوضات اللبنانية- الإسرائيلية برعاية اميركية، وهل من خطوات عملية تقوم بها الجامعة لردع أي عدوان؟
+أجاب: أولا ان كل دولة تحدد مسار مفاوضاتها بقرار منها. وما اعلن مراراً من قبل المسؤولين اللبنانيين عن ان انهاء الاحتلال الإسرائيلي للاراضي اللبنانية هو اولويات، وان الدولة هي أولويات،. والمفاوضات، كما اكدنا بقرارات الجامعة، تحظى بالدعم الكامل لهذا الهدف بالتحديد، والحفاظ على الساحة اللبنانية واستقرارها. نحن داعمون لذلك على الدوام، وسنظل داعمين للامر.
+وفي موضوع الردع، نحن نسعى حاليا لتسهيل الأمور السياسية والدبلوماسية، وهذا كان هدف زيارتي اليوم كي اتحرك في الساحة اللبنانية. وحتى لو كان هناك قرار من الجامعة، فإن اول مكان نقصده هو لبنان. ولذلك تشرفت بلقاء الرئيس اليوم واستمعت الى نصائحه وتقييمه واهتماماته ستكون محط تفكيري في المرحلة القادمة."</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:03.607237+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل وفداً وزاريا فرنسيا برئاسة وزير الخارجية:</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1550</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل وفداً وزاريا فرنسيا برئاسة وزير الخارجية:
+مواقف فرنسا الداعمة للبنان تعبر عن عمق العلاقات التاريخية بين البلدين
+-----------------------
+اسرائيل لم تلتزم بمندرجات اتفاق الاطار وممارساتها تُبقي الاحتلال والتوتر قائمين
+ما يحول دون انتشار الجيش حتى الحدود الجنوبية
+-----------------------
+لبنان يرغب في التمديد للقوات الدولية
+وإذا تعذر ذلك يرحّب بأي صيغة بوجود دولي يمنع حصول الفراغ
+--------------------
+الجيش والقوى الأمنية تنفذ قرارات السلطة السياسية بمنع المظاهر المسلحة
+ومصادرة الأسلحة والذخائر والقضاء يقوم بواجبه في تطبيق القوانين
+---------------------
+لبنان يتطلّع إلى شراكة استراتيجية مع الاتحاد الأوروبي
+لأن أمنه واستقراره من أمن واستقرار هذه الدول
+--------------------
+الوزير بارو: فرنسا تقف إلى جانب لبنان ومستمرة في تقديم الدعم في المجالات كافة
+وملتزمة دعم سيادة لبنان واستقراره وأمنه
+------------------------
+الوزير الفرنسي: فرنسا مستعدة للإضطلاع بدورها كاملاً لمنع نشوء فراغ أمني بعد انسحاب "اليونيفيل"
+---------------------------
+استقبل رئيس الجمهورية العماد جوزاف عون في السابعة مساء اليوم في قصر بعبدا ، وفدا وزاريا فرنسياً رأسه السيد جان نويل بارو، وزير أوروبا والشؤون الخارجية في الجمهورية الفرنسية ، وضم السيدة أليس روفو، الوزيرة المنتدبة لدى وزيرة القوات المسلحة وقدامى المحاربين. والسيد باتريك دوريل، سفير فرنسا لدى لبنان. والسيدة أميليا لاكرافي، نائبة عن الفرنسيين المقيمين في الخارج. والسيدة كريستين لافارد، عضو مجلس الشيوخ عن مقاطعة أو- دو- سين. والسيد روماريك روانيان، مدير إدارة أفريقيا وشمال أفريقيا والشرق الأوسط. والسيدة باربارا فروجييه، مديرة مكتب الوزيرة أليس روفو والسيد رافاييل دويزاند، مستشار شؤون أفريقيا وشمال أفريقيا والشرق الأوسط في مكتب الوزير والسيدة بولين لورو، مستشارة دبلوماسية في وزارة القوات المسلحة (MINARM).
+في مستهل الاجتماع شكر الرئيس عون الرئيس الفرنسي ايمانويل ماكرون على قراره اعادة الطيران التجاري الفرنسي إلى بيروت وموقفه الداعم لانضمام مرفأي بيروت وطرابلس الى " نادي موانىء الممر الاقتصادي IMEC ، اضافة إلى الدور الذي لعبه لاتخاذ الاتحاد الاوروبي القرار بإنشاء بعثة دعم جديدة في لبنان، تتولى تقديم المشورة والمساندة للجيش اللبناني وقوى الأمن الداخلي لمدة ثلاث سنوات.
+واعتبر الرئيس عون ان هذه المواقف الفرنسية تعبر عن عمق العلاقات المتجذرة التي تربط بين لبنان وفرنسا عبر التاريخ ، متمنياً ان يكون الحضور الفرنسي في لبنان مستمرا لما فيه مصلحة البلدين الصديقين .
+وتم خلال اللقاء مناقشة المواضيع الراهنة ، فأكد الرئيس عون في معرض حديثه عن الوضع في الجنوب ان أسرائيل تواصل اعتداءاتها على القرى والبلدات الجنوبية وتمعن في أعمال الجرف وتدمير المنازل ومنع المزارعين من الوصول إلى أراضيهم لجني المحاصيل الزراعية ، وهي بالتالي لم تلتزم بمندرجات اتفاق الاطار الذي تم التوصل اليه بين البلدين برعاية اميركية. ولفت إلى ان هذه الممارسات تبقي الاحتلال والتوتر قائمين في الجنوب ما يحول دون تمكين الجيش اللبناني من الانتشار حتى الحدود الجنوبية الدولية تنفيذا للقرار ١٧٠١. ولفت رئيس الجمهورية الى ان الوفد اللبناني العسكري سيشارك في الاجتماع الثلاثي المرتقب عقده في تامبا في ولاية فلوريدا الأميركية في ٢٠ تشرين الاول الجاري لوضع المطالب اللبنانية بوقف التصعيد الاسرائيلي على الطاولة على امل ان يحقق الاجتماع المرتقب نتائج تنسجم مع مندرجات اتفاق الاطار .
+وبالنسبة الى مرحلة ما بعد انتهاء المهام الامنية لقوات " اليونيفيل " مع نهاية السنة الجاريةً، جدد الرئيس عون التأكيد ان لبنان يرغب في ان يصار إلى التمديد للقوات الدولية او الاستمرار في مهامها الامنية خلال العام ٢٠٢٧ المحدد لانسحاب هذه القوات ، واذا تعذر ذلك فان لبنان يرحب باي صيغة تضمن وجودا دوليا في الجنوب لمنع حصول الفراغ عند انسحاب اليونيفيل وبالتالي جعل الجيش اللبناني على تماس مع الجيش الاسرائيلي في المناطق المحتلة . وفي هذا السياق رحب الرئيس عون باي جهد فرنسي داخل الامم المتحدة ومجلس الامن للوصول إلى الصيغة التي تأتلف مع الرغبة اللبنانية في منع حصول اي فراغ .
+وفي الشأن الداخلي اكد الرئيس عون ان تنفيذ قرارات الحكومة في شأن بسط سلطة الدولة ومنع المظاهر المسلحة ومصادرة الأسلحة والذخائر ، يتولى الجيش والقوى الامنية الأخرى تنفيذه وتتم احالة المخالفين إلى القضاء الذي يقوم بواجبه كاملا في تطبيق القوانين وقرارت السلطة السياسية ، مركزا على اهمية تقوية الجيش وتجهيزه بالعتاد اللازم ليقوم مع القوى الامنية الأخرى بالمهام الموكلة اليها ، متمنيا في هذا الاطار ان يكون التئام المؤتمر الدولي لدعم الجيش وقوى الامن الداخلي بات قريباً لاسيما بعد الاجواء الايجابية التي سادت المؤتمر التحضيري في باريس الشهر الماضي .
+وجدد الرئيس عون التأكيد على استمرار العمل لانجاز الإصلاحات الاقتصادية والمالية التي اقرتها الحكومة وإحالتها الى مجلس النواب .
+وشدد رئيس الجمهورية بان لبنان هو شريك استراتيجي طبيعي للدول الاوروبية لان امن لبنان واستقراره من أمن هذه الدول واستقرارها .
+الوزيربارو
+وكان الوزير بارو نقل في مستهل اللقاء إلى الرئيس عون تحيات الرئيس ماكرون وتأكيده وقوف فرنسا الى جانب لبنان واستمرارها في تقديم الدعم له في المجالات كافة بالتعاون مع الشركاء الأوروبيين . وجدّد الوزير تأكيد دعم فرنسا الثابت لسيادة لبنان واستقراره وأمنه ، كما اكد التزام بلاده العمل على التنفيذ الكامل لاتفاق وقف الأعمال العدائية المبرم في 26 حزيران 2026، وقرار مجلس الأمن الدولي الرقم ١٧٠١ . وشدّد الوزير بارو على ضرورة إرساء بنية دولية جديدة لدعم سيادة لبنان، باعتبارها ضرورة لا غنى عنها لمساندة إعادة انتشار القوات المسلحة اللبنانية وتفادي نشوء فراغ أمني قد تترتب عليه عواقب خطيرة. وستكون فرنسا مستعدة للاضطلاع بدورها كاملاً في هذا الإطار.
+واكد الوزير الفرنسي على أهمية المضي قدماً في تنفيذ الإصلاحات الأساسية اللازمة للنهوض بالبلاد معربا عن استعداد فرنسا لتعبئة إمكاناتها والاستجابة للاحتياجات الإنسانية الطارئة في لبنان.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:05.859423+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية مستقبلاً رئيس الوزراء القطري:</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1549</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية مستقبلاً رئيس الوزراء القطري:
+نقدر الدور الذي يلعبه أمير دولة قطر والقيادة القطرية في السعي الدائم من اجل عودة الاستقرار إلى دول المنطقة
+---------------
+الرئيس عون : نتمنى ان تواصل قطر مساعيها مع الدول العربية الشقيقة والدول الصديقة للضغط على اسرائيل لوقف اعتداءاتها في الجنوب وتطبيق اتفاق الاطار
+-------------
+رئيس الجمهورية: نجدد ادانتنا للاعتداءات التي تعرضت لها دول الخليج
+ونؤكد تضامن لبنان قيادة وشعبا مع الأشقاء في هذه الدول
+------------
+رئيس وزراء قطر أكد استعداد بلاده لمساعدة لبنان في مختلف المجالات
+ودعمها الكامل للقضية اللبنانية
+------------
+الشيخ محمد بن عبد الرحمن: ندعم لبنان في كل الخطوات التي يقوم بها
+ونؤكد على ضرورة انسحاب جيش الاحتلال الاسرائيلي من الاراضي المحتلة
+-------------
+رئيس وزراء قطر: سيتم وضع خطة لحلول متكاملة لأزمة الطاقة في لبنان
+سواء من خلال شركة قطر للطاقة او من خلال الشركات الخاصة
+----------
+اعرب رئيس الجمهورية العماد جوزاف عون خلال استقباله رئيس مجلس الوزراء وزير الخارجية القطري الشيخ محمد بن عبد الرحمن بن جاسم آل ثاني قبل ظهر اليوم في قصر بعبدا، عن تقديره للدور الذي يلعبه أمير دولة قطر الشيخ تميم بن حمد ال ثاني والقيادة القطرية في السعي الدائم من اجل عودة الاستقرار إلى دول المنطقة من خلال تقريب وجهات النظر وازالة الاسباب التي تؤدي إلى التصعيد . وخلال اللقاء الذي حضره وزير الخارجية والمغتربين يوسف رجي ووزير الدولة القطري الدكتور محمد بن عبد العزيز الخليفي وسفير قطر في لبنان الشيخ سعود بن عبد الرحمن آل ثاني، شكر الرئيس عون امير قطر والحكومة القطرية على الدعم الذي يلقاه لبنان في المجالات كافة ، متمنياً ان تواصل قطر مساعيها مع الدول العربية الشقيقة والدول الصديقة للضغط على اسرائيل لوقف اعتداءاتها في الجنوب وتطبيق اتفاق الاطار الذي تم التوصل اليه نتيجة المفاوضات بين لبنان وإسرائيل برعاية أميركية . وجدد رئيس الجمهورية ادانته للاعتداءات التي تعرضت لها دول الخليج وآخرها الاعتداءات على المملكة العربية السعودية، مؤكدا تضامن لبنان قيادة وشعبا مع الأشقاء في دول الخليج .
+وتطرق الرئيس عون إلى العلاقات اللبنانية القطرية، فجدد ترحيبه بأي تعاون بين البلدين في مختلف المجالات لا سيما في مجال الطاقة التي سبق لقطر ان أبدت استعدادها للمساعدة في ايجاد حلول لازمة الكهرباء التي يعاني منها لبنان . وعرض الرئيس عون لما يتعرض له الجنوب من اعتداءات اسرائيلية متواصلة وما نتج عنها من ضحايا واصابات وتدمير للقرى والبلدات الجنوبية التي تحتلها إسرائيل .
+وحمّل الرئيس عون رئيس الوزراء القطري تحياته إلى أمير قطر وتمنياته له بدوام التوفيق ولدولة قطر بمزيد من الامان والاستقرار والتقدم، مؤكدا ان الشعب اللبناني لن ينسى ما قدمته قطر ولا تزال للشعب اللبناني في الظروف الصعبة التي مر بها . وشكر رئيس مجلس الوزراء على زيارته إلى بيروت "التي تعبر عن محبة دولة قطر ودعمها وهي رسالة امل جديدة إلى اللبنانيين ."
+وكان رئيس مجلس الوزراء وزير الخارجية القطري قد نقل في بداية اللقاء تحيات امير قطر للرئيس عون ولشعب لبنان، متمنياً لرئيس الجمهورية كل التوفيق في ظل الظروف الصعبة التي يمر بها لبنان والمنطقة، مشدداً على ان بلاده ستقف دائماً الى جانب لبنان، على امل ان يتم تجاوز هذه الظروف بالتضامن والتنسيق المشترك بين البلدين.
+وأكد رئيس الوزراء القطري ان هذه الزيارة تأتي في سياق متابعة واستكمال الخطط التي وضعت لدعم لبنان وتعزيز التعاون بين البلدين في المجالات كافة وتفعيل المبادرات المشتركة التي تعود بالنفع الى اللبنانيين.
+وتم خلال اللقاء التطرق الى الوضعين الاقليمي والدولي، لا سيما الوضع في الجنوب حيث اعرب الشيخ بن جاسم آل ثاني عن استعداد بلاده لمساعدة لبنان في هذا المجال مؤكداً دعمها الكامل للقضية اللبنانية.
+كما تناول البحث موضوع الطاقة ومساهمة دولة قطر في حل مشكلة الكهرباء في لبنان، متحدثاً عن التوصل لمراحل متقدمة في المشاريع المتعلقة في هذا المجال، لافتاً الى انه سيتم وضع حلول متكاملة لأزمة الطاقة في لبنان سواء من خلال شركة قطر للطاقة، وهي شركة حكومية كما من خلال الشركات الخاصة ايضاً، متحدثاً عن مشروع الطاقة الاستراتيجي المهم الذي يربط بين لبنان وسوريا والعراق.
+وبعد المحادثات الموسعة، عقد الرئيس عون ورئيس الوزراء القطري خلوة استكمل فيها البحث في المواضيع التي تهم البلدين.
+تصريح رئيس الوزراء القطري
+وبعد اللقاء أدلى رئيس الوزراء القطري بالتصريح الآتي: "يسعدني ان أكون اليوم بين اهلنا واخواننا في بيروت كما بلقاء فخامة الرئيس ومعالي وزير الخارجية. وكانت لقاءات مثمرة، حيث تم التطرق الى الملف المهم بالنسبة لنا وهو ملف العلاقات الثنائية بين البلدين وكيفية تنسيق وتفعيل المشاريع المشتركة بيننا والتي من شأنها ان تساهم في تحقيق امن واستقرار المنطقة وازدهارها في المستقبل إن شاء الله."
+وتابع:" إن قطاع الطاقة يأتي في أولوية اهتمامات جمهورية لبنان الشقيقة، ودولة قطر تسعى لتقديم حلول متكاملة في هذا المجال وستكون لنا اجتماعات مع رئيس الحكومة لاحقاً ليكون هناك تفعيل للمشاريع التي تم الاتفاق عليها. وتم ايضاً مناقشة الوضع الاقليمي والدولي، ولا سيما الوضع في جنوب لبنان وتصرفات الاحتلال الاسرائيلي تجاه لبنان. إن دولة قطر تدعم طبعاً لبنان في كل الخطوات التي يقوم بها وتدعم توجه الدولة اللبنانية، وأن يكون هناك انسحاب للجيش الاحتلال الاسرائيلي من الاراضي المحتلة وتسليم العهدة الى الجيش اللبناني الذي ستبقى دولة قطر داعمة له في المستقبل إن شاء الله."</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:08.234139+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>لقاءات وزارية وروحية في قصر بعبدا</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1548</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>لقاءات وزارية وروحية في قصر بعبدا
+رئيس الجمهورية عرض مع الوزير الصدي وضع الطاقة الكهربائية في البلاد
+والإجراءات المعتمدة لتقوية انتاج المعامل الكهربائية
+------
+الرئيس عون اطلع من الوزير الحاج على انطلاق مشروع الألياف الضوئية على مستوى لبنان
+--------------
+المطران خيرالله والمونسنيور أبو كسم وجها دعوة للرئيس عون لحضور حفل اطلاق
+كتاب يوثق الصور والخطابات التي رافقت زيارة قداسة البابا لاون الى لبنان
+-------
+شهد قصر بعبدا قبل ظهر اليوم لقاءات وزارية وروحية، حيث تابع رئيس الجمهورية العماد جوزاف عون عمل عدد من الوزارات وشؤونها.
+وزير الطاقة
+وفي هذا المجال استقبل الرئيس عون وزير الطاقة والمياه جو صدي وعرض معه وضع الطاقة الكهربائية في البلاد والإجراءات المعتمدة لتقوية انتاج المعامل الكهربائية.
+وزير الاتصالات
+واطلع رئيس الجمهورية من وزير الاتصالات شارل الحاج على انطلاق مشروع الألياف الضوئية على مستوى لبنان، ضمن خطة إيصال الألياف إلى 700 ألف منزل خلال ثلاث سنوات. وقد بدأ التنفيذ في 9 مناطق، وينطلق في 16 منطقة إضافية نهاية العام، وصولاً إلى المدن الرئيسية كافة، ليكون 2027 عام الألياف الضوئية.
+وفي موضوع الخليوي، أشار الوزير الحاج إلى أن تخفيف الازدحام ونشر نقاط اتصال 5G سيتحقق هذا العام، فيما سيتم توسيع 5G إلى المدن الرئيسية العام المقبل. كما تناول اللقاء ملف أوجيرو وليبان تيليكوم، مع التأكيد على الحرص على حقوق الموظفين ومكتسباتهم .وأبدى الرئيس عون دعمه لخطة الوزارة.
+المطران خير الله والمونسنيور أبو كسم
+الى ذلك، استقبل الرئيس عون راعي ابرشية البترون المارونية رئيس اللجنة الأسقفية لوسائل الاعلام المطران منير خير الله، ورئيس المركز الكاثوليكي للاعلام المونسنيور عبدو أبو كسم، واطلع منهما على مسودة كتاب زيارة قداسة البابا لاون الرابع عشر الى لبنان، وهو بعنوان "طوبى للساعين الى السلام"، ويوثق الصور والخطابات التي رافقت هذه الزيارة التاريخية. ووجها دعوة لرئيس الجمهورية لحضور حفل اطلاق الكتاب الذي سيقام في الصرح البطريركي في بكركي في أواخر شهر تشرين الثاني او أوائل شهر كانون الأول 2026 لمناسبة الذكرى السنوية الأولى لهذه الزيارة.
+وسيشارك في هذا الحفل المقامات الرسمية اللبنانية، رؤساء الطوائف المسيحية والإسلامية، وسفراء وبعثات ديبلوماسية. وتلقى فيه كلمات لرئيس اللجنة الأسقفية لوسائل الاعلام، والسفير البابوي، والبطريرك الكاردينال مار بشارة بطرس الراعي، ورئيس الجمهورية العماد جوزاف عون ويلي الاحتفال توزيع الكتاب مجانا للحضور.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:12.792035+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>المطران خيرالله والمونسنيور أبو كسم وجها دعوة للرئيس عون لحضور حفل اطلاق كتاب يوثق الصور والخطابات التي رافقت زيارة قداسة البابا لاون الى لبنان</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1547</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>المطران خيرالله والمونسنيور أبو كسم وجها دعوة للرئيس عون لحضور حفل اطلاق كتاب يوثق الصور والخطابات التي رافقت زيارة قداسة البابا لاون الى لبنان
+استقبل الرئيس عون راعي ابرشية البترون المارونية رئيس اللجنة الأسقفية لوسائل الاعلام المطران منير خير الله، ورئيس المركز الكاثوليكي للاعلام المونسنيور عبدو أبو كسم، واطلع منهما على مسودة كتاب زيارة قداسة البابا لاون الرابع عشر الى لبنان، وهو بعنوان "طوبى للساعين الى السلام"، ويوثق الصور والخطابات التي رافقت هذه الزيارة التاريخية. ووجها دعوة لرئيس الجمهورية لحضور حفل اطلاق الكتاب الذي سيقام في الصرح البطريركي في بكركي في أواخر شهر تشرين الثاني او أوائل شهر كانون الأول 2026 لمناسبة الذكرى السنوية الأولى لهذه الزيارة.
+وسيشارك في هذا الحفل المقامات الرسمية اللبنانية، رؤساء الطوائف المسيحية والإسلامية، وسفراء وبعثات ديبلوماسية. وتلقى فيه كلمات لرئيس اللجنة الأسقفية لوسائل الاعلام، والسفير البابوي، والبطريرك الكاردينال مار بشارة بطرس الراعي، ورئيس الجمهورية العماد جوزاف عون ويلي الاحتفال توزيع الكتاب مجانا للحضور.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:14.995002+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من الوزير الحاج على انطلاق مشروع الألياف الضوئية على مستوى لبنان</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1546</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من الوزير الحاج على انطلاق مشروع الألياف الضوئية على مستوى لبنان
+اطلع رئيس الجمهورية من وزير الاتصالات شارل الحاج على انطلاق مشروع الألياف الضوئية على مستوى لبنان، ضمن خطة إيصال الألياف إلى 700 ألف منزل خلال ثلاث سنوات. وقد بدأ التنفيذ في 9 مناطق، وينطلق في 16 منطقة إضافية نهاية العام، وصولاً إلى المدن الرئيسية كافة، ليكون 2027 عام الألياف الضوئية.
+وفي موضوع الخليوي، أشار الوزير الحاج إلى أن تخفيف الازدحام ونشر نقاط اتصال 5G سيتحقق هذا العام، فيما سيتم توسيع 5G إلى المدن الرئيسية العام المقبل. كما تناول اللقاء ملف أوجيرو وليبان تيليكوم، مع التأكيد على الحرص على حقوق الموظفين ومكتسباتهم .وأبدى الرئيس عون دعمه لخطة الوزارة.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:17.189571+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض مع الوزير الصدي وضع الطاقة الكهربائية في البلاد والإجراءات المعتمدة لتقوية انتاج المعامل الكهربائية</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1545</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض مع الوزير الصدي وضع الطاقة الكهربائية في البلاد والإجراءات المعتمدة لتقوية انتاج المعامل الكهربائية
+استقبل الرئيس عون وزير الطاقة والمياه جو صدي وعرض معه وضع الطاقة الكهربائية في البلاد والإجراءات المعتمدة لتقوية انتاج المعامل الكهربائية.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:19.386692+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية تلقى اتصالا هاتفيا من وزير الخارجية الاميركية</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1544</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية تلقى اتصالا هاتفيا من وزير الخارجية الاميركية
+الرئيس عون طلب من الوزير روبيو الضغط على إسرائيل
+لوقف اعتداءاتها وتمكين المزارعين من الوصول الى حقولهم
+-----------------------------
+رئيس الجمهورية : الجيش والقوى الامنية تقوم بواجباتها كاملة في منع المظاهر المسلحة ومصادرة الأسلحة
+والذخائر ومكافحة التهريب والقضاء لن يتساهل في تطبيق القانون
+---------------------------------
+تلقى رئيس الجمهورية العماد جوزاف عون اتصالا هاتفيا مساء اليوم من وزير الخارجية الاميركية ماركو روبيو وعرض معه الأوضاع العامة في لبنان والمنطقة في ضوء التطورات الأخيرة . وتطرق البحث أيضا إلى الوضع في الجنوب في ضوء استمرار الاعتداءات الاسرائيلية على القرى والبلدات الجنوبية . وطلب الرئيس عون من الوزير روبيو الضغط على إسرائيل لوقف هذه الاعتداءات والتزام مندرجات اتفاق الاطار والتوقف عن أعمال التجريف وتمكين المزارعين من الوصول إلى حقولهم وعدم التعرض لهم .
+وخلال الاتصال أكد الرئيس عون للوزير روبيو أن الجيش والقوى الامنية تقوم بواجباتها كاملة في تطبيق القرارات المتعلقة بمنع المظاهر المسلحة ومصادرة الأسلحة والذخائر ومكافحة التهريب وما سجل في الايام القليلة الماضية من اجراءات يندرج في هذا السياق ، لافتا إلى ان الاجهزة القضائية تتابع كل الملفات التي تحال اليها ولن يكون هناك اي تساهل مع المرتكبين وان القوانين ستطبق من دون اي محاباة .</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:21.686688+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>لقاءات وزارية ودبلوماسية واكاديمية ورياضية في قصر بعبدا</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1543</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>لقاءات وزارية ودبلوماسية واكاديمية ورياضية في قصر بعبدا
+الرئيس عون لوفد طلاب الاعلام في جامعة الروح القدس - الكسليك: دور الاعلام
+نقل الرسالة بامانة فكونوا رسلا للحقيقة ولا تبيعوا قلمكم واعملوا بموجب ضميركم
+----
+رئيس الجمهورية: ليس هناك من حرية مطلقة لانها بذلك تتحول الى فوضى
+والامن الوطني يشكل سقفا لها
+----
+الرئيس عون:على أي أساس بدأ الاعلام الإضاءة على الاخبار بحق السفيرة اللبنانية
+في واشنطن والمس بكرامتها الشخصية وبسياسة الدولة الخارجية في حدث لم يحصل؟
+----
+رئيس الجمهورية: التطورات الإقليمية والدولية والانتخابات الإسرائيلية
+ربما ابطأت من وتيرة المفاوضات الا ان هذا لا يعني انها توقفت وهدفنا مصلحة لبنان
+----
+الرئيس عون: انا مسؤول عما أقوم به
+فمن لا يستطيع تحمل مسؤولية موقعه لا يجب ان يتبوأه
+---
+رئيس الجمهورية للطلاب: انتم والشباب اللبناني امانة في عنقي وسأفعل المستحيل لبقائكم في لبنان داعيا الى الاضاءة على الإيجابيات والانجازات لا السلبيات
+---
+الرئيس عون اطلع من الوزير شحادة وقنصل لبنان الفخري في سان فرانسيسكو على تنظيم مسابقة في برامج الذكاء الاصطناعي يشترك فيها طلاب الجامعات اللبنانية والشركات الناشئة
+---
+الرئيس عون عرض مع السفير الكندي في لبنان العلاقات الثنائية
+والبحث تطرق الى إمكانية عودة الطيران الكندي الى لبنان
+----
+في قصر بعبدا رئيس الجمعية الكندية لقادة الشرطة
+ووفد من اتحادات رياضية لبنانية تنظم معرضا دوليا
+---
+شدد رئيس الجمهورية العماد جوزاف عون على دور الاعلام في نقل الرسالة بامانة، معتبرا ان الاعلام سلاح يمكن ان يكون معمرا او مدمرا. وأعاد التأكيد على ان الهدف الذي نعمل عليه هو وقف الحرب وتحقيق الانسحاب الإسرائيلي وانقاذ الجنوب واعماره وإعادة الاسرى وعودة النازحين والا تتوسع الحرب لتطاول كل الأراضي اللبنانية، لافتا الى ان المفاوضات ربما اُبطىء مسارها الا ان هذا لا يعني انها توقفت.
+مواقف الرئيس عون جاءت خلال استقباله قبل ظهر اليوم في قصر بعبدا، وفدا من طلاب السنة الثالثة والماستر في الاعلام جامعة الروح القدس-الكسليك برئاسة الاستاذ في الجامعة داني حداد الذي شكر الرئيس عون على استقباله والوفد، مشيرا الى ان مواقفه تعطي الامل للجيل الشاب للتمسك والبقاء بارضهم.
+ورد الرئيس عون مرحبا بالوفد وقال: "حين أقول اعلام وجامعة الروح القدس أتذكر البابا القديس يوحنا بولس الثاني، كان يقول "ان الإعلاميين هم رسل هذا العصر" والرسول واجبه ان يعلن الحقيقة وان يشهد لها كوسيلة لتحقيق الخير العام للبشر وهذه رسالة الاعلام الحقيقي. كما قلت مرة وأكرر، لسوء الحظ نحن نعيش في زمن قال عنه احد المفكرين: ان الحقيقة فيه باتت مملة بينما الكذبة صارت مثيرة. ولذلك صار بعض الناس يفضلون الكذبة حتى لو كانوا يدركون انها كذبة ويتهربون من الحقيقة حتى ولو كانوا يعرفون انها حقيقة والامثلة في عالمنا وفي حياتنا اليومية لا تعد ولا تحصى".
+وشدد الرئيس عون على دور الاعلام في نقل الرسالة بامانة في زمن بات البعض يستعمل مهنته لابتزاز الناس او يبيع قلمه لاهداف شخصية ومادية أحيانا. واستذكر ابرز ما قيل في الاعلام ودوره في المجتمع، معتبرا ان الاعلام سلاح يمكن ان يكون معمرا او مدمرا، متناولا على سبيل المثال القبض على شحنة المتفجرات على طريق ضهر البيدر وكيفية تعاطي الاعلام معها بشكل استبق فيه التحقيق الذي يسير بعيدا عن كل ما يتم التداول به، لافتا الى "ان كل ما لا يمت الى الحقيقة بصلة يضر بالبلد وبسمعته".
+وتوجه رئيس الجمهورية الى الوفد بالقول: "واجباتكم هي نقل الحقيقة مهما كانت صعبة فكونوا رسلا لها، لان مصلحة لبنان ومستقبله تكمن في ما تكتبون ولذلك لا تبيعوا قلمكم واعملوا بموجب ضميركم". وشدد على ضرورة تحلي الإعلامي بالاخلاق التي هي أساس كل المهن، لافتا الى "ان الانتقاد في السياسة حق ولكن ليكن بناء، والمس بالكرامة الشخصية امر غير مقبول"، مشيرا في هذا السياق، الى ان هدف بعض الوسائل الإعلامية الربح المادي والابتزاز لا المصلحة الوطنية. وشدد على حرية التعبير والاعلام، لكنه قال "ليس هناك من حرية مطلقة، لانها تتحول بذلك الى فوضى". واكد على ان "الامن الوطني يشكل سقف الحرية كما يحصل في ارقى الديموقراطيات في العالم وبعض ما يقال في الاعلام لا يمت الى الحقيقة بصلة والهدف منه زعزعة الاستقرار لمصالح واجندات خارجية او زعزعة الامن لمصالح شخصية".
+ثم دار حوار بين الرئيس عون والطلاب فاكد، ردا على سؤال حول عدم وجود تدخل قضائي حين يتم تجاوز سقف الحرية، انه بموجب قانون الاعلام الجديد تقوم النيابة العامة بالتحضير لكيفية الملاحقة القضائية، مشيرا الى انه كان يرفض سابقا حين كان قائدا للجيش رفع دعوى على من يتهجمون عليه، "لكن لا بد من ان تكون هناك دائما من حدود".
+وتحدث رئيس الجمهورية عن الاخبار المقدم بحق السفيرة اللبنانية في واشنطن ندى معوض لعدم نفيها خبر الاتصال بالسفير الإسرائيلي بعد استهداف نجله والذي نقلته احدى القنوات الإخبارية الإسرائيلية، فسأل على أي أساس بدأ الاعلام الإضاءة على هذا الموضوع والمس بكرامتها الشخصية وبسياسة الدولة الخارجية في حدث لم يحصل وبدأ بتناوله بعيدا عن الحقيقة والواقع؟ وقال اذا كان هدف من يقوم بهذا الامر استهداف المسار الذي سلكناه لانهاء حالة الحرب وإنقاذ لبنان، فهو مجرم بحق البلد".
+وشدد الرئيس عون، ردا على سؤال على ان الهدف الذي نعمل عليه هو وقف الحرب وتحقيق الانسحاب الإسرائيلي وانقاذ الجنوب واعماره وإعادة الاسرى وعودة النازحين والا تتوسع الحرب لتطاول كل الأراضي اللبنانية، مشيرا الى انه "لو لم نلجأ الى التفاوض لكان طاول العدوان الإسرائيلي بيروت ومختلف المرافق العامة".
+وعن مسار التفاوض، لم ينف الرئيس عون وجود صعوبات تعترضه، لكنه اعطى امثلة عن مسارات تفاوض عديدة استغرقت سنوات للوصول الى الحلول المرجوة، لافتا الى ان التطورات الإقليمية والدولية والانتخابات الإسرائيلية ربما ابطأت من وتيرة المفاوضات، الا ان هذا لا يعني انها توقفت في ظل استمرار الاتصالات التي تقودها السفيرة معوض مع الإدارة الأميركية للدفع بها الى الامام.
+وأعاد التأكيد على ان لا خيار ثالثا بين الحرب والمفاوضات "واذا ما كان لدى البعض أي خيار آخر فليقله لي"، مشيرا الى ان الحروب تنتهي عادة اما بتحقيق احد الأطراف نصرا ساحقا على الاخر الذي يستسلم، او بالتفاوض. وقال :"انا مسؤول عما أقوم به فمن لا يستطيع تحمل مسؤولية موقعه لا يجب ان يتبوأه".
+وتوجه الرئيس عون الى الوفد بالقول: "انتم، مثل كل الطلاب والشباب اللبناني،امانة في عنقي وسأفعل المستحيل لبقائكم في لبنان"، متحدثا عن وجود فريق لبناني يشكل نقيض الدولة لان دوره ينتهي فور قيامها، داعيا، في معرض حديثه عن النظام السياسي في لبنان، الجميع الى وضع المصلحة العامة فوق كل اعتبار.
+وقال: هناك صعوبات لكن ليس هناك من مستحيلات، والدليل على ذلك مجموعة الإنجازات التي تحققت والتي لا تتم الإضاءة عليها بشكل كاف، في حين تتم على السلبيات فقط لافتا، على سبيل المثال لا الحصر، الى دخول لبنان عضوية نادي موانئ الممر الاقتصادي بين الهند والشرق الأوسط وأوروبا (IMEC) بمرفأي طرابلس وبيروت فيما وقع عليه عدد من الدول بمرفأ واحد، بالإضافة الى توقيع الرئيس الاميركي قرارا رئاسيا قضى بإلغاء القيود والقرارات الرئاسية السابقة المفروضة على النقل الجوي مع لبنان، وترسيم الحدود البحرية مع قبرص. كما تحدث عن أوتوستراد ضهر البيدر الذي لزم العمل به وزير الاشغال بكلفة اقل مما كان يحكى عنها في السابق، ومطار القليعات ومعرض رشيد كرامي والمرافىء والمنطقة الاقتصادية في الشمال، متسائلا اليست كلها إنجازات ويجب الإضاءة عليها؟
+كما لفت الرئيس عون الى ما حققه لبنان من نمو السنة السابقة بنسبة 4% بفائض حققته وزارة المال بقيمة 1,3 مليار دولار والى زيادة موجودات مصرف لبنان من العملات الصعبة بقيمة ملياري دولار "وكنا نتوقع نسبة 6% هذا العام، ولكن الحرب حالت دون ذلك".
+وإذ دعا أعضاء الوفد الى التحلي بالايجابية، فانه تناول ما يحكى عن تحركات بسبب ارتفاع اسعار النفط، مشيرا الى ان الارتفاع يعود سببه الى الحرب القائمة في الخليج والتي تطال تأثيرتها العالم اجمع. وقال ان ما يؤثر أيضا في ذلك، الحرب القائمة بالإضافة الى جشع التجار، مشددا على ان الدولة تعمل على التخفيف من وطأة الوضع الاقتصادي قدر الإمكان.
+وبعد اللقاء، جال أعضاء الوفد الطلابي في قاعات القصر الجمهوري وقاعة مجلس الوزراء وعلى اقسام مكتب الاعلام حيث قدم لهم مدير الاعلام في رئاسة الجمهورية الأستاذ رفيق شلالا شرحاً مفصلا عن مهام المكتب وطريقة عمله وكيفية تغطيته لنشاط رئيس الجمهورية، واللبنانية الأولى والمديرية العامة لرئاسة الجمهورية.
+الوزير شحادة وقنصل لبنان في سان فرانسيسكو
+إلى ذلك، استقبل الرئيس عون، في حضور وزير المهجرين ووزير الدولة لشؤون التكنولوجيا والذكاء الاصطناعي كمال شحادة، قنصل لبنان الفخري في سان فرانسيسكو السيد جورج شماس ورئيس جمعية BeryTech السيد مارون شماس. وخلال اللقاء اطلع القنصل شماس رئيس الجمهورية على العمل على إحداث جسر تواصل بين لبنان وأبناء الجالية اللبنانية في سان فرانسيسكو لإطلاق مشاريع تعنى بالتحول الرقمي والذكاء الاصطناعي في لبنان. كما اطلع السيد مارون شماس الرئيس عون على تنظيم جمعية BeryTech مسابقة في حقل برامج الذكاء الاصطناعي يشترك فيها طلاب من الجامعات في لبنان والشركات الناشئة سوف تشكل حافزاً لتطوير مشاريع التحول الرقمي في لبنان.
+سفير كندا في لبنان
+دبلوماسيا، استقبل الرئيس عون سفير كندا في لبنان Gregory Galligan واجرى معه جولة افق تناولت الأوضاع الراهنة في لبنان والمنطقة في ضوء التطورات الأخيرة والعلاقات اللبنانية-الكندية وسبل تطويرها في مختلف المجالات. كما تطرق البحث الى إمكانية عودة الطيران الكندي الى لبنان.
+رئيس الجمعية الكندية لقادة الشرطة
+وفي قصر بعبدا، رئيس الجمعية الكندية لقادة الشرطة السيد فادي فيليب داغر مع وفد من العائلة ضم السادة : ناصيف داغر، اسعد داغر ووليد داغر. وهنأ الرئيس عون السيد داغر على توليه مهام رئاسة قادة الشرطة في كندا منوها بالمسؤوليات التي تولاها في كندا وصولا الى المركز الجديد، معربا عن اعتزاز لبنان بابنائه المنتشرين في دول العالم والمتحدرين من اصل لبناني "الذين أينما حلوا يحملون لبنان في قلوبهم ويرفعون اسمه عاليا".
+وأشار السيد داغر الى تعلقه بلبنان مبديا استعداده للمساعدة من موقعه الجديد في كل ما يمكن ان يعزز عمل القوى الأمنية اللبنانية.
+المفتي علي الغزاوي
+على صعيد آخر، استقبل الرئيس عون مفتي زحلة والبقاع الدكتورعلي الغزاوي مع وفد من العائلة شكره على تعزيته واللبنانية الأولى السيدة نعمت عون بوفاة والده. وفي خلال اللقاء، القى المفتي الغزاوي كلمة أشاد فيها بمواقف رئيس الجمهورية الشجاعة وتصميمه على إعادة النهوض بالبلاد ووضعها على المسار الصحيح.
+من جهته، رحب الرئيس عون بالمفتي الغزاوي والوفد المرافق مثنيا على مواقفه الوطنية الجامعة وحرصه على تأدية رسالته الروحية والإنسانية بامانة وإخلاص.
+وفد اتحادات رياضية في لبنان
+رياضيا، استقبل الرئيس عون وفدا من اتحادات رياضية في لبنان تحدث باسمه الأستاذ حسنين مقلد الذي القى كلمة في مستهل اللقاء جاء فيها:
+"فخامة الرئيس، قلتم في خطاب القسم: "ومهما اختلفنا، عند الشدة نحتضن بعضنا، لأنه إذا انكسر أحدنا انكسرنا جميعا". ونحن نلتقي اليوم على هذا المعنى: أن نعمل معا ونجعل من الرياضة مساحة للالتقاء والتعاون. نحن رؤساء الاتحادات الرياضية، المجتمعون من جميع المحافظات اللبنانية: من بيروت، وجبل لبنان، والشمال، وعكار، والبقاع، وبعلبك الهرمل، والجنوب، والنبطية. نعمل معا لتنظم بطولاتنا ومنافساتنا في قلب العاصمة، تحت مظلة الدولة اللبنانية، وملتفين حول العلم اللبناني.
+ويقوم فيتنس باور إكسبو على جهد مشترك بين أكثر من عشرين اتحادا رياضيا. فلكل اتحاد دوره في تنظيم بطولاته ومنافساته، بكوادره الإدارية والفنية والتحكيمية، ومدربيه ولاعبيه. وتقام بطولات لبنان في عدد من الألعاب، ويشارك رياضيو الاتحاد الرياضي للجامعات في المنافسات الفعلية".
+وأضاف:"رغم الجراح والظروف الصعبة التي يمر بها لبنان، نختار أن نلتقي بلغة الرياضة: لغة الحضارة، والروح الرياضية العالية، والتسامح والتنافس الشريف. وهي فرصة لنبرز مواهب رياضيينا، ولنكرمهم أمام ذويهم؛ فهم أساس هذا الحدث وروحه.
+يقام فيتنس باور إكسبو في الفوروم دو بيروت يومي السابع والثامن من تشرين الثاني 2026، ويجمع نحو أربعة آلاف رياضي من جميع الفئات العمرية، مع مشاركات دولية من أكثر من خمس عشرة دولة في عدد من البطولات.
+ونعمل على تجهيز المكان بأحدث المعدات الفنية والتقنية، وبشاشاتعملاقة تتجاوز مساحتها الإجمالية ثمانمائة متر مربع، ومدرجات للجمهور، وفق معايير دولية.
+ونتطلع إلى رعايتكم الكريمة لهذا الحدث، الذي نقدمه جميعا بتعاوننا وجهدنا، ونأمل أن يكون فرصة للالتقاء والتنافس الشريف، وصورة تجمع اتحادات لبنان الرياضية في قلب العاصمة".
+وضم الوفد المشارك في اللقاء، ممثلين عن الاتحاد اللبناني للجمباز، الاتحاد اللبناني لكرة الطاولة، الاتحاد اللبناني للكيوكوشنكاي، الاتحاد اللبناني للملاكمة، الاتحاد اللبناني لرياضات الكيك بوكسينغ، الاتحاد اللبناني لفنون القتال المختلطة، الاتحاد اللبناني للووشو كونغ فو، الاتحاد اللبناني للريشة الطائرة، الاتحاد اللبناني للتراث والرياضات التقليدية، الاتحاد اللبناني للكمبو، الاتحاد اللبناني للجامعات، الاتحاد اللبناني للتايكواندو، الاتحاد اللبناني للمواي تاي، الاتحاد اللبناني للجوجيتسو، الاتحاد اللبناني للرماية، الاتحاد اللبناني للقوة والتربية البدنية، الاتحاد اللبناني لرفع الأثقال، الاتحاد اللبناني للمصارعة، اللجنة اللبنانية للـ Calisthenics، اللجنة اللبنانية للـ Grappling و Amateur MMA، واللجنة اللبنانية للـ Crossfit و Hyrox.
+رد الرئيس عون
+ورد الرئيس عون مرحبا بالوفد، مشددا على "ان الرياضة تجمع والهدف الأساسي يبقى ان نعمل معا من اجل خدمة لبنان فوحده يحمي الجميع."
+وأشار رئيس الجمهورية الى ان للرياضة مكانة بارزة في المجتمع، لأنها قادرة على ان تجمع شبيبتنا وتحميهم من الآفات التي تعرفها معظم المجتمعات كالمخدرات التي تشكَّل خطرا يفوق خطر الإرهاب لانها قد تدخل كل بيت وتفكك عائلات بأكملها.
+وقال الرئيس عون: "إن الجيل الجديد أمانة بين أياديكم كإتحادات رياضية. وعليكم ان توقظوا الوعي في ضمائر شبيبتنا وحب التنافس الشريف لربح البطولات كقيمة مضافة الى ربح انفسهم، على الرغم من الظروف الصعبة والإمكانيات المادية الضيئلة، لكنكم تحققون إنجازات بفضل تصميمكم وإرادتكم الصلبة. وهذا أمر يبعث الأمل في نفوس اللبنانيين. أبقوا هدفكم لبنان، ولا تدعوا الطائفية والمذهبية والأمور الحزبية تفرَّق في ما بينكم."
+وتوجه الى أعضاء الوفد بالقول: "كل قضية لا إيمان فيها، لا يكتب لها النجاح، وانتم تنجحون على الرغم من الظروف الصعبة. وبهذا يظهر مدى صلابة المسؤول في مواجهة الظروف الصعبة. قبطان السفينة لا يتركها وقت العواصف، بل هو من يبقى على رأٍسها في وسط ازمنة العواصف للوصول بها الى بر الأمان."
+وختم رئيس الجمهورية بالقول: "لبنان يستأهل ان يعطي العالم صورة مشرّفة عنه، فهذه حقيقته. والكثير من أبنائه يحققون إنجازات كبيرة في الخارج. نحن نشد على اياديكم، والحدث الذي تعدون له سيعطي رسالة إيجابية للبنان وللخارج لتأكيد الثقة بوطننا، وأنتم من بناة هذه الثقة. هذه مسؤوليتنا جميعا تجاه بلدنا، كل في القطاع الذي يعمل في إطاره."</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:23.932140+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل وفد من اتحادات رياضية لبنانية تنظم معرضا دوليا</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1542</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل وفد من اتحادات رياضية لبنانية تنظم معرضا دوليا
+استقبل رئيس الجمهورية العماد جوزاف عون وفدا من اتحادات رياضية في لبنان تحدث باسمه الأستاذ حسنين مقلد الذي القى كلمة في مستهل اللقاء جاء فيها:
+"فخامة الرئيس، قلتم في خطاب القسم: "ومهما اختلفنا، عند الشدة نحتضن بعضنا، لأنه إذا انكسر أحدنا انكسرنا جميعا". ونحن نلتقي اليوم على هذا المعنى: أن نعمل معا ونجعل من الرياضة مساحة للالتقاء والتعاون. نحن رؤساء الاتحادات الرياضية، المجتمعون من جميع المحافظات اللبنانية: من بيروت، وجبل لبنان، والشمال، وعكار، والبقاع، وبعلبك الهرمل، والجنوب، والنبطية. نعمل معا لتنظم بطولاتنا ومنافساتنا في قلب العاصمة، تحت مظلة الدولة اللبنانية، وملتفين حول العلم اللبناني.
+ويقوم فيتنس باور إكسبو على جهد مشترك بين أكثر من عشرين اتحادا رياضيا. فلكل اتحاد دوره في تنظيم بطولاته ومنافساته، بكوادره الإدارية والفنية والتحكيمية، ومدربيه ولاعبيه. وتقام بطولات لبنان في عدد من الألعاب، ويشارك رياضيو الاتحاد الرياضي للجامعات في المنافسات الفعلية".
+وأضاف:"رغم الجراح والظروف الصعبة التي يمر بها لبنان، نختار أن نلتقي بلغة الرياضة: لغة الحضارة، والروح الرياضية العالية، والتسامح والتنافس الشريف. وهي فرصة لنبرز مواهب رياضيينا، ولنكرمهم أمام ذويهم؛ فهم أساس هذا الحدث وروحه.
+يقام فيتنس باور إكسبو في الفوروم دو بيروت يومي السابع والثامن من تشرين الثاني 2026، ويجمع نحو أربعة آلاف رياضي من جميع الفئات العمرية، مع مشاركات دولية من أكثر من خمس عشرة دولة في عدد من البطولات.
+ونعمل على تجهيز المكان بأحدث المعدات الفنية والتقنية، وبشاشات عملاقة تتجاوز مساحتها الإجمالية ثمانمائة متر مربع، ومدرجات للجمهور، وفق معايير دولية.
+ونتطلع إلى رعايتكم الكريمة لهذا الحدث، الذي نقدمه جميعا بتعاوننا وجهدنا، ونأمل أن يكون فرصة للالتقاء والتنافس الشريف، وصورة تجمع اتحادات لبنان الرياضية في قلب العاصمة".
+وضم الوفد المشارك في اللقاء، ممثلين عن الاتحاد اللبناني للجمباز، الاتحاد اللبناني لكرة الطاولة، الاتحاد اللبناني للكيوكوشنكاي، الاتحاد اللبناني للملاكمة، الاتحاد اللبناني لرياضات الكيك بوكسينغ، الاتحاد اللبناني لفنون القتال المختلطة، الاتحاد اللبناني للووشو كونغ فو، الاتحاد اللبناني للريشة الطائرة، الاتحاد اللبناني للتراث والرياضات التقليدية، الاتحاد اللبناني للكمبو، الاتحاد اللبناني للجامعات، الاتحاد اللبناني للتايكواندو، الاتحاد اللبناني للمواي تاي، الاتحاد اللبناني للجوجيتسو، الاتحاد اللبناني للرماية، الاتحاد اللبناني للقوة والتربية البدنية، الاتحاد اللبناني لرفع الأثقال، الاتحاد اللبناني للمصارعة، اللجنة اللبنانية للـ Calisthenics، اللجنة اللبنانية للـ Grappling و Amateur MMA، واللجنة اللبنانية للـ Crossfit و Hyrox.
+رد الرئيس عون
+ورد الرئيس عون مرحبا بالوفد، مشددا على "ان الرياضة تجمع والهدف الأساسي يبقى ان نعمل معا من اجل خدمة لبنان فوحده يحمي الجميع."
+وأشار رئيس الجمهورية الى ان للرياضة مكانة بارزة في المجتمع، لأنها قادرة على ان تجمع شبيبتنا وتحميهم من الآفات التي تعرفها معظم المجتمعات كالمخدرات التي تشكَّل خطرا يفوق خطر الإرهاب لانها قد تدخل كل بيت وتفكك عائلات بأكملها.
+وقال الرئيس عون: "إن الجيل الجديد أمانة بين أياديكم كإتحادات رياضية. وعليكم ان توقظوا الوعي في ضمائر شبيبتنا وحب التنافس الشريف لربح البطولات كقيمة مضافة الى ربح انفسهم، على الرغم من الظروف الصعبة والإمكانيات المادية الضئيلة، لكنكم تحققون إنجازات بفضل تصميمكم وإرادتكم الصلبة. وهذا أمر يبعث الأمل في نفوس اللبنانيين. أبقوا هدفكم لبنان، ولا تدعوا الطائفية والمذهبية والأمور الحزبية تفرَّق في ما بينكم."
+وتوجه الى أعضاء الوفد بالقول: "كل قضية لا إيمان فيها، لا يكتب لها النجاح، وانتم تنجحون على الرغم من الظروف الصعبة. وبهذا يظهر مدى صلابة المسؤول في مواجهة الظروف الصعبة. قبطان السفينة لا يتركها وقت العواصف، بل هو من يبقى على رأٍسها في وسط ازمنة العواصف للوصول بها الى بر الأمان."
+وختم رئيس الجمهورية بالقول: "لبنان يستأهل ان يعطي العالم صورة مشرّفة عنه، فهذه حقيقته. والكثير من أبنائه يحققون إنجازات كبيرة في الخارج. نحن نشد على اياديكم، والحدث الذي تعدون له سيعطي رسالة إيجابية للبنان وللخارج لتأكيد الثقة بوطننا، وأنتم من بناة هذه الثقة. هذه مسؤوليتنا جميعا تجاه بلدنا، كل في القطاع الذي يعمل في إطاره."</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:26.176673+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل المفتي الغزاوي</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1541</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل المفتي الغزاوي
+استقبل الرئيس عون مفتي زحلة والبقاع الدكتورعلي الغزاوي مع وفد من العائلة شكره على تعزيته واللبنانية الأولى السيدة نعمت عون بوفاة والده. وفي خلال اللقاء، القى المفتي الغزاوي كلمة أشاد فيها بمواقف رئيس الجمهورية الشجاعة وتصميمه على إعادة النهوض بالبلاد ووضعها على المسار الصحيح.
+من جهته، رحب الرئيس عون بالمفتي الغزاوي والوفد المرافق مثنيا على مواقفه الوطنية الجامعة وحرصه على تأدية رسالته الروحية والإنسانية بامانة وإخلاص.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:28.409402+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل رئيس الجمعية الكندية لقادة الشرطة</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1540</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل رئيس الجمعية الكندية لقادة الشرطة
+استقبل رئيس الجمهورية العماد جوزاف عون رئيس الجمعية الكندية لقادة الشرطة السيد فادي فيليب داغر مع وفد من العائلة ضم السادة : ناصيف داغر، اسعد داغر ووليد داغر. وهنأ الرئيس عون السيد داغر على توليه مهام رئاسة قادة الشرطة في كندا منوها بالمسؤوليات التي تولاها في كندا وصولا الى المركز الجديد، معربا عن اعتزاز لبنان بابنائه المنتشرين في دول العالم والمتحدرين من اصل لبناني "الذين أينما حلوا يحملون لبنان في قلوبهم ويرفعون اسمه عاليا".
+وأشار السيد داغر الى تعلقه بلبنان مبديا استعداده للمساعدة من موقعه الجديد في كل ما يمكن ان يعزز عمل القوى الأمنية اللبنانية.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:30.606185+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>الرئيس عون عرض مع السفير الكندي في لبنان العلاقات الثنائية والبحث تطرق الى إمكانية عودة الطيران الكندي الى لبنان</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1539</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>الرئيس عون عرض مع السفير الكندي في لبنان العلاقات الثنائية والبحث تطرق الى إمكانية عودة الطيران الكندي الى لبنان
+استقبل الرئيس عون سفير كندا في لبنان Gregory Galligan واجرى معه جولة افق تناولت الأوضاع الراهنة في لبنان والمنطقة في ضوء التطورات الأخيرة والعلاقات اللبنانية-الكندية وسبل تطويرها في مختلف المجالات. كما تطرق البحث الى إمكانية عودة الطيران الكندي الى لبنان.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:32.820063+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من الوزير شحادة وقنصل لبنان الفخري في سان فرانسيسكو على تنظيم مسابقة في برامج الذكاء الاصطناعي يشترك فيها طلاب الجامعات اللبنانية والشركات الناشئة</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1538</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من الوزير شحادة وقنصل لبنان الفخري في سان فرانسيسكو على تنظيم مسابقة في برامج الذكاء الاصطناعي يشترك فيها طلاب الجامعات اللبنانية والشركات الناشئة
+استقبل الرئيس عون، في حضور وزير المهجرين ووزير الدولة لشؤون التكنولوجيا والذكاء الاصطناعي كمال شحادة، قنصل لبنان الفخري في سان فرانسيسكو السيد جورج شماس ورئيس جمعية BeryTech السيد مارون شماس. وخلال اللقاء اطلع القنصل شماس رئيس الجمهورية على العمل على إحداث جسر تواصل بين لبنان وأبناء الجالية اللبنانية في سان فرانسيسكو لإطلاق مشاريع تعنى بالتحول الرقمي والذكاء الاصطناعي في لبنان. كما اطلع السيد مارون شماس الرئيس عون على تنظيم جمعية BeryTech مسابقة في حقل برامج الذكاء الاصطناعي يشترك فيها طلاب من الجامعات في لبنان والشركات الناشئة سوف تشكل حافزاً لتطوير مشاريع التحول الرقمي في لبنان.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:35.103885+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>الرئيس عون لوفد طلاب الاعلام في جامعة الروح القدس - الكسليك: دور الاعلام نقل الرسالة بامانة فكونوا رسلا للحقيقة ولا تبيعوا قلمكم واعملوا بموجب ضميركم</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1537</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>الرئيس عون لوفد طلاب الاعلام في جامعة الروح القدس - الكسليك: دور الاعلام نقل الرسالة بامانة فكونوا رسلا للحقيقة ولا تبيعوا قلمكم واعملوا بموجب ضميركم
+رئيس الجمهورية: ليس هناك من حرية مطلقة لانها بذلك تتحول الى فوضى
+والامن الوطني يشكل سقفا لها
+----
+الرئيس عون: على أي أساس بدأ الاعلام الإضاءة على الاخبار بحق السفيرة اللبنانية
+في واشنطن والمس بكرامتها الشخصية وبسياسة الدولة الخارجية في حدث لم يحصل؟
+----
+رئيس الجمهورية: التطورات الإقليمية والدولية والانتخابات الإسرائيلية
+ربما ابطأت من وتيرة المفاوضات الا ان هذا لا يعني انها توقفت وهدفنا مصلحة لبنان
+----
+الرئيس عون: انا مسؤول عما أقوم به
+فمن لا يستطيع تحمل مسؤولية موقعه لا يجب ان يتبوأه
+---
+رئيس الجمهورية للطلاب: انتم والشباب اللبناني امانة في عنقي وسأفعل المستحيل لبقائكم في لبنان
+داعيا الى الاضاءة على الإيجابيات والانجازات لا السلبيات
+شدد رئيس الجمهورية العماد جوزاف عون على دور الاعلام في نقل الرسالة بامانة، معتبرا ان الاعلام سلاح يمكن ان يكون معمرا او مدمرا. وأعاد التأكيد على ان الهدف الذي نعمل عليه هو وقف الحرب وتحقيق الانسحاب الإسرائيلي وانقاذ الجنوب واعماره وإعادة الاسرى وعودة النازحين والا تتوسع الحرب لتطاول كل الأراضي اللبنانية، لافتا الى ان المفاوضات ربما اُبطىء مسارها الا ان هذا لا يعني انها توقفت.
+مواقف الرئيس عون جاءت خلال استقباله قبل ظهر اليوم في قصر بعبدا، وفدا من طلاب السنة الثالثة والماستر في الاعلام جامعة الروح القدس-الكسليك برئاسة الاستاذ في الجامعة داني حداد الذي شكر الرئيس عون على استقباله والوفد، مشيرا الى ان مواقفه تعطي الامل للجيل الشاب للتمسك والبقاء بارضهم.
+ورد الرئيس عون مرحبا بالوفد وقال: "حين أقول اعلام وجامعة الروح القدس أتذكر البابا القديس يوحنا بولس الثاني، كان يقول "ان الإعلاميين هم رسل هذا العصر" والرسول واجبه ان يعلن الحقيقة وان يشهد لها كوسيلة لتحقيق الخير العام للبشر وهذه رسالة الاعلام الحقيقي. كما قلت مرة وأكرر، لسوء الحظ نحن نعيش في زمن قال عنه احد المفكرين: ان الحقيقة فيه باتت مملة بينما الكذبة صارت مثيرة. ولذلك صار بعض الناس يفضلون الكذبة حتى لو كانوا يدركون انها كذبة ويتهربون من الحقيقة حتى ولو كانوا يعرفون انها حقيقة والامثلة في عالمنا وفي حياتنا اليومية لا تعد ولا تحصى".
+وشدد الرئيس عون على دور الاعلام في نقل الرسالة بامانة في زمن بات البعض يستعمل مهنته لابتزاز الناس او يبيع قلمه لاهداف شخصية ومادية أحيانا. واستذكر ابرز ما قيل في الاعلام ودوره في المجتمع، معتبرا ان الاعلام سلاح يمكن ان يكون معمرا او مدمرا، متناولا على سبيل المثال القبض على شحنة المتفجرات على طريق ضهر البيدر وكيفية تعاطي الاعلام معها بشكل استبق فيه التحقيق الذي يسير بعيدا عن كل ما يتم التداول به، لافتا الى "ان كل ما لا يمت الى الحقيقة بصلة يضر بالبلد وبسمعته".
+وتوجه رئيس الجمهورية الى الوفد بالقول: "واجباتكم هي نقل الحقيقة مهما كانت صعبة فكونوا رسلا لها، لان مصلحة لبنان ومستقبله تكمن في ما تكتبون ولذلك لا تبيعوا قلمكم واعملوا بموجب ضميركم". وشدد على ضرورة تحلي الإعلامي بالاخلاق التي هي أساس كل المهن، لافتا الى "ان الانتقاد في السياسة حق ولكن ليكن بناء، والمس بالكرامة الشخصية امر غير مقبول"، مشيرا في هذا السياق، الى ان هدف بعض الوسائل الإعلامية الربح المادي والابتزاز لا المصلحة الوطنية. وشدد على حرية التعبير والاعلام، لكنه قال "ليس هناك من حرية مطلقة، لانها تتحول بذلك الى فوضى". واكد على ان "الامن الوطني يشكل سقف الحرية كما يحصل في ارقى الديموقراطيات في العالم وبعض ما يقال في الاعلام لا يمت الى الحقيقة بصلة والهدف منه زعزعة الاستقرار لمصالح واجندات خارجية او زعزعة الامن لمصالح شخصية".
+ثم دار حوار بين الرئيس عون والطلاب فاكد، ردا على سؤال حول عدم وجود تدخل قضائي حين يتم تجاوز سقف الحرية، انه بموجب قانون الاعلام الجديد تقوم النيابة العامة بالتحضير لكيفية الملاحقة القضائية، مشيرا الى انه كان يرفض سابقا حين كان قائدا للجيش رفع دعوى على من يتهجمون عليه، "لكن لا بد من ان تكون هناك دائما من حدود".
+وتحدث رئيس الجمهورية عن الاخبار المقدم بحق السفيرة اللبنانية في واشنطن ندى معوض لعدم نفيها خبر الاتصال بالسفير الإسرائيلي بعد استهداف نجله والذي نقلته احدى القنوات الإخبارية الإسرائيلية، فسأل على أي أساس بدأ الاعلام الإضاءة على هذا الموضوع والمس بكرامتها الشخصية وبسياسة الدولة الخارجية في حدث لم يحصل وبدأ بتناوله بعيدا عن الحقيقة والواقع؟ وقال اذا كان هدف من يقوم بهذا الامر استهداف المسار الذي سلكناه لانهاء حالة الحرب وإنقاذ لبنان، فهو مجرم بحق البلد".
+وشدد الرئيس عون، ردا على سؤال على ان الهدف الذي نعمل عليه هو وقف الحرب وتحقيق الانسحاب الإسرائيلي وانقاذ الجنوب واعماره وإعادة الاسرى وعودة النازحين والا تتوسع الحرب لتطاول كل الأراضي اللبنانية، مشيرا الى انه "لو لم نلجأ الى التفاوض لكان طاول العدوان الإسرائيلي بيروت ومختلف المرافق العامة".
+وعن مسار التفاوض، لم ينف الرئيس عون وجود صعوبات تعترضه، لكنه اعطى امثلة عن مسارات تفاوض عديدة استغرقت سنوات للوصول الى الحلول المرجوة، لافتا الى ان التطورات الإقليمية والدولية والانتخابات الإسرائيلية ربما ابطأت من وتيرة المفاوضات، الا ان هذا لا يعني انها توقفت في ظل استمرار الاتصالات التي تقودها السفيرة معوض مع الإدارة الأميركية للدفع بها الى الامام.
+وأعاد التأكيد على ان لا خيار ثالثا بين الحرب والمفاوضات "واذا ما كان لدى البعض أي خيار آخر فليقله لي"، مشيرا الى ان الحروب تنتهي عادة اما بتحقيق احد الأطراف نصرا ساحقا على الاخر الذي يستسلم، او بالتفاوض. وقال :"انا مسؤول عما أقوم به فمن لا يستطيع تحمل مسؤولية موقعه لا يجب ان يتبوأه".
+وتوجه الرئيس عون الى الوفد بالقول: "انتم، مثل كل الطلاب والشباب اللبناني، امانة في عنقي وسأفعل المستحيل لبقائكم في لبنان"، متحدثا عن وجود فريق لبناني يشكل نقيض الدولة لان دوره ينتهي فور قيامها، داعيا، في معرض حديثه عن النظام السياسي في لبنان، الجميع الى وضع المصلحة العامة فوق كل اعتبار.
+وقال: هناك صعوبات لكن ليس هناك من مستحيلات، والدليل على ذلك مجموعة الإنجازات التي تحققت والتي لا تتم الإضاءة عليها بشكل كاف، في حين تتم على السلبيات فقط لافتا، على سبيل المثال لا الحصر، الى دخول لبنان عضوية نادي موانئ الممر الاقتصادي بين الهند والشرق الأوسط وأوروبا (IMEC) بمرفأي طرابلس وبيروت فيما وقع عليه عدد من الدول بمرفأ واحد، بالإضافة الى توقيع الرئيس الاميركي قرارا رئاسيا قضى بإلغاء القيود والقرارات الرئاسية السابقة المفروضة على النقل الجوي مع لبنان، وترسيم الحدود البحرية مع قبرص. كما تحدث عن أوتوستراد ضهر البيدر الذي لزم العمل به وزير الاشغال بكلفة اقل مما كان يحكى عنها في السابق، ومطار القليعات ومعرض رشيد كرامي والمرافىء والمنطقة الاقتصادية في الشمال، متسائلا اليست كلها إنجازات ويجب الإضاءة عليها؟
+كما لفت الرئيس عون الى ما حققه لبنان من نمو السنة السابقة بنسبة 4% بفائض حققته وزارة المال بقيمة 1,3 مليار دولار والى زيادة موجودات مصرف لبنان من العملات الصعبة بقيمة ملياري دولار "وكنا نتوقع نسبة 6% هذا العام، ولكن الحرب حالت دون ذلك".
+وإذ دعا أعضاء الوفد الى التحلي بالايجابية، فانه تناول ما يحكى عن تحركات بسبب ارتفاع اسعار النفط، مشيرا الى ان الارتفاع يعود سببه الى الحرب القائمة في الخليج والتي تطال تأثيراتها العالم اجمع. وقال ان ما يؤثر أيضا في ذلك، الحرب القائمة بالإضافة الى جشع التجار، مشددا على ان الدولة تعمل على التخفيف من وطأة الوضع الاقتصادي قدر الإمكان.
+وبعد اللقاء، جال أعضاء الوفد الطلابي في قاعات القصر الجمهوري وقاعة مجلس الوزراء وعلى اقسام مكتب الاعلام حيث قدم لهم مدير الاعلام في رئاسة الجمهورية الأستاذ رفيق شلالا شرحاً مفصلا عن مهام المكتب وطريقة عمله وكيفية تغطيته لنشاط رئيس الجمهورية، واللبنانية الأولى والمديرية العامة لرئاسة الجمهورية.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:37.382319+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية تسلم أوراق إعتماد ستة سفراء جدد لدى لبنان لكل من ماليزيا ومصر والعراق وفيتنام وغواتيمالا وغانا</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1536</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية تسلم أوراق إعتماد ستة سفراء جدد لدى لبنان لكل من ماليزيا ومصر والعراق وفيتنام وغواتيمالا وغانا
+تسلم رئيس الجمهورية العماد جوزاف عون، قبل ظهر اليوم في قصر بعبدا، اوراق اعتماد ستة سفراء جدد معتمدين في لبنان هم: سفير ماليزيا ANWAR BIN UDZIR، سفير مصر تميم هاني عبد المنعم خلاف، سفير العراق محمد رضا الحسيني، سفير فييتنامNGUYEN NAM DUONG، سفير غواتيمالا GEORGES DE LA ROCHE، وسفير غاناJUSTICE SOLOMON KORANTWI-BARIMAH.
+وحضر تقديم أوراق الاعتماد الأمين العام لوزارة الخارجية والمغتربين السفير عبد الستار عيسى، ومدير عام المراسم في القصر الجمهوري الدكتور نبيل شديد، ومديرة المراسم في وزارة الخارجية السفيرة رلى نور الدين.
+ولدى وصول السفراء تباعا الى القصر، أقيمت المراسم والتشريفات المعتمدة، فعزفت موسيقى الجيش نشيد البلاد التي يمثلها السفير في الوقت الذي رفع فيه علم دولته على سارية القصر الجمهوري الى جانب العلم اللبناني. بعد ذلك حيا سفير كل من الدول الست العلم، ثم عرض سرية من لواء الحرس الجمهوري، دخل بعدها الى صالون 22 تشرين، ومنه الى صالون السفراء حيث قدَّم اوراق اعتماده الى الرئيس عون كما قدم له اعضاء البعثة الديبلوماسية. ولدى مغادرة كل سفير، بعد تقديم اوراق الاعتماد، عزفت موسيقى الجيش النشيد الوطني اللبناني.
+ونقل السفراء الى الرئيس عون تحيات رؤساء دولهم، كما تمنوا له التوفيق في مسؤولياته الوطنية، مؤكدين له العمل من أجل تعزيز العلاقات التي تجمع بين لبنان وبلدانهم. وحمّل رئيس الجمهورية السفراء تحياته الى رؤساء دولهم، متمنيا لهم التوفيق في مهماتهم الديبلوماسية.
+وفي ما يلي نبذة عن السفراء الجدد الذين قدموا أوراق اعتمادهم:
+سفير ماليزيا ANWAR BIN UDZIR
+- حائز على ماجستير في القانون من جامعة ابيريستويث في المملكة المتحدة.
+- حائز على بكالوريوس في الآداب مع مرتبة الشرف من جامعة سيراكيوز في نيويورك.
+- تولى مناصب دبلوماسية عدة، حيث عين مسؤولا إداريا ودبلوماسيا في وزارة خارجية بلاده، قبل ان يعين مساعدا للوزير في قسم شرق آسيا ومن ثم في قسم المراسم.
+- عين سكرتيرا ثانيا في سفارة بلاده في البحرين.
+- شغل منصب مدير مركز الصداقة والتجارة و الماليزي في تايبه، قبل ان يعين مدير المكتب الإقليمي لوزارة خارجية بلاده في ولاية صباح.
+- شغل منصب نائب رئيس بعثة بلاده في اليابان.
+سفير مصر تميم هاني عبد المنعم خلاف
+- عمل في وزارة خارجية بلاده منذ 25 عاما، وتقلب في مناصب إدارية ودبلوماسية عدة.
+- حائز على ماجستير في العلاقات الدولية من جامعة لندن للإقتصاد.
+- عين ملحقا دبلوماسيا لشؤون الأمم المتحدة في وزارة خارجية بلاده، قبل ان يعين بين عامي 2004-2008 سكرتيرا ثالثا ببعثة مصر لدى الأمم المتحدة في جنيف.
+- بين عامي 2009-2011 عين سكرتيرا ثانيا منتدبا الى رئاسة الجمهورية.
+- بين عامي 2012-2015 عين سكرتيرا اول في سفارة بلاده لدى برازيليا.
+- بين عامي 2018-2022 عين وزيرا مفوضا في سفارة بلاده في واشنطن.
+- بين عامي 2022-2024 شغل منصب نائب مساعد لوزير الخارجية لشؤون اميركا الشمالية.
+- بين عامي 2024-2026 شغل منصب المتحدث الرسمي باسم وزارة خارجية بلاده والمشرف على إدارة الدبلوماسية العامة.
+سفير العراق محمد رضا الحسيني
+- حائز على ماجستير في الوسائط المتعددة من جامعة لندن سوث بانك في المملكة المتحدة.
+- شغل مناصب عدة في مؤسسات عراقية سياسية وأكاديمية في عدة دول من بينها المملكة المتحدة وسوريا.
+- بين عامي 2007-2009 عين مدير قسم المنظمات الدولية في دائرة حقوق الإنسان في وزارة خارجية بلاده.
+- بين عامي 2009-2014 شغل منصب رئيس القسم السياسي ومن ثم قنصل و قائم بالاعمال مؤقت في سفارة بلاده في دمشق.
+- بين عامي 2014-2018 شغل منصب رئيس دائرة حقوق الإنسان في وزارة خارجية بلاده.
+- بين عامي 2023-2025 شغل منصب رئيس دائرة الدول المجاورة في وزارة خارجية بلاده.
+- بين حزيران 2025 وتشرين الأول 2025 شغل منصب قائم بالأعمال في سفارة بلاده في بيروت.
+سفير فييتنامNGUYEN NAM DUONG
+- حائز على دكتوراه في السياسة الدولية من استراليا، وعلى ماجستير في العلاقات الدولية من سنغافورة، وبكالوريوس في العلاقات الدولية من الاكاديمية الدبلوماسية الفيتنامية.
+- تقلب في مناصب إدارية ودبلوماسية عدة.
+- بين شهري شباط وايار 2010 عمل في معهد السياسات الخارجية والدراسات الإستراتيجية في الأكاديمية الدبلوماسية الفيتنامية.
+- بين عامي 2010-2013 شغل منصب نائب المدير العام في معهد السياسات الخارجية والدراسات الإستراتيجية، ومدير مركز الدراسات السياسية والأمنية في الأكاديمية الديبلوماسية الفيتنامية التابعة لوزارة خارجية بلاده.
+- بين عامي 2016-2019 عين مستشارا لدى البعثة الدائمة لبلاده في الأمم المتحدة في نيويورك.
+- بين عامي 2019-2025 عين سفيرا فوق العادة ومفوضا لبلاده لدى جمهورية مصر العربية.
+- منذ أيار 2025 يشغل منصب نائب المدير العام في معهد بحر الصين الشرقي في الأكاديمية الدبلوماسية الفيتنامية التابعة لوزارة خارجية بلاده.
+سفير غواتيمالا GEORGES DE LA ROCHE
+- حائز على ماستر في السياسات الدولية العامة من جامعة جون هوبكينز في الولايات المتحدة الأميركية.
+- حائز على دبلوم في العلوم السياسية والتاريخ من جامعة تافتس الأميركية.
+- تقلب في مناصب إدارية ودبلوماسية عدة، حيث شغل منصب مستشار في سفارة بلاده لدى الولايات المتحدة الأميركية في العام 2002، بعدما شغل منصب سكرتيرا اول في السفارة عينها في العام 2001.
+- في العام 2008 عين سفيرا فوق العادة ووزيرا مفوضا لبلاده في كندا.
+- في العام 2020 عين سفيرا فوق العادة ووزيرا مفوضا لبلاده لدى كل من السويد، والدانمارك، وإستونيا ولاتفيا وفنلندا وليتوانيا والدانمارك.
+- في أيلول 2025 عين سفيرا فوق العادة ووزيرا مفوضا لبلاده في جمهورية مصر العربية.
+سفير غانا JUSTICE SOLOMON KORANTWI-BARIMAH
+- حائز على دكتورا في التكنولوجيا من جامعة تشواني في جنوب إفريقيا.
+- حائز على ماستر في إدارة المصادر البشرية، وإجازة في العلوم السياسية والإدارية من جامعة غانا.
+- تقلب في مناصب اكاديمية وإدارية عدة.
+- اشرف على عدد من الرسائل البحثية الجامعية وله عدد من المؤلفات والمقالات العلمية .
+- عضو في عدد من المؤسسات والجمعيات العلمية.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:39.726257+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>نشاط الرئيس العماد جوزاف عون ب.ظ في 14-10-2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1535</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>نشاط الرئيس العماد جوزاف عون ب.ظ في 14-10-2026
+الرئيس عون تلقى اتصالا من الوزير عراقجي
+واتفاق في الرأي على ان الحلول الدبلوماسية هي الأفضل للحد من النزاعات في المنطقة
+----
+رئيس الجمهورية اطلع من وزير الدفاع على نتائج زيارته الى المغرب
+----
+تلقى رئيس الجمهورية العماد جوزاف عون اتصالاً هاتفياً بعد ظهر اليوم، من وزير خارجية الجمهورية الإسلامية الإيرانية عباس عراقجي، تم خلاله التداول في الأوضاع الراهنة في المنطقة في ضوء التطورات الأخيرة.
+وكان الرأي متفقاً على ضرورة دعم الحلول الدبلوماسية باعتبارها افضل الحلول لوضع حد للنزاعات في المنطقة.
+الوزير منسى
+وكان الرئيس عون استقبل وزير الدفاع الوطني اللواء ميشال منسى، الذي اطلعه على نتائج زيارته الى المغرب والمحادثات التي اجراها مع المسؤولين المغاربة والتي تركزت على تعزيز العلاقات الثنائية بين البلدين، وتطويرها في المجالات كافة.
+وعرضت خلال اللقاء، الأوضاع الأمنية في لبنان عموماً، وفي الجنوب خصوصاً، في ضوء استمرار الاعتداءات الإسرائيلية.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:41.932077+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل الوزير منسى</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1534</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>الرئيس عون استقبل الوزير منسى
+استقبل رئيس الجمهورية العماد جوزاف عون وزير الدفاع الوطني اللواء ميشال منسى، الذي اطلعه على نتائج زيارته الى المغرب والمحادثات التي اجراها مع المسؤولين المغاربة والتي تركزت على تعزيز العلاقات الثنائية بين البلدين، وتطويرها في المجالات كافة.
+وعرضت خلال اللقاء، الأوضاع الأمنية في لبنان عموماً، وفي الجنوب خصوصاً، في ضوء استمرار الاعتداءات الإسرائيلية.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:04:44.181289+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Lebanese_Presidency.xlsx
+++ b/Lebanese_Presidency.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3598,6 +3598,464 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>توقيع مذكرة تفاهم بين المديرية العامة لرئاسة الجمهورية وجامعة الروح القدس – الكسليك حول أرشفة العهود الرئاسية السابقة</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1619</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>توقيع مذكرة تفاهم بين المديرية العامة لرئاسة الجمهورية وجامعة الروح القدس – الكسليك حول أرشفة العهود الرئاسية السابقة
+توقيع مذكرة تفاهم بين المديرية العامة لرئاسة الجمهورية وجامعة الروح القدس – الكسليك
+حول أرشفة العهود الرئاسية السابقة
+------
+الرئيس عون: الحفاظ على هذا الإرث ليس مجرد عمل توثيقي
+بل هو مسؤولية وطنية تسهم في صون تاريخ لبنان وتعزيز الوعي به
+--------
+الدكتور شقير: هدفنا استعادة ما أمكن من الذاكرة الرئاسية اللبنانية وبناء أرشيف مؤسساتي في خدمة الباحثين والأكاديميين والطلاب والأجيال القادمة
+-------
+الأب مكرزل: نحن الى جانب رئيس الجمهورية في التضحيات التي يقوم بها
+من اجل الحفاظ على هوية الوطن وذاكرته
+-------
+اكد رئيس الجمهورية العماد جوزاف عون ان جامعة الروح القدس – الكسليك، تؤدي دوراً تربوياً وأكاديمياً ووطنياً مميزاً، لا يقتصر على إعداد الأجيال الشابة بالعلم والمعرفة، بل يمتد إلى الإسهام في حفظ هوية لبنان الثقافية وتراثه الفكري والتاريخي. وأضاف:"نقدّر عالياً ما تضطلع به مكتبة الجامعة من دور في صون الذاكرة الوطنية من خلال ما تحتضنه من أرشيف غني وثمين، يشمل وثائق ومحفوظات تعود إلى رؤساء الجمهورية في لبنان وشخصيات وطنية بارزة، بما يشكّل ثروة معرفية وتاريخية للأجيال الحاضرة والمستقبلية."
+وقال الرئيس عون: "إن الحفاظ على هذا الإرث ليس مجرد عمل توثيقي، بل هو مسؤولية وطنية تسهم في صون تاريخ لبنان وتعزيز الوعي به، وتؤكد أهمية الجامعات ومؤسساتها العلمية والثقافية في بناء المستقبل على أساس المعرفة واحترام الذاكرة الوطني".
+كلام رئيس الجمهورية جاء في خلال استقباله قبل ظهر اليوم في قصر بعبدا، وفدا من جامعة الروح القدس- الكسليك برئاسة رئيس الجامعة الأب البروفسور جوزف مكرزل، في اعقاب توقيع مذكرة تفاهم بين المديرية العامة لرئاسة الجمهورية، وجامعة الروح القدس، حول أرشفة العهود الرئاسية السابقة.
+توقيع المذكرة
+وكان حفل التوقيع تم قبل ظهر اليوم في المديرية العامة لرئاسة الجمهورية، حيث وقع مديرها العام الدكتور أنطوان شقير مع رئيس الجامعة الاب مكرزل، في حضور وفد من الجامعة، والمديرين العامين في الرئاسة وعدد من المستشارين.
+كلمة د. شقير
+وفي مستهل حفل التوقيع، ألقى الدكتور شقير الكلمة التالية:
+"أولئك الذين لا يستطيعون تذكّر الماضي محكوم عليهم بتكراره"، كما يقول الفيلسوف والمؤرخ جورج سانتايانا.
+الأب رئيس جامعة الروح القدس الكسليك الدكتور جوزيف مكرزل والأب رئيس مكتبة الجامعة الدكتور فادي كميد،
+زميلاتي زملائي،
+إنّ التاريخ ليس مجرد سجلّ للأحداث التي مضت، بل هو ذاكرة الوطن، ومرآة مؤسساته، ومرجع الأجيال القادمة لفهم مسيرة الدولة وتطورها.
+ومن هذا المنطلق، يأتي توقيع مذكرة التفاهم مع جامعة الروح القدس – الكسليك، في إطار مشروع أرشفة العهود الرئاسية السابقة، ليشكّل خطوة مهمة في سبيل صون الذاكرة الرئاسية اللبنانية، وحفظ الوثائق والمراجع التي توثّق مراحل أساسية من تاريخ الجمهورية اللبنانية.
+ولعلّ ما يضاعف أهمية هذا المشروع هو أنّ الوثائق العائدة إلى العهود الرئاسية السابقة لم تُحفظ جميعها في القصر الجمهوري، سواء بسبب عدم توثيقها وأرشفتها في حينه، أو بسبب غياب أي أثر لها.
+وللأسف، فإنّ الظروف الاستثنائية والحروب التي مرّ بها لبنان، وما تعرّض له القصر الجمهوري من أحداث واستهدافات، كان آخرها في العام 1990، أدّت إلى فقدان وضياع جزء كبير من الوثائق التي كانت تشكّل ذاكرة الرئاسة اللبنانية.
+وفي هذا السياق، أودّ الإشارة إلى أنّنا، وضمن المشاريع والمبادرات التي أطلقناها منذ العام 2011، بادرنا إلى تكوين أرشيف للعهود الرئاسية السابقة، إدراكاً منا لأهمية هذا الإرث وضرورة الحفاظ عليه.
+إلا أنّنا لم نتمكّن من استكمال هذه المبادرة، بسبب الظروف الصعبة التي مرّت بها البلاد، وانشغالنا بمواجهة تحدياتها، إضافة إلى افتقارنا إلى الخبرات والاختصاصات اللازمة في مجال الأرشفة التاريخية والمؤسساتية.
+من هنا، جاء تعاوننا مع جامعة الروح القدس – الكسليك، هذه الجامعة العريقة التي تربطني بها علاقة اعتزاز خاصة، إذ كان لي الشرف أن أكون من طلابها، ولاحقاً من أساتذتها.
+إنّ هذا التعاون ليس مجرد اتفاق بين مؤسستين، بل هو شراكة مع مؤسسة أكاديمية أعرفها وأعتز بتاريخها ودورها العلمي والوطني.
+كما أنّ جامعة الروح القدس – الكسليك سبق أن بادرت إلى تجميع أرشيف لرؤساء سابقين وشخصيات تاريخية في الحياة اللبنانية، وهي مبادرة نحيّيها ونقدّرها عالياً.
+وفي هذا السياق، لا بدّ من الإشادة بالأب الرئيس الدكتور جوزيف مكرزل، الذي سبق وتولّى مسؤولية رئاسة مكتبة الجامعة، وبالدور الذي أدّاه في هذا المجال، كما نحيّي الأب الرئيس فادي كميد، الذي يتولى اليوم هذه المسؤولية، وهو خير خلف لخير سلف.
+وإنّني على ثقة بأنّ الأب الرئيس فادي كميد بخبرته في هذا المجال سيعمل على تطوير هذا المشروع المشترك، والبناء على ما تحقق سابقاً، ليصبح مرجعاً أساسياً للأبحاث التاريخية والسياسية والمؤسساتية، مستنداً إلى أسس علمية رصينة وإلى أحدث الوسائل التكنولوجية في مجال الأرشفة وحفظ الوثائق وإتاحتها.
+إنّ هدفنا لا يقتصر على جمع الوثائق المتوافرة وأرشفتها، بل يتجاوز ذلك إلى استعادة ما أمكن من الذاكرة الرئاسية اللبنانية، وبناء أرشيف مؤسساتي موثوق يكون في خدمة موظفي المديرية العامة لرئاسة الجمهورية والباحثين والأكاديميين والطلاب والأجيال القادمة.
+ولضمان حسن تنفيذ هذا المشروع واستمراريته، سنخصّص فريق عمل من المديرية العامة لرئاسة الجمهورية لمتابعته، برئاسة مدير عام فرع الأمانة العامة، العميد إيلي مينا، بالتنسيق مع مكتب الاعلام ودائرة المعلوماتية وتكنولوجيا المعلومات وتحت إشرافي المباشر، حيث سأكون متابعاً عن كثب لمراحل إنجازه، حرصاً على تحقيق الأهداف المرجوة منه.
+ولا يسعني في هذه المناسبة إلا أن أتوجّه بالشكر إلى السيد رئيس الجمهورية على دعمه لهذه المبادرة، إذ كان الداعم الأول لتوقيع هذه الاتفاقية، عندما عرضتها عليه، انطلاقاً من إيمانه بأنّ حفظ الذاكرة الرئاسية والأرشفة المؤسساتية يشكّلان ركناً أساسياً من أركان العمل المؤسساتي، ومسؤولية الدولة تجاه تاريخها وأجيالها.
+إنّ توقيع هذه المذكرة اليوم هو بداية لمسار نأمل أن يكون مستداماً، وأن يساهم في صون إرث الرئاسة اللبنانية ووضعه في خدمة المعرفة والبحث العلمي.
+فالمؤسسات لا تُبنى فقط بما تقوم به في الحاضر، بل أيضاً بما تحفظه من إرث الماضي، وبما تتركه للأجيال القادمة من ذاكرة موثّقة ومرجعيات موثوقة.
+أشكركم جميعاً، وأخصّ بالشكر جامعة الروح القدس – الكسليك، إدارةً وأكاديميين، على تعاونهم ومساهمتهم في هذا المشروع الوطني، آملاً أن يشكّل توقيع هذه المذكرة بداية لشراكة مثمرة تليق بتاريخ لبنان ورئاسة الجمهورية."
+كلمة الأب مكرزل
+ثم ألقى الأب مكرزل كلمة لفت فيها الى ان توقيع المذكرة، قد يعتبره البعض ترفاً فكرياً، في ظل ما يجري في لبنان، ولكن في الحقيقة، وفي مواجهة الذين يشككون اليوم بهوية الوطن، او ينادون بهويات متعددة، فإن أرشيف رئاسة الجمهورية هو الجواب، لأنه ذاكرة الوطن للذين يريدون الوطن.
+واعتبر ان سيادة الوطن تقوم على تضحيات البشر والمؤسسات، وعلى الحبر الذي يحفظ الذاكرة. وقال : "نحن الى جانب رئيس الجمهورية في التضحيات التي يقوم بها من اجل الحفاظ على هوية الوطن وذاكرته. لذلك اتفاقنا اليوم هو اتفاق سيادة بامتياز، واتفاق مؤسساتي يؤكد على إمكانية الشراكة بين المؤسسات الخاصة والدولة. وهو أيضا اتفاق اكاديمي، سيتيح في المستقبل الاطلاع على ذاكرة الوطن الحقيقية."
+شلالا
+وعرض رئيس مكتب الاعلام في رئاسة الجمهورية رفيق شلالا للخطوات العملية التي رافقت جمع أرشيف الرؤساء خلال الأعوام الماضية، وما تم إنجازه في هذا المجال من خلال جمع معلومات عن الرؤساء السابقين، وصور لأهم الاحداث في عهودهم، وذلك من مختلف المصادر العائلية والإعلامية والرسمية والاجتماعية، منوها بالتجاوب الذي ابدته الجهات التي ساهمت في توفير المعلومات التوثيقية المطلوبة.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:16:53.882004+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>نشاط الرئيس العماد جوزاف عون ب.ظ في 29-10-2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1618</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>نشاط الرئيس العماد جوزاف عون ب.ظ في 29-10-2026
+الرئيس عون اطلع من وزير الدفاع على نتائج زيارتيه إلى الأردن وتشيكيا
+-------
+وزير الصحة اطلع رئيس الجمهورية على الخطوات التي تقوم بها الوزارة
+في ملف تسجيل الدواء ووقف عمل الشركات التي لا تستوفي الشروط
+--------
+رئيس المؤسسة العامة للإسكان اطلع الرئيس عون على التحضيرات الجارية
+لبدء المؤسسة منح قروض إسكانيّة بعد اقرار موازنة ٢٠٢٧
+--------
+واصل رئيس الجمهورية العماد جوزاف عون لقاءاته بعد ظهر اليوم في قصر بعبدا، واستهلها بلقاء وزير الدفاع الوطني اللواء ميشال منسى، حيث اطلع منه على نتائج الزيارتين اللتين قام بهما إلى الأردن وتشيكيا، والمحادثات التي اجراها مع المسؤولين في هاتين الدولتين، والتي تناولت الأوضاع في لبنان والمنطقة، ودور الجيش في بسط سلطة الدولة وسيادتها على أراضيها، ومرحلة ما بعد انتهاء مهمة القوات الدولية العاملة في الجنوب.
+وزير الصحة
+وزير الصحة الدكتور راكان ناصر الدين، اطلع رئيس الجمهورية على شؤون الوزارة والخطوات التي تقوم بها في ملف تسجيل الدواء، ووقف عمل الشركات التي لا تستوفي الشروط. كما عرض لابرز الإجراءات الإصلاحية التي تم اعتمادها بالتنسيق مع منظمة الصحة العالمية.
+رئيس المؤسسة العامة للإسكان
+كما استقبل الرئيس عون رئيس المؤسسة العامة للإسكان المهندس روني لحود، واطلع منه على التحضيرات الجارية لبدء المؤسسة منح قروض إسكانيّة بعد اقرار موازنة ٢٠٢٧ وصدورها.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:16:56.214914+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>رئيس المؤسسة العامة للإسكان اطلع الرئيس عون على التحضيرات الجارية لبدء المؤسسة منح قروض إسكانيّة بعد اقرار موازنة ٢٠٢٧</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1617</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>رئيس المؤسسة العامة للإسكان اطلع الرئيس عون على التحضيرات الجارية لبدء المؤسسة منح قروض إسكانيّة بعد اقرار موازنة ٢٠٢٧
+استقبل الرئيس عون رئيس المؤسسة العامة للإسكان المهندس روني لحود، واطلع منه على التحضيرات الجارية لبدء المؤسسة منح قروض إسكانيّة بعد اقرار موازنة ٢٠٢٧ وصدورها.
+اكد رئيس الجمهورية العماد جوزاف عون ان جامعة الروح القدس – الكسليك، تؤدي دوراً تربوياً وأكاديمياً ووطنياً مميزاً، لا يقتصر على إعداد الأجيال الشابة بالعلم والمعرفة، بل يمتد إلى الإسهام في حفظ هوية لبنان الثقافية وتراثه ا...
+واصل رئيس الجمهورية العماد جوزاف عون لقاءاته بعد ظهر اليوم في قصر بعبدا، واستهلها بلقاء وزير الدفاع الوطني اللواء ميشال منسى، حيث اطلع منه على نتائج الزيارتين اللتين قام بهما إلى الأردن وتشيكيا،
+اطلع وزير الصحة الدكتور راكان ناصر الدين رئيس الجمهورية على شؤون الوزارة والخطوات التي تقوم بها في ملف تسجيل الدواء، ووقف عمل الشركات التي لا تستوفي الشروط</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:16:58.668841+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>وزير الصحة اطلع رئيس الجمهورية على الخطوات التي تقوم بها الوزارة في ملف تسجيل الدواء ووقف عمل الشركات التي لا تستوفي الشروط</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1616</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>وزير الصحة اطلع رئيس الجمهورية على الخطوات التي تقوم بها الوزارة في ملف تسجيل الدواء ووقف عمل الشركات التي لا تستوفي الشروط
+اطلع وزير الصحة الدكتور راكان ناصر الدين رئيس الجمهورية على شؤون الوزارة والخطوات التي تقوم بها في ملف تسجيل الدواء، ووقف عمل الشركات التي لا تستوفي الشروط. كما عرض لابرز الإجراءات الإصلاحية التي تم اعتمادها بالتنسيق مع منظمة الصحة العالمية.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:17:01.584571+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من وزير الدفاع على نتائج زيارتيه إلى الأردن وتشيكيا</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1615</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع من وزير الدفاع على نتائج زيارتيه إلى الأردن وتشيكيا
+واصل رئيس الجمهورية العماد جوزاف عون لقاءاته بعد ظهر اليوم في قصر بعبدا، واستهلها بلقاء وزير الدفاع الوطني اللواء ميشال منسى، حيث اطلع منه على نتائج الزيارتين اللتين قام بهما إلى الأردن وتشيكيا، والمحادثات التي اجراها مع المسؤولين في هاتين الدولتين، والتي تناولت الأوضاع في لبنان والمنطقة، ودور الجيش في بسط سلطة الدولة وسيادتها على أراضيها، ومرحلة ما بعد انتهاء مهمة القوات الدولية العاملة في الجنوب.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:17:04.238896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع بحضور قائد الجيش من الوفد العسكري على نتائج الاجتماعات اللبنانية الأميركية الإسرائيلية في تامبا</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1614</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>الرئيس عون اطلع بحضور قائد الجيش من الوفد العسكري على نتائج الاجتماعات اللبنانية الأميركية الإسرائيلية في تامبا
+ترأس رئيس الجمهورية العماد جوزاف عون بعد ظهر اليوم، اجتماعا حضره قائد الجيش العماد رودولف هيكل ورئيس وفد لبنان الى المفاوضات اللبنانية – الأميركية – الإسرائيلية السفير السابق سيمون كرم، ورئيس الوفد العسكري الى المفاوضات العميد الركن جورج رزق الله، وأعضاء الوفد: العميد الركن زياد رزق الله، العميد الركن وائل عباس، العقيد الركن مازن الحاج، العقيد الركن رشاد بوكروم، والعقيد وديع رفول.
+واطلع الوفد العسكري الرئيس عون والحاضرين، على نتائج الاجتماعات اللبنانية – الأميركية – الإسرائيلية التي عقدت في تامبا في الولايات المتحدة الأميركية في 20 و21 تشرين الأول الجاري.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:17:06.680167+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>نشاط الرئيس العماد جوزاف عون في 29-10-2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1613</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>نشاط الرئيس العماد جوزاف عون في 29-10-2026
+رئيس الجمهورية إستقبل وفدين من إتحادي بلديات جبيل والضنية:
+البلديات هي خط الدفاع الإنمائي الأول
+واللامركزية الإدارية الموسعة ليست خيارا بل ضرورة للانماء المتوازن
+---
+الرئيس عون: لضرورة الانتقال من الروتين الإداري الى الانماء الفعلي
+والبدء بخطوات أساسية على طريق النهوض بالدولة من خلال الحوكمة الرقمية والشفافية
+---
+رئيس الجمهورية: لا احد يحمينا في لبنان الا مؤسسات الدولة
+ولتبقَ الثقة كبيرة بها لأنها ضمانة الجميع وتحمي الجميع
+---
+الرئيس عون: اللبنانيون من اقصى الشمال الى اقصى الجنوب والبقاع تعبوا من حالة الحرب
+ولا مستحيل عند الإرادة الصلبة وتغليب المصلحة العامة على المصلحة الخاصة
+---
+رئيس الجمهورية ابرق الى نظيره التركي مهنئا بذكرى اعلان الجمهورية
+والى الرئيس البرازيلي لمناسبة تجديد انتخابه لرئاسة جمهورية البرازيل
+---
+الرئيس عون أبرق الى ملك اسبانيا معزيا بضحايا حادث التصادم بين قطارين في طليطلة
+---
+رئيس هيئة الطيران المدني اطلع رئيس الجمهورية
+على الخطة الموضوعة لاعادة الرحلات بين بيروت ونيويورك
+----
+اكد رئيس الجمهورية العماد جوزاف عون على ان البلديات هي خط الدفاع الإنمائي الأول، مشددا على ضرورة الانتقال من الروتين الإداري الى الانماء الفعلي.
+وشدد على ان اللامركزية الإدارية الموسعة ليست خيارا بل ضرورة للانماء المتوازن، لافتا الى البدء بخطوات أساسية على طريق النهوض بالدولة من خلال الحوكمة الرقمية والشفافية.
+وإذ جدد التأكيد على أن لا احد يحمينا في لبنان الا مؤسسات الدولة، مشددا على انه من المهم الا ننسى الماضي بتجاربه المؤلمة لكي لا نكرره في المستقبل، وداعيا الى ان تبقى ثقة اللبنانيين كبيرة بالدولة وسقفها لأنها الضمانة للجميع وتحمي الجميع، فإنه إعتبر ان كل اللبنانيين من اقصى الشمال الى اقصى الجنوب والبقاع تعبوا من حالة الحرب واللاستقرار.
+وأكد "إن حق الإختلاف مقدس ولكن الخلاف ليس مسموحا. أهميتنا التنوع ضمن الوحدة. والعالم يحسدنا على هذا الأمر الأساسي الذي من واجبنا الحفاظ عليه"، مشيرا الى ان لا مستحيل عند الإرادة الصلبة وتغليب المصلحة العامة على المصلحة الخاصة.
+كلام رئيس الجمهورية جاء في خلال إستقباله، ظهر اليوم في قصر بعبدا، وفدا من إتحاد بلديات جبيل ووفدا من إتحاد بلديات الضنية.
+وفد اتحاد بلديات جبيل
+وكان رئيس اتحاد بلديات جبيل السيد فادي مارتينوس الذي زار قصر بعبدا قبل ظهر اليوم واستقبله الرئيس عون على رأس وفد من رؤساء بلديات القضاء، القى كلمة قال فيها:
+" فخامة رئيس الجمهورية العماد جوزاف عون،
+من قلب بلداتنا وقرانا النابضة بالوفاء والولاء للوطن، جئنا اليوم لنؤكد أن البلديات ليست مجرد جدران ومؤسسات خدماتية، بل هي خط الدفاع الأول عن وحدة هذا الشعب وتماسك أبنائه.
+نأتي إليكم، يا فخامة الرئيس، ونحن نحمل في عيوننا تطلعات أهلنا، وفي قلوبنا إيماناً راسخاً بأن قوة هذا الوطن تكمن في وحدة صَفّه، وأن سفينته لن تصل إلى بر الأمان إلا بالالتفاف حول الدولة ومؤسساتها الشرعية التي تمثلون حصنها الدستوري الجامع.
+وفي هذا المجال ننتظر زيارة فخامتكم إلى جبيل لتدشين مبنى الاتحاد الجديد الذي نأمل أن يحتضن البلديات الراغبة في الإنضمام مرة واحدة أو تدريجياً، لأننا نرى في قيادتكم الحكيمة الأمل المرتجى لترسيخ قيم التلاحم وصون السيادة وحفظ السلم الأهلي في زمن التحديات الكبرى. عهدنا لكم، باسم اتحاد بلديات قضاء جبيل، أن نبقى الأوفياء للوطن، الساهرين على تنمية مجتمعاتنا، والملتزمين بمسيرة الدولة لبناء غدٍ مشرق وآمن لكل لبناني.
+ختاماً، نجدد العهد أمام فخامتكم، بأن تظل بلدياتنا امتداداً لظل الدولة، وجسوراً تعبر بالوطن نحو الاستقرار والازدهار. ونمضي خلف قيادتكم واثقين بأن التحديات مهما عظمت، تتلاشى أمام صخرة وحدتنا الوطنية وإصراركم على صون الأمانة.
+حفظكم الله يا فخامة الرئيس، وسدد خطاكم على طريق العزة والكرامة الوطنية".
+الرئيس عون
+ورد الرئيس عون مرحبا، ومؤكدا على ان الدولة هي الخيار الوحيد والحامية لجميع أبناء الوطن. وإذ عاد بالذاكرة الى احداث العام 1975 الذي تراجع بفعلها حضور الدولة ودمرالاقتصاد اللبناني ما انعكس خسارة للجميع دون ان يحقق أي فريق انتصارا على الاخر، فانه شدد على أهمية الشراكة والتعاون بين اللبنانيين بما يحقق المصلحة الوطنية العليا. وقال: "من لم يدرك حتى الان ان الدولة هي مظلة الجميع وبانه لا يمكنه الاستمرار في تقوقعه خلف طائفته او حزبه هو ضد بلده".
+وشدد رئيس الجمهورية على دور البلديات معتبرا انها خط الدفاع الإنمائي الاول "فهي وجدت لخدمة أبناء منطقتها أولا، بعيدا عن الغايات الشخصية او الحزبية او الطائفية لاعضائها"، لافتا الى الانجازات التي يحققها عدد من البلديات رغم صغر حجمه، وتعثر عدد آخر رغم كبر حجمه بسبب الفساد والفوضى اللذين يعتريان العمل البلدي.
+وتوجه الى أعضاء الوفد بالقول: "جبيل، هذا القضاء العريق هو مسؤوليتكم فحافظوا على تألقه، وضعوا مصلحته فوق الاعتبارات والزواريب السياسية والطائفية والحزبية الضيقة"، مشددا على ان "وحدتنا الوطنية هي سلاحنا الاقوى"، وعلى ضرورة استغلال الظروف المتاحة لاعادة النهوض بالبلد من جديد وتوجيه طاقات وقدرات اللبنانيين باتجاه مصلحة بلدهم.
+ثم دار حوار بين الرئيس عون وأعضاء الوفد الذين عددوا مطالبهم، فلفت الرئيس عون، الى الاتصالات التي اجراها مع المعنيين لمعالجة بعض القضايا ومنها قضية التفاح اللبناني، منتقدا في هذا السياق جشع بعض التجار. وقال: "لن نوفر جهدا لدعم القطاع الزراعي بكل قدرتنا والطرق الممكنة". وجدد التأكيد على ان سنوات من الهدر والفساد وضعف الادارة لا يمكن معالجة تداعياتها بين ليلة وضحاها.
+وفد اتحاد بلديات الضنية
+كما استقبل رئيس الجمهورية وفدا من بلديات قضاء الضنية ضم السيد مصطفى سعادة على رأس وفد من اتحاد بلديات الضنية، ورئيس اتحاد بلديات الجرد طارق شفشق مع وفد من بلديات الاتحاد .
+في مستهل اللقاء، القى السيد سعادة كلمة شكر فيها الرئيس عون على استقباله والوفد، وعدد مجموعة من المطالب الإنمائية الأساسية للقضاء ابرزها:
+أولاً: حماية الثروة المائية والبيئة حيث تحتاج الضنية إلى إنشاء شبكات للصرف الصحي ومحطات لمعالجة المياه المبتذلة، بما يمنع تلوّث الينابيع والمجاري المائية ويحافظ على سلامة مصادر المياه التي تشكّل ثروة حيوية للشمال ولبنان.
+ثانياً: تطوير شبكة الطرق وتحسين الربط بين المناطق: ونطالب بإعادة تأهيل الطرق الرئيسية القائمة وتطويرها، وتحسين وصل الضنية بطرابلس عبر انشاء مدخل للقضاء واستكمال وصل الضنية بعكار والمنية والاقضية المجاورة والداخل اللبناني وصولا الى الداخل السوري بما يسهّل حركة المواطنين والبضائع، ويدعم القطاعات الزراعية والسياحية والتجارية، ويعزّز استفادة المنطقة من المشاريع والمرافق الاقتصادية في الشمال.
+ثالثًا: إنشاء منشأة لمعالجة النفايات الصلبة: إنّ معالجة هذا الملف تتطلّب حلًا مستدامًا يحمي البيئة والصحة العامة، ويضع حدًا للمشكلات المتفاقمة في إدارة النفايات. وفي هذا الإطار، نعلن الاستعداد الكامل والجهوزية للتعاون في تأمين عقار من الأملاك العامة البلدية وفق الأصول القانونية، وبالتنسيق مع وزارة البيئة والهيئة الوطنية لمعالجة النفايات الصلبة، تمهيدًا لإجراء الدراسات الفنية والبيئية اللازمة واعتماد الحلول العلمية الآمنة
+رابعًا: اعتماد مقاربة إنمائية شاملة للضنية: نأمل أن تحظى المنطقة بخطة إنمائية متكاملة تعزّز قدرات البلديات، وتدعم الزراعة والسياحة البيئية، وتفتح المجال أمام الاستثمارات وفرص العمل، بما يحدّ من الهجرة ويتيح لأبناء المنطقة التمسّك بأرضهم والمساهمة في نهضة وطنهم.
+وتحدث عدد من رؤساء البلديات الذين عددوا حاجات بلدياتهم في مختلف المجالات.
+الرئيس عون
+ورد الرئيس عون مرحبا بالوفد، وقال: "لا احد يحمينا في لبنان الا مؤسسات الدولة، وكلنا نشهد الى اين اوصلتنا الإنقسامات في البلد، حيث لم يربح احد، لكن لبنان بأسره هو الذي خسر، لبنان بكافة مكوناته من اقصى الشمال الى الجنوب. المهم الا ننسى الماضي بتجاربه المؤلمة لكي لا نكرره في المستقبل. اما العبرة الأساسية التي علينا إستخلاصها هي ان لا احد يحمينا الا الدولة التي تحمينا جميعا."
+وتوجه الى رؤساء البلديات في الوفد بالقول: "أنتم رمز الدولة، وانتم صورة عنها في النطاق البلدي. فإذا ما عملت كل بلدية في نطاقها لمصلحة أبناء البلدة او المدينة التي هي منتخبة لخدمتها، تقوم بإنعاشها وتساهم في تطويرها، والعكس صحيح. "
+وتابع: "أنتم منتخبون من الشعب، أي ان الشعب أوكلكم القيام بمسؤولياتكم في خدمته. ونشاطكم ضمن إطاركم البلدي يعكس صورة بلدتكم او مدينتكم. من هنا، إن المطلوب ان تتقدم المصلحة العامة على المصالح الشخصية او الفئوية، وحتى على الإعتبارات السياسية او الحزبية. إن دوركم أساسي، ونحن الى جانبكم."
+وشدد رئيس الجمهورية على ان اللامركزية الإدارية الموسعة ليست خيارا بل ضرورة للانماء المتوازن، لافتا الى البدء بخطوات أساسية على طريق النهوض بالدولة من خلال الحوكمة الرقمية والشفافية.
+أضاف: " انا الى جانكم، وسنتابع معا مطالبكم. فليبق إيمانكم كبيرا بلبنان، ولتبق ثقتكم كبيرة بالدولة وسقفها لأنها الضمانة للجميع وتحمي الجميع. وإذا لم نتعلم من الماضي فإن التاريخ سيهملنا. ان كل اللبنانيين من اقصى الشمال الى اقصى الجنوب والبقاع، تعبوا من حالة الحرب واللاستقرار، وكلنا مطلبنا العيش من اجل أبنائنا وابنائهم من بعدهم. إن المسؤولية مشتركة، وجميعنا لدينا هوية واحدة وعلم واحد."
+وقال الرئيس عون: "إن حق الإختلاف مقدس ولكن الخلاف ليس مسموحا. أهميتنا التنوع ضمن الوحدة. والعالم يحسدنا على هذا الأمر الأساسي الذي من واجبنا الحفاظ عليه. ونحن مهما تقاتلنا، فإننا عدنا الى بعضنا البعض. هل هناك من خيار آخر لنا؟ هل خيارنا ان نصبح مهجرين في أرضنا؟ إن دول العالم ترغب في مساعدتنا، لكن المهم هو ان نحب وطننا ونساعد انفسنا. لا مستحيل عند الإرادة الصلبة وتغليب المصلحة العامة على المصلحة الخاصة."
+الوزير والنائب السابق غازي العريضي
+الرئيس عون عرض مع الوزير والنائب السابق غازي العريضي الأوضاع العامة محلياً وإقليمياً، في ضوء التطورات الأخيرة.
+رئيس هيئة الطيران المدني
+الى ذلك، اطلع الرئيس عون من رئيس هيئة الطيران المدني الكابتن محمد عزيز على مراحل تقدم عمل الهيئة ووضع مطار رفيق الحريري الدولي والخطة الموضوعة لمباشرة الرحلات الجوية مع الولايات المتحدة الأميركية وكندا، مشددا على إيلاء موضوع سلامة الطيران والتقيد بالإجراءات وتعليمات منظمة الطيران المدني الدولي ICAO الأولوية المطلقة، كما واطلع على مراحل تقدم العمل في مطار رنيه معوض.
+برقيات
+الى ذلك، ابرق الرئيس عون الى الرئيس التركي رجب طيب اردوغان مهنئا بذكرى اعلان الجمهورية التركية.
+كما ابرق مهنئا الى الرئيس البرازيلي لويس ايناسيو لولا دا سيلفا لمناسبة تجديد انتخابه لرئاسة جمهورية البرازيل الاتحادية.
+وابرق رئيس الجمهورية الى ملك اسبانيا الملك فيليبي السادس معزيا بضحايا حادث التصادم بين قطارين فائقي السرعة في مقاطعة طليطلة، متمنيا الشفاء العاجل للجرحى والمصابين.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:17:09.313487+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>استقبل الرئيس عون الوزير والنائب السابق غازي العريضي</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1611</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>اكد رئيس الجمهورية العماد جوزاف عون ان جامعة الروح القدس – الكسليك، تؤدي دوراً تربوياً وأكاديمياً ووطنياً مميزاً، لا يقتصر على إعداد الأجيال الشابة بالعلم والمعرفة، بل يمتد إلى الإسهام في حفظ هوية لبنان الثقافية وتراثه ا...
+واصل رئيس الجمهورية العماد جوزاف عون لقاءاته بعد ظهر اليوم في قصر بعبدا، واستهلها بلقاء وزير الدفاع الوطني اللواء ميشال منسى، حيث اطلع منه على نتائج الزيارتين اللتين قام بهما إلى الأردن وتشيكيا،</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:17:11.857365+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية إستقبل وفدين من إتحادي بلديات جبيل والضنية:</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1610</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية إستقبل وفدين من إتحادي بلديات جبيل والضنية:
+البلديات هي خط الدفاع الإنمائي الأول
+واللامركزية الإدارية الموسعة ليست خيارا بل ضرورة للانماء المتوازن
+---
+الرئيس عون: لضرورة الانتقال من الروتين الإداري الى الانماء الفعلي
+والبدء بخطوات أساسية على طريق النهوض بالدولة من خلال الحوكمة الرقمية والشفافية
+---
+رئيس الجمهورية: لا احد يحمينا في لبنان الا مؤسسات الدولة
+ولتبقَ الثقة كبيرة بها لأنها ضمانة الجميع وتحمي الجميع
+---
+الرئيس عون: اللبنانيون من اقصى الشمال الى اقصى الجنوب والبقاع تعبوا من حالة الحرب
+ولا مستحيل عند الإرادة الصلبة وتغليب المصلحة العامة على المصلحة الخاصة
+---
+اكد رئيس الجمهورية العماد جوزاف عون على ان البلديات هي خط الدفاع الإنمائي الأول، مشددا على ضرورة الانتقال من الروتين الإداري الى الانماء الفعلي.
+وشدد على ان اللامركزية الإدارية الموسعة ليست خيارا بل ضرورة للانماء المتوازن، لافتا الى البدء بخطوات أساسية على طريق النهوض بالدولة من خلال الحوكمة الرقمية والشفافية.
+وإذ جدد التأكيد على أن لا احد يحمينا في لبنان الا مؤسسات الدولة، مشددا على انه من المهم الا ننسى الماضي بتجاربه المؤلمة لكي لا نكرره في المستقبل، وداعيا الى ان تبقى ثقة اللبنانيين كبيرة بالدولة وسقفها لأنها الضمانة للجميع وتحمي الجميع، فإنه إعتبر ان كل اللبنانيين من اقصى الشمال الى اقصى الجنوب والبقاع تعبوا من حالة الحرب واللاستقرار.
+وأكد "إن حق الإختلاف مقدس ولكن الخلاف ليس مسموحا. أهميتنا التنوع ضمن الوحدة. والعالم يحسدنا على هذا الأمر الأساسي الذي من واجبنا الحفاظ عليه"، مشيرالى ان لا مستحيل عند الإرادة الصلبة وتغليب المصلحة العامة على المصلحة الخاصة.
+كلام رئيس الجمهورية جاء في خلال إستقباله، ظهر اليوم في قصر بعبدا، وفدا من إتحاد بلديات جبيل ووفدا من إتحاد بلديات الضنية.
+وفد اتحاد بلديات جبيل
+وكان رئيس اتحاد بلديات جبيل السيد فادي مارتينوس الذي زار قصر بعبدا قبل ظهر اليوم واستقبله الرئيس عون على رأس وفد من رؤساء بلديات القضاء، القى كلمة قال فيها:
+" فخامة رئيس الجمهورية العماد جوزاف عون،
+من قلب بلداتنا وقرانا النابضة بالوفاء والولاء للوطن، جئنا اليوم لنؤكد أن البلديات ليست مجرد جدران ومؤسسات خدماتية، بل هي خط الدفاع الأول عن وحدة هذا الشعب وتماسك أبنائه.
+نأتي إليكم، يا فخامة الرئيس، ونحن نحمل في عيوننا تطلعات أهلنا، وفي قلوبنا إيماناً راسخاً بأن قوة هذا الوطن تكمن في وحدة صَفّه، وأن سفينته لن تصل إلى بر الأمان إلا بالالتفاف حول الدولة ومؤسساتها الشرعية التي تمثلون حصنها الدستوري الجامع.
+وفي هذا المجال ننتظر زيارة فخامتكم إلى جبيل لتدشين مبنى الاتحاد الجديد الذي نأمل أن يحتضن البلديات الراغبة في الإنضمام مرة واحدة أو تدريجياً، لأننا نرى في قيادتكم الحكيمة الأمل المرتجى لترسيخ قيم التلاحم وصون السيادة وحفظ السلم الأهلي في زمن التحديات الكبرى. عهدنا لكم، باسم اتحاد بلديات قضاء جبيل، أن نبقى الأوفياء للوطن، الساهرين على تنمية مجتمعاتنا، والملتزمين بمسيرة الدولة لبناء غدٍ مشرق وآمن لكل لبناني.
+ختاماً، نجدد العهد أمام فخامتكم، بأن تظل بلدياتنا امتداداً لظل الدولة، وجسوراً تعبر بالوطن نحو الاستقرار والازدهار. ونمضي خلف قيادتكم واثقين بأن التحديات مهما عظمت، تتلاشى أمام صخرة وحدتنا الوطنية وإصراركم على صون الأمانة.
+حفظكم الله يا فخامة الرئيس، وسدد خطاكم على طريق العزة والكرامة الوطنية".
+الرئيس عون
+ورد الرئيس عون مرحبا، ومؤكدا على ان الدولة هي الخيار الوحيد والحامية لجميع أبناء الوطن. وإذ عاد بالذاكرة الى احداث العام 1975 الذي تراجع بفعلها حضور الدولة ودمرالاقتصاد اللبناني ما انعكس خسارة للجميع دون ان يحقق أي فريق انتصارا على الاخر، فانه شدد على أهمية الشراكة والتعاون بين اللبنانيين بما يحقق المصلحة الوطنية العليا. وقال: "من لم يدرك حتى الان ان الدولة هي مظلة الجميع وبانه لا يمكنه الاستمرار في تقوقعه خلف طائفته او حزبه هو ضد بلده".
+وشدد رئيس الجمهورية على دور البلديات معتبرا انها خط الدفاع الإنمائي الاول "فهي وجدت لخدمة أبناء منطقتها أولا، بعيدا عن الغايات الشخصية او الحزبية او الطائفية لاعضائها"، لافتا الى الانجازات التي يحققها عدد من البلديات رغم صغر حجمه، وتعثر عدد آخر رغم كبر حجمه بسبب الفساد والفوضى اللذين يعتريان العمل البلدي.
+وتوجه الى أعضاء الوفد بالقول: "جبيل، هذا القضاء العريق هو مسؤوليتكم فحافظوا على تألقه، وضعوا مصلحته فوق الاعتبارات والزواريب السياسية والطائفية والحزبية الضيقة"، مشددا على ان "وحدتنا الوطنية هي سلاحنا الاقوى"، وعلى ضرورة استغلال الظروف المتاحة لاعادة النهوض بالبلد من جديد وتوجيه طاقات وقدرات اللبنانيين باتجاه مصلحة بلدهم.
+ثم دار حوار بين الرئيس عون وأعضاء الوفد الذين عددوا مطالبهم، فلفت الرئيس عون، الى الاتصالات التي اجراها مع المعنيين لمعالجة بعض القضايا ومنها قضية التفاح اللبناني، منتقدا في هذا السياق جشع بعض التجار. وقال: "لن نوفر جهدا لدعم القطاع الزراعي بكل قدرتنا والطرق الممكنة". وجدد التأكيد على ان سنوات من الهدر والفساد وضعف الادارة لا يمكن معالجة تداعياتها بين ليلة وضحاها.
+وفد اتحاد بلديات الضنية
+كما استقبل رئيس الجمهورية وفدا من بلديات قضاء الضنية ضم السيد مصطفى سعادة على رأس وفد من اتحاد بلديات الضنية، ورئيس اتحاد بلديات الجرد طارق شفشق مع وفد من بلديات الاتحاد .
+في مستهل اللقاء، القى السيد سعادة كلمة شكر فيها الرئيس عون على استقباله والوفد، وعدد مجموعة من المطالب الإنمائية الأساسية للقضاء ابرزها:
+أولاً: حماية الثروة المائية والبيئة حيث تحتاج الضنية إلى إنشاء شبكات للصرف الصحي ومحطات لمعالجة المياه المبتذلة، بما يمنع تلوّث الينابيع والمجاري المائية ويحافظ على سلامة مصادر المياه التي تشكّل ثروة حيوية للشمال ولبنان.
+ثانياً: تطوير شبكة الطرق وتحسين الربط بين المناطق: ونطالب بإعادة تأهيل الطرق الرئيسية القائمة وتطويرها، وتحسين وصل الضنية بطرابلس عبر انشاء مدخل للقضاء واستكمال وصل الضنية بعكار والمنية والاقضية المجاورة والداخل اللبناني وصولا الى الداخل السوري بما يسهّل حركة المواطنين والبضائع، ويدعم القطاعات الزراعية والسياحية والتجارية، ويعزّز استفادة المنطقة من المشاريع والمرافق الاقتصادية في الشمال.
+ثالثًا: إنشاء منشأة لمعالجة النفايات الصلبة: إنّ معالجة هذا الملف تتطلّب حلًا مستدامًا يحمي البيئة والصحة العامة، ويضع حدًا للمشكلات المتفاقمة في إدارة النفايات. وفي هذا الإطار، نعلن الاستعداد الكامل والجهوزية للتعاون في تأمين عقار من الأملاك العامة البلدية وفق الأصول القانونية، وبالتنسيق مع وزارة البيئة والهيئة الوطنية لمعالجة النفايات الصلبة، تمهيدًا لإجراء الدراسات الفنية والبيئية اللازمة واعتماد الحلول العلمية الآمنة
+رابعًا: اعتماد مقاربة إنمائية شاملة للضنية: نأمل أن تحظى المنطقة بخطة إنمائية متكاملة تعزّز قدرات البلديات، وتدعم الزراعة والسياحة البيئية، وتفتح المجال أمام الاستثمارات وفرص العمل، بما يحدّ من الهجرة ويتيح لأبناء المنطقة التمسّك بأرضهم والمساهمة في نهضة وطنهم.
+وتحدث عدد من رؤساء البلديات الذين عددوا حاجات بلدياتهم في مختلف المجالات.
+الرئيس عون
+ورد الرئيس عون مرحبا بالوفد، وقال: "لا احد يحمينا في لبنان الا مؤسسات الدولة، وكلنا نشهد الى اين اوصلتنا الإنقسامات في البلد، حيث لم يربح احد، لكن لبنان بأسره هو الذي خسر، لبنان بكافة مكوناته من اقصى الشمال الى الجنوب. المهم الا ننسى الماضي بتجاربه المؤلمة لكي لا نكرره في المستقبل. اما العبرة الأساسية التي علينا إستخلاصها هي ان لا احد يحمينا الا الدولة التي تحمينا جميعا."
+وتوجه الى رؤساء البلديات في الوفد بالقول: "أنتم رمز الدولة، وانتم صورة عنها في النطاق البلدي. فإذا ما عملت كل بلدية في نطاقها لمصلحة أبناء البلدة او المدينة التي هي منتخبة لخدمتها، تقوم بإنعاشها وتساهم في تطويرها، والعكس صحيح. "
+وتابع: "أنتم منتخبون من الشعب، أي ان الشعب أوكلكم القيام بمسؤولياتكم في خدمته. ونشاطكم ضمن إطاركم البلدي يعكس صورة بلدتكم او مدينتكم. من هنا، إن المطلوب ان تتقدم المصلحة العامة على المصالح الشخصية او الفئوية، وحتى على الإعتبارات السياسية او الحزبية. إن دوركم أساسي، ونحن الى جانبكم."
+وشدد رئيس الجمهورية على ان اللامركزية الإدارية الموسعة ليست خيارا بل ضرورة للانماء المتوازن، لافتا الى البدء بخطوات أساسية على طريق النهوض بالدولة من خلال الحوكمة الرقمية والشفافية.
+أضاف: " انا الى جانكم، وسنتابع معا مطالبكم. فليبق إيمانكم كبيرا بلبنان، ولتبق ثقتكم كبيرة بالدولة وسقفها لأنها الضمانة للجميع وتحمي الجميع. وإذا لم نتعلم من الماضي فإن التاريخ سيهملنا. ان كل اللبنانيين من اقصى الشمال الى اقصى الجنوب والبقاع، تعبوا من حالة الحرب واللاستقرار، وكلنا مطلبنا العيش من اجل أبنائنا وابنائهم من بعدهم. إن المسؤولية مشتركة، وجميعنا لدينا هوية واحدة وعلم واحد."
+وقال الرئيس عون: "إن حق الإختلاف مقدس ولكن الخلاف ليس مسموحا. أهميتنا التنوع ضمن الوحدة. والعالم يحسدنا على هذا الأمر الأساسي الذي من واجبنا الحفاظ عليه. ونحن مهما تقاتلنا، فإننا عدنا الى بعضنا البعض. هل هناك من خيار آخر لنا؟ هل خيارنا ان نصبح مهجرين في أرضنا؟ إن دول العالم ترغب في مساعدتنا، لكن المهم هو ان نحب وطننا ونساعد انفسنا. لا مستحيل عند الإرادة الصلبة وتغليب المصلحة العامة على المصلحة الخاصة."</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:17:14.372832+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من نادي الحكمة كأس البطولة العربية لكرة السلة وقميص النادي رقم واحد عربون محبة وتقدير</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1609</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>الرئيس عون تسلم من نادي الحكمة كأس البطولة العربية لكرة السلة وقميص النادي رقم واحد عربون محبة وتقدير
+رئيس الجمهورية: فوزكم هو للبنان ككل وموضع اعتزاز جميع أبنائه
+والعزيمة والإرادة الصلبة قادرتان على تخطي الصعاب مهما بلغت
+----
+جدد رئيس الجمهورية العماد جوزاف عون تهنئته ل نادي الحكمة على فوزه للمرة الثالثة في تاريخه في البطولة العربية لكرة السلة في المباراة النهائية التي اقميت في 20 من الشهر الحالي، معتبرا ان فوزه هو فوز للبنان ككل، ومشددا على اهمية المحافظة عليه.
+كلام الرئيس عون جاء خلال استقباله قبل ظهر اليوم في قصر بعبدا رئيس الاتحاد اللبناني لكرة السلة السيد اكرم الحلبي، ورئيس نادي الحكمة الفخري النائب جهاد بقرادوني ورئيس النادي السيد راغب حداد مع أعضاء النادي واللاعبين الذين حضروا لشكر الرئيس عون على رعايته لبطولة الأندية العربية لكرة السلة، وقدموا له كأس البطولة وقميص النادي رقم واحد عربون محبة ووفاء.
+في مستهل اللقاء، القى السيد حداد كلمة قال فيها:
+"فخامة الرئيس،
+يتشرف وفد نادي الحكمة، ومعه الاتحاد اللبناني لكرة السلة، بأن يقف اليوم في حضرتكم ليرفع إليكم أسمى آيات الشكر والامتنان على رعايتكم الكريمة لبطولة الأندية العربية لكرة السلة التي احتضنتها بيروت. فقد كانت رعايتكم مصدر ثقة لأشقائنا العرب، ورسالة بأن لبنان سيبقى قبلتهم وبيتهم الثاني.
+فخامة الرئيس،
+إنه لفخر لنا أننا أعدنا العرب إلى لبنان، وأعدنا الكأس إلى لبنان بعد إحراز نادي الحكمة اللقب العربي للمرة الثالثة في تاريخه، ليتوج معه لبنان بهذه البطولة للمرة العاشرة. وجاء هذا الإنجاز، في ظل الظروف الاستثنائية التي تعيشها منطقتنا، تأكيدا على أن إرادة اللبنانيين أقوى من الصعاب، وأن الأندية اللبنانية قادرة على رفع اسم لبنان عاليا. وقد سجلت هذه البطولة، للمرة الأولى، بلوغ كل الأندية اللبنانية المشاركة الدور ربع النهائي، في دليل على المستوى المتقدم لكرة السلة اللبنانية.
+واسمحوا لنا أخيرا، فخامة الرئيس، أن نشكركم على تهنئتكم نادي الحكمة بهذا الفوز، وأن نقدم لكم كأس البطولة، وأن نقدم لكم أيضا قميص نادي الحكمة يحمل الرقم 1، عربون محبة ووفاء من إداريي ولاعبي نادي الحكمة، ومنهم نجلكم خليل، فهذا الفوز انتصار يسجل باسم لبنان في عهدكم، معاهدينكم أن نبقى سفراء للبنان في كل المحافل العربية والدولية."
+الرئيس عون
+ورحب الرئيس عون بالوفد مجددا تهنئته على فوزه بالبطولة. وقال: ان فوزكم ليس فوزا لنادي الحكمة فحسب بل للبنان ككل الذي رفعتم اسمه عاليا، وقد تمكنتم رغم ظروفه الصعبة من تحقيق نتائج مبهرة هي موضع اعتزاز جميع اللبنانيين، وهذا ان دل على شيء فعلى ان العزيمة والإرادة الصلبة قادرتان على تخطي الصعاب مهما بلغت".
+وختم: "فوزكم مصدر فخر للبنان الذي اثبتم انه ليس معزولا بل هو موجود على الساحة الرياضية، وعلى الساحتين العربية والدولية "، مشددا على انه "ليس المهم تحقيق الفوز فحسب بل المحافظة عليه".
+وشدد الرئيس عون على ضرورة إبقاء الرياضة بعيدا عن السياسة و المصالح الشخصية ،
+وإبراز الانتماء الوطني للرياضيين في لبنان .</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:17:16.796963+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Lebanese_Presidency.xlsx
+++ b/Lebanese_Presidency.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4056,6 +4056,219 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض مع السفير الاماراتي في لبنان الأوضاع العامة في المنطقة</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1626</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض مع السفير الاماراتي في لبنان الأوضاع العامة في المنطقة
+استقبل الرئيس عون في قصر بعبدا بعد ظهر اليوم، سفير دولة الإمارات العربية المتحدة في لبنان فهد سالم سعيد الكعبي، وجرى بحث العلاقات الثنائية بين لبنان والإمارات، إضافة إلى الأوضاع العامة في لبنان والمنطقة في ضوء التطورات الراهنة.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:49:29.145134+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>الرئيس عون اتصل بعاهل البحرين واكد الوقوف الى جانب المملكة وشعبها الشقيق وتمنى تعيين سفير لها في لبنان وإعادة تفعيل الخط الجوي بين البلدين</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1625</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>الرئيس عون اتصل بعاهل البحرين واكد الوقوف الى جانب المملكة وشعبها الشقيق وتمنى تعيين سفير لها في لبنان وإعادة تفعيل الخط الجوي بين البلدين
+اجرى رئيس الجمهورية العماد جوزاف عون بعد ظهر اليوم، اتصالاً بجلالة ملك البحرين حمد بن عيسى آل خليفة، وعرض معه الأوضاع في المنطقة عموماً، وفي دول الخليج خصوصاً، في ضوء التطورات الأخيرة.
+وخلال الاتصال اكد الرئيس عون وقوف لبنان رئيساً وشعباً إلى جانب مملكة البحرين وشعبها الشقيق . وتناول البحث العلاقات الثنائية بين البلدين حيث تمنى الرئيس عون تعيين سفير لمملكة البحرين في لبنان، واعادة تفعيل الخط الجوي بين لبنان والبحرين، وعودة الطيران البحريني الى مطار رفيق الحريري الدولي .
+وأكد العاهل البحريني على عمق العلاقة بين البلدين الشقيقين ووقوف المملكة الى جانب لبنان وشعبه الشقيق.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:49:31.430172+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>رسالة تهنئة الى رئيس الجزائري</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1624</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>رسالة تهنئة الى رئيس الجزائري
+وجه الرئيس عون رسالة تهنئة الى الرئيس الجزائري عبد المجيد تبون، بمناسبة احتفال بلاده بذكرى ثورة التحرير التي تصادف يوم الاحد المقبل، مما جاء فيها:
+"إن هذه المناسبة الوطنية، تجسّد ما تحلّى به الشعب الجزائري الشقيق من إرادة صلبة وما قدمه من تضحيات جسام في سبيل الحرية والاستقلال والكرامة، وتبقى مصدر اعتزاز وإلهام للأجيال العربية المتعاقبة.
+وإذ أعبّر لفخامتكم عن تقديري للعلاقات الأخوية التي تجمع لبنان والجزائر، فإنني أتطلّع إلى تعزيز التعاون بين بلدينا الشقيقين، بما يخدم مصالح شعبينا ويسهم في ترسيخ التضامن العربي."</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:49:33.668696+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل المدير العام للامن العام</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1623</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض مع السفير الاماراتي في لبنان الأوضاع العامة في المنطقة ٣٠ تشرين الأول ٢٠٢٦ استقبل الرئيس عون في قصر بعبدا بعد ظهر اليوم، سفير دولة الإمارات العربية المتحدة اقرأ المزيد &gt;
+رسالة تهنئة الى رئيس الجزائري ٣٠ تشرين الأول ٢٠٢٦ وجه الرئيس عون رسالة تهنئة الى الرئيس الجزائري عبد المجيد تبون، بمناسبة احتفال بلاده بذكرى ثورة التحرير التي تصادف يوم الاحد المقبل، اقرأ المزيد &gt;
+رئيس الجمهورية لمجلس الادارة الجديد للمصلحة الوطنية لليطاني:على المصلحة ان تكون نموذجاً في الإدارة المنتجة التي تحوّل الموارد الوطنية إلى خدمات وفرص تنموية ٣٠ تشرين الأول ٢٠٢٦ استقبل الرئيس عون مجلس الادارة الجديد للمصلحة الوطنية لنهر الليطاني برئاسة الدكتور سامي علوية وعضوية السادة اقرأ المزيد &gt;</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:49:35.990718+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية لمجلس الادارة الجديد للمصلحة الوطنية لليطاني:على المصلحة ان تكون نموذجاً في الإدارة المنتجة التي تحوّل الموارد الوطنية إلى خدمات وفرص تنموية</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1622</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية لمجلس الادارة الجديد للمصلحة الوطنية لليطاني:على المصلحة ان تكون نموذجاً في الإدارة المنتجة التي تحوّل الموارد الوطنية إلى خدمات وفرص تنموية
+رئيس مصلحة الليطاني نوّه بدور الرئيس عون في حماية سد القرعون
+من القصف الاسرائيلي: المصلحة تحقق اكتفاء ماليا ذاتيًا
+---------
+استقبل الرئيس عون مجلس الادارة الجديد للمصلحة الوطنية لنهر الليطاني برئاسة الدكتور سامي علوية وعضوية السادة: ياسر ابو النصر، جو عقيقي، فريد كرم، مارون نبهان، خالد سعد، وناجي بري. واطلع الوفد رئيس الجمهورية على اوضاع المصلحة والخدمات التي تقدمها في مختلف المجالات لا سيما انتاج الكهرباء، اضافة الى المشاريع التي تعمل على اعدادها. وعرض الدكتور علوية للأضرار الجانبية التي وقعت في سد القرعون نتيجة القصف الاسرائيلي الذي استهدف محيط السد، منوهاً بالدور الذي لعبه الرئيس عون في حماية السد وتحييده. واشار الى ان المصلحة تحقق اكتفاء ماليا ذاتيًا.
+وهنأ الرئيس عون مجلس الادارة الجديد متمنياً لأعضائه التوفيق في مهامهم انطلاقاً من المسؤولية التي القيت على عاتقهم، معتبراً أن نهر الليطاني ثروة وطنية ومسؤولية تجاه الأجيال المقبلة وإن المصلحة الوطنية لنهر الليطاني تؤدي دوراً أساسياً في إدارة واحدة من أهم الثروات المائية في لبنان، بما يضمن حسن استثمارها في الريّ وإنتاج الطاقة الكهرومائية، ويسهم في دعم الزراعة والاقتصاد الوطني، وأن المحافظة على هذه الثروة، وحمايتها من التلوث والهدر، ليست مسؤولية مؤسسة بعينها فحسب، بل واجب وطني يتطلب تكامل جهود الدولة والمواطنين.
+واعتبر الرئيس عون ان الإدارة الفاعلة والشفافية أساس حماية المصلحة العامة وإن مسؤولية المجلس الجديد لا تقتصر على إدارة المشاريع والمنشآت، بل تشمل تطوير الأداء، وتعزيز الحوكمة والشفافية، وتسريع تنفيذ المشاريع التي تحسّن الاستفادة من المياه والطاقة، ومواجهة التعديات والتلوث. ورأى ان المطلوب أن تكون المصلحة نموذجاً في الإدارة المنتجة التي تحوّل الموارد الوطنية إلى خدمات وفرص تنموية، وتضع المصلحة العامة فوق أي اعتبار آخر.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:49:38.244102+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>الرئيس عون عرض مع السفير عساف العلاقات بين لبنان والفاتيكان واطلع من اللواء شقير على نتائج زيارته الى السعودية وعلى عمل الامن العام</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1621</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية عرض مع السفير الاماراتي في لبنان الأوضاع العامة في المنطقة ٣٠ تشرين الأول ٢٠٢٦ استقبل الرئيس عون في قصر بعبدا بعد ظهر اليوم، سفير دولة الإمارات العربية المتحدة اقرأ المزيد &gt;
+رسالة تهنئة الى رئيس الجزائري ٣٠ تشرين الأول ٢٠٢٦ وجه الرئيس عون رسالة تهنئة الى الرئيس الجزائري عبد المجيد تبون، بمناسبة احتفال بلاده بذكرى ثورة التحرير التي تصادف يوم الاحد المقبل، اقرأ المزيد &gt;
+رئيس الجمهورية استقبل المدير العام للامن العام ٣٠ تشرين الأول ٢٠٢٦ اطلع الرئيس عون من المدير العام للامن العام اللواء حسن شقير على نتائج زيارته إلى السعودية، وعرض معه الأوضاع العامة في البلاد وعمل الامن العام. اقرأ المزيد &gt;</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:49:40.443909+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل رئيس الوزراء السابق للاتحاد الروسي الذي يشارك في افتتاح ممثلية للجمعية الامبراطورية الارثوذكسية في لبنان</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.presidency.gov.lb/media/news/1620</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>رئيس الجمهورية استقبل رئيس الوزراء السابق للاتحاد الروسي الذي يشارك في افتتاح ممثلية للجمعية الامبراطورية الارثوذكسية في لبنان
+الرئيس ستيباشين اطلع الرئيس عون على المشاريع التي تود الجمعية القيام بها في لبنان:
+افتتاح الممثلية يساهم في تنشيط علاقات الاخوة والصداقة كما الزيارات الدينية
+------------
+وفي هذا الاطار استقبل رئيس الجمهورية رئيس الوزراء السابق للاتحاد الروسي سيرغي ستيباشين على رأس وفد من الكنيسة الارثوذكسية يرافقه السفير الروسي في لبنان الكسندر روداكوف .
+رئيس الوزراء السابق الذي يزور لبنان للمشاركة في احتفال افتتاح ممثلية للجمعية الامبراطورية الارثوذكسية في لبنان، نقل تحيات الرئيس الروسي فلاديمير بوتين كما تحيات بطريرك الكنيسة الارثوذكسية في روسيا كيريل الأول، مشيدا بالعلاقات بين البلدين، ومثمنا جهود رئيس الجمهورية ومواقفه لا سيما بقوله انه رئيس للدولة اللبنانية وليس للمسلمين او المسيحيين، معتبرا ان هناك قواسم مشتركة بين البلدين في التعددية.
+الرئيس ستيباشين اطلع رئيس الجمهورية على المشاريع التي تود الجمعية القيام بها لا سيما في ملف التربية ودعم المدارس الارثوذكسية، معتبرا ان افتتاح الممثلية في لبنان يساهم في تنشيط علاقات الاخوة والصداقة كما الزيارات الدينية ورحلات الحجاج للاماكن المقدسة بين البلدين.
+رئيس الجمهورية الذي رحب بزيارة رئيس الوزراء السابق والوفد المرافق، ودعاه الى نقل تحياته للرئيس الروسي، ثمن الخطوات التي تقوم بها الجمعية تجاه الطائفة الارثوذكسية في لبنان ما ينعكس ايجابا على البلدين، مرحبًا بأي مبادرة تعزز العلاقات على المستويين السياسي او الديني، مشيرا الى الدور الايجابي الذي تلعبه روسيا لتطوير العلاقات بين البلدين .</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:49:42.672107+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
